--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,81 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:45:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Estudiantes Rio Cuarto</t>
+  </si>
+  <si>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Cordoba</t>
+  </si>
+  <si>
+    <t>Deportivo Riestra</t>
+  </si>
+  <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>America de Cali S.A</t>
+  </si>
+  <si>
+    <t>Kongsvinger</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>Central Cordoba (SdE)</t>
+  </si>
+  <si>
+    <t>Sportivo Luqueno</t>
+  </si>
+  <si>
+    <t>2026-10-03 01:04:06</t>
   </si>
 </sst>
 </file>
@@ -585,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +903,1458 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2">
+        <v>4.5</v>
+      </c>
+      <c r="G2">
+        <v>4.9</v>
+      </c>
+      <c r="H2">
+        <v>2.02</v>
+      </c>
+      <c r="I2">
+        <v>2.1</v>
+      </c>
+      <c r="J2">
+        <v>3.15</v>
+      </c>
+      <c r="K2">
+        <v>3.4</v>
+      </c>
+      <c r="L2">
+        <v>1.59</v>
+      </c>
+      <c r="M2">
+        <v>1.14</v>
+      </c>
+      <c r="N2">
+        <v>2.5</v>
+      </c>
+      <c r="O2">
+        <v>1.6</v>
+      </c>
+      <c r="P2">
+        <v>1.51</v>
+      </c>
+      <c r="Q2">
+        <v>2.8</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>5.7</v>
+      </c>
+      <c r="T2">
+        <v>2.36</v>
+      </c>
+      <c r="U2">
+        <v>1.66</v>
+      </c>
+      <c r="V2">
+        <v>1.9</v>
+      </c>
+      <c r="W2">
+        <v>1.26</v>
+      </c>
+      <c r="X2">
+        <v>8</v>
+      </c>
+      <c r="Y2">
+        <v>6.4</v>
+      </c>
+      <c r="Z2">
+        <v>11</v>
+      </c>
+      <c r="AA2">
+        <v>28</v>
+      </c>
+      <c r="AB2">
+        <v>11.5</v>
+      </c>
+      <c r="AC2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>12.5</v>
+      </c>
+      <c r="AE2">
+        <v>34</v>
+      </c>
+      <c r="AF2">
+        <v>38</v>
+      </c>
+      <c r="AG2">
+        <v>25</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>80</v>
+      </c>
+      <c r="AJ2">
+        <v>150</v>
+      </c>
+      <c r="AK2">
+        <v>110</v>
+      </c>
+      <c r="AL2">
+        <v>140</v>
+      </c>
+      <c r="AM2">
+        <v>290</v>
+      </c>
+      <c r="AN2">
+        <v>180</v>
+      </c>
+      <c r="AO2">
+        <v>29</v>
+      </c>
+      <c r="AP2">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2">
+        <v>5.8</v>
+      </c>
+      <c r="AR2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>7.8</v>
+      </c>
+      <c r="AT2">
+        <v>10</v>
+      </c>
+      <c r="AU2">
+        <v>7.2</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2">
+        <v>8.6</v>
+      </c>
+      <c r="AY2">
+        <v>18.5</v>
+      </c>
+      <c r="AZ2">
+        <v>7.8</v>
+      </c>
+      <c r="BA2">
+        <v>9.6</v>
+      </c>
+      <c r="BB2">
+        <v>10</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>10</v>
+      </c>
+      <c r="BE2">
+        <v>10.5</v>
+      </c>
+      <c r="BF2">
+        <v>10</v>
+      </c>
+      <c r="BG2">
+        <v>21</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.2</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>8.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>5.9</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>3.75</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3">
+        <v>3.55</v>
+      </c>
+      <c r="G3">
+        <v>4.3</v>
+      </c>
+      <c r="H3">
+        <v>2.2</v>
+      </c>
+      <c r="I3">
+        <v>2.42</v>
+      </c>
+      <c r="J3">
+        <v>3.15</v>
+      </c>
+      <c r="K3">
+        <v>3.5</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>3.15</v>
+      </c>
+      <c r="O3">
+        <v>1.35</v>
+      </c>
+      <c r="P3">
+        <v>1.71</v>
+      </c>
+      <c r="Q3">
+        <v>2.12</v>
+      </c>
+      <c r="R3">
+        <v>1.26</v>
+      </c>
+      <c r="S3">
+        <v>3.9</v>
+      </c>
+      <c r="T3">
+        <v>1.81</v>
+      </c>
+      <c r="U3">
+        <v>1.92</v>
+      </c>
+      <c r="V3">
+        <v>1.71</v>
+      </c>
+      <c r="W3">
+        <v>1.31</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>14</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>11</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.26</v>
+      </c>
+      <c r="AQ3">
+        <v>1.16</v>
+      </c>
+      <c r="AR3">
+        <v>1.26</v>
+      </c>
+      <c r="AS3">
+        <v>1.26</v>
+      </c>
+      <c r="AT3">
+        <v>1.26</v>
+      </c>
+      <c r="AU3">
+        <v>5.5</v>
+      </c>
+      <c r="AV3">
+        <v>8</v>
+      </c>
+      <c r="AW3">
+        <v>1.26</v>
+      </c>
+      <c r="AX3">
+        <v>1.26</v>
+      </c>
+      <c r="AY3">
+        <v>1.26</v>
+      </c>
+      <c r="AZ3">
+        <v>1.26</v>
+      </c>
+      <c r="BA3">
+        <v>1.26</v>
+      </c>
+      <c r="BB3">
+        <v>1.26</v>
+      </c>
+      <c r="BC3">
+        <v>1.26</v>
+      </c>
+      <c r="BD3">
+        <v>1.26</v>
+      </c>
+      <c r="BE3">
+        <v>1.26</v>
+      </c>
+      <c r="BF3">
+        <v>1.26</v>
+      </c>
+      <c r="BG3">
+        <v>1.26</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>3.6</v>
+      </c>
+      <c r="G4">
+        <v>5.9</v>
+      </c>
+      <c r="H4">
+        <v>1.63</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>4.5</v>
+      </c>
+      <c r="K4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>3.7</v>
+      </c>
+      <c r="Q4">
+        <v>1.19</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5">
+        <v>1.95</v>
+      </c>
+      <c r="G5">
+        <v>2.18</v>
+      </c>
+      <c r="H5">
+        <v>3.15</v>
+      </c>
+      <c r="I5">
+        <v>5.3</v>
+      </c>
+      <c r="J5">
+        <v>3.55</v>
+      </c>
+      <c r="K5">
+        <v>3.9</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.25</v>
+      </c>
+      <c r="Q5">
+        <v>1.02</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6">
+        <v>1.94</v>
+      </c>
+      <c r="G6">
+        <v>2.06</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>5.5</v>
+      </c>
+      <c r="J6">
+        <v>3.1</v>
+      </c>
+      <c r="K6">
+        <v>3.3</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.5</v>
+      </c>
+      <c r="Q6">
+        <v>2.74</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7">
+        <v>1.72</v>
+      </c>
+      <c r="G7">
+        <v>2.18</v>
+      </c>
+      <c r="H7">
+        <v>3.75</v>
+      </c>
+      <c r="I7">
+        <v>6.4</v>
+      </c>
+      <c r="J7">
+        <v>3.3</v>
+      </c>
+      <c r="K7">
+        <v>6.6</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.66</v>
+      </c>
+      <c r="Q7">
+        <v>1.87</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -328,7 +328,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 01:04:06</t>
+    <t>2026-10-03 03:19:53</t>
   </si>
 </sst>
 </file>
@@ -922,13 +922,13 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G2">
         <v>4.9</v>
       </c>
       <c r="H2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I2">
         <v>2.1</v>
@@ -952,7 +952,7 @@
         <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
         <v>2.8</v>
@@ -964,10 +964,10 @@
         <v>5.7</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
         <v>1.9</v>
@@ -982,7 +982,7 @@
         <v>6.4</v>
       </c>
       <c r="Z2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA2">
         <v>28</v>
@@ -994,7 +994,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE2">
         <v>34</v>
@@ -1003,16 +1003,16 @@
         <v>38</v>
       </c>
       <c r="AG2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AI2">
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AK2">
         <v>110</v>
@@ -1021,7 +1021,7 @@
         <v>140</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN2">
         <v>180</v>
@@ -1036,10 +1036,10 @@
         <v>5.8</v>
       </c>
       <c r="AR2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>10</v>
@@ -1051,10 +1051,10 @@
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
         <v>18.5</v>
@@ -1063,22 +1063,22 @@
         <v>7.8</v>
       </c>
       <c r="BA2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB2">
+        <v>9.4</v>
+      </c>
+      <c r="BC2">
+        <v>9</v>
+      </c>
+      <c r="BD2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE2">
         <v>9.6</v>
       </c>
-      <c r="BB2">
-        <v>10</v>
-      </c>
-      <c r="BC2">
-        <v>10</v>
-      </c>
-      <c r="BD2">
-        <v>10</v>
-      </c>
-      <c r="BE2">
-        <v>10.5</v>
-      </c>
       <c r="BF2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
         <v>21</v>
@@ -1087,61 +1087,61 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>2.76</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>5.9</v>
+        <v>2.28</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>3.75</v>
+        <v>1.83</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="CB2" t="s">
         <v>104</v>
@@ -1191,7 +1191,7 @@
         <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
         <v>1.71</v>
@@ -1287,7 +1287,7 @@
         <v>1.26</v>
       </c>
       <c r="AU3">
-        <v>5.5</v>
+        <v>1.13</v>
       </c>
       <c r="AV3">
         <v>8</v>
@@ -1406,7 +1406,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G4">
         <v>5.9</v>
@@ -1415,13 +1415,13 @@
         <v>1.63</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J4">
         <v>4.5</v>
       </c>
       <c r="K4">
-        <v>9.199999999999999</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1890,16 +1890,16 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
         <v>3.1</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q6">
         <v>2.74</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -328,7 +328,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 03:19:53</t>
+    <t>2026-10-03 05:36:12</t>
   </si>
 </sst>
 </file>
@@ -1287,10 +1287,10 @@
         <v>1.26</v>
       </c>
       <c r="AU3">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="AV3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3">
         <v>1.26</v>
@@ -1418,7 +1418,7 @@
         <v>2.04</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q4">
         <v>1.19</v>
@@ -1902,7 +1902,7 @@
         <v>5.6</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
         <v>3.3</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>01:15:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
     <t>Llaneros FC</t>
   </si>
   <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
     <t>Moss</t>
   </si>
   <si>
@@ -316,6 +325,9 @@
     <t>America de Cali S.A</t>
   </si>
   <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
@@ -328,7 +340,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 05:36:12</t>
+    <t>2026-10-03 07:52:35</t>
   </si>
 </sst>
 </file>
@@ -660,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -910,16 +922,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F2">
         <v>4.6</v>
@@ -1144,7 +1156,7 @@
         <v>1.09</v>
       </c>
       <c r="CB2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1152,16 +1164,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F3">
         <v>3.55</v>
@@ -1287,10 +1299,10 @@
         <v>1.26</v>
       </c>
       <c r="AU3">
-        <v>5.5</v>
+        <v>1.13</v>
       </c>
       <c r="AV3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW3">
         <v>1.26</v>
@@ -1386,7 +1398,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1394,241 +1406,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F4">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="Q4">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1636,40 +1648,40 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F5">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="H5">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="I5">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1678,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1870,42 +1882,42 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G6">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H6">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1920,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2112,249 +2124,491 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <v>1.92</v>
+      </c>
+      <c r="G7">
+        <v>2.04</v>
+      </c>
+      <c r="H7">
+        <v>5.1</v>
+      </c>
+      <c r="I7">
+        <v>5.6</v>
+      </c>
+      <c r="J7">
+        <v>3.15</v>
+      </c>
+      <c r="K7">
+        <v>3.3</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.51</v>
+      </c>
+      <c r="Q7">
+        <v>2.76</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
         <v>85</v>
       </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7">
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8">
         <v>1.72</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>2.18</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>3.75</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>6.4</v>
       </c>
-      <c r="J7">
+      <c r="J8">
         <v>3.3</v>
       </c>
-      <c r="K7">
+      <c r="K8">
         <v>6.6</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>1.66</v>
       </c>
-      <c r="Q7">
+      <c r="Q8">
         <v>1.87</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7">
-        <v>0</v>
-      </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-      <c r="BF7">
-        <v>0</v>
-      </c>
-      <c r="BG7">
-        <v>0</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7">
-        <v>0</v>
-      </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7">
-        <v>0</v>
-      </c>
-      <c r="BS7">
-        <v>0</v>
-      </c>
-      <c r="BT7">
-        <v>0</v>
-      </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
-      <c r="BV7">
-        <v>0</v>
-      </c>
-      <c r="BW7">
-        <v>0</v>
-      </c>
-      <c r="BX7">
-        <v>0</v>
-      </c>
-      <c r="BY7">
-        <v>0</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>104</v>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -256,15 +256,15 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>CONCACAF Nations League A</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
-    <t>CONCACAF Nations League A</t>
-  </si>
-  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
@@ -277,6 +277,9 @@
     <t>2026-10-05</t>
   </si>
   <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
     <t>00:30:00</t>
   </si>
   <si>
@@ -298,6 +301,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
     <t>Estudiantes Rio Cuarto</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Haiti</t>
+  </si>
+  <si>
     <t>Racing Club</t>
   </si>
   <si>
@@ -340,7 +349,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 07:52:35</t>
+    <t>2026-10-03 10:09:05</t>
   </si>
 </sst>
 </file>
@@ -672,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -928,235 +937,235 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F2">
-        <v>4.6</v>
+        <v>1.39</v>
       </c>
       <c r="G2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="I2">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>1.2</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>1.31</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>5.8</v>
+        <v>1.02</v>
       </c>
       <c r="AR2">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>10</v>
+        <v>1.02</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>1.02</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>1.02</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>1.02</v>
       </c>
       <c r="AY2">
-        <v>18.5</v>
+        <v>1.02</v>
       </c>
       <c r="AZ2">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1170,235 +1179,235 @@
         <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="I3">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="P3">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
+        <v>1.18</v>
+      </c>
+      <c r="S3">
+        <v>5.8</v>
+      </c>
+      <c r="T3">
+        <v>2.4</v>
+      </c>
+      <c r="U3">
+        <v>1.65</v>
+      </c>
+      <c r="V3">
+        <v>1.9</v>
+      </c>
+      <c r="W3">
         <v>1.26</v>
       </c>
-      <c r="S3">
-        <v>3.9</v>
-      </c>
-      <c r="T3">
-        <v>1.81</v>
-      </c>
-      <c r="U3">
-        <v>1.92</v>
-      </c>
-      <c r="V3">
-        <v>1.71</v>
-      </c>
-      <c r="W3">
-        <v>1.31</v>
-      </c>
       <c r="X3">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y3">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>13.5</v>
+      </c>
+      <c r="AE3">
+        <v>34</v>
+      </c>
+      <c r="AF3">
+        <v>38</v>
+      </c>
+      <c r="AG3">
+        <v>23</v>
+      </c>
+      <c r="AH3">
+        <v>34</v>
+      </c>
+      <c r="AI3">
+        <v>80</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>110</v>
+      </c>
+      <c r="AL3">
+        <v>140</v>
+      </c>
+      <c r="AM3">
+        <v>300</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>29</v>
+      </c>
+      <c r="AP3">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3">
+        <v>5.8</v>
+      </c>
+      <c r="AR3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3">
+        <v>17.5</v>
+      </c>
+      <c r="AT3">
+        <v>10</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
         <v>11</v>
       </c>
-      <c r="AD3">
-        <v>22</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>1000</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.26</v>
-      </c>
-      <c r="AQ3">
-        <v>1.16</v>
-      </c>
-      <c r="AR3">
-        <v>1.26</v>
-      </c>
-      <c r="AS3">
-        <v>1.26</v>
-      </c>
-      <c r="AT3">
-        <v>1.26</v>
-      </c>
-      <c r="AU3">
-        <v>1.13</v>
-      </c>
-      <c r="AV3">
-        <v>8</v>
-      </c>
       <c r="AW3">
-        <v>1.26</v>
+        <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>1.26</v>
+        <v>19</v>
       </c>
       <c r="AY3">
-        <v>1.26</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3">
-        <v>1.26</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>1.26</v>
+        <v>34</v>
       </c>
       <c r="BB3">
-        <v>1.26</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>1.26</v>
+        <v>11</v>
       </c>
       <c r="BD3">
-        <v>1.26</v>
+        <v>11</v>
       </c>
       <c r="BE3">
-        <v>1.26</v>
+        <v>11</v>
       </c>
       <c r="BF3">
-        <v>1.26</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>1.26</v>
+        <v>18.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="CB3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1412,70 +1421,70 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z4">
         <v>1000</v>
@@ -1487,10 +1496,10 @@
         <v>1000</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1526,58 +1535,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1640,12 +1649,12 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
         <v>86</v>
@@ -1654,240 +1663,240 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="G5">
-        <v>5.9</v>
+        <v>110</v>
       </c>
       <c r="H5">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="I5">
-        <v>2.04</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>86</v>
@@ -1896,34 +1905,34 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F6">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="G6">
-        <v>2.16</v>
+        <v>5.9</v>
       </c>
       <c r="H6">
-        <v>3.9</v>
+        <v>1.63</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1932,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2124,12 +2133,12 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>86</v>
@@ -2138,28 +2147,28 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H7">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="I7">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2174,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>2.76</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2366,12 +2375,12 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>86</v>
@@ -2380,235 +2389,477 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F8">
+        <v>1.91</v>
+      </c>
+      <c r="G8">
+        <v>2.04</v>
+      </c>
+      <c r="H8">
+        <v>5.1</v>
+      </c>
+      <c r="I8">
+        <v>5.6</v>
+      </c>
+      <c r="J8">
+        <v>3.15</v>
+      </c>
+      <c r="K8">
+        <v>3.35</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.51</v>
+      </c>
+      <c r="Q8">
+        <v>2.76</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
         <v>1.72</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>2.18</v>
       </c>
-      <c r="H8">
+      <c r="H9">
         <v>3.75</v>
       </c>
-      <c r="I8">
+      <c r="I9">
         <v>6.4</v>
       </c>
-      <c r="J8">
-        <v>3.3</v>
-      </c>
-      <c r="K8">
+      <c r="J9">
+        <v>3.45</v>
+      </c>
+      <c r="K9">
         <v>6.6</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>1.66</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <v>1.87</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8">
-        <v>0</v>
-      </c>
-      <c r="BE8">
-        <v>0</v>
-      </c>
-      <c r="BF8">
-        <v>0</v>
-      </c>
-      <c r="BG8">
-        <v>0</v>
-      </c>
-      <c r="BH8">
-        <v>0</v>
-      </c>
-      <c r="BI8">
-        <v>0</v>
-      </c>
-      <c r="BJ8">
-        <v>0</v>
-      </c>
-      <c r="BK8">
-        <v>0</v>
-      </c>
-      <c r="BL8">
-        <v>0</v>
-      </c>
-      <c r="BM8">
-        <v>0</v>
-      </c>
-      <c r="BN8">
-        <v>0</v>
-      </c>
-      <c r="BO8">
-        <v>0</v>
-      </c>
-      <c r="BP8">
-        <v>0</v>
-      </c>
-      <c r="BQ8">
-        <v>0</v>
-      </c>
-      <c r="BR8">
-        <v>0</v>
-      </c>
-      <c r="BS8">
-        <v>0</v>
-      </c>
-      <c r="BT8">
-        <v>0</v>
-      </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
-      <c r="BV8">
-        <v>0</v>
-      </c>
-      <c r="BW8">
-        <v>0</v>
-      </c>
-      <c r="BX8">
-        <v>0</v>
-      </c>
-      <c r="BY8">
-        <v>0</v>
-      </c>
-      <c r="BZ8">
-        <v>0</v>
-      </c>
-      <c r="CA8">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>108</v>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -349,7 +349,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 10:09:05</t>
+    <t>2026-10-03 12:24:58</t>
   </si>
 </sst>
 </file>
@@ -943,13 +943,13 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.39</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>1000</v>
@@ -961,19 +961,19 @@
         <v>110</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2">
         <v>1.31</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
         <v>1.31</v>
@@ -991,10 +991,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1054,7 +1054,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
         <v>1.03</v>
@@ -1063,22 +1063,22 @@
         <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
         <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
         <v>1.03</v>
@@ -1218,13 +1218,13 @@
         <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T3">
         <v>2.4</v>
@@ -1251,37 +1251,37 @@
         <v>27</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
         <v>34</v>
       </c>
-      <c r="AF3">
-        <v>38</v>
-      </c>
       <c r="AG3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>920</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>300</v>
@@ -1302,46 +1302,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT3">
         <v>10</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX3">
+        <v>24</v>
+      </c>
+      <c r="AY3">
         <v>19</v>
       </c>
-      <c r="AY3">
-        <v>18.5</v>
-      </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BC3">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BD3">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BE3">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BG3">
         <v>18.5</v>
@@ -1454,7 +1454,7 @@
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
         <v>1.71</v>
@@ -1481,7 +1481,7 @@
         <v>1.31</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y4">
         <v>14</v>
@@ -1535,58 +1535,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AR4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AS4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AT4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AU4">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="AV4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AX4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AY4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AZ4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BA4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BB4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BC4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BD4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BE4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BF4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BG4">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1669,172 +1669,172 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>7.6</v>
       </c>
       <c r="H5">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>1.68</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>900</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -1923,7 +1923,7 @@
         <v>2.04</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -2156,7 +2156,7 @@
         <v>1.76</v>
       </c>
       <c r="G7">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H7">
         <v>3.85</v>
@@ -2165,10 +2165,10 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2637,22 +2637,22 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G9">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H9">
         <v>3.75</v>
       </c>
       <c r="I9">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>3.45</v>
       </c>
       <c r="K9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -349,7 +349,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 12:24:58</t>
+    <t>2026-10-03 14:39:18</t>
   </si>
 </sst>
 </file>
@@ -943,178 +943,178 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>110</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>1.32</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU2">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1123,46 +1123,46 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,7 +1185,7 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
         <v>4.9</v>
@@ -1194,7 +1194,7 @@
         <v>2.04</v>
       </c>
       <c r="I3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J3">
         <v>3.2</v>
@@ -1203,31 +1203,31 @@
         <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
         <v>1.61</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
         <v>1.65</v>
@@ -1251,7 +1251,7 @@
         <v>27</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
         <v>8</v>
@@ -1263,7 +1263,7 @@
         <v>30</v>
       </c>
       <c r="AF3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG3">
         <v>22</v>
@@ -1272,7 +1272,7 @@
         <v>29</v>
       </c>
       <c r="AI3">
-        <v>920</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
@@ -1302,7 +1302,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1314,31 +1314,31 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY3">
         <v>19</v>
       </c>
       <c r="AZ3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BC3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD3">
         <v>65</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>42</v>
@@ -1350,13 +1350,13 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1368,7 +1368,7 @@
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1386,13 +1386,13 @@
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.84</v>
+        <v>1.09</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1427,22 +1427,22 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1454,37 +1454,37 @@
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
+        <v>1.7</v>
+      </c>
+      <c r="Q4">
+        <v>2.1</v>
+      </c>
+      <c r="R4">
+        <v>1.25</v>
+      </c>
+      <c r="S4">
+        <v>3.75</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.86</v>
+      </c>
+      <c r="V4">
         <v>1.71</v>
       </c>
-      <c r="Q4">
-        <v>2.12</v>
-      </c>
-      <c r="R4">
-        <v>1.26</v>
-      </c>
-      <c r="S4">
-        <v>3.85</v>
-      </c>
-      <c r="T4">
-        <v>1.8</v>
-      </c>
-      <c r="U4">
-        <v>1.92</v>
-      </c>
-      <c r="V4">
-        <v>1.7</v>
-      </c>
       <c r="W4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
         <v>1000</v>
@@ -1535,58 +1535,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AQ4">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AR4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AS4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AT4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AU4">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="AV4">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="AW4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AX4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AY4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AZ4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BA4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BB4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BC4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BD4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BE4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BF4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BG4">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1669,112 +1669,112 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="G5">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="I5">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P5">
         <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U5">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="V5">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
         <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AA5">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AB5">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AF5">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AG5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AK5">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AL5">
+        <v>100</v>
+      </c>
+      <c r="AM5">
+        <v>140</v>
+      </c>
+      <c r="AN5">
         <v>120</v>
       </c>
-      <c r="AM5">
-        <v>170</v>
-      </c>
-      <c r="AN5">
-        <v>170</v>
-      </c>
       <c r="AO5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AP5">
         <v>12.5</v>
@@ -1783,16 +1783,16 @@
         <v>6.8</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS5">
         <v>12.5</v>
       </c>
       <c r="AT5">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
         <v>8.6</v>
@@ -1801,31 +1801,31 @@
         <v>15</v>
       </c>
       <c r="AX5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG5">
         <v>7.6</v>
@@ -1834,7 +1834,7 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -1926,19 +1926,19 @@
         <v>4.2</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
         <v>4</v>
@@ -1947,190 +1947,190 @@
         <v>1.19</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2165,10 +2165,10 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>3.15</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L8">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -349,7 +349,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 14:39:18</t>
+    <t>2026-10-03 16:52:32</t>
   </si>
 </sst>
 </file>
@@ -943,22 +943,22 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -991,67 +991,67 @@
         <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB2">
         <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM2">
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AO2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
         <v>11</v>
@@ -1063,46 +1063,46 @@
         <v>23</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BE2">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1120,13 +1120,13 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
         <v>16.5</v>
@@ -1144,7 +1144,7 @@
         <v>7</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>29</v>
@@ -1153,7 +1153,7 @@
         <v>20</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY2">
         <v>28</v>
@@ -1191,19 +1191,19 @@
         <v>4.9</v>
       </c>
       <c r="H3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.14</v>
@@ -1212,25 +1212,25 @@
         <v>2.5</v>
       </c>
       <c r="O3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V3">
         <v>1.9</v>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="Y3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z3">
         <v>10.5</v>
@@ -1254,10 +1254,10 @@
         <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
         <v>30</v>
@@ -1272,13 +1272,13 @@
         <v>29</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1296,13 +1296,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR3">
         <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1314,97 +1314,97 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX3">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AY3">
         <v>19</v>
       </c>
       <c r="AZ3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA3">
         <v>46</v>
       </c>
       <c r="BB3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BC3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BG3">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI3">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.09</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,22 +1427,22 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1451,40 +1451,40 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z4">
         <v>1000</v>
@@ -1493,7 +1493,7 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC4">
         <v>11</v>
@@ -1535,58 +1535,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ4">
-        <v>1.15</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AS4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AT4">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AU4">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="AV4">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="AW4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AX4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AY4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AZ4">
-        <v>1.15</v>
+        <v>11</v>
       </c>
       <c r="BA4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BB4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BC4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BD4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BE4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BF4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BG4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1669,22 +1669,22 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H5">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="I5">
         <v>1.8</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1696,49 +1696,49 @@
         <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P5">
         <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V5">
         <v>2.24</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5">
         <v>11</v>
       </c>
       <c r="AA5">
+        <v>18.5</v>
+      </c>
+      <c r="AB5">
         <v>19.5</v>
       </c>
-      <c r="AB5">
-        <v>19</v>
-      </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
@@ -1747,7 +1747,7 @@
         <v>19.5</v>
       </c>
       <c r="AF5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG5">
         <v>23</v>
@@ -1756,13 +1756,13 @@
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AL5">
         <v>100</v>
@@ -1774,67 +1774,67 @@
         <v>120</v>
       </c>
       <c r="AO5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP5">
         <v>12.5</v>
       </c>
       <c r="AQ5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT5">
         <v>15.5</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
         <v>8.6</v>
       </c>
       <c r="AW5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AY5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC5">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BD5">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
@@ -1911,22 +1911,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G6">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I6">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1935,34 +1935,34 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R6">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="S6">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="V6">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="W6">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1983,7 +1983,7 @@
         <v>1000</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE6">
         <v>1000</v>
@@ -2016,61 +2016,61 @@
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2153,226 +2153,226 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="G7">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
+        <v>3.9</v>
+      </c>
+      <c r="I7">
+        <v>4.5</v>
+      </c>
+      <c r="J7">
+        <v>3.45</v>
+      </c>
+      <c r="K7">
+        <v>4.2</v>
+      </c>
+      <c r="L7">
+        <v>1.38</v>
+      </c>
+      <c r="M7">
+        <v>1.06</v>
+      </c>
+      <c r="N7">
+        <v>3.5</v>
+      </c>
+      <c r="O7">
+        <v>1.29</v>
+      </c>
+      <c r="P7">
+        <v>1.85</v>
+      </c>
+      <c r="Q7">
+        <v>1.85</v>
+      </c>
+      <c r="R7">
+        <v>1.33</v>
+      </c>
+      <c r="S7">
+        <v>3.05</v>
+      </c>
+      <c r="T7">
+        <v>1.7</v>
+      </c>
+      <c r="U7">
+        <v>2.02</v>
+      </c>
+      <c r="V7">
+        <v>1.3</v>
+      </c>
+      <c r="W7">
+        <v>1.92</v>
+      </c>
+      <c r="X7">
+        <v>50</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>16.5</v>
+      </c>
+      <c r="AC7">
+        <v>12</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>25</v>
+      </c>
+      <c r="AG7">
+        <v>19</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>34</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ7">
+        <v>10</v>
+      </c>
+      <c r="AR7">
+        <v>1.4</v>
+      </c>
+      <c r="AS7">
+        <v>1.4</v>
+      </c>
+      <c r="AT7">
+        <v>7</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>10.5</v>
+      </c>
+      <c r="AW7">
+        <v>1.4</v>
+      </c>
+      <c r="AX7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY7">
+        <v>7.4</v>
+      </c>
+      <c r="AZ7">
+        <v>11</v>
+      </c>
+      <c r="BA7">
+        <v>1.4</v>
+      </c>
+      <c r="BB7">
+        <v>1.4</v>
+      </c>
+      <c r="BC7">
+        <v>11.5</v>
+      </c>
+      <c r="BD7">
+        <v>1.4</v>
+      </c>
+      <c r="BE7">
+        <v>1.4</v>
+      </c>
+      <c r="BF7">
+        <v>9.4</v>
+      </c>
+      <c r="BG7">
+        <v>1.4</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>2.94</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>6.8</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
         <v>3.85</v>
       </c>
-      <c r="I7">
-        <v>1000</v>
-      </c>
-      <c r="J7">
-        <v>3.4</v>
-      </c>
-      <c r="K7">
-        <v>4.3</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.02</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7">
-        <v>0</v>
-      </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-      <c r="BF7">
-        <v>0</v>
-      </c>
-      <c r="BG7">
-        <v>0</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7">
-        <v>0</v>
-      </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2398,7 +2398,7 @@
         <v>1.91</v>
       </c>
       <c r="G8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H8">
         <v>5.1</v>
@@ -2410,19 +2410,19 @@
         <v>3.15</v>
       </c>
       <c r="K8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>1.51</v>
@@ -2431,190 +2431,190 @@
         <v>2.76</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,226 +2637,226 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="G9">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H9">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
         <v>3.45</v>
       </c>
       <c r="K9">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9">
         <v>1.66</v>
       </c>
       <c r="Q9">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -349,7 +349,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 16:52:32</t>
+    <t>2026-10-03 19:04:11</t>
   </si>
 </sst>
 </file>
@@ -946,223 +946,223 @@
         <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="Q2">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="U2">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
         <v>15</v>
       </c>
-      <c r="Y2">
-        <v>13</v>
-      </c>
       <c r="Z2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA2">
         <v>120</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>25</v>
+      </c>
+      <c r="AL2">
+        <v>75</v>
+      </c>
+      <c r="AM2">
+        <v>95</v>
+      </c>
+      <c r="AN2">
+        <v>22</v>
+      </c>
+      <c r="AO2">
         <v>32</v>
       </c>
-      <c r="AK2">
-        <v>26</v>
-      </c>
-      <c r="AL2">
-        <v>40</v>
-      </c>
-      <c r="AM2">
-        <v>120</v>
-      </c>
-      <c r="AN2">
-        <v>23</v>
-      </c>
-      <c r="AO2">
-        <v>50</v>
-      </c>
       <c r="AP2">
+        <v>13</v>
+      </c>
+      <c r="AQ2">
         <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>11</v>
       </c>
       <c r="AR2">
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AT2">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BB2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BF2">
         <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
+        <v>5.3</v>
+      </c>
+      <c r="BO2">
+        <v>4</v>
+      </c>
+      <c r="BP2">
+        <v>16</v>
+      </c>
+      <c r="BQ2">
+        <v>11.5</v>
+      </c>
+      <c r="BR2">
+        <v>28</v>
+      </c>
+      <c r="BS2">
+        <v>19.5</v>
+      </c>
+      <c r="BT2">
+        <v>6.8</v>
+      </c>
+      <c r="BU2">
         <v>5.1</v>
       </c>
-      <c r="BO2">
-        <v>4.5</v>
-      </c>
-      <c r="BP2">
-        <v>16.5</v>
-      </c>
-      <c r="BQ2">
-        <v>12</v>
-      </c>
-      <c r="BR2">
-        <v>32</v>
-      </c>
-      <c r="BS2">
-        <v>21</v>
-      </c>
-      <c r="BT2">
-        <v>7</v>
-      </c>
-      <c r="BU2">
-        <v>6</v>
-      </c>
       <c r="BV2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,22 +1185,22 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="H3">
+        <v>2.02</v>
+      </c>
+      <c r="I3">
         <v>2.06</v>
-      </c>
-      <c r="I3">
-        <v>2.1</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1221,22 +1221,22 @@
         <v>2.86</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W3">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X3">
         <v>8</v>
@@ -1248,94 +1248,94 @@
         <v>10.5</v>
       </c>
       <c r="AA3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD3">
         <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG3">
         <v>22</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP3">
         <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS3">
+        <v>20</v>
+      </c>
+      <c r="AT3">
+        <v>10.5</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>11</v>
+      </c>
+      <c r="AW3">
+        <v>22</v>
+      </c>
+      <c r="AX3">
+        <v>25</v>
+      </c>
+      <c r="AY3">
+        <v>19.5</v>
+      </c>
+      <c r="AZ3">
         <v>23</v>
       </c>
-      <c r="AT3">
-        <v>10</v>
-      </c>
-      <c r="AU3">
-        <v>7.4</v>
-      </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>25</v>
-      </c>
-      <c r="AX3">
-        <v>29</v>
-      </c>
-      <c r="AY3">
-        <v>19</v>
-      </c>
-      <c r="AZ3">
-        <v>25</v>
-      </c>
       <c r="BA3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB3">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BC3">
         <v>55</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="BE3">
         <v>50</v>
@@ -1344,7 +1344,7 @@
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH3">
         <v>2.72</v>
@@ -1365,7 +1365,7 @@
         <v>2.76</v>
       </c>
       <c r="BN3">
-        <v>910</v>
+        <v>780</v>
       </c>
       <c r="BO3">
         <v>2.26</v>
@@ -1427,7 +1427,7 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1436,7 +1436,7 @@
         <v>2.2</v>
       </c>
       <c r="I4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1454,7 +1454,7 @@
         <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
         <v>1.71</v>
@@ -1472,19 +1472,19 @@
         <v>1.78</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W4">
         <v>1.33</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
         <v>1000</v>
@@ -1496,7 +1496,7 @@
         <v>25</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>22</v>
@@ -1508,10 +1508,10 @@
         <v>1000</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1535,7 +1535,7 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AQ4">
         <v>6.4</v>
@@ -1544,49 +1544,49 @@
         <v>9</v>
       </c>
       <c r="AS4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="AT4">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AU4">
         <v>5.4</v>
       </c>
       <c r="AV4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AW4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="AX4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="AY4">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AZ4">
         <v>11</v>
       </c>
       <c r="BA4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BB4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BC4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BD4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BE4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BF4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BG4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1595,7 +1595,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
@@ -1604,19 +1604,19 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1625,25 +1625,25 @@
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1669,22 +1669,22 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G5">
         <v>6.2</v>
       </c>
       <c r="H5">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1693,19 +1693,19 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
         <v>1.3</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
         <v>3.3</v>
@@ -1717,7 +1717,7 @@
         <v>1.94</v>
       </c>
       <c r="V5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W5">
         <v>1.19</v>
@@ -1729,10 +1729,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB5">
         <v>19.5</v>
@@ -1744,7 +1744,7 @@
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF5">
         <v>48</v>
@@ -1774,7 +1774,7 @@
         <v>120</v>
       </c>
       <c r="AO5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP5">
         <v>12.5</v>
@@ -1810,22 +1810,22 @@
         <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BB5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG5">
         <v>8.6</v>
@@ -1911,22 +1911,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G6">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1935,19 +1935,19 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P6">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
         <v>1.2</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
         <v>1.55</v>
@@ -1959,10 +1959,10 @@
         <v>3.25</v>
       </c>
       <c r="V6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2156,16 +2156,16 @@
         <v>1.93</v>
       </c>
       <c r="G7">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -2183,7 +2183,7 @@
         <v>1.29</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q7">
         <v>1.85</v>
@@ -2201,10 +2201,10 @@
         <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X7">
         <v>50</v>
@@ -2300,7 +2300,7 @@
         <v>1.4</v>
       </c>
       <c r="BC7">
-        <v>11.5</v>
+        <v>1.4</v>
       </c>
       <c r="BD7">
         <v>1.4</v>
@@ -2395,7 +2395,7 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G8">
         <v>2.02</v>
@@ -2404,7 +2404,7 @@
         <v>5.1</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J8">
         <v>3.15</v>
@@ -2413,208 +2413,208 @@
         <v>3.35</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>1.51</v>
+        <v>2.58</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q8">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
         <v>1.98</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,58 +2637,58 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="G9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="I9">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O9">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P9">
         <v>1.66</v>
       </c>
       <c r="Q9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R9">
         <v>1.24</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2745,52 +2745,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2805,58 +2805,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -349,7 +349,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 19:04:11</t>
+    <t>2026-10-03 21:16:40</t>
   </si>
 </sst>
 </file>
@@ -943,61 +943,61 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y2">
         <v>15</v>
@@ -1039,19 +1039,19 @@
         <v>25</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AO2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
         <v>12.5</v>
@@ -1060,19 +1060,19 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>18.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
         <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1084,34 +1084,34 @@
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB2">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2">
         <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2">
         <v>6.8</v>
@@ -1120,7 +1120,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1147,22 +1147,22 @@
         <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,40 +1185,40 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H3">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P3">
         <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
         <v>1.17</v>
@@ -1233,7 +1233,7 @@
         <v>1.63</v>
       </c>
       <c r="V3">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W3">
         <v>1.24</v>
@@ -1245,10 +1245,10 @@
         <v>6.2</v>
       </c>
       <c r="Z3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB3">
         <v>12</v>
@@ -1266,7 +1266,7 @@
         <v>36</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1290,13 +1290,13 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP3">
         <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR3">
         <v>9</v>
@@ -1308,43 +1308,43 @@
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY3">
         <v>19.5</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB3">
         <v>40</v>
       </c>
       <c r="BC3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BD3">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF3">
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH3">
         <v>2.72</v>
@@ -1365,7 +1365,7 @@
         <v>2.76</v>
       </c>
       <c r="BN3">
-        <v>780</v>
+        <v>690</v>
       </c>
       <c r="BO3">
         <v>2.26</v>
@@ -1430,16 +1430,16 @@
         <v>3.65</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H4">
         <v>2.2</v>
       </c>
       <c r="I4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1448,16 +1448,16 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.12</v>
@@ -1469,124 +1469,124 @@
         <v>3.85</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
         <v>1.73</v>
       </c>
       <c r="W4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB4">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG4">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH4">
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP4">
-        <v>1.74</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AS4">
-        <v>1.87</v>
+        <v>5.3</v>
       </c>
       <c r="AT4">
-        <v>1.74</v>
+        <v>11</v>
       </c>
       <c r="AU4">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>1.87</v>
+        <v>5.2</v>
       </c>
       <c r="AX4">
-        <v>1.87</v>
+        <v>5.2</v>
       </c>
       <c r="AY4">
-        <v>1.7</v>
+        <v>13.5</v>
       </c>
       <c r="AZ4">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>1.87</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
-        <v>1.87</v>
+        <v>5.8</v>
       </c>
       <c r="BC4">
-        <v>1.87</v>
+        <v>5.7</v>
       </c>
       <c r="BD4">
-        <v>1.87</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>1.87</v>
+        <v>6</v>
       </c>
       <c r="BF4">
-        <v>1.87</v>
+        <v>5.7</v>
       </c>
       <c r="BG4">
-        <v>1.87</v>
+        <v>19.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1595,7 +1595,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
@@ -1604,19 +1604,19 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1625,25 +1625,25 @@
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1669,16 +1669,16 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="I5">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="J5">
         <v>3.85</v>
@@ -1693,7 +1693,7 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
         <v>1.3</v>
@@ -1702,7 +1702,7 @@
         <v>1.93</v>
       </c>
       <c r="Q5">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R5">
         <v>1.35</v>
@@ -1711,28 +1711,28 @@
         <v>3.3</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
         <v>1.94</v>
       </c>
       <c r="V5">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
         <v>16</v>
       </c>
       <c r="Y5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z5">
         <v>10.5</v>
       </c>
       <c r="AA5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AB5">
         <v>19.5</v>
@@ -1762,7 +1762,7 @@
         <v>180</v>
       </c>
       <c r="AK5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL5">
         <v>100</v>
@@ -1783,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5">
         <v>14.5</v>
@@ -1801,7 +1801,7 @@
         <v>15.5</v>
       </c>
       <c r="AX5">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AY5">
         <v>18.5</v>
@@ -1813,10 +1813,10 @@
         <v>12.5</v>
       </c>
       <c r="BB5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD5">
         <v>8.800000000000001</v>
@@ -1825,7 +1825,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5">
         <v>8.6</v>
@@ -1911,22 +1911,22 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G6">
         <v>4.9</v>
       </c>
       <c r="H6">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="I6">
         <v>1.91</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1947,7 +1947,7 @@
         <v>1.2</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S6">
         <v>1.55</v>
@@ -2019,55 +2019,55 @@
         <v>5.2</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BF6">
-        <v>9.800000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="BG6">
         <v>3.6</v>
@@ -2159,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I7">
         <v>4.6</v>
@@ -2168,7 +2168,7 @@
         <v>3.6</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.38</v>
@@ -2180,10 +2180,10 @@
         <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q7">
         <v>1.85</v>
@@ -2407,7 +2407,7 @@
         <v>5.5</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
         <v>3.35</v>
@@ -2416,7 +2416,7 @@
         <v>1.54</v>
       </c>
       <c r="M8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8">
         <v>2.58</v>
@@ -2431,10 +2431,10 @@
         <v>2.78</v>
       </c>
       <c r="R8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>2.32</v>
@@ -2449,13 +2449,13 @@
         <v>1.98</v>
       </c>
       <c r="X8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8">
         <v>13</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA8">
         <v>210</v>
@@ -2509,10 +2509,10 @@
         <v>11</v>
       </c>
       <c r="AR8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT8">
         <v>5.6</v>
@@ -2524,7 +2524,7 @@
         <v>20</v>
       </c>
       <c r="AW8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX8">
         <v>9.199999999999999</v>
@@ -2533,28 +2533,28 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BA8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB8">
         <v>21</v>
       </c>
       <c r="BC8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD8">
         <v>11</v>
       </c>
       <c r="BE8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2637,22 +2637,22 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="G9">
         <v>2.06</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>1.33</v>
@@ -2661,7 +2661,7 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="O9">
         <v>1.35</v>
@@ -2670,19 +2670,19 @@
         <v>1.66</v>
       </c>
       <c r="Q9">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R9">
         <v>1.24</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -2805,58 +2805,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -265,15 +265,15 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
     <t>Spanish Segunda Division</t>
   </si>
   <si>
-    <t>Paraguayan Primera Division</t>
-  </si>
-  <si>
     <t>2026-10-05</t>
   </si>
   <si>
@@ -289,6 +289,9 @@
     <t>02:00:00</t>
   </si>
   <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -313,6 +316,9 @@
     <t>Nicaragua</t>
   </si>
   <si>
+    <t>Deportivo Recoleta</t>
+  </si>
+  <si>
     <t>Moss</t>
   </si>
   <si>
@@ -337,6 +343,9 @@
     <t>Dominican Republic</t>
   </si>
   <si>
+    <t>Libertad</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
@@ -349,7 +358,7 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 21:16:40</t>
+    <t>2026-10-03 23:29:48</t>
   </si>
 </sst>
 </file>
@@ -681,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -937,10 +946,10 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F2">
         <v>2.18</v>
@@ -961,7 +970,7 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.05</v>
@@ -970,19 +979,19 @@
         <v>4.3</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <v>2.18</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R2">
         <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T2">
         <v>1.67</v>
@@ -1006,7 +1015,7 @@
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB2">
         <v>12</v>
@@ -1039,7 +1048,7 @@
         <v>25</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>80</v>
@@ -1051,7 +1060,7 @@
         <v>29</v>
       </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ2">
         <v>12.5</v>
@@ -1096,7 +1105,7 @@
         <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BF2">
         <v>11</v>
@@ -1114,13 +1123,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>65</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1132,13 +1141,13 @@
         <v>16</v>
       </c>
       <c r="BQ2">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>28</v>
       </c>
       <c r="BS2">
-        <v>19.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1150,22 +1159,22 @@
         <v>26</v>
       </c>
       <c r="BW2">
-        <v>18</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>22</v>
       </c>
       <c r="CA2">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1179,22 +1188,22 @@
         <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H3">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="J3">
         <v>3.2</v>
@@ -1209,16 +1218,16 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R3">
         <v>1.17</v>
@@ -1227,25 +1236,25 @@
         <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W3">
         <v>1.24</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA3">
         <v>24</v>
@@ -1260,13 +1269,13 @@
         <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF3">
         <v>36</v>
       </c>
       <c r="AG3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1284,19 +1293,19 @@
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR3">
         <v>9</v>
@@ -1308,34 +1317,34 @@
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV3">
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AX3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BA3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC3">
         <v>36</v>
       </c>
       <c r="BD3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BE3">
         <v>100</v>
@@ -1344,7 +1353,7 @@
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH3">
         <v>2.72</v>
@@ -1365,7 +1374,7 @@
         <v>2.76</v>
       </c>
       <c r="BN3">
-        <v>690</v>
+        <v>600</v>
       </c>
       <c r="BO3">
         <v>2.26</v>
@@ -1407,7 +1416,7 @@
         <v>2.76</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1421,10 +1430,10 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F4">
         <v>3.65</v>
@@ -1433,7 +1442,7 @@
         <v>3.9</v>
       </c>
       <c r="H4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I4">
         <v>2.36</v>
@@ -1442,7 +1451,7 @@
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1451,22 +1460,22 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>1.88</v>
@@ -1475,7 +1484,7 @@
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W4">
         <v>1.34</v>
@@ -1484,13 +1493,13 @@
         <v>14</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>16</v>
       </c>
       <c r="AA4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB4">
         <v>14.5</v>
@@ -1544,7 +1553,7 @@
         <v>12</v>
       </c>
       <c r="AS4">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT4">
         <v>11</v>
@@ -1556,10 +1565,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX4">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AY4">
         <v>13.5</v>
@@ -1568,22 +1577,22 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG4">
         <v>19.5</v>
@@ -1649,7 +1658,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1663,64 +1672,64 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G5">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H5">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="I5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P5">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q5">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V5">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
         <v>16</v>
@@ -1732,7 +1741,7 @@
         <v>10.5</v>
       </c>
       <c r="AA5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB5">
         <v>19.5</v>
@@ -1744,7 +1753,7 @@
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF5">
         <v>48</v>
@@ -1762,7 +1771,7 @@
         <v>180</v>
       </c>
       <c r="AK5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL5">
         <v>100</v>
@@ -1774,34 +1783,34 @@
         <v>120</v>
       </c>
       <c r="AO5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5">
         <v>14.5</v>
       </c>
       <c r="AT5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5">
         <v>15.5</v>
       </c>
       <c r="AX5">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
         <v>18.5</v>
@@ -1810,88 +1819,88 @@
         <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BB5">
+        <v>10</v>
+      </c>
+      <c r="BC5">
+        <v>32</v>
+      </c>
+      <c r="BD5">
+        <v>30</v>
+      </c>
+      <c r="BE5">
+        <v>10.5</v>
+      </c>
+      <c r="BF5">
+        <v>10</v>
+      </c>
+      <c r="BG5">
         <v>9.4</v>
       </c>
-      <c r="BC5">
-        <v>9</v>
-      </c>
-      <c r="BD5">
+      <c r="BH5">
+        <v>3.6</v>
+      </c>
+      <c r="BI5">
+        <v>3.15</v>
+      </c>
+      <c r="BJ5">
+        <v>11</v>
+      </c>
+      <c r="BK5">
+        <v>8</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>9.6</v>
+      </c>
+      <c r="BO5">
+        <v>7</v>
+      </c>
+      <c r="BP5">
+        <v>55</v>
+      </c>
+      <c r="BQ5">
+        <v>38</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>42</v>
+      </c>
+      <c r="BT5">
+        <v>4.4</v>
+      </c>
+      <c r="BU5">
+        <v>3.4</v>
+      </c>
+      <c r="BV5">
+        <v>12</v>
+      </c>
+      <c r="BW5">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG5">
-        <v>8.6</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>2.88</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.01</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.01</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.01</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.01</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.01</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.01</v>
-      </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1905,64 +1914,64 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F6">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>4.9</v>
+        <v>680</v>
       </c>
       <c r="H6">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="I6">
-        <v>1.91</v>
+        <v>680</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K6">
-        <v>6.4</v>
+        <v>680</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="S6">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="T6">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1983,19 +1992,19 @@
         <v>1000</v>
       </c>
       <c r="AD6">
-        <v>34</v>
+        <v>750</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF6">
         <v>1000</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>830</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -2010,130 +2019,130 @@
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN6">
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AQ6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AR6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AS6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AT6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AU6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AV6">
-        <v>1.23</v>
+        <v>2.44</v>
       </c>
       <c r="AW6">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AX6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AY6">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="AZ6">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="BA6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="BB6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="BC6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="BD6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="BE6">
-        <v>1.28</v>
+        <v>50</v>
       </c>
       <c r="BF6">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="BG6">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2147,67 +2156,67 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="H7">
+        <v>1.68</v>
+      </c>
+      <c r="I7">
+        <v>1.91</v>
+      </c>
+      <c r="J7">
+        <v>4.3</v>
+      </c>
+      <c r="K7">
+        <v>6.4</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
         <v>4.1</v>
       </c>
-      <c r="I7">
-        <v>4.6</v>
-      </c>
-      <c r="J7">
-        <v>3.6</v>
-      </c>
-      <c r="K7">
+      <c r="O7">
+        <v>1.05</v>
+      </c>
+      <c r="P7">
         <v>4.1</v>
       </c>
-      <c r="L7">
-        <v>1.38</v>
-      </c>
-      <c r="M7">
-        <v>1.06</v>
-      </c>
-      <c r="N7">
-        <v>3.5</v>
-      </c>
-      <c r="O7">
-        <v>1.3</v>
-      </c>
-      <c r="P7">
-        <v>1.87</v>
-      </c>
       <c r="Q7">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>3.05</v>
+        <v>1.55</v>
       </c>
       <c r="T7">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="X7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
         <v>1000</v>
@@ -2219,22 +2228,22 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE7">
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
         <v>1000</v>
@@ -2255,76 +2264,76 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP7">
-        <v>9.800000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>1.28</v>
       </c>
       <c r="AR7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AS7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>1.28</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>1.28</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>1.23</v>
       </c>
       <c r="AW7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AX7">
-        <v>8.199999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="AY7">
-        <v>7.4</v>
+        <v>1.28</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="BA7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BB7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BC7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BD7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BE7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BF7">
-        <v>9.4</v>
+        <v>1.28</v>
       </c>
       <c r="BG7">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2336,13 +2345,13 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2354,7 +2363,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2375,12 +2384,12 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
         <v>86</v>
@@ -2389,240 +2398,240 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F8">
         <v>1.92</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>4.1</v>
+      </c>
+      <c r="I8">
+        <v>4.9</v>
+      </c>
+      <c r="J8">
+        <v>3.45</v>
+      </c>
+      <c r="K8">
+        <v>3.9</v>
+      </c>
+      <c r="L8">
+        <v>1.38</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
+        <v>3.5</v>
+      </c>
+      <c r="O8">
+        <v>1.3</v>
+      </c>
+      <c r="P8">
+        <v>1.96</v>
+      </c>
+      <c r="Q8">
+        <v>1.85</v>
+      </c>
+      <c r="R8">
+        <v>1.33</v>
+      </c>
+      <c r="S8">
+        <v>3.05</v>
+      </c>
+      <c r="T8">
+        <v>1.7</v>
+      </c>
+      <c r="U8">
         <v>2.02</v>
       </c>
-      <c r="H8">
-        <v>5.1</v>
-      </c>
-      <c r="I8">
-        <v>5.5</v>
-      </c>
-      <c r="J8">
-        <v>3.2</v>
-      </c>
-      <c r="K8">
-        <v>3.35</v>
-      </c>
-      <c r="L8">
+      <c r="V8">
+        <v>1.26</v>
+      </c>
+      <c r="W8">
+        <v>2</v>
+      </c>
+      <c r="X8">
+        <v>50</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>970</v>
+      </c>
+      <c r="AC8">
+        <v>970</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>25</v>
+      </c>
+      <c r="AG8">
+        <v>970</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>34</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ8">
+        <v>10</v>
+      </c>
+      <c r="AR8">
+        <v>1.4</v>
+      </c>
+      <c r="AS8">
+        <v>1.4</v>
+      </c>
+      <c r="AT8">
+        <v>7</v>
+      </c>
+      <c r="AU8">
+        <v>6</v>
+      </c>
+      <c r="AV8">
+        <v>10.5</v>
+      </c>
+      <c r="AW8">
+        <v>1.4</v>
+      </c>
+      <c r="AX8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY8">
+        <v>7.4</v>
+      </c>
+      <c r="AZ8">
+        <v>11</v>
+      </c>
+      <c r="BA8">
+        <v>1.4</v>
+      </c>
+      <c r="BB8">
+        <v>1.4</v>
+      </c>
+      <c r="BC8">
+        <v>1.4</v>
+      </c>
+      <c r="BD8">
+        <v>1.4</v>
+      </c>
+      <c r="BE8">
+        <v>1.4</v>
+      </c>
+      <c r="BF8">
+        <v>9.4</v>
+      </c>
+      <c r="BG8">
+        <v>1.4</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.36</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>2.1</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.1</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
         <v>1.54</v>
       </c>
-      <c r="M8">
-        <v>1.14</v>
-      </c>
-      <c r="N8">
-        <v>2.58</v>
-      </c>
-      <c r="O8">
-        <v>1.58</v>
-      </c>
-      <c r="P8">
-        <v>1.52</v>
-      </c>
-      <c r="Q8">
-        <v>2.78</v>
-      </c>
-      <c r="R8">
-        <v>1.18</v>
-      </c>
-      <c r="S8">
-        <v>6</v>
-      </c>
-      <c r="T8">
-        <v>2.32</v>
-      </c>
-      <c r="U8">
-        <v>1.68</v>
-      </c>
-      <c r="V8">
-        <v>1.22</v>
-      </c>
-      <c r="W8">
-        <v>1.98</v>
-      </c>
-      <c r="X8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y8">
-        <v>13</v>
-      </c>
-      <c r="Z8">
-        <v>44</v>
-      </c>
-      <c r="AA8">
-        <v>210</v>
-      </c>
-      <c r="AB8">
-        <v>6.2</v>
-      </c>
-      <c r="AC8">
-        <v>7.8</v>
-      </c>
-      <c r="AD8">
-        <v>23</v>
-      </c>
-      <c r="AE8">
-        <v>140</v>
-      </c>
-      <c r="AF8">
-        <v>10.5</v>
-      </c>
-      <c r="AG8">
-        <v>11.5</v>
-      </c>
-      <c r="AH8">
-        <v>29</v>
-      </c>
-      <c r="AI8">
-        <v>160</v>
-      </c>
-      <c r="AJ8">
-        <v>25</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
-      <c r="AL8">
-        <v>80</v>
-      </c>
-      <c r="AM8">
-        <v>310</v>
-      </c>
-      <c r="AN8">
-        <v>26</v>
-      </c>
-      <c r="AO8">
-        <v>240</v>
-      </c>
-      <c r="AP8">
-        <v>7.4</v>
-      </c>
-      <c r="AQ8">
-        <v>11</v>
-      </c>
-      <c r="AR8">
-        <v>10</v>
-      </c>
-      <c r="AS8">
-        <v>12.5</v>
-      </c>
-      <c r="AT8">
-        <v>5.6</v>
-      </c>
-      <c r="AU8">
-        <v>7</v>
-      </c>
-      <c r="AV8">
-        <v>20</v>
-      </c>
-      <c r="AW8">
-        <v>12</v>
-      </c>
-      <c r="AX8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY8">
-        <v>10</v>
-      </c>
-      <c r="AZ8">
-        <v>9</v>
-      </c>
-      <c r="BA8">
-        <v>12</v>
-      </c>
-      <c r="BB8">
-        <v>21</v>
-      </c>
-      <c r="BC8">
-        <v>9</v>
-      </c>
-      <c r="BD8">
-        <v>11</v>
-      </c>
-      <c r="BE8">
-        <v>12.5</v>
-      </c>
-      <c r="BF8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG8">
-        <v>12.5</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.37</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>2.7</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.08</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.75</v>
-      </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>86</v>
@@ -2631,235 +2640,477 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F9">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="G9">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I9">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="L9">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O9">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Q9">
-        <v>1.92</v>
+        <v>2.78</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V9">
         <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="CB9" t="s">
-        <v>111</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10">
+        <v>1.88</v>
+      </c>
+      <c r="G10">
+        <v>2.04</v>
+      </c>
+      <c r="H10">
+        <v>4.3</v>
+      </c>
+      <c r="I10">
+        <v>5.4</v>
+      </c>
+      <c r="J10">
+        <v>3.45</v>
+      </c>
+      <c r="K10">
+        <v>3.85</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>3.1</v>
+      </c>
+      <c r="O10">
+        <v>1.36</v>
+      </c>
+      <c r="P10">
+        <v>1.78</v>
+      </c>
+      <c r="Q10">
+        <v>1.94</v>
+      </c>
+      <c r="R10">
+        <v>1.29</v>
+      </c>
+      <c r="S10">
+        <v>3.25</v>
+      </c>
+      <c r="T10">
+        <v>1.84</v>
+      </c>
+      <c r="U10">
+        <v>1.88</v>
+      </c>
+      <c r="V10">
+        <v>1.22</v>
+      </c>
+      <c r="W10">
+        <v>1.96</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>970</v>
+      </c>
+      <c r="AC10">
+        <v>970</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>25</v>
+      </c>
+      <c r="AG10">
+        <v>24</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.32</v>
+      </c>
+      <c r="AQ10">
+        <v>1.32</v>
+      </c>
+      <c r="AR10">
+        <v>1.32</v>
+      </c>
+      <c r="AS10">
+        <v>1.32</v>
+      </c>
+      <c r="AT10">
+        <v>1.19</v>
+      </c>
+      <c r="AU10">
+        <v>1.19</v>
+      </c>
+      <c r="AV10">
+        <v>1.32</v>
+      </c>
+      <c r="AW10">
+        <v>1.32</v>
+      </c>
+      <c r="AX10">
+        <v>1.25</v>
+      </c>
+      <c r="AY10">
+        <v>1.25</v>
+      </c>
+      <c r="AZ10">
+        <v>1.32</v>
+      </c>
+      <c r="BA10">
+        <v>1.32</v>
+      </c>
+      <c r="BB10">
+        <v>1.32</v>
+      </c>
+      <c r="BC10">
+        <v>1.32</v>
+      </c>
+      <c r="BD10">
+        <v>1.32</v>
+      </c>
+      <c r="BE10">
+        <v>1.32</v>
+      </c>
+      <c r="BF10">
+        <v>1.32</v>
+      </c>
+      <c r="BG10">
+        <v>1.32</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="124">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
     <t>2026-10-05</t>
   </si>
   <si>
@@ -289,7 +292,7 @@
     <t>02:00:00</t>
   </si>
   <si>
-    <t>13:00:00</t>
+    <t>14:00:00</t>
   </si>
   <si>
     <t>17:00:00</t>
@@ -304,6 +307,12 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Costa Rica</t>
   </si>
   <si>
@@ -331,6 +340,15 @@
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Nacional (Uru)</t>
+  </si>
+  <si>
     <t>Haiti</t>
   </si>
   <si>
@@ -358,7 +376,16 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
-    <t>2026-10-03 23:29:48</t>
+    <t>CA Platense</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>2026-10-04 01:41:40</t>
   </si>
 </sst>
 </file>
@@ -690,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,76 +967,76 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S2">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z2">
         <v>26</v>
@@ -1021,7 +1048,7 @@
         <v>12</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -1030,7 +1057,7 @@
         <v>36</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1039,7 +1066,7 @@
         <v>16.5</v>
       </c>
       <c r="AI2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
         <v>34</v>
@@ -1048,88 +1075,88 @@
         <v>25</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AM2">
         <v>80</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX2">
         <v>14</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
         <v>14.5</v>
       </c>
       <c r="BA2">
+        <v>9.6</v>
+      </c>
+      <c r="BB2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC2">
+        <v>18.5</v>
+      </c>
+      <c r="BD2">
+        <v>9.4</v>
+      </c>
+      <c r="BE2">
+        <v>10.5</v>
+      </c>
+      <c r="BF2">
+        <v>12</v>
+      </c>
+      <c r="BG2">
+        <v>9.6</v>
+      </c>
+      <c r="BH2">
+        <v>3.85</v>
+      </c>
+      <c r="BI2">
+        <v>3.05</v>
+      </c>
+      <c r="BJ2">
         <v>9</v>
       </c>
-      <c r="BB2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC2">
-        <v>19.5</v>
-      </c>
-      <c r="BD2">
-        <v>8.6</v>
-      </c>
-      <c r="BE2">
-        <v>30</v>
-      </c>
-      <c r="BF2">
-        <v>11</v>
-      </c>
-      <c r="BG2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH2">
-        <v>3.75</v>
-      </c>
-      <c r="BI2">
-        <v>2.94</v>
-      </c>
-      <c r="BJ2">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1138,16 +1165,16 @@
         <v>4</v>
       </c>
       <c r="BP2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1156,25 +1183,25 @@
         <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,70 +1209,70 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P3">
         <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="R3">
         <v>1.17</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="W3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X3">
         <v>7.8</v>
@@ -1254,31 +1281,31 @@
         <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
         <v>34</v>
       </c>
       <c r="AF3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>1000</v>
@@ -1293,28 +1320,28 @@
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS3">
         <v>20</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1323,16 +1350,16 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AY3">
+        <v>19</v>
+      </c>
+      <c r="AZ3">
         <v>20</v>
-      </c>
-      <c r="AZ3">
-        <v>26</v>
       </c>
       <c r="BA3">
         <v>48</v>
@@ -1344,58 +1371,58 @@
         <v>36</v>
       </c>
       <c r="BD3">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BI3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BN3">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="BO3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU3">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1407,16 +1434,16 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1424,70 +1451,70 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F4">
         <v>3.65</v>
       </c>
       <c r="G4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I4">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J4">
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X4">
         <v>14</v>
@@ -1601,64 +1628,64 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1666,28 +1693,28 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F5">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I5">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1696,58 +1723,58 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
@@ -1756,43 +1783,43 @@
         <v>18.5</v>
       </c>
       <c r="AF5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AG5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ5">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AK5">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AL5">
         <v>100</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>840</v>
       </c>
       <c r="AN5">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AO5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5">
         <v>14.5</v>
@@ -1801,106 +1828,106 @@
         <v>16</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW5">
         <v>15.5</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AY5">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BB5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BD5">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BE5">
+        <v>38</v>
+      </c>
+      <c r="BF5">
         <v>10.5</v>
       </c>
-      <c r="BF5">
-        <v>10</v>
-      </c>
       <c r="BG5">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
         <v>3.15</v>
       </c>
       <c r="BJ5">
+        <v>10.5</v>
+      </c>
+      <c r="BK5">
+        <v>5.6</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>11</v>
       </c>
-      <c r="BK5">
-        <v>8</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
       <c r="BN5">
+        <v>9</v>
+      </c>
+      <c r="BO5">
+        <v>5.2</v>
+      </c>
+      <c r="BP5">
+        <v>44</v>
+      </c>
+      <c r="BQ5">
         <v>9.6</v>
       </c>
-      <c r="BO5">
-        <v>7</v>
-      </c>
-      <c r="BP5">
-        <v>55</v>
-      </c>
-      <c r="BQ5">
-        <v>38</v>
-      </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
         <v>4.4</v>
       </c>
       <c r="BU5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BV5">
         <v>12</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BX5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BY5">
+        <v>8.4</v>
+      </c>
+      <c r="BZ5">
         <v>20</v>
       </c>
-      <c r="BZ5">
-        <v>23</v>
-      </c>
       <c r="CA5">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1908,16 +1935,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F6">
         <v>1.04</v>
@@ -2142,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2150,28 +2177,28 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F7">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>1.68</v>
       </c>
       <c r="I7">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="J7">
         <v>4.3</v>
@@ -2186,13 +2213,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
         <v>1.05</v>
       </c>
       <c r="P7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q7">
         <v>1.2</v>
@@ -2201,19 +2228,19 @@
         <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="U7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2285,7 +2312,7 @@
         <v>1.28</v>
       </c>
       <c r="AU7">
-        <v>1.28</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
         <v>1.23</v>
@@ -2300,10 +2327,10 @@
         <v>1.28</v>
       </c>
       <c r="AZ7">
-        <v>1.28</v>
+        <v>8</v>
       </c>
       <c r="BA7">
-        <v>1.28</v>
+        <v>9.6</v>
       </c>
       <c r="BB7">
         <v>1.28</v>
@@ -2318,7 +2345,7 @@
         <v>1.28</v>
       </c>
       <c r="BF7">
-        <v>1.28</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
         <v>1.03</v>
@@ -2384,7 +2411,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2392,22 +2419,22 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F8">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H8">
         <v>4.1</v>
@@ -2425,7 +2452,7 @@
         <v>1.38</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
         <v>3.5</v>
@@ -2434,7 +2461,7 @@
         <v>1.3</v>
       </c>
       <c r="P8">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
         <v>1.85</v>
@@ -2446,19 +2473,19 @@
         <v>3.05</v>
       </c>
       <c r="T8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V8">
         <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="X8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y8">
         <v>1000</v>
@@ -2506,22 +2533,22 @@
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
+        <v>9.4</v>
+      </c>
+      <c r="AQ8">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ8">
-        <v>10</v>
-      </c>
       <c r="AR8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AS8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AT8">
         <v>7</v>
@@ -2533,37 +2560,37 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AX8">
         <v>8.199999999999999</v>
       </c>
       <c r="AY8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BB8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BC8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BD8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BE8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF8">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2575,7 +2602,7 @@
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2626,7 +2653,7 @@
         <v>1.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2634,16 +2661,16 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F9">
         <v>1.92</v>
@@ -2658,28 +2685,28 @@
         <v>5.5</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P9">
         <v>1.52</v>
       </c>
       <c r="Q9">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2700,28 +2727,28 @@
         <v>1.98</v>
       </c>
       <c r="X9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA9">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB9">
         <v>6.2</v>
       </c>
       <c r="AC9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9">
         <v>23</v>
       </c>
       <c r="AE9">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF9">
         <v>10.5</v>
@@ -2730,7 +2757,7 @@
         <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AI9">
         <v>160</v>
@@ -2748,7 +2775,7 @@
         <v>310</v>
       </c>
       <c r="AN9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AO9">
         <v>240</v>
@@ -2760,22 +2787,22 @@
         <v>11</v>
       </c>
       <c r="AR9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS9">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT9">
         <v>5.6</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX9">
         <v>9.199999999999999</v>
@@ -2784,40 +2811,40 @@
         <v>10</v>
       </c>
       <c r="AZ9">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BA9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB9">
         <v>21</v>
       </c>
       <c r="BC9">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD9">
+        <v>10</v>
+      </c>
+      <c r="BE9">
         <v>11</v>
       </c>
-      <c r="BE9">
-        <v>12.5</v>
-      </c>
       <c r="BF9">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2835,7 +2862,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -2847,7 +2874,7 @@
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -2868,7 +2895,7 @@
         <v>1.08</v>
       </c>
       <c r="CB9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2876,28 +2903,28 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F10">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H10">
         <v>4.3</v>
       </c>
       <c r="I10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J10">
         <v>3.45</v>
@@ -2912,31 +2939,31 @@
         <v>1.06</v>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
         <v>1.36</v>
       </c>
       <c r="P10">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q10">
         <v>1.94</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T10">
         <v>1.84</v>
       </c>
       <c r="U10">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V10">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W10">
         <v>1.96</v>
@@ -2966,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
         <v>24</v>
@@ -2996,58 +3023,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10">
-        <v>1.32</v>
+        <v>8.4</v>
       </c>
       <c r="AR10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AS10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AT10">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AU10">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AV10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AW10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AX10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AY10">
-        <v>1.25</v>
+        <v>6.8</v>
       </c>
       <c r="AZ10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BA10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BB10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BC10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BD10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BE10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BF10">
-        <v>1.32</v>
+        <v>8</v>
       </c>
       <c r="BG10">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3110,7 +3137,733 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>114</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11">
+        <v>1.92</v>
+      </c>
+      <c r="G11">
+        <v>2.1</v>
+      </c>
+      <c r="H11">
+        <v>4.9</v>
+      </c>
+      <c r="I11">
+        <v>5.8</v>
+      </c>
+      <c r="J11">
+        <v>3.15</v>
+      </c>
+      <c r="K11">
+        <v>3.4</v>
+      </c>
+      <c r="L11">
+        <v>1.64</v>
+      </c>
+      <c r="M11">
+        <v>1.12</v>
+      </c>
+      <c r="N11">
+        <v>2.24</v>
+      </c>
+      <c r="O11">
+        <v>1.67</v>
+      </c>
+      <c r="P11">
+        <v>1.45</v>
+      </c>
+      <c r="Q11">
+        <v>3.05</v>
+      </c>
+      <c r="R11">
+        <v>1.15</v>
+      </c>
+      <c r="S11">
+        <v>6.8</v>
+      </c>
+      <c r="T11">
+        <v>2.46</v>
+      </c>
+      <c r="U11">
+        <v>1.49</v>
+      </c>
+      <c r="V11">
+        <v>1.21</v>
+      </c>
+      <c r="W11">
+        <v>1.93</v>
+      </c>
+      <c r="X11">
+        <v>9.6</v>
+      </c>
+      <c r="Y11">
+        <v>14</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>5.9</v>
+      </c>
+      <c r="AC11">
+        <v>970</v>
+      </c>
+      <c r="AD11">
+        <v>28</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>12.5</v>
+      </c>
+      <c r="AG11">
+        <v>14</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>28</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>5.4</v>
+      </c>
+      <c r="AQ11">
+        <v>9.6</v>
+      </c>
+      <c r="AR11">
+        <v>2.92</v>
+      </c>
+      <c r="AS11">
+        <v>2.92</v>
+      </c>
+      <c r="AT11">
+        <v>4.6</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>18</v>
+      </c>
+      <c r="AW11">
+        <v>2.92</v>
+      </c>
+      <c r="AX11">
+        <v>8.4</v>
+      </c>
+      <c r="AY11">
+        <v>11</v>
+      </c>
+      <c r="AZ11">
+        <v>2.92</v>
+      </c>
+      <c r="BA11">
+        <v>2.92</v>
+      </c>
+      <c r="BB11">
+        <v>18.5</v>
+      </c>
+      <c r="BC11">
+        <v>2.92</v>
+      </c>
+      <c r="BD11">
+        <v>2.92</v>
+      </c>
+      <c r="BE11">
+        <v>2.92</v>
+      </c>
+      <c r="BF11">
+        <v>2.92</v>
+      </c>
+      <c r="BG11">
+        <v>2.92</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>2.12</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>2.86</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.31</v>
+      </c>
+      <c r="BN11">
+        <v>5.9</v>
+      </c>
+      <c r="BO11">
+        <v>3.3</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>2.86</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.31</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>2.42</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.31</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.31</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.31</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12">
+        <v>1.72</v>
+      </c>
+      <c r="G12">
+        <v>1.81</v>
+      </c>
+      <c r="H12">
+        <v>5.6</v>
+      </c>
+      <c r="I12">
+        <v>6.2</v>
+      </c>
+      <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
+        <v>4.3</v>
+      </c>
+      <c r="L12">
+        <v>1.43</v>
+      </c>
+      <c r="M12">
+        <v>1.06</v>
+      </c>
+      <c r="N12">
+        <v>3.05</v>
+      </c>
+      <c r="O12">
+        <v>1.42</v>
+      </c>
+      <c r="P12">
+        <v>1.71</v>
+      </c>
+      <c r="Q12">
+        <v>2.2</v>
+      </c>
+      <c r="R12">
+        <v>1.26</v>
+      </c>
+      <c r="S12">
+        <v>4.2</v>
+      </c>
+      <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>1.76</v>
+      </c>
+      <c r="V12">
+        <v>1.19</v>
+      </c>
+      <c r="W12">
+        <v>2.22</v>
+      </c>
+      <c r="X12">
+        <v>11.5</v>
+      </c>
+      <c r="Y12">
+        <v>16.5</v>
+      </c>
+      <c r="Z12">
+        <v>50</v>
+      </c>
+      <c r="AA12">
+        <v>220</v>
+      </c>
+      <c r="AB12">
+        <v>7</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>25</v>
+      </c>
+      <c r="AE12">
+        <v>130</v>
+      </c>
+      <c r="AF12">
+        <v>10</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>29</v>
+      </c>
+      <c r="AI12">
+        <v>130</v>
+      </c>
+      <c r="AJ12">
+        <v>19</v>
+      </c>
+      <c r="AK12">
+        <v>23</v>
+      </c>
+      <c r="AL12">
+        <v>60</v>
+      </c>
+      <c r="AM12">
+        <v>210</v>
+      </c>
+      <c r="AN12">
+        <v>15.5</v>
+      </c>
+      <c r="AO12">
+        <v>190</v>
+      </c>
+      <c r="AP12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ12">
+        <v>14</v>
+      </c>
+      <c r="AR12">
+        <v>30</v>
+      </c>
+      <c r="AS12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT12">
+        <v>6</v>
+      </c>
+      <c r="AU12">
+        <v>7.6</v>
+      </c>
+      <c r="AV12">
+        <v>20</v>
+      </c>
+      <c r="AW12">
+        <v>9.4</v>
+      </c>
+      <c r="AX12">
+        <v>8.4</v>
+      </c>
+      <c r="AY12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12">
+        <v>20</v>
+      </c>
+      <c r="BA12">
+        <v>9.4</v>
+      </c>
+      <c r="BB12">
+        <v>15.5</v>
+      </c>
+      <c r="BC12">
+        <v>18</v>
+      </c>
+      <c r="BD12">
+        <v>38</v>
+      </c>
+      <c r="BE12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF12">
+        <v>13</v>
+      </c>
+      <c r="BG12">
+        <v>9.6</v>
+      </c>
+      <c r="BH12">
+        <v>3.35</v>
+      </c>
+      <c r="BI12">
+        <v>2.64</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>2.06</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2.06</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>2.92</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>2.06</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>2.06</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>2.06</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>2.06</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>2.06</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>2.06</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13">
+        <v>2.08</v>
+      </c>
+      <c r="G13">
+        <v>2.34</v>
+      </c>
+      <c r="H13">
+        <v>3.3</v>
+      </c>
+      <c r="I13">
+        <v>3.95</v>
+      </c>
+      <c r="J13">
+        <v>3.65</v>
+      </c>
+      <c r="K13">
+        <v>3.9</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.04</v>
+      </c>
+      <c r="N13">
+        <v>3.55</v>
+      </c>
+      <c r="O13">
+        <v>1.3</v>
+      </c>
+      <c r="P13">
+        <v>1.92</v>
+      </c>
+      <c r="Q13">
+        <v>1.87</v>
+      </c>
+      <c r="R13">
+        <v>1.34</v>
+      </c>
+      <c r="S13">
+        <v>3.1</v>
+      </c>
+      <c r="T13">
+        <v>1.69</v>
+      </c>
+      <c r="U13">
+        <v>2.04</v>
+      </c>
+      <c r="V13">
+        <v>1.34</v>
+      </c>
+      <c r="W13">
+        <v>1.75</v>
+      </c>
+      <c r="X13">
+        <v>16.5</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>90</v>
+      </c>
+      <c r="AB13">
+        <v>970</v>
+      </c>
+      <c r="AC13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13">
+        <v>16.5</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>22</v>
+      </c>
+      <c r="AH13">
+        <v>19</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>17.5</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.64</v>
+      </c>
+      <c r="AQ13">
+        <v>1.82</v>
+      </c>
+      <c r="AR13">
+        <v>18</v>
+      </c>
+      <c r="AS13">
+        <v>1.79</v>
+      </c>
+      <c r="AT13">
+        <v>1.66</v>
+      </c>
+      <c r="AU13">
+        <v>1.52</v>
+      </c>
+      <c r="AV13">
+        <v>1.64</v>
+      </c>
+      <c r="AW13">
+        <v>1.82</v>
+      </c>
+      <c r="AX13">
+        <v>1.82</v>
+      </c>
+      <c r="AY13">
+        <v>7.8</v>
+      </c>
+      <c r="AZ13">
+        <v>1.66</v>
+      </c>
+      <c r="BA13">
+        <v>1.82</v>
+      </c>
+      <c r="BB13">
+        <v>19</v>
+      </c>
+      <c r="BC13">
+        <v>1.82</v>
+      </c>
+      <c r="BD13">
+        <v>1.82</v>
+      </c>
+      <c r="BE13">
+        <v>1.82</v>
+      </c>
+      <c r="BF13">
+        <v>1.65</v>
+      </c>
+      <c r="BG13">
+        <v>1.82</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>2.8</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
   <si>
     <t>League</t>
   </si>
@@ -268,12 +268,21 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Serbian First League</t>
+  </si>
+  <si>
+    <t>Turkish 2 Lig</t>
+  </si>
+  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
     <t>Spanish Segunda Division</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
@@ -295,12 +304,18 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
     <t>18:30:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>19:45:00</t>
   </si>
   <si>
@@ -328,12 +343,21 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
+    <t>FK Backa Topola</t>
+  </si>
+  <si>
+    <t>Sanliurfaspor</t>
+  </si>
+  <si>
     <t>Moss</t>
   </si>
   <si>
     <t>Cordoba</t>
   </si>
   <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -346,6 +370,9 @@
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Martinique</t>
+  </si>
+  <si>
     <t>Nacional (Uru)</t>
   </si>
   <si>
@@ -364,12 +391,21 @@
     <t>Libertad</t>
   </si>
   <si>
+    <t>FK Graficar</t>
+  </si>
+  <si>
+    <t>Belediye Derincespor</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
     <t>Tenerife</t>
   </si>
   <si>
+    <t>St Lucia</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
@@ -382,10 +418,13 @@
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 01:41:40</t>
+    <t>2026-10-04 03:53:43</t>
   </si>
 </sst>
 </file>
@@ -717,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -967,34 +1006,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
+        <v>3.05</v>
+      </c>
+      <c r="I2">
         <v>3.2</v>
-      </c>
-      <c r="I2">
-        <v>3.45</v>
       </c>
       <c r="J2">
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1006,97 +1045,97 @@
         <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
         <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>16.5</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
         <v>34</v>
       </c>
       <c r="AK2">
+        <v>28</v>
+      </c>
+      <c r="AL2">
+        <v>34</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
+        <v>18</v>
+      </c>
+      <c r="AO2">
         <v>25</v>
       </c>
-      <c r="AL2">
-        <v>32</v>
-      </c>
-      <c r="AM2">
-        <v>80</v>
-      </c>
-      <c r="AN2">
-        <v>14</v>
-      </c>
-      <c r="AO2">
-        <v>34</v>
-      </c>
       <c r="AP2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ2">
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1108,7 +1147,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1120,73 +1159,73 @@
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="BH2">
         <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2">
         <v>9</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR2">
         <v>26</v>
       </c>
       <c r="BS2">
+        <v>10</v>
+      </c>
+      <c r="BT2">
+        <v>6.6</v>
+      </c>
+      <c r="BU2">
+        <v>5</v>
+      </c>
+      <c r="BV2">
+        <v>24</v>
+      </c>
+      <c r="BW2">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BT2">
-        <v>6.8</v>
-      </c>
-      <c r="BU2">
-        <v>5.1</v>
-      </c>
-      <c r="BV2">
-        <v>25</v>
-      </c>
-      <c r="BW2">
-        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1198,10 +1237,10 @@
         <v>21</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1209,28 +1248,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F3">
         <v>4.6</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1239,13 +1278,13 @@
         <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
         <v>1.63</v>
@@ -1254,7 +1293,7 @@
         <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
         <v>1.17</v>
@@ -1266,13 +1305,13 @@
         <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X3">
         <v>7.8</v>
@@ -1281,31 +1320,31 @@
         <v>6.4</v>
       </c>
       <c r="Z3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
         <v>34</v>
       </c>
       <c r="AF3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI3">
         <v>1000</v>
@@ -1314,31 +1353,31 @@
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL3">
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1347,25 +1386,25 @@
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
         <v>20</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC3">
         <v>36</v>
@@ -1383,67 +1422,67 @@
         <v>19</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="BI3">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>520</v>
+        <v>8</v>
       </c>
       <c r="BO3">
-        <v>2.28</v>
+        <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ3">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS3">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="BT3">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW3">
         <v>8.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA3">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1451,16 +1490,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F4">
         <v>3.65</v>
@@ -1625,67 +1664,67 @@
         <v>19.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1693,76 +1732,76 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H5">
         <v>1.72</v>
       </c>
       <c r="I5">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
+        <v>2.16</v>
+      </c>
+      <c r="Q5">
+        <v>1.8</v>
+      </c>
+      <c r="R5">
+        <v>1.45</v>
+      </c>
+      <c r="S5">
+        <v>3.1</v>
+      </c>
+      <c r="T5">
+        <v>1.78</v>
+      </c>
+      <c r="U5">
         <v>2.1</v>
       </c>
-      <c r="Q5">
-        <v>1.84</v>
-      </c>
-      <c r="R5">
-        <v>1.43</v>
-      </c>
-      <c r="S5">
-        <v>3.2</v>
-      </c>
-      <c r="T5">
-        <v>1.81</v>
-      </c>
-      <c r="U5">
-        <v>2.08</v>
-      </c>
       <c r="V5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W5">
         <v>1.23</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
         <v>11.5</v>
@@ -1771,7 +1810,7 @@
         <v>18</v>
       </c>
       <c r="AB5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1780,7 +1819,7 @@
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF5">
         <v>42</v>
@@ -1789,10 +1828,10 @@
         <v>20</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ5">
         <v>140</v>
@@ -1804,10 +1843,10 @@
         <v>100</v>
       </c>
       <c r="AM5">
-        <v>840</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO5">
         <v>10</v>
@@ -1846,22 +1885,22 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5">
         <v>8.4</v>
@@ -1876,7 +1915,7 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1894,13 +1933,13 @@
         <v>44</v>
       </c>
       <c r="BQ5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>4.4</v>
@@ -1921,13 +1960,13 @@
         <v>8.4</v>
       </c>
       <c r="BZ5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA5">
         <v>7.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1935,16 +1974,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F6">
         <v>1.04</v>
@@ -2169,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2177,34 +2216,34 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.68</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
-        <v>1.94</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2213,34 +2252,34 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="O7">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="P7">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="Q7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>1.08</v>
       </c>
       <c r="S7">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2261,7 +2300,7 @@
         <v>1000</v>
       </c>
       <c r="AD7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2294,61 +2333,61 @@
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2411,7 +2450,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2419,73 +2458,73 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>1.88</v>
+        <v>1.1</v>
       </c>
       <c r="G8">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
         <v>1000</v>
@@ -2497,10 +2536,10 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
         <v>1000</v>
@@ -2509,10 +2548,10 @@
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
         <v>1000</v>
@@ -2533,482 +2572,482 @@
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="G9">
-        <v>2.02</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>5.1</v>
+        <v>1.68</v>
       </c>
       <c r="I9">
-        <v>5.5</v>
+        <v>1.94</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.52</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="P9">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.74</v>
+        <v>1.2</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>6</v>
+        <v>1.54</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="U9">
-        <v>1.68</v>
+        <v>3.35</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
       <c r="W9">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>34</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>48</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>970</v>
+      </c>
+      <c r="AP9">
+        <v>1.32</v>
+      </c>
+      <c r="AQ9">
+        <v>1.32</v>
+      </c>
+      <c r="AR9">
+        <v>1.32</v>
+      </c>
+      <c r="AS9">
+        <v>1.32</v>
+      </c>
+      <c r="AT9">
+        <v>1.32</v>
+      </c>
+      <c r="AU9">
         <v>8.4</v>
       </c>
-      <c r="Y9">
-        <v>12.5</v>
-      </c>
-      <c r="Z9">
-        <v>48</v>
-      </c>
-      <c r="AA9">
-        <v>200</v>
-      </c>
-      <c r="AB9">
-        <v>6.2</v>
-      </c>
-      <c r="AC9">
-        <v>7.6</v>
-      </c>
-      <c r="AD9">
-        <v>23</v>
-      </c>
-      <c r="AE9">
-        <v>130</v>
-      </c>
-      <c r="AF9">
-        <v>10.5</v>
-      </c>
-      <c r="AG9">
-        <v>11.5</v>
-      </c>
-      <c r="AH9">
-        <v>36</v>
-      </c>
-      <c r="AI9">
-        <v>160</v>
-      </c>
-      <c r="AJ9">
-        <v>25</v>
-      </c>
-      <c r="AK9">
-        <v>29</v>
-      </c>
-      <c r="AL9">
-        <v>80</v>
-      </c>
-      <c r="AM9">
-        <v>310</v>
-      </c>
-      <c r="AN9">
-        <v>32</v>
-      </c>
-      <c r="AO9">
-        <v>240</v>
-      </c>
-      <c r="AP9">
-        <v>7.4</v>
-      </c>
-      <c r="AQ9">
-        <v>11</v>
-      </c>
-      <c r="AR9">
-        <v>9.4</v>
-      </c>
-      <c r="AS9">
-        <v>11</v>
-      </c>
-      <c r="AT9">
-        <v>5.6</v>
-      </c>
-      <c r="AU9">
-        <v>6.8</v>
-      </c>
       <c r="AV9">
-        <v>20</v>
+        <v>1.27</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>1.32</v>
       </c>
       <c r="AX9">
-        <v>9.199999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>1.32</v>
       </c>
       <c r="AZ9">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BA9">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BB9">
-        <v>21</v>
+        <v>1.32</v>
       </c>
       <c r="BC9">
-        <v>8.199999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="BD9">
-        <v>10</v>
+        <v>1.32</v>
       </c>
       <c r="BE9">
-        <v>11</v>
+        <v>1.32</v>
       </c>
       <c r="BF9">
         <v>8.4</v>
       </c>
       <c r="BG9">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G10">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J10">
         <v>3.45</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P10">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W10">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC10">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG10">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL10">
         <v>1000</v>
@@ -3017,369 +3056,369 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.22</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
+        <v>11.5</v>
+      </c>
+      <c r="AR10">
+        <v>6.2</v>
+      </c>
+      <c r="AS10">
+        <v>1.98</v>
+      </c>
+      <c r="AT10">
+        <v>7.8</v>
+      </c>
+      <c r="AU10">
+        <v>6.4</v>
+      </c>
+      <c r="AV10">
+        <v>11.5</v>
+      </c>
+      <c r="AW10">
+        <v>14.5</v>
+      </c>
+      <c r="AX10">
+        <v>9.4</v>
+      </c>
+      <c r="AY10">
         <v>8.4</v>
       </c>
-      <c r="AR10">
-        <v>1.22</v>
-      </c>
-      <c r="AS10">
-        <v>1.22</v>
-      </c>
-      <c r="AT10">
-        <v>1.13</v>
-      </c>
-      <c r="AU10">
-        <v>1.12</v>
-      </c>
-      <c r="AV10">
-        <v>1.22</v>
-      </c>
-      <c r="AW10">
-        <v>1.22</v>
-      </c>
-      <c r="AX10">
-        <v>1.22</v>
-      </c>
-      <c r="AY10">
-        <v>6.8</v>
-      </c>
       <c r="AZ10">
-        <v>1.22</v>
+        <v>14</v>
       </c>
       <c r="BA10">
-        <v>1.22</v>
+        <v>16</v>
       </c>
       <c r="BB10">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="BC10">
-        <v>1.22</v>
+        <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>1.22</v>
+        <v>13</v>
       </c>
       <c r="BE10">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="BF10">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG10">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="CB10" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>1.92</v>
+        <v>5.3</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="H11">
-        <v>4.9</v>
+        <v>1.59</v>
       </c>
       <c r="I11">
-        <v>5.8</v>
+        <v>1.66</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="K11">
+        <v>5.2</v>
+      </c>
+      <c r="L11">
+        <v>1.27</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>1.01</v>
+      </c>
+      <c r="O11">
+        <v>1.21</v>
+      </c>
+      <c r="P11">
+        <v>2.22</v>
+      </c>
+      <c r="Q11">
+        <v>1.53</v>
+      </c>
+      <c r="R11">
+        <v>1.51</v>
+      </c>
+      <c r="S11">
+        <v>2.34</v>
+      </c>
+      <c r="T11">
+        <v>1.74</v>
+      </c>
+      <c r="U11">
+        <v>2.14</v>
+      </c>
+      <c r="V11">
+        <v>2.5</v>
+      </c>
+      <c r="W11">
+        <v>1.19</v>
+      </c>
+      <c r="X11">
+        <v>28</v>
+      </c>
+      <c r="Y11">
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <v>11.5</v>
+      </c>
+      <c r="AA11">
+        <v>19</v>
+      </c>
+      <c r="AB11">
+        <v>25</v>
+      </c>
+      <c r="AC11">
+        <v>11.5</v>
+      </c>
+      <c r="AD11">
+        <v>12.5</v>
+      </c>
+      <c r="AE11">
+        <v>16.5</v>
+      </c>
+      <c r="AF11">
+        <v>60</v>
+      </c>
+      <c r="AG11">
+        <v>24</v>
+      </c>
+      <c r="AH11">
+        <v>25</v>
+      </c>
+      <c r="AI11">
+        <v>36</v>
+      </c>
+      <c r="AJ11">
+        <v>170</v>
+      </c>
+      <c r="AK11">
+        <v>85</v>
+      </c>
+      <c r="AL11">
+        <v>80</v>
+      </c>
+      <c r="AM11">
+        <v>110</v>
+      </c>
+      <c r="AN11">
+        <v>85</v>
+      </c>
+      <c r="AO11">
+        <v>8.6</v>
+      </c>
+      <c r="AP11">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11">
+        <v>1.03</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.03</v>
+      </c>
+      <c r="AT11">
+        <v>1.03</v>
+      </c>
+      <c r="AU11">
+        <v>1.03</v>
+      </c>
+      <c r="AV11">
+        <v>1.03</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
+        <v>1.03</v>
+      </c>
+      <c r="AY11">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11">
+        <v>1.03</v>
+      </c>
+      <c r="BA11">
+        <v>1.03</v>
+      </c>
+      <c r="BB11">
+        <v>1.03</v>
+      </c>
+      <c r="BC11">
+        <v>1.03</v>
+      </c>
+      <c r="BD11">
+        <v>1.03</v>
+      </c>
+      <c r="BE11">
+        <v>1.03</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>5.5</v>
+      </c>
+      <c r="BH11">
+        <v>4.3</v>
+      </c>
+      <c r="BI11">
+        <v>3.25</v>
+      </c>
+      <c r="BJ11">
+        <v>10.5</v>
+      </c>
+      <c r="BK11">
+        <v>7.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>10</v>
+      </c>
+      <c r="BO11">
+        <v>7</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>4.6</v>
+      </c>
+      <c r="BU11">
         <v>3.4</v>
       </c>
-      <c r="L11">
-        <v>1.64</v>
-      </c>
-      <c r="M11">
-        <v>1.12</v>
-      </c>
-      <c r="N11">
-        <v>2.24</v>
-      </c>
-      <c r="O11">
-        <v>1.67</v>
-      </c>
-      <c r="P11">
-        <v>1.45</v>
-      </c>
-      <c r="Q11">
-        <v>3.05</v>
-      </c>
-      <c r="R11">
-        <v>1.15</v>
-      </c>
-      <c r="S11">
-        <v>6.8</v>
-      </c>
-      <c r="T11">
-        <v>2.46</v>
-      </c>
-      <c r="U11">
-        <v>1.49</v>
-      </c>
-      <c r="V11">
-        <v>1.21</v>
-      </c>
-      <c r="W11">
-        <v>1.93</v>
-      </c>
-      <c r="X11">
-        <v>9.6</v>
-      </c>
-      <c r="Y11">
-        <v>14</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>5.9</v>
-      </c>
-      <c r="AC11">
-        <v>970</v>
-      </c>
-      <c r="AD11">
-        <v>28</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>12.5</v>
-      </c>
-      <c r="AG11">
-        <v>14</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>28</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>1000</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>5.4</v>
-      </c>
-      <c r="AQ11">
-        <v>9.6</v>
-      </c>
-      <c r="AR11">
-        <v>2.92</v>
-      </c>
-      <c r="AS11">
-        <v>2.92</v>
-      </c>
-      <c r="AT11">
-        <v>4.6</v>
-      </c>
-      <c r="AU11">
-        <v>7</v>
-      </c>
-      <c r="AV11">
-        <v>18</v>
-      </c>
-      <c r="AW11">
-        <v>2.92</v>
-      </c>
-      <c r="AX11">
-        <v>8.4</v>
-      </c>
-      <c r="AY11">
-        <v>11</v>
-      </c>
-      <c r="AZ11">
-        <v>2.92</v>
-      </c>
-      <c r="BA11">
-        <v>2.92</v>
-      </c>
-      <c r="BB11">
-        <v>18.5</v>
-      </c>
-      <c r="BC11">
-        <v>2.92</v>
-      </c>
-      <c r="BD11">
-        <v>2.92</v>
-      </c>
-      <c r="BE11">
-        <v>2.92</v>
-      </c>
-      <c r="BF11">
-        <v>2.92</v>
-      </c>
-      <c r="BG11">
-        <v>2.92</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>2.12</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>2.86</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.31</v>
-      </c>
-      <c r="BN11">
-        <v>5.9</v>
-      </c>
-      <c r="BO11">
-        <v>3.3</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>2.86</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.31</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>2.42</v>
-      </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW11">
-        <v>1.31</v>
+        <v>7.4</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY11">
-        <v>1.31</v>
+        <v>15.5</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA11">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3387,315 +3426,315 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="G12">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="H12">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
+        <v>5.5</v>
+      </c>
+      <c r="J12">
+        <v>3.2</v>
+      </c>
+      <c r="K12">
+        <v>3.4</v>
+      </c>
+      <c r="L12">
+        <v>1.61</v>
+      </c>
+      <c r="M12">
+        <v>1.13</v>
+      </c>
+      <c r="N12">
+        <v>2.46</v>
+      </c>
+      <c r="O12">
+        <v>1.58</v>
+      </c>
+      <c r="P12">
+        <v>1.52</v>
+      </c>
+      <c r="Q12">
+        <v>2.76</v>
+      </c>
+      <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>6</v>
+      </c>
+      <c r="T12">
+        <v>2.32</v>
+      </c>
+      <c r="U12">
+        <v>1.68</v>
+      </c>
+      <c r="V12">
+        <v>1.22</v>
+      </c>
+      <c r="W12">
+        <v>1.98</v>
+      </c>
+      <c r="X12">
+        <v>8.4</v>
+      </c>
+      <c r="Y12">
+        <v>12.5</v>
+      </c>
+      <c r="Z12">
+        <v>48</v>
+      </c>
+      <c r="AA12">
+        <v>200</v>
+      </c>
+      <c r="AB12">
         <v>6.2</v>
       </c>
-      <c r="J12">
-        <v>3.5</v>
-      </c>
-      <c r="K12">
-        <v>4.3</v>
-      </c>
-      <c r="L12">
-        <v>1.43</v>
-      </c>
-      <c r="M12">
-        <v>1.06</v>
-      </c>
-      <c r="N12">
-        <v>3.05</v>
-      </c>
-      <c r="O12">
-        <v>1.42</v>
-      </c>
-      <c r="P12">
-        <v>1.71</v>
-      </c>
-      <c r="Q12">
-        <v>2.2</v>
-      </c>
-      <c r="R12">
-        <v>1.26</v>
-      </c>
-      <c r="S12">
-        <v>4.2</v>
-      </c>
-      <c r="T12">
-        <v>2</v>
-      </c>
-      <c r="U12">
-        <v>1.76</v>
-      </c>
-      <c r="V12">
-        <v>1.19</v>
-      </c>
-      <c r="W12">
-        <v>2.22</v>
-      </c>
-      <c r="X12">
-        <v>11.5</v>
-      </c>
-      <c r="Y12">
-        <v>16.5</v>
-      </c>
-      <c r="Z12">
-        <v>50</v>
-      </c>
-      <c r="AA12">
-        <v>220</v>
-      </c>
-      <c r="AB12">
-        <v>7</v>
-      </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE12">
         <v>130</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG12">
+        <v>11.5</v>
+      </c>
+      <c r="AH12">
+        <v>36</v>
+      </c>
+      <c r="AI12">
+        <v>160</v>
+      </c>
+      <c r="AJ12">
+        <v>25</v>
+      </c>
+      <c r="AK12">
+        <v>29</v>
+      </c>
+      <c r="AL12">
+        <v>80</v>
+      </c>
+      <c r="AM12">
+        <v>310</v>
+      </c>
+      <c r="AN12">
+        <v>32</v>
+      </c>
+      <c r="AO12">
+        <v>240</v>
+      </c>
+      <c r="AP12">
+        <v>7.4</v>
+      </c>
+      <c r="AQ12">
         <v>11</v>
       </c>
-      <c r="AH12">
-        <v>29</v>
-      </c>
-      <c r="AI12">
-        <v>130</v>
-      </c>
-      <c r="AJ12">
-        <v>19</v>
-      </c>
-      <c r="AK12">
-        <v>23</v>
-      </c>
-      <c r="AL12">
-        <v>60</v>
-      </c>
-      <c r="AM12">
-        <v>210</v>
-      </c>
-      <c r="AN12">
-        <v>15.5</v>
-      </c>
-      <c r="AO12">
-        <v>190</v>
-      </c>
-      <c r="AP12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ12">
-        <v>14</v>
-      </c>
       <c r="AR12">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="AS12">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT12">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
         <v>20</v>
       </c>
       <c r="AW12">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
         <v>8.4</v>
       </c>
-      <c r="AY12">
+      <c r="BA12">
+        <v>10.5</v>
+      </c>
+      <c r="BB12">
+        <v>21</v>
+      </c>
+      <c r="BC12">
+        <v>8</v>
+      </c>
+      <c r="BD12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE12">
+        <v>10.5</v>
+      </c>
+      <c r="BF12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG12">
+        <v>10.5</v>
+      </c>
+      <c r="BH12">
+        <v>2.64</v>
+      </c>
+      <c r="BI12">
+        <v>2.46</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>5.9</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>10.5</v>
+      </c>
+      <c r="BN12">
+        <v>4.3</v>
+      </c>
+      <c r="BO12">
+        <v>3.9</v>
+      </c>
+      <c r="BP12">
+        <v>18.5</v>
+      </c>
+      <c r="BQ12">
+        <v>6.8</v>
+      </c>
+      <c r="BR12">
+        <v>55</v>
+      </c>
+      <c r="BS12">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ12">
-        <v>20</v>
-      </c>
-      <c r="BA12">
-        <v>9.4</v>
-      </c>
-      <c r="BB12">
-        <v>15.5</v>
-      </c>
-      <c r="BC12">
-        <v>18</v>
-      </c>
-      <c r="BD12">
-        <v>38</v>
-      </c>
-      <c r="BE12">
+      <c r="BT12">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF12">
-        <v>13</v>
-      </c>
-      <c r="BG12">
+      <c r="BU12">
+        <v>7.6</v>
+      </c>
+      <c r="BV12">
+        <v>75</v>
+      </c>
+      <c r="BW12">
         <v>9.6</v>
       </c>
-      <c r="BH12">
-        <v>3.35</v>
-      </c>
-      <c r="BI12">
-        <v>2.64</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>2.06</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>2.06</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>2.92</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>2.06</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>2.06</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>2.06</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>2.06</v>
-      </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY12">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA12">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="G13">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="H13">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I13">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="J13">
+        <v>3.5</v>
+      </c>
+      <c r="K13">
+        <v>3.85</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.06</v>
+      </c>
+      <c r="N13">
+        <v>3.1</v>
+      </c>
+      <c r="O13">
+        <v>1.36</v>
+      </c>
+      <c r="P13">
+        <v>1.75</v>
+      </c>
+      <c r="Q13">
+        <v>1.94</v>
+      </c>
+      <c r="R13">
+        <v>1.32</v>
+      </c>
+      <c r="S13">
         <v>3.65</v>
       </c>
-      <c r="K13">
-        <v>3.9</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.04</v>
-      </c>
-      <c r="N13">
-        <v>3.55</v>
-      </c>
-      <c r="O13">
-        <v>1.3</v>
-      </c>
-      <c r="P13">
-        <v>1.92</v>
-      </c>
-      <c r="Q13">
-        <v>1.87</v>
-      </c>
-      <c r="R13">
-        <v>1.34</v>
-      </c>
-      <c r="S13">
-        <v>3.1</v>
-      </c>
       <c r="T13">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="U13">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="X13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
         <v>1000</v>
@@ -3704,166 +3743,1134 @@
         <v>1000</v>
       </c>
       <c r="AA13">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
         <v>970</v>
       </c>
       <c r="AC13">
+        <v>970</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>24</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.22</v>
+      </c>
+      <c r="AQ13">
+        <v>8.4</v>
+      </c>
+      <c r="AR13">
+        <v>1.22</v>
+      </c>
+      <c r="AS13">
+        <v>1.22</v>
+      </c>
+      <c r="AT13">
+        <v>1.13</v>
+      </c>
+      <c r="AU13">
+        <v>1.12</v>
+      </c>
+      <c r="AV13">
+        <v>1.22</v>
+      </c>
+      <c r="AW13">
+        <v>1.22</v>
+      </c>
+      <c r="AX13">
+        <v>1.22</v>
+      </c>
+      <c r="AY13">
+        <v>6.8</v>
+      </c>
+      <c r="AZ13">
+        <v>1.22</v>
+      </c>
+      <c r="BA13">
+        <v>1.22</v>
+      </c>
+      <c r="BB13">
+        <v>1.22</v>
+      </c>
+      <c r="BC13">
+        <v>1.22</v>
+      </c>
+      <c r="BD13">
+        <v>1.22</v>
+      </c>
+      <c r="BE13">
+        <v>1.22</v>
+      </c>
+      <c r="BF13">
+        <v>8</v>
+      </c>
+      <c r="BG13">
+        <v>1.22</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14">
+        <v>1.95</v>
+      </c>
+      <c r="G14">
+        <v>2.04</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>5.7</v>
+      </c>
+      <c r="J14">
+        <v>3.15</v>
+      </c>
+      <c r="K14">
+        <v>3.25</v>
+      </c>
+      <c r="L14">
+        <v>1.64</v>
+      </c>
+      <c r="M14">
+        <v>1.12</v>
+      </c>
+      <c r="N14">
+        <v>2.24</v>
+      </c>
+      <c r="O14">
+        <v>1.62</v>
+      </c>
+      <c r="P14">
+        <v>1.45</v>
+      </c>
+      <c r="Q14">
+        <v>3.05</v>
+      </c>
+      <c r="R14">
+        <v>1.11</v>
+      </c>
+      <c r="S14">
+        <v>5.8</v>
+      </c>
+      <c r="T14">
+        <v>2.46</v>
+      </c>
+      <c r="U14">
+        <v>1.49</v>
+      </c>
+      <c r="V14">
+        <v>1.21</v>
+      </c>
+      <c r="W14">
+        <v>1.96</v>
+      </c>
+      <c r="X14">
+        <v>7.2</v>
+      </c>
+      <c r="Y14">
+        <v>12</v>
+      </c>
+      <c r="Z14">
+        <v>40</v>
+      </c>
+      <c r="AA14">
+        <v>230</v>
+      </c>
+      <c r="AB14">
+        <v>5.6</v>
+      </c>
+      <c r="AC14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14">
+        <v>27</v>
+      </c>
+      <c r="AE14">
+        <v>150</v>
+      </c>
+      <c r="AF14">
+        <v>10</v>
+      </c>
+      <c r="AG14">
+        <v>13</v>
+      </c>
+      <c r="AH14">
+        <v>38</v>
+      </c>
+      <c r="AI14">
+        <v>200</v>
+      </c>
+      <c r="AJ14">
+        <v>27</v>
+      </c>
+      <c r="AK14">
+        <v>38</v>
+      </c>
+      <c r="AL14">
+        <v>95</v>
+      </c>
+      <c r="AM14">
+        <v>400</v>
+      </c>
+      <c r="AN14">
+        <v>32</v>
+      </c>
+      <c r="AO14">
+        <v>310</v>
+      </c>
+      <c r="AP14">
+        <v>6.6</v>
+      </c>
+      <c r="AQ14">
+        <v>10</v>
+      </c>
+      <c r="AR14">
+        <v>9</v>
+      </c>
+      <c r="AS14">
+        <v>11</v>
+      </c>
+      <c r="AT14">
+        <v>5.2</v>
+      </c>
+      <c r="AU14">
+        <v>7</v>
+      </c>
+      <c r="AV14">
+        <v>21</v>
+      </c>
+      <c r="AW14">
+        <v>10.5</v>
+      </c>
+      <c r="AX14">
+        <v>9</v>
+      </c>
+      <c r="AY14">
+        <v>11</v>
+      </c>
+      <c r="AZ14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA14">
+        <v>11</v>
+      </c>
+      <c r="BB14">
+        <v>21</v>
+      </c>
+      <c r="BC14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD14">
+        <v>10</v>
+      </c>
+      <c r="BE14">
+        <v>11</v>
+      </c>
+      <c r="BF14">
+        <v>8.4</v>
+      </c>
+      <c r="BG14">
+        <v>11</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>2.12</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>2.86</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.31</v>
+      </c>
+      <c r="BN14">
+        <v>5.9</v>
+      </c>
+      <c r="BO14">
+        <v>3.3</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>2.86</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.31</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>2.42</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.31</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.31</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.31</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15">
+        <v>1.72</v>
+      </c>
+      <c r="G15">
+        <v>1.81</v>
+      </c>
+      <c r="H15">
+        <v>5.6</v>
+      </c>
+      <c r="I15">
+        <v>6.2</v>
+      </c>
+      <c r="J15">
+        <v>3.5</v>
+      </c>
+      <c r="K15">
+        <v>3.9</v>
+      </c>
+      <c r="L15">
+        <v>1.43</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>3.05</v>
+      </c>
+      <c r="O15">
+        <v>1.42</v>
+      </c>
+      <c r="P15">
+        <v>1.66</v>
+      </c>
+      <c r="Q15">
+        <v>2.16</v>
+      </c>
+      <c r="R15">
+        <v>1.26</v>
+      </c>
+      <c r="S15">
+        <v>4.2</v>
+      </c>
+      <c r="T15">
+        <v>2</v>
+      </c>
+      <c r="U15">
+        <v>1.76</v>
+      </c>
+      <c r="V15">
+        <v>1.19</v>
+      </c>
+      <c r="W15">
+        <v>2.22</v>
+      </c>
+      <c r="X15">
+        <v>11.5</v>
+      </c>
+      <c r="Y15">
+        <v>16.5</v>
+      </c>
+      <c r="Z15">
+        <v>50</v>
+      </c>
+      <c r="AA15">
+        <v>220</v>
+      </c>
+      <c r="AB15">
+        <v>7</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>25</v>
+      </c>
+      <c r="AE15">
+        <v>130</v>
+      </c>
+      <c r="AF15">
+        <v>10</v>
+      </c>
+      <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
+        <v>29</v>
+      </c>
+      <c r="AI15">
+        <v>130</v>
+      </c>
+      <c r="AJ15">
+        <v>19</v>
+      </c>
+      <c r="AK15">
+        <v>23</v>
+      </c>
+      <c r="AL15">
+        <v>60</v>
+      </c>
+      <c r="AM15">
+        <v>210</v>
+      </c>
+      <c r="AN15">
+        <v>15.5</v>
+      </c>
+      <c r="AO15">
+        <v>190</v>
+      </c>
+      <c r="AP15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ15">
+        <v>14</v>
+      </c>
+      <c r="AR15">
+        <v>30</v>
+      </c>
+      <c r="AS15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT15">
+        <v>6</v>
+      </c>
+      <c r="AU15">
+        <v>7.6</v>
+      </c>
+      <c r="AV15">
+        <v>20</v>
+      </c>
+      <c r="AW15">
+        <v>9.4</v>
+      </c>
+      <c r="AX15">
+        <v>8.4</v>
+      </c>
+      <c r="AY15">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD13">
-        <v>16.5</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>1000</v>
-      </c>
-      <c r="AG13">
+      <c r="AZ15">
+        <v>20</v>
+      </c>
+      <c r="BA15">
+        <v>9.4</v>
+      </c>
+      <c r="BB15">
+        <v>15.5</v>
+      </c>
+      <c r="BC15">
+        <v>18</v>
+      </c>
+      <c r="BD15">
+        <v>38</v>
+      </c>
+      <c r="BE15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF15">
+        <v>13</v>
+      </c>
+      <c r="BG15">
+        <v>9.6</v>
+      </c>
+      <c r="BH15">
+        <v>3.35</v>
+      </c>
+      <c r="BI15">
+        <v>2.64</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>2.06</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>2.06</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>2.92</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>2.06</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>2.06</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>2.06</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>2.06</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>2.06</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>2.06</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16">
+        <v>2.58</v>
+      </c>
+      <c r="G16">
+        <v>110</v>
+      </c>
+      <c r="H16">
+        <v>1.29</v>
+      </c>
+      <c r="I16">
+        <v>2.52</v>
+      </c>
+      <c r="J16">
+        <v>1.12</v>
+      </c>
+      <c r="K16">
+        <v>5.2</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>1.33</v>
+      </c>
+      <c r="O16">
+        <v>1.11</v>
+      </c>
+      <c r="P16">
+        <v>1.33</v>
+      </c>
+      <c r="Q16">
+        <v>1.11</v>
+      </c>
+      <c r="R16">
+        <v>1.33</v>
+      </c>
+      <c r="S16">
+        <v>1.11</v>
+      </c>
+      <c r="T16">
+        <v>1.01</v>
+      </c>
+      <c r="U16">
+        <v>1.01</v>
+      </c>
+      <c r="V16">
+        <v>1.66</v>
+      </c>
+      <c r="W16">
+        <v>1.02</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16">
+        <v>1.03</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>1.03</v>
+      </c>
+      <c r="AU16">
+        <v>1.03</v>
+      </c>
+      <c r="AV16">
+        <v>1.03</v>
+      </c>
+      <c r="AW16">
+        <v>1.03</v>
+      </c>
+      <c r="AX16">
+        <v>1.03</v>
+      </c>
+      <c r="AY16">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16">
+        <v>1.03</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17">
+        <v>2.08</v>
+      </c>
+      <c r="G17">
+        <v>2.34</v>
+      </c>
+      <c r="H17">
+        <v>3.3</v>
+      </c>
+      <c r="I17">
+        <v>3.95</v>
+      </c>
+      <c r="J17">
+        <v>3.65</v>
+      </c>
+      <c r="K17">
+        <v>3.9</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.04</v>
+      </c>
+      <c r="N17">
+        <v>3.55</v>
+      </c>
+      <c r="O17">
+        <v>1.3</v>
+      </c>
+      <c r="P17">
+        <v>1.92</v>
+      </c>
+      <c r="Q17">
+        <v>1.8</v>
+      </c>
+      <c r="R17">
+        <v>1.34</v>
+      </c>
+      <c r="S17">
+        <v>3.1</v>
+      </c>
+      <c r="T17">
+        <v>1.69</v>
+      </c>
+      <c r="U17">
+        <v>2.04</v>
+      </c>
+      <c r="V17">
+        <v>1.34</v>
+      </c>
+      <c r="W17">
+        <v>1.75</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>90</v>
+      </c>
+      <c r="AB17">
+        <v>970</v>
+      </c>
+      <c r="AC17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
         <v>22</v>
       </c>
-      <c r="AH13">
+      <c r="AH17">
         <v>19</v>
       </c>
-      <c r="AI13">
-        <v>1000</v>
-      </c>
-      <c r="AJ13">
-        <v>1000</v>
-      </c>
-      <c r="AK13">
-        <v>1000</v>
-      </c>
-      <c r="AL13">
-        <v>1000</v>
-      </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>17.5</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>1.64</v>
-      </c>
-      <c r="AQ13">
-        <v>1.82</v>
-      </c>
-      <c r="AR13">
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.38</v>
+      </c>
+      <c r="AQ17">
+        <v>1.38</v>
+      </c>
+      <c r="AR17">
         <v>18</v>
       </c>
-      <c r="AS13">
-        <v>1.79</v>
-      </c>
-      <c r="AT13">
-        <v>1.66</v>
-      </c>
-      <c r="AU13">
-        <v>1.52</v>
-      </c>
-      <c r="AV13">
-        <v>1.64</v>
-      </c>
-      <c r="AW13">
-        <v>1.82</v>
-      </c>
-      <c r="AX13">
-        <v>1.82</v>
-      </c>
-      <c r="AY13">
-        <v>7.8</v>
-      </c>
-      <c r="AZ13">
-        <v>1.66</v>
-      </c>
-      <c r="BA13">
-        <v>1.82</v>
-      </c>
-      <c r="BB13">
+      <c r="AS17">
+        <v>1.36</v>
+      </c>
+      <c r="AT17">
+        <v>1.28</v>
+      </c>
+      <c r="AU17">
+        <v>1.19</v>
+      </c>
+      <c r="AV17">
+        <v>1.38</v>
+      </c>
+      <c r="AW17">
+        <v>1.38</v>
+      </c>
+      <c r="AX17">
+        <v>1.38</v>
+      </c>
+      <c r="AY17">
+        <v>1.3</v>
+      </c>
+      <c r="AZ17">
+        <v>1.28</v>
+      </c>
+      <c r="BA17">
+        <v>1.38</v>
+      </c>
+      <c r="BB17">
         <v>19</v>
       </c>
-      <c r="BC13">
-        <v>1.82</v>
-      </c>
-      <c r="BD13">
-        <v>1.82</v>
-      </c>
-      <c r="BE13">
-        <v>1.82</v>
-      </c>
-      <c r="BF13">
-        <v>1.65</v>
-      </c>
-      <c r="BG13">
-        <v>1.82</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
+      <c r="BC17">
+        <v>1.38</v>
+      </c>
+      <c r="BD17">
+        <v>1.38</v>
+      </c>
+      <c r="BE17">
+        <v>1.38</v>
+      </c>
+      <c r="BF17">
+        <v>1.38</v>
+      </c>
+      <c r="BG17">
+        <v>1.38</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
         <v>2.8</v>
       </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.01</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.01</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.01</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.01</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>1.01</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>123</v>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="142">
   <si>
     <t>League</t>
   </si>
@@ -265,12 +265,12 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Serbian First League</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
-    <t>Serbian First League</t>
-  </si>
-  <si>
     <t>Turkish 2 Lig</t>
   </si>
   <si>
@@ -301,6 +301,9 @@
     <t>02:00:00</t>
   </si>
   <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -340,15 +343,21 @@
     <t>Nicaragua</t>
   </si>
   <si>
+    <t>Fk Smederevo</t>
+  </si>
+  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
+    <t>FK Napredak</t>
+  </si>
+  <si>
+    <t>Sanliurfaspor</t>
+  </si>
+  <si>
     <t>FK Backa Topola</t>
   </si>
   <si>
-    <t>Sanliurfaspor</t>
-  </si>
-  <si>
     <t>Moss</t>
   </si>
   <si>
@@ -364,15 +373,15 @@
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Martinique</t>
+  </si>
+  <si>
     <t>Velez Sarsfield</t>
   </si>
   <si>
     <t>Estudiantes</t>
   </si>
   <si>
-    <t>Martinique</t>
-  </si>
-  <si>
     <t>Nacional (Uru)</t>
   </si>
   <si>
@@ -388,15 +397,21 @@
     <t>Dominican Republic</t>
   </si>
   <si>
+    <t>Vozdovac</t>
+  </si>
+  <si>
     <t>Libertad</t>
   </si>
   <si>
+    <t>FK Loznica</t>
+  </si>
+  <si>
+    <t>Belediye Derincespor</t>
+  </si>
+  <si>
     <t>FK Graficar</t>
   </si>
   <si>
-    <t>Belediye Derincespor</t>
-  </si>
-  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
@@ -412,19 +427,19 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
     <t>CA Platense</t>
   </si>
   <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
-    <t>El Salvador</t>
-  </si>
-  <si>
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 03:53:43</t>
+    <t>2026-10-04 06:06:38</t>
   </si>
 </sst>
 </file>
@@ -756,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1012,10 +1027,10 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>2.3</v>
@@ -1051,13 +1066,13 @@
         <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R2">
         <v>1.49</v>
       </c>
       <c r="S2">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T2">
         <v>1.65</v>
@@ -1072,7 +1087,7 @@
         <v>1.72</v>
       </c>
       <c r="X2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y2">
         <v>15.5</v>
@@ -1084,19 +1099,19 @@
         <v>50</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
         <v>32</v>
       </c>
       <c r="AF2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1105,7 +1120,7 @@
         <v>16.5</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
         <v>34</v>
@@ -1126,10 +1141,10 @@
         <v>25</v>
       </c>
       <c r="AP2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR2">
         <v>20</v>
@@ -1147,7 +1162,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1162,16 +1177,16 @@
         <v>32</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1183,19 +1198,19 @@
         <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>9</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>5.4</v>
@@ -1207,16 +1222,16 @@
         <v>16</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
         <v>5</v>
@@ -1225,22 +1240,22 @@
         <v>24</v>
       </c>
       <c r="BW2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>21</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1254,28 +1269,28 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I3">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J3">
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
         <v>1.64</v>
@@ -1293,7 +1308,7 @@
         <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R3">
         <v>1.17</v>
@@ -1308,13 +1323,13 @@
         <v>1.67</v>
       </c>
       <c r="V3">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y3">
         <v>6.4</v>
@@ -1323,7 +1338,7 @@
         <v>11</v>
       </c>
       <c r="AA3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB3">
         <v>11</v>
@@ -1335,28 +1350,28 @@
         <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF3">
         <v>32</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM3">
         <v>310</v>
@@ -1371,43 +1386,43 @@
         <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR3">
         <v>9.6</v>
       </c>
       <c r="AS3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AT3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU3">
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AX3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BA3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3">
         <v>40</v>
       </c>
       <c r="BC3">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BD3">
         <v>42</v>
@@ -1419,43 +1434,43 @@
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BH3">
         <v>2.56</v>
       </c>
       <c r="BI3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO3">
         <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
         <v>4.5</v>
@@ -1464,25 +1479,25 @@
         <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
         <v>55</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1496,10 +1511,10 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>3.65</v>
@@ -1511,7 +1526,7 @@
         <v>2.24</v>
       </c>
       <c r="I4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
         <v>3.3</v>
@@ -1550,7 +1565,7 @@
         <v>2</v>
       </c>
       <c r="V4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W4">
         <v>1.35</v>
@@ -1724,7 +1739,7 @@
         <v>5.7</v>
       </c>
       <c r="CB4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1738,58 +1753,58 @@
         <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
         <v>1.76</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
+        <v>2.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.74</v>
+      </c>
+      <c r="R5">
+        <v>1.48</v>
+      </c>
+      <c r="S5">
+        <v>2.92</v>
+      </c>
+      <c r="T5">
+        <v>1.74</v>
+      </c>
+      <c r="U5">
         <v>2.16</v>
-      </c>
-      <c r="Q5">
-        <v>1.8</v>
-      </c>
-      <c r="R5">
-        <v>1.45</v>
-      </c>
-      <c r="S5">
-        <v>3.1</v>
-      </c>
-      <c r="T5">
-        <v>1.78</v>
-      </c>
-      <c r="U5">
-        <v>2.1</v>
       </c>
       <c r="V5">
         <v>2.3</v>
@@ -1798,10 +1813,10 @@
         <v>1.23</v>
       </c>
       <c r="X5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5">
         <v>11.5</v>
@@ -1813,13 +1828,13 @@
         <v>21</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF5">
         <v>42</v>
@@ -1834,7 +1849,7 @@
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK5">
         <v>85</v>
@@ -1843,16 +1858,16 @@
         <v>100</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP5">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
         <v>8.6</v>
@@ -1867,13 +1882,13 @@
         <v>16</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV5">
         <v>9</v>
       </c>
       <c r="AW5">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AX5">
         <v>32</v>
@@ -1885,88 +1900,88 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BB5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BF5">
+        <v>8.6</v>
+      </c>
+      <c r="BG5">
+        <v>7.6</v>
+      </c>
+      <c r="BH5">
+        <v>4.1</v>
+      </c>
+      <c r="BI5">
+        <v>3.2</v>
+      </c>
+      <c r="BJ5">
+        <v>10</v>
+      </c>
+      <c r="BK5">
+        <v>5.2</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BG5">
-        <v>8.4</v>
-      </c>
-      <c r="BH5">
-        <v>3.8</v>
-      </c>
-      <c r="BI5">
-        <v>3.15</v>
-      </c>
-      <c r="BJ5">
-        <v>10.5</v>
-      </c>
-      <c r="BK5">
-        <v>5.7</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>11</v>
       </c>
       <c r="BN5">
         <v>9</v>
       </c>
       <c r="BO5">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BQ5">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BU5">
         <v>3.6</v>
       </c>
       <c r="BV5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW5">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BX5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA5">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1980,65 +1995,65 @@
         <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="G6">
-        <v>680</v>
+        <v>2.32</v>
       </c>
       <c r="H6">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>680</v>
+        <v>5.5</v>
       </c>
       <c r="J6">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>680</v>
+        <v>950</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="Q6">
-        <v>1.27</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>2.84</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.21</v>
+      </c>
+      <c r="W6">
         <v>1.75</v>
       </c>
-      <c r="S6">
-        <v>1.03</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>1.01</v>
-      </c>
-      <c r="W6">
-        <v>1.01</v>
-      </c>
       <c r="X6">
         <v>1000</v>
       </c>
@@ -2058,19 +2073,19 @@
         <v>1000</v>
       </c>
       <c r="AD6">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
         <v>1000</v>
       </c>
       <c r="AG6">
-        <v>830</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -2085,7 +2100,7 @@
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
         <v>1000</v>
@@ -2094,121 +2109,121 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2222,240 +2237,240 @@
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>680</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>4.1</v>
+      </c>
+      <c r="Q7">
+        <v>1.27</v>
+      </c>
+      <c r="R7">
+        <v>1.75</v>
+      </c>
+      <c r="S7">
+        <v>1.03</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>750</v>
+      </c>
+      <c r="AE7">
+        <v>18</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>830</v>
+      </c>
+      <c r="AH7">
+        <v>990</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>65</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
         <v>1.08</v>
       </c>
-      <c r="O7">
-        <v>1.21</v>
-      </c>
-      <c r="P7">
+      <c r="AQ7">
         <v>1.08</v>
       </c>
-      <c r="Q7">
-        <v>1.21</v>
-      </c>
-      <c r="R7">
+      <c r="AR7">
         <v>1.08</v>
       </c>
-      <c r="S7">
-        <v>1.21</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
+      <c r="AS7">
+        <v>1.08</v>
+      </c>
+      <c r="AT7">
+        <v>1.08</v>
+      </c>
+      <c r="AU7">
+        <v>1.08</v>
+      </c>
+      <c r="AV7">
+        <v>2.44</v>
+      </c>
+      <c r="AW7">
         <v>1.02</v>
       </c>
-      <c r="W7">
-        <v>1.02</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7">
-        <v>1.03</v>
-      </c>
-      <c r="AR7">
-        <v>1.03</v>
-      </c>
-      <c r="AS7">
-        <v>1.03</v>
-      </c>
-      <c r="AT7">
-        <v>1.03</v>
-      </c>
-      <c r="AU7">
-        <v>1.03</v>
-      </c>
-      <c r="AV7">
-        <v>1.03</v>
-      </c>
-      <c r="AW7">
-        <v>1.03</v>
-      </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
@@ -2464,28 +2479,28 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2494,22 +2509,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2518,10 +2533,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2578,52 +2593,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2692,12 +2707,12 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>90</v>
@@ -2706,28 +2721,28 @@
         <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>1.68</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
-        <v>1.94</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2736,34 +2751,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q9">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>1.06</v>
       </c>
       <c r="S9">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="T9">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2784,7 +2799,7 @@
         <v>1000</v>
       </c>
       <c r="AD9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
         <v>1000</v>
@@ -2796,7 +2811,7 @@
         <v>1000</v>
       </c>
       <c r="AH9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
         <v>1000</v>
@@ -2817,61 +2832,61 @@
         <v>1000</v>
       </c>
       <c r="AO9">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2934,120 +2949,120 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F10">
-        <v>1.93</v>
+        <v>1.13</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J10">
+        <v>3.6</v>
+      </c>
+      <c r="K10">
+        <v>950</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>2.46</v>
+      </c>
+      <c r="O10">
+        <v>1.18</v>
+      </c>
+      <c r="P10">
+        <v>2.46</v>
+      </c>
+      <c r="Q10">
+        <v>1.4</v>
+      </c>
+      <c r="R10">
+        <v>1.59</v>
+      </c>
+      <c r="S10">
+        <v>1.9</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.02</v>
+      </c>
+      <c r="W10">
         <v>3.45</v>
       </c>
-      <c r="K10">
-        <v>3.95</v>
-      </c>
-      <c r="L10">
-        <v>1.38</v>
-      </c>
-      <c r="M10">
-        <v>1.07</v>
-      </c>
-      <c r="N10">
-        <v>3.5</v>
-      </c>
-      <c r="O10">
-        <v>1.29</v>
-      </c>
-      <c r="P10">
-        <v>1.87</v>
-      </c>
-      <c r="Q10">
-        <v>1.87</v>
-      </c>
-      <c r="R10">
-        <v>1.39</v>
-      </c>
-      <c r="S10">
-        <v>3.05</v>
-      </c>
-      <c r="T10">
-        <v>1.71</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10">
-        <v>1.27</v>
-      </c>
-      <c r="W10">
-        <v>1.99</v>
-      </c>
       <c r="X10">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
         <v>1000</v>
@@ -3056,318 +3071,318 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F11">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="G11">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="H11">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="I11">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="J11">
+        <v>4.3</v>
+      </c>
+      <c r="K11">
+        <v>6.4</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
         <v>4.2</v>
       </c>
-      <c r="K11">
-        <v>5.2</v>
-      </c>
-      <c r="L11">
+      <c r="O11">
+        <v>1.05</v>
+      </c>
+      <c r="P11">
+        <v>4.2</v>
+      </c>
+      <c r="Q11">
+        <v>1.2</v>
+      </c>
+      <c r="R11">
+        <v>2.38</v>
+      </c>
+      <c r="S11">
+        <v>1.54</v>
+      </c>
+      <c r="T11">
+        <v>1.28</v>
+      </c>
+      <c r="U11">
+        <v>3.35</v>
+      </c>
+      <c r="V11">
+        <v>2.06</v>
+      </c>
+      <c r="W11">
         <v>1.27</v>
       </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>1.01</v>
-      </c>
-      <c r="O11">
-        <v>1.21</v>
-      </c>
-      <c r="P11">
-        <v>2.22</v>
-      </c>
-      <c r="Q11">
-        <v>1.53</v>
-      </c>
-      <c r="R11">
-        <v>1.51</v>
-      </c>
-      <c r="S11">
-        <v>2.34</v>
-      </c>
-      <c r="T11">
-        <v>1.74</v>
-      </c>
-      <c r="U11">
-        <v>2.14</v>
-      </c>
-      <c r="V11">
-        <v>2.5</v>
-      </c>
-      <c r="W11">
-        <v>1.19</v>
-      </c>
       <c r="X11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="AE11">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG11">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="BH11">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3376,10 +3391,10 @@
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3394,464 +3409,464 @@
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
         <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G12">
         <v>2.02</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="L12">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="M12">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="O12">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="Q12">
-        <v>2.76</v>
+        <v>1.83</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S12">
+        <v>3.05</v>
+      </c>
+      <c r="T12">
+        <v>1.71</v>
+      </c>
+      <c r="U12">
+        <v>2</v>
+      </c>
+      <c r="V12">
+        <v>1.29</v>
+      </c>
+      <c r="W12">
+        <v>1.99</v>
+      </c>
+      <c r="X12">
+        <v>18.5</v>
+      </c>
+      <c r="Y12">
+        <v>40</v>
+      </c>
+      <c r="Z12">
+        <v>95</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>14.5</v>
+      </c>
+      <c r="AC12">
+        <v>12</v>
+      </c>
+      <c r="AD12">
+        <v>32</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>18</v>
+      </c>
+      <c r="AG12">
+        <v>16</v>
+      </c>
+      <c r="AH12">
+        <v>75</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>90</v>
+      </c>
+      <c r="AK12">
+        <v>85</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>26</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>12</v>
+      </c>
+      <c r="AQ12">
+        <v>11.5</v>
+      </c>
+      <c r="AR12">
+        <v>6.4</v>
+      </c>
+      <c r="AS12">
+        <v>1.99</v>
+      </c>
+      <c r="AT12">
+        <v>7.6</v>
+      </c>
+      <c r="AU12">
         <v>6</v>
       </c>
-      <c r="T12">
-        <v>2.32</v>
-      </c>
-      <c r="U12">
-        <v>1.68</v>
-      </c>
-      <c r="V12">
-        <v>1.22</v>
-      </c>
-      <c r="W12">
-        <v>1.98</v>
-      </c>
-      <c r="X12">
+      <c r="AV12">
+        <v>12.5</v>
+      </c>
+      <c r="AW12">
+        <v>15</v>
+      </c>
+      <c r="AX12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY12">
         <v>8.4</v>
       </c>
-      <c r="Y12">
-        <v>12.5</v>
-      </c>
-      <c r="Z12">
-        <v>48</v>
-      </c>
-      <c r="AA12">
-        <v>200</v>
-      </c>
-      <c r="AB12">
+      <c r="AZ12">
+        <v>11</v>
+      </c>
+      <c r="BA12">
+        <v>16</v>
+      </c>
+      <c r="BB12">
+        <v>6</v>
+      </c>
+      <c r="BC12">
+        <v>13.5</v>
+      </c>
+      <c r="BD12">
+        <v>13.5</v>
+      </c>
+      <c r="BE12">
+        <v>1.99</v>
+      </c>
+      <c r="BF12">
+        <v>8.6</v>
+      </c>
+      <c r="BG12">
+        <v>1.99</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.47</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
         <v>6.2</v>
       </c>
-      <c r="AC12">
-        <v>7.8</v>
-      </c>
-      <c r="AD12">
-        <v>23</v>
-      </c>
-      <c r="AE12">
-        <v>130</v>
-      </c>
-      <c r="AF12">
-        <v>10.5</v>
-      </c>
-      <c r="AG12">
-        <v>11.5</v>
-      </c>
-      <c r="AH12">
-        <v>36</v>
-      </c>
-      <c r="AI12">
-        <v>160</v>
-      </c>
-      <c r="AJ12">
-        <v>25</v>
-      </c>
-      <c r="AK12">
-        <v>29</v>
-      </c>
-      <c r="AL12">
-        <v>80</v>
-      </c>
-      <c r="AM12">
-        <v>310</v>
-      </c>
-      <c r="AN12">
-        <v>32</v>
-      </c>
-      <c r="AO12">
-        <v>240</v>
-      </c>
-      <c r="AP12">
-        <v>7.4</v>
-      </c>
-      <c r="AQ12">
-        <v>11</v>
-      </c>
-      <c r="AR12">
-        <v>9</v>
-      </c>
-      <c r="AS12">
-        <v>10.5</v>
-      </c>
-      <c r="AT12">
-        <v>5.6</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>20</v>
-      </c>
-      <c r="AW12">
-        <v>10</v>
-      </c>
-      <c r="AX12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY12">
-        <v>10</v>
-      </c>
-      <c r="AZ12">
-        <v>8.4</v>
-      </c>
-      <c r="BA12">
-        <v>10.5</v>
-      </c>
-      <c r="BB12">
-        <v>21</v>
-      </c>
-      <c r="BC12">
-        <v>8</v>
-      </c>
-      <c r="BD12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE12">
-        <v>10.5</v>
-      </c>
-      <c r="BF12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG12">
-        <v>10.5</v>
-      </c>
-      <c r="BH12">
-        <v>2.64</v>
-      </c>
-      <c r="BI12">
-        <v>2.46</v>
-      </c>
-      <c r="BJ12">
-        <v>12.5</v>
-      </c>
-      <c r="BK12">
-        <v>5.9</v>
-      </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>1.17</v>
       </c>
       <c r="BN12">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.9</v>
+        <v>1.69</v>
       </c>
       <c r="BP12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="BR12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9.199999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="BT12">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>7.6</v>
+        <v>1.99</v>
       </c>
       <c r="BV12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>9.6</v>
+        <v>1.17</v>
       </c>
       <c r="BX12">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>1.17</v>
       </c>
       <c r="BZ12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>9.199999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="CB12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>1.89</v>
+        <v>5.4</v>
       </c>
       <c r="G13">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="H13">
-        <v>4.3</v>
+        <v>1.55</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>1.63</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="O13">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q13">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="R13">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="T13">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="U13">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="W13">
-        <v>1.96</v>
+        <v>1.19</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB13">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AC13">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG13">
         <v>24</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP13">
-        <v>1.22</v>
+        <v>3.5</v>
       </c>
       <c r="AQ13">
-        <v>8.4</v>
+        <v>3.05</v>
       </c>
       <c r="AR13">
-        <v>1.22</v>
+        <v>2.96</v>
       </c>
       <c r="AS13">
-        <v>1.22</v>
+        <v>3.3</v>
       </c>
       <c r="AT13">
-        <v>1.13</v>
+        <v>3.5</v>
       </c>
       <c r="AU13">
-        <v>1.12</v>
+        <v>3.95</v>
       </c>
       <c r="AV13">
-        <v>1.22</v>
+        <v>2.92</v>
       </c>
       <c r="AW13">
-        <v>1.22</v>
+        <v>3.2</v>
       </c>
       <c r="AX13">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="AY13">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="AZ13">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="BA13">
-        <v>1.22</v>
+        <v>3.55</v>
       </c>
       <c r="BB13">
-        <v>1.22</v>
+        <v>3.9</v>
       </c>
       <c r="BC13">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="BD13">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="BE13">
-        <v>1.22</v>
+        <v>3.85</v>
       </c>
       <c r="BF13">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="BG13">
-        <v>1.22</v>
+        <v>2.64</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3860,10 +3875,10 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BP13">
         <v>1000</v>
@@ -3878,31 +3893,31 @@
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3913,243 +3928,243 @@
         <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G14">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L14">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M14">
         <v>1.12</v>
       </c>
       <c r="N14">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="O14">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="P14">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Q14">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="R14">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="U14">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X14">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA14">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AB14">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC14">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE14">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG14">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI14">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK14">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL14">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM14">
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="AN14">
         <v>32</v>
       </c>
       <c r="AO14">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="AP14">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ14">
+        <v>11</v>
+      </c>
+      <c r="AR14">
+        <v>19</v>
+      </c>
+      <c r="AS14">
+        <v>10.5</v>
+      </c>
+      <c r="AT14">
+        <v>5.6</v>
+      </c>
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
+        <v>20</v>
+      </c>
+      <c r="AW14">
         <v>10</v>
       </c>
-      <c r="AR14">
-        <v>9</v>
-      </c>
-      <c r="AS14">
-        <v>11</v>
-      </c>
-      <c r="AT14">
-        <v>5.2</v>
-      </c>
-      <c r="AU14">
-        <v>7</v>
-      </c>
-      <c r="AV14">
-        <v>21</v>
-      </c>
-      <c r="AW14">
+      <c r="AX14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14">
+        <v>10</v>
+      </c>
+      <c r="AZ14">
+        <v>14.5</v>
+      </c>
+      <c r="BA14">
         <v>10.5</v>
-      </c>
-      <c r="AX14">
-        <v>9</v>
-      </c>
-      <c r="AY14">
-        <v>11</v>
-      </c>
-      <c r="AZ14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA14">
-        <v>11</v>
       </c>
       <c r="BB14">
         <v>21</v>
       </c>
       <c r="BC14">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BD14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE14">
+        <v>10.5</v>
+      </c>
+      <c r="BF14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG14">
+        <v>10.5</v>
+      </c>
+      <c r="BH14">
+        <v>2.64</v>
+      </c>
+      <c r="BI14">
+        <v>2.46</v>
+      </c>
+      <c r="BJ14">
+        <v>12.5</v>
+      </c>
+      <c r="BK14">
+        <v>6.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>12.5</v>
+      </c>
+      <c r="BN14">
+        <v>4.3</v>
+      </c>
+      <c r="BO14">
+        <v>3.95</v>
+      </c>
+      <c r="BP14">
+        <v>18.5</v>
+      </c>
+      <c r="BQ14">
+        <v>7.6</v>
+      </c>
+      <c r="BR14">
+        <v>55</v>
+      </c>
+      <c r="BS14">
+        <v>10.5</v>
+      </c>
+      <c r="BT14">
+        <v>8.6</v>
+      </c>
+      <c r="BU14">
+        <v>7.6</v>
+      </c>
+      <c r="BV14">
+        <v>75</v>
+      </c>
+      <c r="BW14">
         <v>11</v>
       </c>
-      <c r="BF14">
-        <v>8.4</v>
-      </c>
-      <c r="BG14">
-        <v>11</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>2.12</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>2.86</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.31</v>
-      </c>
-      <c r="BN14">
-        <v>5.9</v>
-      </c>
-      <c r="BO14">
-        <v>3.3</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>2.86</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.31</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>2.42</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.31</v>
-      </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY14">
-        <v>1.31</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA14">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
@@ -4158,235 +4173,235 @@
         <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F15">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="G15">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="H15">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="I15">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="J15">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L15">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="Q15">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T15">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="U15">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="V15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="X15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC15">
+        <v>970</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>26</v>
+      </c>
+      <c r="AG15">
+        <v>24</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.29</v>
+      </c>
+      <c r="AQ15">
         <v>8.4</v>
       </c>
-      <c r="AD15">
-        <v>25</v>
-      </c>
-      <c r="AE15">
-        <v>130</v>
-      </c>
-      <c r="AF15">
-        <v>10</v>
-      </c>
-      <c r="AG15">
-        <v>11</v>
-      </c>
-      <c r="AH15">
-        <v>29</v>
-      </c>
-      <c r="AI15">
-        <v>130</v>
-      </c>
-      <c r="AJ15">
-        <v>19</v>
-      </c>
-      <c r="AK15">
-        <v>23</v>
-      </c>
-      <c r="AL15">
-        <v>60</v>
-      </c>
-      <c r="AM15">
-        <v>210</v>
-      </c>
-      <c r="AN15">
-        <v>15.5</v>
-      </c>
-      <c r="AO15">
-        <v>190</v>
-      </c>
-      <c r="AP15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ15">
-        <v>14</v>
-      </c>
       <c r="AR15">
-        <v>30</v>
+        <v>1.29</v>
       </c>
       <c r="AS15">
-        <v>9.800000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="AT15">
-        <v>6</v>
+        <v>1.18</v>
       </c>
       <c r="AU15">
-        <v>7.6</v>
+        <v>1.17</v>
       </c>
       <c r="AV15">
-        <v>20</v>
+        <v>1.29</v>
       </c>
       <c r="AW15">
-        <v>9.4</v>
+        <v>1.29</v>
       </c>
       <c r="AX15">
-        <v>8.4</v>
+        <v>1.23</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AZ15">
-        <v>20</v>
+        <v>1.29</v>
       </c>
       <c r="BA15">
-        <v>9.4</v>
+        <v>1.29</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>1.29</v>
       </c>
       <c r="BC15">
-        <v>18</v>
+        <v>1.29</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>1.29</v>
       </c>
       <c r="BE15">
-        <v>9.800000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="BF15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BG15">
-        <v>9.6</v>
+        <v>1.29</v>
       </c>
       <c r="BH15">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4397,175 +4412,175 @@
         <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
-        <v>110</v>
+        <v>2.94</v>
       </c>
       <c r="H16">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="I16">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="J16">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="P16">
-        <v>1.33</v>
+        <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="S16">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4628,12 +4643,12 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>90</v>
@@ -4642,235 +4657,719 @@
         <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F17">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="G17">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="H17">
+        <v>5.1</v>
+      </c>
+      <c r="I17">
+        <v>5.7</v>
+      </c>
+      <c r="J17">
+        <v>3.15</v>
+      </c>
+      <c r="K17">
+        <v>3.4</v>
+      </c>
+      <c r="L17">
+        <v>1.64</v>
+      </c>
+      <c r="M17">
+        <v>1.12</v>
+      </c>
+      <c r="N17">
+        <v>2.36</v>
+      </c>
+      <c r="O17">
+        <v>1.57</v>
+      </c>
+      <c r="P17">
+        <v>1.46</v>
+      </c>
+      <c r="Q17">
+        <v>2.82</v>
+      </c>
+      <c r="R17">
+        <v>1.16</v>
+      </c>
+      <c r="S17">
+        <v>6.6</v>
+      </c>
+      <c r="T17">
+        <v>2.36</v>
+      </c>
+      <c r="U17">
+        <v>1.51</v>
+      </c>
+      <c r="V17">
+        <v>1.21</v>
+      </c>
+      <c r="W17">
+        <v>1.99</v>
+      </c>
+      <c r="X17">
+        <v>7.6</v>
+      </c>
+      <c r="Y17">
+        <v>12</v>
+      </c>
+      <c r="Z17">
+        <v>40</v>
+      </c>
+      <c r="AA17">
+        <v>220</v>
+      </c>
+      <c r="AB17">
+        <v>5.6</v>
+      </c>
+      <c r="AC17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17">
+        <v>26</v>
+      </c>
+      <c r="AE17">
+        <v>150</v>
+      </c>
+      <c r="AF17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG17">
+        <v>12.5</v>
+      </c>
+      <c r="AH17">
+        <v>34</v>
+      </c>
+      <c r="AI17">
+        <v>190</v>
+      </c>
+      <c r="AJ17">
+        <v>26</v>
+      </c>
+      <c r="AK17">
+        <v>36</v>
+      </c>
+      <c r="AL17">
+        <v>90</v>
+      </c>
+      <c r="AM17">
+        <v>390</v>
+      </c>
+      <c r="AN17">
+        <v>32</v>
+      </c>
+      <c r="AO17">
+        <v>290</v>
+      </c>
+      <c r="AP17">
+        <v>6.8</v>
+      </c>
+      <c r="AQ17">
+        <v>10</v>
+      </c>
+      <c r="AR17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS17">
+        <v>12</v>
+      </c>
+      <c r="AT17">
+        <v>5.2</v>
+      </c>
+      <c r="AU17">
+        <v>7</v>
+      </c>
+      <c r="AV17">
+        <v>21</v>
+      </c>
+      <c r="AW17">
+        <v>11.5</v>
+      </c>
+      <c r="AX17">
+        <v>9</v>
+      </c>
+      <c r="AY17">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA17">
+        <v>12</v>
+      </c>
+      <c r="BB17">
+        <v>21</v>
+      </c>
+      <c r="BC17">
+        <v>9.4</v>
+      </c>
+      <c r="BD17">
+        <v>11</v>
+      </c>
+      <c r="BE17">
+        <v>12.5</v>
+      </c>
+      <c r="BF17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG17">
+        <v>12</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>2.12</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>2.86</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.31</v>
+      </c>
+      <c r="BN17">
+        <v>5.9</v>
+      </c>
+      <c r="BO17">
         <v>3.3</v>
       </c>
-      <c r="I17">
-        <v>3.95</v>
-      </c>
-      <c r="J17">
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>2.86</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.31</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>2.42</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.31</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.31</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.31</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18">
+        <v>1.72</v>
+      </c>
+      <c r="G18">
+        <v>1.81</v>
+      </c>
+      <c r="H18">
+        <v>5.6</v>
+      </c>
+      <c r="I18">
+        <v>6.2</v>
+      </c>
+      <c r="J18">
+        <v>3.5</v>
+      </c>
+      <c r="K18">
+        <v>3.9</v>
+      </c>
+      <c r="L18">
+        <v>1.43</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>3.05</v>
+      </c>
+      <c r="O18">
+        <v>1.42</v>
+      </c>
+      <c r="P18">
+        <v>1.66</v>
+      </c>
+      <c r="Q18">
+        <v>2.16</v>
+      </c>
+      <c r="R18">
+        <v>1.26</v>
+      </c>
+      <c r="S18">
+        <v>4.2</v>
+      </c>
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18">
+        <v>1.76</v>
+      </c>
+      <c r="V18">
+        <v>1.19</v>
+      </c>
+      <c r="W18">
+        <v>2.22</v>
+      </c>
+      <c r="X18">
+        <v>11.5</v>
+      </c>
+      <c r="Y18">
+        <v>16.5</v>
+      </c>
+      <c r="Z18">
+        <v>50</v>
+      </c>
+      <c r="AA18">
+        <v>220</v>
+      </c>
+      <c r="AB18">
+        <v>7</v>
+      </c>
+      <c r="AC18">
+        <v>8.4</v>
+      </c>
+      <c r="AD18">
+        <v>25</v>
+      </c>
+      <c r="AE18">
+        <v>130</v>
+      </c>
+      <c r="AF18">
+        <v>10</v>
+      </c>
+      <c r="AG18">
+        <v>11</v>
+      </c>
+      <c r="AH18">
+        <v>29</v>
+      </c>
+      <c r="AI18">
+        <v>130</v>
+      </c>
+      <c r="AJ18">
+        <v>19</v>
+      </c>
+      <c r="AK18">
+        <v>23</v>
+      </c>
+      <c r="AL18">
+        <v>60</v>
+      </c>
+      <c r="AM18">
+        <v>210</v>
+      </c>
+      <c r="AN18">
+        <v>15.5</v>
+      </c>
+      <c r="AO18">
+        <v>190</v>
+      </c>
+      <c r="AP18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18">
+        <v>14</v>
+      </c>
+      <c r="AR18">
+        <v>30</v>
+      </c>
+      <c r="AS18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT18">
+        <v>6</v>
+      </c>
+      <c r="AU18">
+        <v>7.6</v>
+      </c>
+      <c r="AV18">
+        <v>20</v>
+      </c>
+      <c r="AW18">
+        <v>9.4</v>
+      </c>
+      <c r="AX18">
+        <v>8.4</v>
+      </c>
+      <c r="AY18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18">
+        <v>20</v>
+      </c>
+      <c r="BA18">
+        <v>9.4</v>
+      </c>
+      <c r="BB18">
+        <v>15.5</v>
+      </c>
+      <c r="BC18">
+        <v>18</v>
+      </c>
+      <c r="BD18">
+        <v>38</v>
+      </c>
+      <c r="BE18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF18">
+        <v>13</v>
+      </c>
+      <c r="BG18">
+        <v>9.6</v>
+      </c>
+      <c r="BH18">
+        <v>3.35</v>
+      </c>
+      <c r="BI18">
+        <v>2.64</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>2.06</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>2.06</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>2.92</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>2.06</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>2.06</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>2.06</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>2.06</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>2.06</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>2.06</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19">
+        <v>2.16</v>
+      </c>
+      <c r="G19">
+        <v>2.38</v>
+      </c>
+      <c r="H19">
+        <v>3.3</v>
+      </c>
+      <c r="I19">
+        <v>3.75</v>
+      </c>
+      <c r="J19">
         <v>3.65</v>
       </c>
-      <c r="K17">
+      <c r="K19">
         <v>3.9</v>
       </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
         <v>1.04</v>
       </c>
-      <c r="N17">
+      <c r="N19">
         <v>3.55</v>
       </c>
-      <c r="O17">
+      <c r="O19">
+        <v>1.29</v>
+      </c>
+      <c r="P19">
+        <v>1.92</v>
+      </c>
+      <c r="Q19">
+        <v>1.8</v>
+      </c>
+      <c r="R19">
+        <v>1.34</v>
+      </c>
+      <c r="S19">
+        <v>3.1</v>
+      </c>
+      <c r="T19">
+        <v>1.69</v>
+      </c>
+      <c r="U19">
+        <v>2.04</v>
+      </c>
+      <c r="V19">
+        <v>1.36</v>
+      </c>
+      <c r="W19">
+        <v>1.73</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>90</v>
+      </c>
+      <c r="AB19">
+        <v>970</v>
+      </c>
+      <c r="AC19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>22</v>
+      </c>
+      <c r="AH19">
+        <v>19</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.38</v>
+      </c>
+      <c r="AQ19">
+        <v>1.38</v>
+      </c>
+      <c r="AR19">
+        <v>18</v>
+      </c>
+      <c r="AS19">
+        <v>1.36</v>
+      </c>
+      <c r="AT19">
+        <v>1.28</v>
+      </c>
+      <c r="AU19">
+        <v>7</v>
+      </c>
+      <c r="AV19">
+        <v>1.38</v>
+      </c>
+      <c r="AW19">
+        <v>1.38</v>
+      </c>
+      <c r="AX19">
+        <v>1.38</v>
+      </c>
+      <c r="AY19">
         <v>1.3</v>
       </c>
-      <c r="P17">
-        <v>1.92</v>
-      </c>
-      <c r="Q17">
-        <v>1.8</v>
-      </c>
-      <c r="R17">
-        <v>1.34</v>
-      </c>
-      <c r="S17">
-        <v>3.1</v>
-      </c>
-      <c r="T17">
-        <v>1.69</v>
-      </c>
-      <c r="U17">
-        <v>2.04</v>
-      </c>
-      <c r="V17">
-        <v>1.34</v>
-      </c>
-      <c r="W17">
-        <v>1.75</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>90</v>
-      </c>
-      <c r="AB17">
-        <v>970</v>
-      </c>
-      <c r="AC17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>22</v>
-      </c>
-      <c r="AH17">
+      <c r="AZ19">
+        <v>1.28</v>
+      </c>
+      <c r="BA19">
+        <v>1.38</v>
+      </c>
+      <c r="BB19">
         <v>19</v>
       </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
+      <c r="BC19">
         <v>1.38</v>
       </c>
-      <c r="AQ17">
+      <c r="BD19">
         <v>1.38</v>
       </c>
-      <c r="AR17">
-        <v>18</v>
-      </c>
-      <c r="AS17">
-        <v>1.36</v>
-      </c>
-      <c r="AT17">
-        <v>1.28</v>
-      </c>
-      <c r="AU17">
-        <v>1.19</v>
-      </c>
-      <c r="AV17">
+      <c r="BE19">
         <v>1.38</v>
       </c>
-      <c r="AW17">
+      <c r="BF19">
         <v>1.38</v>
       </c>
-      <c r="AX17">
+      <c r="BG19">
         <v>1.38</v>
       </c>
-      <c r="AY17">
-        <v>1.3</v>
-      </c>
-      <c r="AZ17">
-        <v>1.28</v>
-      </c>
-      <c r="BA17">
-        <v>1.38</v>
-      </c>
-      <c r="BB17">
-        <v>19</v>
-      </c>
-      <c r="BC17">
-        <v>1.38</v>
-      </c>
-      <c r="BD17">
-        <v>1.38</v>
-      </c>
-      <c r="BE17">
-        <v>1.38</v>
-      </c>
-      <c r="BF17">
-        <v>1.38</v>
-      </c>
-      <c r="BG17">
-        <v>1.38</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
         <v>2.8</v>
       </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.01</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
-      <c r="BO17">
-        <v>1.01</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>1.01</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.01</v>
-      </c>
-      <c r="BT17">
-        <v>1000</v>
-      </c>
-      <c r="BU17">
-        <v>1.01</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.01</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.01</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>1.01</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>136</v>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
   <si>
     <t>League</t>
   </si>
@@ -283,6 +283,9 @@
     <t>CONCACAF Nations League B</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
@@ -352,12 +355,12 @@
     <t>FK Napredak</t>
   </si>
   <si>
+    <t>FK Backa Topola</t>
+  </si>
+  <si>
     <t>Sanliurfaspor</t>
   </si>
   <si>
-    <t>FK Backa Topola</t>
-  </si>
-  <si>
     <t>Moss</t>
   </si>
   <si>
@@ -373,13 +376,16 @@
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
     <t>Martinique</t>
   </si>
   <si>
-    <t>Velez Sarsfield</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
+    <t>Bogota</t>
   </si>
   <si>
     <t>Nacional (Uru)</t>
@@ -406,12 +412,12 @@
     <t>FK Loznica</t>
   </si>
   <si>
+    <t>FK Graficar</t>
+  </si>
+  <si>
     <t>Belediye Derincespor</t>
   </si>
   <si>
-    <t>FK Graficar</t>
-  </si>
-  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
@@ -427,19 +433,22 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>CA Platense</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
     <t>El Salvador</t>
   </si>
   <si>
-    <t>CA Platense</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
+    <t>Envigado</t>
   </si>
   <si>
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 06:06:38</t>
+    <t>2026-10-04 08:18:31</t>
   </si>
 </sst>
 </file>
@@ -771,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1021,31 +1030,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>3.2</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
         <v>4.1</v>
@@ -1063,13 +1072,13 @@
         <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
         <v>1.77</v>
       </c>
       <c r="R2">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S2">
         <v>2.96</v>
@@ -1081,10 +1090,10 @@
         <v>2.36</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X2">
         <v>19</v>
@@ -1096,7 +1105,7 @@
         <v>24</v>
       </c>
       <c r="AA2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB2">
         <v>12.5</v>
@@ -1105,7 +1114,7 @@
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
         <v>32</v>
@@ -1162,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1177,16 +1186,16 @@
         <v>32</v>
       </c>
       <c r="BB2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1195,7 +1204,7 @@
         <v>17</v>
       </c>
       <c r="BH2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI2">
         <v>3.05</v>
@@ -1204,58 +1213,58 @@
         <v>9</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
         <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
         <v>24</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>21</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1263,19 +1272,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G3">
         <v>4.7</v>
@@ -1299,13 +1308,13 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
         <v>2.96</v>
@@ -1317,10 +1326,10 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
         <v>1.86</v>
@@ -1359,7 +1368,7 @@
         <v>21</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI3">
         <v>75</v>
@@ -1377,7 +1386,7 @@
         <v>310</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO3">
         <v>32</v>
@@ -1410,19 +1419,19 @@
         <v>27</v>
       </c>
       <c r="AY3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BB3">
         <v>40</v>
       </c>
       <c r="BC3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BD3">
         <v>42</v>
@@ -1434,7 +1443,7 @@
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH3">
         <v>2.56</v>
@@ -1497,7 +1506,7 @@
         <v>12</v>
       </c>
       <c r="CB3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1505,100 +1514,100 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
         <v>2</v>
       </c>
       <c r="V4">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA4">
         <v>32</v>
       </c>
       <c r="AB4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
         <v>32</v>
       </c>
       <c r="AF4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG4">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1607,7 +1616,7 @@
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK4">
         <v>60</v>
@@ -1622,7 +1631,7 @@
         <v>65</v>
       </c>
       <c r="AO4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1637,13 +1646,13 @@
         <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>5.9</v>
@@ -1667,22 +1676,22 @@
         <v>6.2</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG4">
         <v>19.5</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
@@ -1694,25 +1703,25 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BN4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO4">
         <v>6</v>
       </c>
       <c r="BP4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BT4">
         <v>5</v>
@@ -1724,22 +1733,22 @@
         <v>20</v>
       </c>
       <c r="BW4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BX4">
+        <v>34</v>
+      </c>
+      <c r="BY4">
+        <v>6.2</v>
+      </c>
+      <c r="BZ4">
         <v>40</v>
       </c>
-      <c r="BY4">
-        <v>5.9</v>
-      </c>
-      <c r="BZ4">
-        <v>34</v>
-      </c>
       <c r="CA4">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1747,16 +1756,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F5">
         <v>4.9</v>
@@ -1765,13 +1774,13 @@
         <v>5.3</v>
       </c>
       <c r="H5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>4.6</v>
@@ -1792,31 +1801,31 @@
         <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W5">
         <v>1.23</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
         <v>11.5</v>
@@ -1828,7 +1837,7 @@
         <v>21</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
@@ -1837,10 +1846,10 @@
         <v>17.5</v>
       </c>
       <c r="AF5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH5">
         <v>19.5</v>
@@ -1855,13 +1864,13 @@
         <v>85</v>
       </c>
       <c r="AL5">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AO5">
         <v>9.800000000000001</v>
@@ -1870,7 +1879,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR5">
         <v>9.800000000000001</v>
@@ -1879,16 +1888,16 @@
         <v>14.5</v>
       </c>
       <c r="AT5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
         <v>9</v>
       </c>
       <c r="AW5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX5">
         <v>32</v>
@@ -1903,22 +1912,22 @@
         <v>8</v>
       </c>
       <c r="BB5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC5">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC5">
+      <c r="BD5">
+        <v>25</v>
+      </c>
+      <c r="BE5">
+        <v>38</v>
+      </c>
+      <c r="BF5">
         <v>9</v>
       </c>
-      <c r="BD5">
-        <v>22</v>
-      </c>
-      <c r="BE5">
-        <v>32</v>
-      </c>
-      <c r="BF5">
-        <v>8.6</v>
-      </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>4.1</v>
@@ -1981,7 +1990,7 @@
         <v>6.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1989,70 +1998,70 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="G6">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
         <v>950</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
         <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S6">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
         <v>1.21</v>
       </c>
       <c r="W6">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2223,7 +2232,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2231,16 +2240,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>1.04</v>
@@ -2465,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2473,169 +2482,169 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="G8">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="H8">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="J8">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O8">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P8">
+        <v>1.65</v>
+      </c>
+      <c r="Q8">
+        <v>2.16</v>
+      </c>
+      <c r="R8">
+        <v>1.24</v>
+      </c>
+      <c r="S8">
+        <v>3.05</v>
+      </c>
+      <c r="T8">
+        <v>1.87</v>
+      </c>
+      <c r="U8">
+        <v>1.91</v>
+      </c>
+      <c r="V8">
+        <v>1.37</v>
+      </c>
+      <c r="W8">
         <v>1.58</v>
       </c>
-      <c r="Q8">
-        <v>2.02</v>
-      </c>
-      <c r="R8">
-        <v>1.09</v>
-      </c>
-      <c r="S8">
-        <v>2.82</v>
-      </c>
-      <c r="T8">
-        <v>1.01</v>
-      </c>
-      <c r="U8">
-        <v>1.01</v>
-      </c>
-      <c r="V8">
-        <v>1.32</v>
-      </c>
-      <c r="W8">
-        <v>1.51</v>
-      </c>
       <c r="X8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
         <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
         <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
         <v>1.03</v>
@@ -2707,39 +2716,39 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>1.38</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2751,22 +2760,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="P9">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R9">
-        <v>1.06</v>
+        <v>1.59</v>
       </c>
       <c r="S9">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2778,7 +2787,7 @@
         <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2949,39 +2958,39 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>1.41</v>
+        <v>110</v>
       </c>
       <c r="H10">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -2993,22 +3002,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.46</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
-        <v>2.46</v>
+        <v>1.1</v>
       </c>
       <c r="Q10">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="R10">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="S10">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3020,7 +3029,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3191,7 +3200,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3199,34 +3208,34 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G11">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I11">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="J11">
         <v>4.3</v>
       </c>
       <c r="K11">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3262,7 +3271,7 @@
         <v>2.06</v>
       </c>
       <c r="W11">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3433,7 +3442,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3441,22 +3450,22 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="G12">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
         <v>4.1</v>
@@ -3465,154 +3474,154 @@
         <v>4.4</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K12">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <v>1.38</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R12">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="X12">
         <v>18.5</v>
       </c>
       <c r="Y12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z12">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC12">
         <v>12</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AE12">
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AG12">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
+        <v>29</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
         <v>75</v>
       </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>90</v>
-      </c>
       <c r="AK12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM12">
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS12">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="AT12">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU12">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
         <v>12.5</v>
       </c>
       <c r="AW12">
-        <v>15</v>
+        <v>2.6</v>
       </c>
       <c r="AX12">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12">
         <v>8.4</v>
       </c>
       <c r="AZ12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA12">
-        <v>16</v>
+        <v>2.6</v>
       </c>
       <c r="BB12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC12">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD12">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE12">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="BF12">
         <v>8.6</v>
       </c>
       <c r="BG12">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3675,7 +3684,7 @@
         <v>1.17</v>
       </c>
       <c r="CB12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3683,70 +3692,70 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="G13">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H13">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="I13">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P13">
+        <v>2.4</v>
+      </c>
+      <c r="Q13">
+        <v>1.56</v>
+      </c>
+      <c r="R13">
+        <v>1.58</v>
+      </c>
+      <c r="S13">
+        <v>2.4</v>
+      </c>
+      <c r="T13">
+        <v>1.65</v>
+      </c>
+      <c r="U13">
+        <v>2.22</v>
+      </c>
+      <c r="V13">
         <v>2.28</v>
       </c>
-      <c r="Q13">
-        <v>1.57</v>
-      </c>
-      <c r="R13">
-        <v>1.57</v>
-      </c>
-      <c r="S13">
-        <v>2.34</v>
-      </c>
-      <c r="T13">
-        <v>1.69</v>
-      </c>
-      <c r="U13">
-        <v>2.2</v>
-      </c>
-      <c r="V13">
-        <v>2.58</v>
-      </c>
       <c r="W13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X13">
         <v>28</v>
@@ -3755,16 +3764,16 @@
         <v>13</v>
       </c>
       <c r="Z13">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD13">
         <v>11</v>
@@ -3773,97 +3782,97 @@
         <v>16.5</v>
       </c>
       <c r="AF13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG13">
         <v>24</v>
       </c>
       <c r="AH13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI13">
         <v>34</v>
       </c>
       <c r="AJ13">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AK13">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL13">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM13">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN13">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO13">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AP13">
+        <v>4.8</v>
+      </c>
+      <c r="AQ13">
+        <v>4</v>
+      </c>
+      <c r="AR13">
+        <v>4</v>
+      </c>
+      <c r="AS13">
+        <v>4.4</v>
+      </c>
+      <c r="AT13">
+        <v>4.7</v>
+      </c>
+      <c r="AU13">
+        <v>4.1</v>
+      </c>
+      <c r="AV13">
+        <v>3.8</v>
+      </c>
+      <c r="AW13">
+        <v>4.3</v>
+      </c>
+      <c r="AX13">
+        <v>5.2</v>
+      </c>
+      <c r="AY13">
+        <v>4.7</v>
+      </c>
+      <c r="AZ13">
+        <v>4.7</v>
+      </c>
+      <c r="BA13">
+        <v>5</v>
+      </c>
+      <c r="BB13">
+        <v>5.6</v>
+      </c>
+      <c r="BC13">
+        <v>5.4</v>
+      </c>
+      <c r="BD13">
+        <v>5.4</v>
+      </c>
+      <c r="BE13">
+        <v>5.5</v>
+      </c>
+      <c r="BF13">
+        <v>5.3</v>
+      </c>
+      <c r="BG13">
         <v>3.5</v>
       </c>
-      <c r="AQ13">
-        <v>3.05</v>
-      </c>
-      <c r="AR13">
-        <v>2.96</v>
-      </c>
-      <c r="AS13">
-        <v>3.3</v>
-      </c>
-      <c r="AT13">
-        <v>3.5</v>
-      </c>
-      <c r="AU13">
-        <v>3.95</v>
-      </c>
-      <c r="AV13">
-        <v>2.92</v>
-      </c>
-      <c r="AW13">
-        <v>3.2</v>
-      </c>
-      <c r="AX13">
-        <v>3.75</v>
-      </c>
-      <c r="AY13">
-        <v>3.4</v>
-      </c>
-      <c r="AZ13">
-        <v>3.4</v>
-      </c>
-      <c r="BA13">
-        <v>3.55</v>
-      </c>
-      <c r="BB13">
+      <c r="BH13">
+        <v>4.5</v>
+      </c>
+      <c r="BI13">
         <v>3.9</v>
       </c>
-      <c r="BC13">
-        <v>3.8</v>
-      </c>
-      <c r="BD13">
-        <v>3.8</v>
-      </c>
-      <c r="BE13">
-        <v>3.85</v>
-      </c>
-      <c r="BF13">
-        <v>3.8</v>
-      </c>
-      <c r="BG13">
-        <v>2.64</v>
-      </c>
-      <c r="BH13">
-        <v>4.6</v>
-      </c>
-      <c r="BI13">
-        <v>3.4</v>
-      </c>
       <c r="BJ13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK13">
         <v>7.2</v>
@@ -3875,49 +3884,49 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
+        <v>9.4</v>
+      </c>
+      <c r="BO13">
+        <v>7.6</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>4.7</v>
+      </c>
+      <c r="BU13">
+        <v>3.9</v>
+      </c>
+      <c r="BV13">
         <v>10.5</v>
       </c>
-      <c r="BO13">
-        <v>7.2</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.01</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>4.6</v>
-      </c>
-      <c r="BU13">
-        <v>3.45</v>
-      </c>
-      <c r="BV13">
-        <v>10</v>
-      </c>
       <c r="BW13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
         <v>22</v>
       </c>
       <c r="BY13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3925,16 +3934,16 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F14">
         <v>1.92</v>
@@ -3961,7 +3970,7 @@
         <v>1.12</v>
       </c>
       <c r="N14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
         <v>1.58</v>
@@ -4000,7 +4009,7 @@
         <v>48</v>
       </c>
       <c r="AA14">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB14">
         <v>6.2</v>
@@ -4012,7 +4021,7 @@
         <v>23</v>
       </c>
       <c r="AE14">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF14">
         <v>10.5</v>
@@ -4066,7 +4075,7 @@
         <v>20</v>
       </c>
       <c r="AW14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4087,16 +4096,16 @@
         <v>13.5</v>
       </c>
       <c r="BD14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH14">
         <v>2.64</v>
@@ -4159,7 +4168,7 @@
         <v>10.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4167,43 +4176,43 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F15">
         <v>1.89</v>
       </c>
       <c r="G15">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>4.4</v>
       </c>
       <c r="I15">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
         <v>1.36</v>
@@ -4221,429 +4230,429 @@
         <v>3.7</v>
       </c>
       <c r="T15">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U15">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V15">
         <v>1.25</v>
       </c>
       <c r="W15">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB15">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF15">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
+        <v>21</v>
+      </c>
+      <c r="AI15">
+        <v>80</v>
+      </c>
+      <c r="AJ15">
         <v>24</v>
       </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP15">
-        <v>1.29</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15">
+        <v>13</v>
+      </c>
+      <c r="AR15">
+        <v>7.4</v>
+      </c>
+      <c r="AS15">
+        <v>8.6</v>
+      </c>
+      <c r="AT15">
+        <v>7.4</v>
+      </c>
+      <c r="AU15">
+        <v>7.2</v>
+      </c>
+      <c r="AV15">
+        <v>15.5</v>
+      </c>
+      <c r="AW15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX15">
+        <v>10</v>
+      </c>
+      <c r="AY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>17</v>
+      </c>
+      <c r="BA15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB15">
+        <v>17</v>
+      </c>
+      <c r="BC15">
+        <v>16.5</v>
+      </c>
+      <c r="BD15">
+        <v>7.6</v>
+      </c>
+      <c r="BE15">
+        <v>8.6</v>
+      </c>
+      <c r="BF15">
+        <v>12.5</v>
+      </c>
+      <c r="BG15">
         <v>8.4</v>
       </c>
-      <c r="AR15">
-        <v>1.29</v>
-      </c>
-      <c r="AS15">
-        <v>1.29</v>
-      </c>
-      <c r="AT15">
-        <v>1.18</v>
-      </c>
-      <c r="AU15">
-        <v>1.17</v>
-      </c>
-      <c r="AV15">
-        <v>1.29</v>
-      </c>
-      <c r="AW15">
-        <v>1.29</v>
-      </c>
-      <c r="AX15">
-        <v>1.23</v>
-      </c>
-      <c r="AY15">
-        <v>6.8</v>
-      </c>
-      <c r="AZ15">
-        <v>1.29</v>
-      </c>
-      <c r="BA15">
-        <v>1.29</v>
-      </c>
-      <c r="BB15">
-        <v>1.29</v>
-      </c>
-      <c r="BC15">
-        <v>1.29</v>
-      </c>
-      <c r="BD15">
-        <v>1.29</v>
-      </c>
-      <c r="BE15">
-        <v>1.29</v>
-      </c>
-      <c r="BF15">
-        <v>8</v>
-      </c>
-      <c r="BG15">
-        <v>1.29</v>
-      </c>
       <c r="BH15">
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="CB15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="G16">
-        <v>2.94</v>
+        <v>2.02</v>
       </c>
       <c r="H16">
-        <v>2.52</v>
+        <v>5.2</v>
       </c>
       <c r="I16">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>3.25</v>
+      </c>
+      <c r="L16">
+        <v>1.59</v>
+      </c>
+      <c r="M16">
+        <v>1.15</v>
+      </c>
+      <c r="N16">
+        <v>2.36</v>
+      </c>
+      <c r="O16">
+        <v>1.68</v>
+      </c>
+      <c r="P16">
+        <v>1.45</v>
+      </c>
+      <c r="Q16">
+        <v>3.05</v>
+      </c>
+      <c r="R16">
+        <v>1.16</v>
+      </c>
+      <c r="S16">
+        <v>6.8</v>
+      </c>
+      <c r="T16">
+        <v>2.62</v>
+      </c>
+      <c r="U16">
+        <v>1.59</v>
+      </c>
+      <c r="V16">
+        <v>1.22</v>
+      </c>
+      <c r="W16">
+        <v>1.98</v>
+      </c>
+      <c r="X16">
+        <v>7.4</v>
+      </c>
+      <c r="Y16">
+        <v>11.5</v>
+      </c>
+      <c r="Z16">
+        <v>38</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>5.6</v>
+      </c>
+      <c r="AC16">
+        <v>8</v>
+      </c>
+      <c r="AD16">
+        <v>26</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG16">
+        <v>12.5</v>
+      </c>
+      <c r="AH16">
+        <v>34</v>
+      </c>
+      <c r="AI16">
+        <v>980</v>
+      </c>
+      <c r="AJ16">
+        <v>25</v>
+      </c>
+      <c r="AK16">
+        <v>36</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>390</v>
+      </c>
+      <c r="AN16">
+        <v>32</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>6.8</v>
+      </c>
+      <c r="AQ16">
+        <v>10</v>
+      </c>
+      <c r="AR16">
+        <v>22</v>
+      </c>
+      <c r="AS16">
+        <v>44</v>
+      </c>
+      <c r="AT16">
+        <v>5.3</v>
+      </c>
+      <c r="AU16">
+        <v>7.2</v>
+      </c>
+      <c r="AV16">
+        <v>21</v>
+      </c>
+      <c r="AW16">
+        <v>65</v>
+      </c>
+      <c r="AX16">
+        <v>9</v>
+      </c>
+      <c r="AY16">
+        <v>11</v>
+      </c>
+      <c r="AZ16">
+        <v>25</v>
+      </c>
+      <c r="BA16">
+        <v>46</v>
+      </c>
+      <c r="BB16">
+        <v>21</v>
+      </c>
+      <c r="BC16">
+        <v>21</v>
+      </c>
+      <c r="BD16">
+        <v>55</v>
+      </c>
+      <c r="BE16">
+        <v>95</v>
+      </c>
+      <c r="BF16">
+        <v>19.5</v>
+      </c>
+      <c r="BG16">
+        <v>100</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>2.2</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>2.78</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.33</v>
+      </c>
+      <c r="BN16">
+        <v>5.9</v>
+      </c>
+      <c r="BO16">
         <v>3.3</v>
       </c>
-      <c r="K16">
-        <v>4.3</v>
-      </c>
-      <c r="L16">
-        <v>1.2</v>
-      </c>
-      <c r="M16">
-        <v>1.03</v>
-      </c>
-      <c r="N16">
-        <v>5</v>
-      </c>
-      <c r="O16">
-        <v>1.19</v>
-      </c>
-      <c r="P16">
-        <v>2.42</v>
-      </c>
-      <c r="Q16">
-        <v>1.56</v>
-      </c>
-      <c r="R16">
-        <v>1.59</v>
-      </c>
-      <c r="S16">
-        <v>2.36</v>
-      </c>
-      <c r="T16">
-        <v>1.51</v>
-      </c>
-      <c r="U16">
-        <v>2.56</v>
-      </c>
-      <c r="V16">
-        <v>1.51</v>
-      </c>
-      <c r="W16">
-        <v>1.52</v>
-      </c>
-      <c r="X16">
-        <v>27</v>
-      </c>
-      <c r="Y16">
-        <v>17</v>
-      </c>
-      <c r="Z16">
-        <v>22</v>
-      </c>
-      <c r="AA16">
-        <v>40</v>
-      </c>
-      <c r="AB16">
-        <v>17</v>
-      </c>
-      <c r="AC16">
-        <v>10.5</v>
-      </c>
-      <c r="AD16">
-        <v>13.5</v>
-      </c>
-      <c r="AE16">
-        <v>27</v>
-      </c>
-      <c r="AF16">
-        <v>22</v>
-      </c>
-      <c r="AG16">
-        <v>13.5</v>
-      </c>
-      <c r="AH16">
-        <v>15.5</v>
-      </c>
-      <c r="AI16">
-        <v>32</v>
-      </c>
-      <c r="AJ16">
-        <v>40</v>
-      </c>
-      <c r="AK16">
-        <v>26</v>
-      </c>
-      <c r="AL16">
-        <v>32</v>
-      </c>
-      <c r="AM16">
-        <v>70</v>
-      </c>
-      <c r="AN16">
-        <v>15.5</v>
-      </c>
-      <c r="AO16">
-        <v>15.5</v>
-      </c>
-      <c r="AP16">
-        <v>6.6</v>
-      </c>
-      <c r="AQ16">
-        <v>5.8</v>
-      </c>
-      <c r="AR16">
-        <v>6.2</v>
-      </c>
-      <c r="AS16">
-        <v>7.2</v>
-      </c>
-      <c r="AT16">
-        <v>5.8</v>
-      </c>
-      <c r="AU16">
-        <v>4.8</v>
-      </c>
-      <c r="AV16">
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>2.78</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.33</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
         <v>5.3</v>
       </c>
-      <c r="AW16">
-        <v>6.6</v>
-      </c>
-      <c r="AX16">
-        <v>6.2</v>
-      </c>
-      <c r="AY16">
-        <v>5.3</v>
-      </c>
-      <c r="AZ16">
-        <v>5.6</v>
-      </c>
-      <c r="BA16">
-        <v>6.8</v>
-      </c>
-      <c r="BB16">
-        <v>7.2</v>
-      </c>
-      <c r="BC16">
-        <v>6.6</v>
-      </c>
-      <c r="BD16">
-        <v>6.8</v>
-      </c>
-      <c r="BE16">
-        <v>7.8</v>
-      </c>
-      <c r="BF16">
-        <v>5.6</v>
-      </c>
-      <c r="BG16">
-        <v>5.6</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.01</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.01</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.01</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.01</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.01</v>
-      </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="CB16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4651,483 +4660,483 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="G17">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="H17">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I17">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J17">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="L17">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="M17">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="P17">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="Q17">
-        <v>2.82</v>
+        <v>2.14</v>
       </c>
       <c r="R17">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S17">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="T17">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="V17">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W17">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="X17">
+        <v>11.5</v>
+      </c>
+      <c r="Y17">
+        <v>16.5</v>
+      </c>
+      <c r="Z17">
+        <v>50</v>
+      </c>
+      <c r="AA17">
+        <v>230</v>
+      </c>
+      <c r="AB17">
+        <v>7</v>
+      </c>
+      <c r="AC17">
+        <v>8.4</v>
+      </c>
+      <c r="AD17">
+        <v>25</v>
+      </c>
+      <c r="AE17">
+        <v>130</v>
+      </c>
+      <c r="AF17">
+        <v>10</v>
+      </c>
+      <c r="AG17">
+        <v>11</v>
+      </c>
+      <c r="AH17">
+        <v>29</v>
+      </c>
+      <c r="AI17">
+        <v>140</v>
+      </c>
+      <c r="AJ17">
+        <v>19</v>
+      </c>
+      <c r="AK17">
+        <v>23</v>
+      </c>
+      <c r="AL17">
+        <v>60</v>
+      </c>
+      <c r="AM17">
+        <v>220</v>
+      </c>
+      <c r="AN17">
+        <v>15.5</v>
+      </c>
+      <c r="AO17">
+        <v>200</v>
+      </c>
+      <c r="AP17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ17">
+        <v>14</v>
+      </c>
+      <c r="AR17">
+        <v>30</v>
+      </c>
+      <c r="AS17">
+        <v>10</v>
+      </c>
+      <c r="AT17">
+        <v>6.2</v>
+      </c>
+      <c r="AU17">
         <v>7.6</v>
       </c>
-      <c r="Y17">
-        <v>12</v>
-      </c>
-      <c r="Z17">
-        <v>40</v>
-      </c>
-      <c r="AA17">
-        <v>220</v>
-      </c>
-      <c r="AB17">
-        <v>5.6</v>
-      </c>
-      <c r="AC17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD17">
-        <v>26</v>
-      </c>
-      <c r="AE17">
-        <v>150</v>
-      </c>
-      <c r="AF17">
+      <c r="AV17">
+        <v>20</v>
+      </c>
+      <c r="AW17">
+        <v>9.6</v>
+      </c>
+      <c r="AX17">
+        <v>8.4</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>20</v>
+      </c>
+      <c r="BA17">
+        <v>9.6</v>
+      </c>
+      <c r="BB17">
+        <v>15.5</v>
+      </c>
+      <c r="BC17">
+        <v>18</v>
+      </c>
+      <c r="BD17">
+        <v>38</v>
+      </c>
+      <c r="BE17">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG17">
-        <v>12.5</v>
-      </c>
-      <c r="AH17">
-        <v>34</v>
-      </c>
-      <c r="AI17">
-        <v>190</v>
-      </c>
-      <c r="AJ17">
-        <v>26</v>
-      </c>
-      <c r="AK17">
-        <v>36</v>
-      </c>
-      <c r="AL17">
-        <v>90</v>
-      </c>
-      <c r="AM17">
-        <v>390</v>
-      </c>
-      <c r="AN17">
-        <v>32</v>
-      </c>
-      <c r="AO17">
-        <v>290</v>
-      </c>
-      <c r="AP17">
-        <v>6.8</v>
-      </c>
-      <c r="AQ17">
-        <v>10</v>
-      </c>
-      <c r="AR17">
+      <c r="BF17">
+        <v>13</v>
+      </c>
+      <c r="BG17">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS17">
-        <v>12</v>
-      </c>
-      <c r="AT17">
-        <v>5.2</v>
-      </c>
-      <c r="AU17">
-        <v>7</v>
-      </c>
-      <c r="AV17">
-        <v>21</v>
-      </c>
-      <c r="AW17">
-        <v>11.5</v>
-      </c>
-      <c r="AX17">
-        <v>9</v>
-      </c>
-      <c r="AY17">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA17">
-        <v>12</v>
-      </c>
-      <c r="BB17">
-        <v>21</v>
-      </c>
-      <c r="BC17">
-        <v>9.4</v>
-      </c>
-      <c r="BD17">
-        <v>11</v>
-      </c>
-      <c r="BE17">
-        <v>12.5</v>
-      </c>
-      <c r="BF17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG17">
-        <v>12</v>
-      </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI17">
-        <v>2.12</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="BN17">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="CB17" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18">
+        <v>2.38</v>
+      </c>
+      <c r="G18">
+        <v>3.1</v>
+      </c>
+      <c r="H18">
+        <v>2.22</v>
+      </c>
+      <c r="I18">
+        <v>3.5</v>
+      </c>
+      <c r="J18">
+        <v>2.56</v>
+      </c>
+      <c r="K18">
+        <v>950</v>
+      </c>
+      <c r="L18">
+        <v>1.2</v>
+      </c>
+      <c r="M18">
+        <v>1.04</v>
+      </c>
+      <c r="N18">
+        <v>4.9</v>
+      </c>
+      <c r="O18">
+        <v>1.22</v>
+      </c>
+      <c r="P18">
+        <v>1.89</v>
+      </c>
+      <c r="Q18">
+        <v>1.64</v>
+      </c>
+      <c r="R18">
+        <v>1.35</v>
+      </c>
+      <c r="S18">
+        <v>2.66</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.45</v>
+      </c>
+      <c r="W18">
+        <v>1.47</v>
+      </c>
+      <c r="X18">
+        <v>95</v>
+      </c>
+      <c r="Y18">
+        <v>80</v>
+      </c>
+      <c r="Z18">
         <v>90</v>
       </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>139</v>
-      </c>
-      <c r="F18">
-        <v>1.72</v>
-      </c>
-      <c r="G18">
-        <v>1.81</v>
-      </c>
-      <c r="H18">
-        <v>5.6</v>
-      </c>
-      <c r="I18">
-        <v>6.2</v>
-      </c>
-      <c r="J18">
-        <v>3.5</v>
-      </c>
-      <c r="K18">
-        <v>3.9</v>
-      </c>
-      <c r="L18">
-        <v>1.43</v>
-      </c>
-      <c r="M18">
-        <v>1.06</v>
-      </c>
-      <c r="N18">
-        <v>3.05</v>
-      </c>
-      <c r="O18">
-        <v>1.42</v>
-      </c>
-      <c r="P18">
-        <v>1.66</v>
-      </c>
-      <c r="Q18">
-        <v>2.16</v>
-      </c>
-      <c r="R18">
-        <v>1.26</v>
-      </c>
-      <c r="S18">
-        <v>4.2</v>
-      </c>
-      <c r="T18">
-        <v>2</v>
-      </c>
-      <c r="U18">
-        <v>1.76</v>
-      </c>
-      <c r="V18">
-        <v>1.19</v>
-      </c>
-      <c r="W18">
-        <v>2.22</v>
-      </c>
-      <c r="X18">
-        <v>11.5</v>
-      </c>
-      <c r="Y18">
-        <v>16.5</v>
-      </c>
-      <c r="Z18">
-        <v>50</v>
-      </c>
       <c r="AA18">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="AC18">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="AD18">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AE18">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="AG18">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AH18">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="AI18">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AQ18">
-        <v>14</v>
+        <v>3.4</v>
       </c>
       <c r="AR18">
-        <v>30</v>
+        <v>1.12</v>
       </c>
       <c r="AS18">
-        <v>9.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="AT18">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AU18">
-        <v>7.6</v>
+        <v>1.11</v>
       </c>
       <c r="AV18">
-        <v>20</v>
+        <v>3.15</v>
       </c>
       <c r="AW18">
-        <v>9.4</v>
+        <v>1.13</v>
       </c>
       <c r="AX18">
-        <v>8.4</v>
+        <v>1.12</v>
       </c>
       <c r="AY18">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="AZ18">
-        <v>20</v>
+        <v>3.75</v>
       </c>
       <c r="BA18">
-        <v>9.4</v>
+        <v>1.13</v>
       </c>
       <c r="BB18">
-        <v>15.5</v>
+        <v>1.13</v>
       </c>
       <c r="BC18">
-        <v>18</v>
+        <v>1.13</v>
       </c>
       <c r="BD18">
-        <v>38</v>
+        <v>1.13</v>
       </c>
       <c r="BE18">
-        <v>9.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="BF18">
-        <v>13</v>
+        <v>1.13</v>
       </c>
       <c r="BG18">
-        <v>9.6</v>
+        <v>1.13</v>
       </c>
       <c r="BH18">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5135,241 +5144,483 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
         <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F19">
+        <v>2.66</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <v>2.36</v>
+      </c>
+      <c r="I19">
+        <v>3.4</v>
+      </c>
+      <c r="J19">
+        <v>2.6</v>
+      </c>
+      <c r="K19">
+        <v>950</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20">
         <v>2.16</v>
       </c>
-      <c r="G19">
-        <v>2.38</v>
-      </c>
-      <c r="H19">
-        <v>3.3</v>
-      </c>
-      <c r="I19">
+      <c r="G20">
+        <v>2.42</v>
+      </c>
+      <c r="H20">
+        <v>3.05</v>
+      </c>
+      <c r="I20">
         <v>3.75</v>
       </c>
-      <c r="J19">
-        <v>3.65</v>
-      </c>
-      <c r="K19">
-        <v>3.9</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
+      <c r="J20">
+        <v>3.45</v>
+      </c>
+      <c r="K20">
+        <v>4.1</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
         <v>1.04</v>
       </c>
-      <c r="N19">
-        <v>3.55</v>
-      </c>
-      <c r="O19">
+      <c r="N20">
+        <v>3.75</v>
+      </c>
+      <c r="O20">
         <v>1.29</v>
       </c>
-      <c r="P19">
+      <c r="P20">
         <v>1.92</v>
       </c>
-      <c r="Q19">
-        <v>1.8</v>
-      </c>
-      <c r="R19">
+      <c r="Q20">
+        <v>1.83</v>
+      </c>
+      <c r="R20">
         <v>1.34</v>
       </c>
-      <c r="S19">
+      <c r="S20">
         <v>3.1</v>
       </c>
-      <c r="T19">
+      <c r="T20">
+        <v>1.74</v>
+      </c>
+      <c r="U20">
+        <v>2.04</v>
+      </c>
+      <c r="V20">
+        <v>1.37</v>
+      </c>
+      <c r="W20">
+        <v>1.71</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>90</v>
+      </c>
+      <c r="AB20">
+        <v>11.5</v>
+      </c>
+      <c r="AC20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>710</v>
+      </c>
+      <c r="AH20">
+        <v>19</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>17.5</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.68</v>
+      </c>
+      <c r="AQ20">
+        <v>9.6</v>
+      </c>
+      <c r="AR20">
+        <v>18</v>
+      </c>
+      <c r="AS20">
+        <v>1.66</v>
+      </c>
+      <c r="AT20">
+        <v>7.6</v>
+      </c>
+      <c r="AU20">
+        <v>7.4</v>
+      </c>
+      <c r="AV20">
+        <v>1.68</v>
+      </c>
+      <c r="AW20">
+        <v>1.68</v>
+      </c>
+      <c r="AX20">
         <v>1.69</v>
       </c>
-      <c r="U19">
-        <v>2.04</v>
-      </c>
-      <c r="V19">
-        <v>1.36</v>
-      </c>
-      <c r="W19">
-        <v>1.73</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>90</v>
-      </c>
-      <c r="AB19">
-        <v>970</v>
-      </c>
-      <c r="AC19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>22</v>
-      </c>
-      <c r="AH19">
+      <c r="AY20">
+        <v>1.57</v>
+      </c>
+      <c r="AZ20">
+        <v>1.55</v>
+      </c>
+      <c r="BA20">
+        <v>1.68</v>
+      </c>
+      <c r="BB20">
         <v>19</v>
       </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.38</v>
-      </c>
-      <c r="AQ19">
-        <v>1.38</v>
-      </c>
-      <c r="AR19">
-        <v>18</v>
-      </c>
-      <c r="AS19">
-        <v>1.36</v>
-      </c>
-      <c r="AT19">
-        <v>1.28</v>
-      </c>
-      <c r="AU19">
-        <v>7</v>
-      </c>
-      <c r="AV19">
-        <v>1.38</v>
-      </c>
-      <c r="AW19">
-        <v>1.38</v>
-      </c>
-      <c r="AX19">
-        <v>1.38</v>
-      </c>
-      <c r="AY19">
-        <v>1.3</v>
-      </c>
-      <c r="AZ19">
-        <v>1.28</v>
-      </c>
-      <c r="BA19">
-        <v>1.38</v>
-      </c>
-      <c r="BB19">
-        <v>19</v>
-      </c>
-      <c r="BC19">
-        <v>1.38</v>
-      </c>
-      <c r="BD19">
-        <v>1.38</v>
-      </c>
-      <c r="BE19">
-        <v>1.38</v>
-      </c>
-      <c r="BF19">
-        <v>1.38</v>
-      </c>
-      <c r="BG19">
-        <v>1.38</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
+      <c r="BC20">
+        <v>1.68</v>
+      </c>
+      <c r="BD20">
+        <v>1.68</v>
+      </c>
+      <c r="BE20">
+        <v>1.68</v>
+      </c>
+      <c r="BF20">
+        <v>1.54</v>
+      </c>
+      <c r="BG20">
+        <v>1.68</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
         <v>2.8</v>
       </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.01</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.01</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.01</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.01</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
-      <c r="BU19">
-        <v>1.01</v>
-      </c>
-      <c r="BV19">
-        <v>1000</v>
-      </c>
-      <c r="BW19">
-        <v>1.01</v>
-      </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
-        <v>1.01</v>
-      </c>
-      <c r="BZ19">
-        <v>1000</v>
-      </c>
-      <c r="CA19">
-        <v>1.01</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>141</v>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.17</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.17</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.35</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.17</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.17</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.17</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.17</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.17</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.17</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -448,7 +448,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 08:18:31</t>
+    <t>2026-10-04 10:31:07</t>
   </si>
 </sst>
 </file>
@@ -1042,16 +1042,16 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="I2">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="J2">
         <v>3.8</v>
@@ -1066,22 +1066,22 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T2">
         <v>1.65</v>
@@ -1090,40 +1090,40 @@
         <v>2.36</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
         <v>19</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC2">
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>16.5</v>
@@ -1132,7 +1132,7 @@
         <v>48</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK2">
         <v>28</v>
@@ -1141,13 +1141,13 @@
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AN2">
         <v>18</v>
       </c>
       <c r="AO2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP2">
         <v>16.5</v>
@@ -1156,10 +1156,10 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1168,46 +1168,46 @@
         <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AX2">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BE2">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2">
         <v>9</v>
@@ -1219,37 +1219,37 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1261,7 +1261,7 @@
         <v>21</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>144</v>
@@ -1326,10 +1326,10 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
         <v>1.86</v>
@@ -1383,7 +1383,7 @@
         <v>130</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AN3">
         <v>150</v>
@@ -1398,7 +1398,7 @@
         <v>6</v>
       </c>
       <c r="AR3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3">
         <v>24</v>
@@ -1425,7 +1425,7 @@
         <v>26</v>
       </c>
       <c r="BA3">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BB3">
         <v>40</v>
@@ -1461,7 +1461,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
         <v>7.8</v>
@@ -1470,7 +1470,7 @@
         <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BQ3">
         <v>12</v>
@@ -1526,16 +1526,16 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H4">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J4">
         <v>3.25</v>
@@ -1544,13 +1544,13 @@
         <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
         <v>1.41</v>
@@ -1568,31 +1568,31 @@
         <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
         <v>1.73</v>
       </c>
       <c r="W4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>9.4</v>
       </c>
       <c r="Z4">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
         <v>32</v>
       </c>
       <c r="AB4">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1604,10 +1604,10 @@
         <v>32</v>
       </c>
       <c r="AF4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1616,25 +1616,25 @@
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL4">
         <v>70</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO4">
         <v>28</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>7.8</v>
@@ -1643,49 +1643,49 @@
         <v>12</v>
       </c>
       <c r="AS4">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="AT4">
         <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="AX4">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="AY4">
         <v>13.5</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BC4">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>85</v>
       </c>
       <c r="BF4">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BG4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH4">
         <v>3.4</v>
@@ -1703,7 +1703,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN4">
         <v>7.6</v>
@@ -1715,13 +1715,13 @@
         <v>36</v>
       </c>
       <c r="BQ4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT4">
         <v>5</v>
@@ -1733,16 +1733,16 @@
         <v>20</v>
       </c>
       <c r="BW4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX4">
+        <v>40</v>
+      </c>
+      <c r="BY4">
+        <v>6.4</v>
+      </c>
+      <c r="BZ4">
         <v>34</v>
-      </c>
-      <c r="BY4">
-        <v>6.2</v>
-      </c>
-      <c r="BZ4">
-        <v>40</v>
       </c>
       <c r="CA4">
         <v>6.4</v>
@@ -1768,7 +1768,7 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5.3</v>
@@ -1780,7 +1780,7 @@
         <v>1.75</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
         <v>4.6</v>
@@ -1801,10 +1801,10 @@
         <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
         <v>2.94</v>
@@ -1864,13 +1864,13 @@
         <v>85</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO5">
         <v>9.800000000000001</v>
@@ -1909,22 +1909,22 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BB5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BD5">
         <v>25</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
         <v>8.199999999999999</v>
@@ -1933,7 +1933,7 @@
         <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>4.7</v>
       </c>
       <c r="BU5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV5">
         <v>11.5</v>
@@ -2019,10 +2019,10 @@
         <v>3.05</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2034,10 +2034,10 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P6">
         <v>1.65</v>
@@ -2046,10 +2046,10 @@
         <v>2.04</v>
       </c>
       <c r="R6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="T6">
         <v>1.76</v>
@@ -2058,7 +2058,7 @@
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
         <v>1.86</v>
@@ -2500,7 +2500,7 @@
         <v>2.72</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
         <v>3.65</v>
@@ -2518,22 +2518,22 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
         <v>1.65</v>
       </c>
       <c r="Q8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
         <v>1.24</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="T8">
         <v>1.87</v>
@@ -2736,22 +2736,22 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="G9">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="H9">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2760,22 +2760,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="O9">
         <v>1.16</v>
       </c>
       <c r="P9">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
         <v>1.4</v>
       </c>
       <c r="R9">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="S9">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2787,7 +2787,7 @@
         <v>1.02</v>
       </c>
       <c r="W9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2981,7 +2981,7 @@
         <v>1.1</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H10">
         <v>1.1</v>
@@ -2990,7 +2990,7 @@
         <v>110</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3014,7 +3014,7 @@
         <v>1.02</v>
       </c>
       <c r="R10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="S10">
         <v>1.03</v>
@@ -3226,7 +3226,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I11">
         <v>1.87</v>
@@ -3268,10 +3268,10 @@
         <v>3.35</v>
       </c>
       <c r="V11">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3462,10 +3462,10 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H12">
         <v>4.1</v>
@@ -3477,7 +3477,7 @@
         <v>3.55</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.38</v>
@@ -3489,40 +3489,40 @@
         <v>4</v>
       </c>
       <c r="O12">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T12">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X12">
         <v>18.5</v>
       </c>
       <c r="Y12">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Z12">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3534,7 +3534,7 @@
         <v>12</v>
       </c>
       <c r="AD12">
-        <v>18.5</v>
+        <v>44</v>
       </c>
       <c r="AE12">
         <v>1000</v>
@@ -3543,7 +3543,7 @@
         <v>13</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH12">
         <v>29</v>
@@ -3552,25 +3552,25 @@
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK12">
         <v>80</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM12">
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
@@ -3579,19 +3579,19 @@
         <v>6.6</v>
       </c>
       <c r="AS12">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AT12">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AU12">
         <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW12">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AX12">
         <v>9.199999999999999</v>
@@ -3603,25 +3603,25 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BB12">
         <v>6.2</v>
       </c>
       <c r="BC12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE12">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BF12">
         <v>8.6</v>
       </c>
       <c r="BG12">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3719,7 +3719,7 @@
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
         <v>1.28</v>
@@ -3961,16 +3961,16 @@
         <v>3.2</v>
       </c>
       <c r="K14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L14">
         <v>1.61</v>
       </c>
       <c r="M14">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O14">
         <v>1.58</v>
@@ -3979,7 +3979,7 @@
         <v>1.52</v>
       </c>
       <c r="Q14">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R14">
         <v>1.18</v>
@@ -4060,7 +4060,7 @@
         <v>11</v>
       </c>
       <c r="AR14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS14">
         <v>10.5</v>
@@ -4093,7 +4093,7 @@
         <v>21</v>
       </c>
       <c r="BC14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD14">
         <v>10</v>
@@ -4197,7 +4197,7 @@
         <v>4.4</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4392,7 +4392,7 @@
         <v>5.3</v>
       </c>
       <c r="BV15">
-        <v>940</v>
+        <v>830</v>
       </c>
       <c r="BW15">
         <v>1.83</v>
@@ -4439,13 +4439,13 @@
         <v>5.2</v>
       </c>
       <c r="I16">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J16">
         <v>3.2</v>
       </c>
       <c r="K16">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L16">
         <v>1.59</v>
@@ -4454,10 +4454,10 @@
         <v>1.15</v>
       </c>
       <c r="N16">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P16">
         <v>1.45</v>
@@ -4466,13 +4466,13 @@
         <v>3.05</v>
       </c>
       <c r="R16">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S16">
         <v>6.8</v>
       </c>
       <c r="T16">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="U16">
         <v>1.59</v>
@@ -4484,10 +4484,10 @@
         <v>1.98</v>
       </c>
       <c r="X16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z16">
         <v>38</v>
@@ -4496,7 +4496,7 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -4508,7 +4508,7 @@
         <v>1000</v>
       </c>
       <c r="AF16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG16">
         <v>12.5</v>
@@ -4517,7 +4517,7 @@
         <v>34</v>
       </c>
       <c r="AI16">
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="AJ16">
         <v>25</v>
@@ -4541,7 +4541,7 @@
         <v>6.8</v>
       </c>
       <c r="AQ16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
         <v>22</v>
@@ -4568,7 +4568,7 @@
         <v>11</v>
       </c>
       <c r="AZ16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA16">
         <v>46</v>
@@ -4577,16 +4577,16 @@
         <v>21</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD16">
         <v>55</v>
       </c>
       <c r="BE16">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG16">
         <v>100</v>
@@ -4672,10 +4672,10 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G17">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H17">
         <v>5.6</v>
@@ -4684,7 +4684,7 @@
         <v>6.2</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
         <v>3.85</v>
@@ -4693,7 +4693,7 @@
         <v>1.43</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N17">
         <v>3.05</v>
@@ -4705,16 +4705,16 @@
         <v>1.71</v>
       </c>
       <c r="Q17">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
         <v>1.26</v>
       </c>
       <c r="S17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
         <v>1.8</v>
@@ -4723,7 +4723,7 @@
         <v>1.19</v>
       </c>
       <c r="W17">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X17">
         <v>11.5</v>
@@ -4914,22 +4914,22 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G18">
         <v>3.1</v>
       </c>
       <c r="H18">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I18">
         <v>3.5</v>
       </c>
       <c r="J18">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="L18">
         <v>1.2</v>
@@ -4941,7 +4941,7 @@
         <v>4.9</v>
       </c>
       <c r="O18">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P18">
         <v>1.89</v>
@@ -4962,7 +4962,7 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
         <v>1.47</v>
@@ -5022,10 +5022,10 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AQ18">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AR18">
         <v>1.12</v>
@@ -5159,16 +5159,16 @@
         <v>2.66</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H19">
         <v>2.36</v>
       </c>
       <c r="I19">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="J19">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5410,22 +5410,22 @@
         <v>3.75</v>
       </c>
       <c r="J20">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20">
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P20">
         <v>1.92</v>
@@ -5440,7 +5440,7 @@
         <v>3.1</v>
       </c>
       <c r="T20">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U20">
         <v>2.04</v>
@@ -5452,10 +5452,10 @@
         <v>1.71</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="Z20">
         <v>1000</v>
@@ -5464,22 +5464,22 @@
         <v>90</v>
       </c>
       <c r="AB20">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC20">
         <v>9.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE20">
         <v>1000</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AG20">
-        <v>710</v>
+        <v>550</v>
       </c>
       <c r="AH20">
         <v>19</v>
@@ -5500,64 +5500,64 @@
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AO20">
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.68</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20">
-        <v>9.6</v>
+        <v>1.85</v>
       </c>
       <c r="AR20">
         <v>18</v>
       </c>
       <c r="AS20">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AT20">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU20">
         <v>7.4</v>
       </c>
       <c r="AV20">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AW20">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AX20">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AY20">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AZ20">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BA20">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="BB20">
         <v>19</v>
       </c>
       <c r="BC20">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BD20">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BE20">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BF20">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="BG20">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BH20">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="156">
   <si>
     <t>League</t>
   </si>
@@ -271,12 +271,18 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>Turkish 2 Lig</t>
   </si>
   <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
+    <t>Argentinian Primera B Metropolitana</t>
+  </si>
+  <si>
     <t>Spanish Segunda Division</t>
   </si>
   <si>
@@ -310,12 +316,18 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>18:30:00</t>
   </si>
   <si>
@@ -331,6 +343,9 @@
     <t>22:00:00</t>
   </si>
   <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -355,6 +370,9 @@
     <t>FK Napredak</t>
   </si>
   <si>
+    <t>Tatran Lip Mikulas</t>
+  </si>
+  <si>
     <t>FK Backa Topola</t>
   </si>
   <si>
@@ -364,6 +382,9 @@
     <t>Moss</t>
   </si>
   <si>
+    <t>Uai Urquiza</t>
+  </si>
+  <si>
     <t>Cordoba</t>
   </si>
   <si>
@@ -388,6 +409,9 @@
     <t>Bogota</t>
   </si>
   <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
     <t>Nacional (Uru)</t>
   </si>
   <si>
@@ -412,6 +436,9 @@
     <t>FK Loznica</t>
   </si>
   <si>
+    <t>Samorin</t>
+  </si>
+  <si>
     <t>FK Graficar</t>
   </si>
   <si>
@@ -421,6 +448,9 @@
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>CA Ituzaingo</t>
+  </si>
+  <si>
     <t>Tenerife</t>
   </si>
   <si>
@@ -445,10 +475,13 @@
     <t>Envigado</t>
   </si>
   <si>
+    <t>Club 2 de Mayo</t>
+  </si>
+  <si>
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 10:31:07</t>
+    <t>2026-10-04 12:43:03</t>
   </si>
 </sst>
 </file>
@@ -780,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1030,85 +1063,85 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F2">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H2">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="I2">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q2">
         <v>1.76</v>
       </c>
       <c r="R2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC2">
         <v>9.4</v>
@@ -1117,7 +1150,7 @@
         <v>13</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF2">
         <v>19</v>
@@ -1126,10 +1159,10 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AJ2">
         <v>38</v>
@@ -1144,22 +1177,22 @@
         <v>90</v>
       </c>
       <c r="AN2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
@@ -1180,64 +1213,64 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC2">
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN2">
         <v>5.7</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
@@ -1246,25 +1279,25 @@
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1272,16 +1305,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F3">
         <v>4.4</v>
@@ -1305,7 +1338,7 @@
         <v>1.64</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
         <v>2.54</v>
@@ -1329,7 +1362,7 @@
         <v>2.38</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
         <v>1.86</v>
@@ -1347,7 +1380,7 @@
         <v>11</v>
       </c>
       <c r="AA3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB3">
         <v>11</v>
@@ -1383,7 +1416,7 @@
         <v>130</v>
       </c>
       <c r="AM3">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AN3">
         <v>150</v>
@@ -1425,7 +1458,7 @@
         <v>26</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>40</v>
@@ -1506,7 +1539,7 @@
         <v>12</v>
       </c>
       <c r="CB3" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1514,28 +1547,28 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F4">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="G4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="I4">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="J4">
         <v>3.25</v>
@@ -1574,127 +1607,127 @@
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="W4">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X4">
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AF4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
+        <v>21</v>
+      </c>
+      <c r="AX4">
         <v>23</v>
       </c>
-      <c r="AX4">
-        <v>21</v>
-      </c>
       <c r="AY4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4">
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BB4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD4">
+        <v>48</v>
+      </c>
+      <c r="BE4">
+        <v>90</v>
+      </c>
+      <c r="BF4">
         <v>44</v>
       </c>
-      <c r="BE4">
-        <v>85</v>
-      </c>
-      <c r="BF4">
-        <v>38</v>
-      </c>
       <c r="BG4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH4">
         <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
         <v>8</v>
@@ -1703,52 +1736,52 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO4">
         <v>6</v>
       </c>
       <c r="BP4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS4">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BT4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU4">
         <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BW4">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BY4">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1756,94 +1789,94 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H5">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="I5">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="T5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V5">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="W5">
         <v>1.23</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5">
         <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF5">
         <v>40</v>
@@ -1864,16 +1897,16 @@
         <v>85</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5">
         <v>80</v>
       </c>
       <c r="AO5">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AP5">
         <v>17.5</v>
@@ -1882,22 +1915,22 @@
         <v>9</v>
       </c>
       <c r="AR5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS5">
         <v>14.5</v>
       </c>
       <c r="AT5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV5">
         <v>9</v>
       </c>
       <c r="AW5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX5">
         <v>32</v>
@@ -1909,61 +1942,61 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BB5">
+        <v>70</v>
+      </c>
+      <c r="BC5">
+        <v>42</v>
+      </c>
+      <c r="BD5">
+        <v>40</v>
+      </c>
+      <c r="BE5">
+        <v>60</v>
+      </c>
+      <c r="BF5">
+        <v>34</v>
+      </c>
+      <c r="BG5">
+        <v>7.2</v>
+      </c>
+      <c r="BH5">
+        <v>4.3</v>
+      </c>
+      <c r="BI5">
+        <v>3.4</v>
+      </c>
+      <c r="BJ5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK5">
+        <v>5.3</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>10</v>
-      </c>
-      <c r="BC5">
-        <v>9.6</v>
-      </c>
-      <c r="BD5">
-        <v>25</v>
-      </c>
-      <c r="BE5">
-        <v>42</v>
-      </c>
-      <c r="BF5">
-        <v>9.4</v>
-      </c>
-      <c r="BG5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH5">
-        <v>4.1</v>
-      </c>
-      <c r="BI5">
-        <v>3.25</v>
-      </c>
-      <c r="BJ5">
-        <v>10</v>
-      </c>
-      <c r="BK5">
-        <v>5.2</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
         <v>9</v>
       </c>
       <c r="BO5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP5">
         <v>42</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT5">
         <v>4.7</v>
@@ -1972,25 +2005,25 @@
         <v>3.65</v>
       </c>
       <c r="BV5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA5">
         <v>6.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1998,16 +2031,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F6">
         <v>1.83</v>
@@ -2022,7 +2055,7 @@
         <v>5.3</v>
       </c>
       <c r="J6">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2118,52 +2151,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2175,64 +2208,64 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2240,34 +2273,34 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F7">
         <v>1.04</v>
       </c>
       <c r="G7">
-        <v>680</v>
+        <v>2.2</v>
       </c>
       <c r="H7">
         <v>1.08</v>
       </c>
       <c r="I7">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="J7">
         <v>1.01</v>
       </c>
       <c r="K7">
-        <v>680</v>
+        <v>1000</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2324,7 +2357,7 @@
         <v>1000</v>
       </c>
       <c r="AD7">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
         <v>18</v>
@@ -2333,7 +2366,7 @@
         <v>1000</v>
       </c>
       <c r="AG7">
-        <v>830</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
         <v>990</v>
@@ -2360,31 +2393,31 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AQ7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AS7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AU7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AV7">
         <v>2.44</v>
       </c>
       <c r="AW7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AY7">
         <v>3</v>
@@ -2393,22 +2426,22 @@
         <v>2.02</v>
       </c>
       <c r="BA7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BB7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BC7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BD7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BE7">
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG7">
         <v>3.95</v>
@@ -2474,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2482,16 +2515,16 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F8">
         <v>2.36</v>
@@ -2518,13 +2551,13 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="O8">
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q8">
         <v>2.18</v>
@@ -2533,7 +2566,7 @@
         <v>1.24</v>
       </c>
       <c r="S8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T8">
         <v>1.87</v>
@@ -2602,156 +2635,156 @@
         <v>60</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F9">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="G9">
-        <v>1.41</v>
+        <v>2.54</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>2.92</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J9">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2760,34 +2793,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="O9">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="R9">
         <v>1.51</v>
       </c>
       <c r="S9">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>3.4</v>
+        <v>1.64</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2958,42 +2991,42 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>1.41</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>5.2</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3002,34 +3035,34 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R10">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="S10">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3200,7 +3233,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3208,34 +3241,34 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F11">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="H11">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="I11">
-        <v>1.87</v>
+        <v>110</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3244,34 +3277,34 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="P11">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q11">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>1.08</v>
       </c>
       <c r="S11">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="T11">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="W11">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3292,7 +3325,7 @@
         <v>1000</v>
       </c>
       <c r="AD11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
         <v>1000</v>
@@ -3304,7 +3337,7 @@
         <v>1000</v>
       </c>
       <c r="AH11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
         <v>1000</v>
@@ -3325,61 +3358,61 @@
         <v>1000</v>
       </c>
       <c r="AO11">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.32</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3442,7 +3475,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3450,241 +3483,241 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F12">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="G12">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="I12">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="J12">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
+        <v>5.8</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
         <v>4.2</v>
       </c>
-      <c r="L12">
-        <v>1.38</v>
-      </c>
-      <c r="M12">
-        <v>1.06</v>
-      </c>
-      <c r="N12">
-        <v>4</v>
-      </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="P12">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>3.1</v>
+        <v>1.54</v>
       </c>
       <c r="T12">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="U12">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>2.14</v>
       </c>
       <c r="W12">
-        <v>1.96</v>
+        <v>1.26</v>
       </c>
       <c r="X12">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>34</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>48</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>970</v>
+      </c>
+      <c r="AP12">
+        <v>1.32</v>
+      </c>
+      <c r="AQ12">
+        <v>1.32</v>
+      </c>
+      <c r="AR12">
+        <v>1.32</v>
+      </c>
+      <c r="AS12">
+        <v>1.32</v>
+      </c>
+      <c r="AT12">
+        <v>1.32</v>
+      </c>
+      <c r="AU12">
+        <v>8.4</v>
+      </c>
+      <c r="AV12">
+        <v>1.27</v>
+      </c>
+      <c r="AW12">
+        <v>1.32</v>
+      </c>
+      <c r="AX12">
+        <v>1.32</v>
+      </c>
+      <c r="AY12">
+        <v>1.32</v>
+      </c>
+      <c r="AZ12">
+        <v>8</v>
+      </c>
+      <c r="BA12">
         <v>9.6</v>
       </c>
-      <c r="AC12">
-        <v>12</v>
-      </c>
-      <c r="AD12">
-        <v>44</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>13</v>
-      </c>
-      <c r="AG12">
-        <v>15.5</v>
-      </c>
-      <c r="AH12">
-        <v>29</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>80</v>
-      </c>
-      <c r="AK12">
-        <v>80</v>
-      </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>14.5</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>11.5</v>
-      </c>
-      <c r="AQ12">
-        <v>11.5</v>
-      </c>
-      <c r="AR12">
-        <v>6.6</v>
-      </c>
-      <c r="AS12">
-        <v>2.78</v>
-      </c>
-      <c r="AT12">
-        <v>7</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>12</v>
-      </c>
-      <c r="AW12">
-        <v>2.78</v>
-      </c>
-      <c r="AX12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY12">
+      <c r="BB12">
+        <v>1.32</v>
+      </c>
+      <c r="BC12">
+        <v>1.32</v>
+      </c>
+      <c r="BD12">
+        <v>1.32</v>
+      </c>
+      <c r="BE12">
+        <v>1.32</v>
+      </c>
+      <c r="BF12">
         <v>8.4</v>
       </c>
-      <c r="AZ12">
-        <v>14</v>
-      </c>
-      <c r="BA12">
-        <v>2.78</v>
-      </c>
-      <c r="BB12">
-        <v>6.2</v>
-      </c>
-      <c r="BC12">
-        <v>14.5</v>
-      </c>
-      <c r="BD12">
-        <v>7.6</v>
-      </c>
-      <c r="BE12">
-        <v>2.78</v>
-      </c>
-      <c r="BF12">
-        <v>8.6</v>
-      </c>
       <c r="BG12">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3692,190 +3725,190 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F13">
-        <v>4.5</v>
+        <v>1.59</v>
       </c>
       <c r="G13">
+        <v>1.85</v>
+      </c>
+      <c r="H13">
         <v>5.5</v>
       </c>
-      <c r="H13">
-        <v>1.63</v>
-      </c>
       <c r="I13">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="O13">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q13">
-        <v>1.56</v>
+        <v>2.32</v>
       </c>
       <c r="R13">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="T13">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="W13">
-        <v>1.22</v>
+        <v>2.16</v>
       </c>
       <c r="X13">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="BJ13">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3884,10 +3917,10 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
         <v>1000</v>
@@ -3902,515 +3935,515 @@
         <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F14">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="M14">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="P14">
-        <v>1.52</v>
+        <v>1.99</v>
       </c>
       <c r="Q14">
-        <v>2.78</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S14">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="U14">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X14">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y14">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z14">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA14">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB14">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AD14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE14">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF14">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG14">
+        <v>13.5</v>
+      </c>
+      <c r="AH14">
+        <v>28</v>
+      </c>
+      <c r="AI14">
+        <v>130</v>
+      </c>
+      <c r="AJ14">
+        <v>29</v>
+      </c>
+      <c r="AK14">
+        <v>32</v>
+      </c>
+      <c r="AL14">
+        <v>44</v>
+      </c>
+      <c r="AM14">
+        <v>220</v>
+      </c>
+      <c r="AN14">
+        <v>970</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
         <v>11.5</v>
       </c>
-      <c r="AH14">
-        <v>36</v>
-      </c>
-      <c r="AI14">
-        <v>160</v>
-      </c>
-      <c r="AJ14">
-        <v>25</v>
-      </c>
-      <c r="AK14">
-        <v>29</v>
-      </c>
-      <c r="AL14">
-        <v>80</v>
-      </c>
-      <c r="AM14">
-        <v>310</v>
-      </c>
-      <c r="AN14">
-        <v>32</v>
-      </c>
-      <c r="AO14">
-        <v>240</v>
-      </c>
-      <c r="AP14">
-        <v>7.4</v>
-      </c>
       <c r="AQ14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS14">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="AT14">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AU14">
         <v>6.8</v>
       </c>
       <c r="AV14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AW14">
-        <v>10.5</v>
+        <v>3.1</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14">
+        <v>15</v>
+      </c>
+      <c r="BA14">
+        <v>3.15</v>
+      </c>
+      <c r="BB14">
+        <v>9.6</v>
+      </c>
+      <c r="BC14">
         <v>14.5</v>
       </c>
-      <c r="BA14">
-        <v>10.5</v>
-      </c>
-      <c r="BB14">
-        <v>21</v>
-      </c>
-      <c r="BC14">
+      <c r="BD14">
         <v>13</v>
       </c>
-      <c r="BD14">
-        <v>10</v>
-      </c>
       <c r="BE14">
-        <v>11</v>
+        <v>3.15</v>
       </c>
       <c r="BF14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG14">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="BH14">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="BJ14">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>12.5</v>
+        <v>1.17</v>
       </c>
       <c r="BN14">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.95</v>
+        <v>1.69</v>
       </c>
       <c r="BP14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="BR14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>10.5</v>
+        <v>1.17</v>
       </c>
       <c r="BT14">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>7.6</v>
+        <v>1.99</v>
       </c>
       <c r="BV14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>11</v>
+        <v>1.17</v>
       </c>
       <c r="BX14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>11.5</v>
+        <v>1.17</v>
       </c>
       <c r="BZ14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>10.5</v>
+        <v>1.17</v>
       </c>
       <c r="CB14" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F15">
-        <v>1.89</v>
+        <v>3.8</v>
       </c>
       <c r="G15">
+        <v>4.6</v>
+      </c>
+      <c r="H15">
+        <v>1.78</v>
+      </c>
+      <c r="I15">
+        <v>1.99</v>
+      </c>
+      <c r="J15">
+        <v>4.2</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <v>1.28</v>
+      </c>
+      <c r="M15">
+        <v>1.02</v>
+      </c>
+      <c r="N15">
+        <v>4.6</v>
+      </c>
+      <c r="O15">
+        <v>1.21</v>
+      </c>
+      <c r="P15">
+        <v>2.3</v>
+      </c>
+      <c r="Q15">
+        <v>1.58</v>
+      </c>
+      <c r="R15">
+        <v>1.52</v>
+      </c>
+      <c r="S15">
+        <v>2.54</v>
+      </c>
+      <c r="T15">
+        <v>1.61</v>
+      </c>
+      <c r="U15">
+        <v>2.28</v>
+      </c>
+      <c r="V15">
         <v>2</v>
       </c>
-      <c r="H15">
-        <v>4.4</v>
-      </c>
-      <c r="I15">
-        <v>4.9</v>
-      </c>
-      <c r="J15">
-        <v>3.55</v>
-      </c>
-      <c r="K15">
-        <v>3.8</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.08</v>
-      </c>
-      <c r="N15">
-        <v>3.5</v>
-      </c>
-      <c r="O15">
-        <v>1.36</v>
-      </c>
-      <c r="P15">
-        <v>1.84</v>
-      </c>
-      <c r="Q15">
-        <v>2.02</v>
-      </c>
-      <c r="R15">
-        <v>1.32</v>
-      </c>
-      <c r="S15">
-        <v>3.7</v>
-      </c>
-      <c r="T15">
-        <v>1.88</v>
-      </c>
-      <c r="U15">
-        <v>2</v>
-      </c>
-      <c r="V15">
-        <v>1.25</v>
-      </c>
       <c r="W15">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="X15">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="Y15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z15">
+        <v>14.5</v>
+      </c>
+      <c r="AA15">
+        <v>25</v>
+      </c>
+      <c r="AB15">
+        <v>21</v>
+      </c>
+      <c r="AC15">
+        <v>11.5</v>
+      </c>
+      <c r="AD15">
+        <v>11.5</v>
+      </c>
+      <c r="AE15">
+        <v>21</v>
+      </c>
+      <c r="AF15">
         <v>40</v>
       </c>
-      <c r="AA15">
-        <v>130</v>
-      </c>
-      <c r="AB15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC15">
-        <v>8.4</v>
-      </c>
-      <c r="AD15">
-        <v>19.5</v>
-      </c>
-      <c r="AE15">
-        <v>75</v>
-      </c>
-      <c r="AF15">
-        <v>12</v>
-      </c>
       <c r="AG15">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AH15">
         <v>21</v>
       </c>
       <c r="AI15">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AJ15">
+        <v>85</v>
+      </c>
+      <c r="AK15">
+        <v>55</v>
+      </c>
+      <c r="AL15">
+        <v>48</v>
+      </c>
+      <c r="AM15">
+        <v>85</v>
+      </c>
+      <c r="AN15">
+        <v>44</v>
+      </c>
+      <c r="AO15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP15">
+        <v>18</v>
+      </c>
+      <c r="AQ15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR15">
+        <v>11.5</v>
+      </c>
+      <c r="AS15">
+        <v>5.2</v>
+      </c>
+      <c r="AT15">
+        <v>15.5</v>
+      </c>
+      <c r="AU15">
+        <v>8.4</v>
+      </c>
+      <c r="AV15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15">
+        <v>14.5</v>
+      </c>
+      <c r="AX15">
+        <v>5.7</v>
+      </c>
+      <c r="AY15">
+        <v>13.5</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
+        <v>5.5</v>
+      </c>
+      <c r="BB15">
+        <v>5.9</v>
+      </c>
+      <c r="BC15">
+        <v>5.9</v>
+      </c>
+      <c r="BD15">
+        <v>5.8</v>
+      </c>
+      <c r="BE15">
+        <v>5.8</v>
+      </c>
+      <c r="BF15">
+        <v>5.7</v>
+      </c>
+      <c r="BG15">
+        <v>7.4</v>
+      </c>
+      <c r="BH15">
+        <v>4.3</v>
+      </c>
+      <c r="BI15">
+        <v>3.6</v>
+      </c>
+      <c r="BJ15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK15">
+        <v>7.2</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO15">
+        <v>6.2</v>
+      </c>
+      <c r="BP15">
+        <v>32</v>
+      </c>
+      <c r="BQ15">
         <v>24</v>
       </c>
-      <c r="AK15">
-        <v>23</v>
-      </c>
-      <c r="AL15">
-        <v>46</v>
-      </c>
-      <c r="AM15">
-        <v>140</v>
-      </c>
-      <c r="AN15">
-        <v>15.5</v>
-      </c>
-      <c r="AO15">
-        <v>90</v>
-      </c>
-      <c r="AP15">
-        <v>11.5</v>
-      </c>
-      <c r="AQ15">
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>24</v>
+      </c>
+      <c r="BT15">
+        <v>5.1</v>
+      </c>
+      <c r="BU15">
+        <v>3.9</v>
+      </c>
+      <c r="BV15">
         <v>13</v>
       </c>
-      <c r="AR15">
-        <v>7.4</v>
-      </c>
-      <c r="AS15">
-        <v>8.6</v>
-      </c>
-      <c r="AT15">
-        <v>7.4</v>
-      </c>
-      <c r="AU15">
-        <v>7.2</v>
-      </c>
-      <c r="AV15">
-        <v>15.5</v>
-      </c>
-      <c r="AW15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX15">
-        <v>10</v>
-      </c>
-      <c r="AY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>17</v>
-      </c>
-      <c r="BA15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB15">
-        <v>17</v>
-      </c>
-      <c r="BC15">
-        <v>16.5</v>
-      </c>
-      <c r="BD15">
-        <v>7.6</v>
-      </c>
-      <c r="BE15">
-        <v>8.6</v>
-      </c>
-      <c r="BF15">
-        <v>12.5</v>
-      </c>
-      <c r="BG15">
-        <v>8.4</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.88</v>
-      </c>
-      <c r="BJ15">
+      <c r="BW15">
+        <v>9</v>
+      </c>
+      <c r="BX15">
+        <v>24</v>
+      </c>
+      <c r="BY15">
         <v>14.5</v>
       </c>
-      <c r="BK15">
-        <v>1.66</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.88</v>
-      </c>
-      <c r="BN15">
-        <v>6</v>
-      </c>
-      <c r="BO15">
-        <v>3.2</v>
-      </c>
-      <c r="BP15">
-        <v>19</v>
-      </c>
-      <c r="BQ15">
-        <v>1.71</v>
-      </c>
-      <c r="BR15">
-        <v>40</v>
-      </c>
-      <c r="BS15">
-        <v>1.79</v>
-      </c>
-      <c r="BT15">
-        <v>10.5</v>
-      </c>
-      <c r="BU15">
-        <v>5.3</v>
-      </c>
-      <c r="BV15">
-        <v>830</v>
-      </c>
-      <c r="BW15">
-        <v>1.83</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.84</v>
-      </c>
       <c r="BZ15">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="CA15">
-        <v>1.79</v>
+        <v>12</v>
       </c>
       <c r="CB15" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4418,25 +4451,25 @@
         <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F16">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G16">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I16">
         <v>5.5</v>
@@ -4448,1179 +4481,1905 @@
         <v>3.35</v>
       </c>
       <c r="L16">
+        <v>1.61</v>
+      </c>
+      <c r="M16">
+        <v>1.13</v>
+      </c>
+      <c r="N16">
+        <v>2.52</v>
+      </c>
+      <c r="O16">
         <v>1.59</v>
       </c>
-      <c r="M16">
-        <v>1.15</v>
-      </c>
-      <c r="N16">
-        <v>2.42</v>
-      </c>
-      <c r="O16">
-        <v>1.67</v>
-      </c>
       <c r="P16">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Q16">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="R16">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="U16">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="V16">
         <v>1.22</v>
       </c>
       <c r="W16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X16">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z16">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB16">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI16">
-        <v>940</v>
+        <v>160</v>
       </c>
       <c r="AJ16">
         <v>25</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM16">
-        <v>390</v>
+        <v>310</v>
       </c>
       <c r="AN16">
         <v>32</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP16">
+        <v>7.6</v>
+      </c>
+      <c r="AQ16">
+        <v>11</v>
+      </c>
+      <c r="AR16">
+        <v>18.5</v>
+      </c>
+      <c r="AS16">
+        <v>10.5</v>
+      </c>
+      <c r="AT16">
+        <v>5.6</v>
+      </c>
+      <c r="AU16">
         <v>6.8</v>
       </c>
-      <c r="AQ16">
+      <c r="AV16">
+        <v>20</v>
+      </c>
+      <c r="AW16">
         <v>10.5</v>
       </c>
-      <c r="AR16">
-        <v>22</v>
-      </c>
-      <c r="AS16">
-        <v>44</v>
-      </c>
-      <c r="AT16">
-        <v>5.3</v>
-      </c>
-      <c r="AU16">
-        <v>7.2</v>
-      </c>
-      <c r="AV16">
-        <v>21</v>
-      </c>
-      <c r="AW16">
-        <v>65</v>
-      </c>
       <c r="AX16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BB16">
         <v>21</v>
       </c>
       <c r="BC16">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
+        <v>10</v>
+      </c>
+      <c r="BE16">
+        <v>11</v>
+      </c>
+      <c r="BF16">
+        <v>8.4</v>
+      </c>
+      <c r="BG16">
+        <v>11</v>
+      </c>
+      <c r="BH16">
+        <v>2.64</v>
+      </c>
+      <c r="BI16">
+        <v>2.46</v>
+      </c>
+      <c r="BJ16">
+        <v>12.5</v>
+      </c>
+      <c r="BK16">
+        <v>6.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>12.5</v>
+      </c>
+      <c r="BN16">
+        <v>4.3</v>
+      </c>
+      <c r="BO16">
+        <v>3.95</v>
+      </c>
+      <c r="BP16">
+        <v>18.5</v>
+      </c>
+      <c r="BQ16">
+        <v>7.6</v>
+      </c>
+      <c r="BR16">
         <v>55</v>
       </c>
-      <c r="BE16">
+      <c r="BS16">
+        <v>10.5</v>
+      </c>
+      <c r="BT16">
+        <v>8.6</v>
+      </c>
+      <c r="BU16">
+        <v>7.6</v>
+      </c>
+      <c r="BV16">
+        <v>75</v>
+      </c>
+      <c r="BW16">
+        <v>11</v>
+      </c>
+      <c r="BX16">
         <v>100</v>
       </c>
-      <c r="BF16">
-        <v>19</v>
-      </c>
-      <c r="BG16">
-        <v>100</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>2.2</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>2.78</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.33</v>
-      </c>
-      <c r="BN16">
-        <v>5.9</v>
-      </c>
-      <c r="BO16">
-        <v>3.3</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>2.78</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.33</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>5.3</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.33</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
       <c r="BY16">
-        <v>1.33</v>
+        <v>11.5</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA16">
-        <v>1.33</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F17">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="G17">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O17">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P17">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R17">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S17">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T17">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="U17">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="X17">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z17">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA17">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17">
         <v>8.4</v>
       </c>
       <c r="AD17">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AE17">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG17">
         <v>11</v>
       </c>
       <c r="AH17">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AI17">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AJ17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AK17">
         <v>23</v>
       </c>
       <c r="AL17">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM17">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="AN17">
         <v>15.5</v>
       </c>
       <c r="AO17">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AP17">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR17">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AS17">
+        <v>8.6</v>
+      </c>
+      <c r="AT17">
+        <v>7.4</v>
+      </c>
+      <c r="AU17">
+        <v>7.2</v>
+      </c>
+      <c r="AV17">
+        <v>15.5</v>
+      </c>
+      <c r="AW17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX17">
         <v>10</v>
-      </c>
-      <c r="AT17">
-        <v>6.2</v>
-      </c>
-      <c r="AU17">
-        <v>7.6</v>
-      </c>
-      <c r="AV17">
-        <v>20</v>
-      </c>
-      <c r="AW17">
-        <v>9.6</v>
-      </c>
-      <c r="AX17">
-        <v>8.4</v>
       </c>
       <c r="AY17">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA17">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB17">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC17">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD17">
+        <v>7.6</v>
+      </c>
+      <c r="BE17">
+        <v>8.6</v>
+      </c>
+      <c r="BF17">
+        <v>12.5</v>
+      </c>
+      <c r="BG17">
+        <v>8.4</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.88</v>
+      </c>
+      <c r="BJ17">
+        <v>14.5</v>
+      </c>
+      <c r="BK17">
+        <v>1.66</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.88</v>
+      </c>
+      <c r="BN17">
+        <v>6</v>
+      </c>
+      <c r="BO17">
+        <v>3.2</v>
+      </c>
+      <c r="BP17">
+        <v>19</v>
+      </c>
+      <c r="BQ17">
+        <v>1.71</v>
+      </c>
+      <c r="BR17">
+        <v>40</v>
+      </c>
+      <c r="BS17">
+        <v>1.79</v>
+      </c>
+      <c r="BT17">
+        <v>10.5</v>
+      </c>
+      <c r="BU17">
+        <v>5.3</v>
+      </c>
+      <c r="BV17">
+        <v>740</v>
+      </c>
+      <c r="BW17">
+        <v>1.83</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.84</v>
+      </c>
+      <c r="BZ17">
         <v>38</v>
       </c>
-      <c r="BE17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF17">
-        <v>13</v>
-      </c>
-      <c r="BG17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH17">
-        <v>3.35</v>
-      </c>
-      <c r="BI17">
-        <v>2.64</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>2.4</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>2.24</v>
-      </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
-      <c r="BO17">
-        <v>2.92</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>2.4</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>2.24</v>
-      </c>
-      <c r="BT17">
-        <v>1000</v>
-      </c>
-      <c r="BU17">
-        <v>2.06</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>2.24</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>2.24</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
       <c r="CA17">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="CB17" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F18">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="G18">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="H18">
-        <v>2.24</v>
+        <v>5.2</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J18">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="K18">
+        <v>3.35</v>
+      </c>
+      <c r="L18">
+        <v>1.59</v>
+      </c>
+      <c r="M18">
+        <v>1.15</v>
+      </c>
+      <c r="N18">
+        <v>2.42</v>
+      </c>
+      <c r="O18">
+        <v>1.67</v>
+      </c>
+      <c r="P18">
+        <v>1.45</v>
+      </c>
+      <c r="Q18">
+        <v>3.05</v>
+      </c>
+      <c r="R18">
+        <v>1.15</v>
+      </c>
+      <c r="S18">
+        <v>6.8</v>
+      </c>
+      <c r="T18">
+        <v>2.58</v>
+      </c>
+      <c r="U18">
+        <v>1.59</v>
+      </c>
+      <c r="V18">
+        <v>1.22</v>
+      </c>
+      <c r="W18">
+        <v>1.98</v>
+      </c>
+      <c r="X18">
+        <v>7.6</v>
+      </c>
+      <c r="Y18">
+        <v>12</v>
+      </c>
+      <c r="Z18">
+        <v>38</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>5.7</v>
+      </c>
+      <c r="AC18">
+        <v>8</v>
+      </c>
+      <c r="AD18">
+        <v>26</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>9.6</v>
+      </c>
+      <c r="AG18">
+        <v>12.5</v>
+      </c>
+      <c r="AH18">
+        <v>34</v>
+      </c>
+      <c r="AI18">
+        <v>900</v>
+      </c>
+      <c r="AJ18">
+        <v>25</v>
+      </c>
+      <c r="AK18">
+        <v>36</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>390</v>
+      </c>
+      <c r="AN18">
+        <v>32</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>6.8</v>
+      </c>
+      <c r="AQ18">
+        <v>10.5</v>
+      </c>
+      <c r="AR18">
+        <v>22</v>
+      </c>
+      <c r="AS18">
+        <v>44</v>
+      </c>
+      <c r="AT18">
+        <v>5.3</v>
+      </c>
+      <c r="AU18">
+        <v>7.2</v>
+      </c>
+      <c r="AV18">
+        <v>21</v>
+      </c>
+      <c r="AW18">
+        <v>65</v>
+      </c>
+      <c r="AX18">
+        <v>9</v>
+      </c>
+      <c r="AY18">
+        <v>11</v>
+      </c>
+      <c r="AZ18">
+        <v>26</v>
+      </c>
+      <c r="BA18">
+        <v>46</v>
+      </c>
+      <c r="BB18">
+        <v>21</v>
+      </c>
+      <c r="BC18">
         <v>23</v>
       </c>
-      <c r="L18">
-        <v>1.2</v>
-      </c>
-      <c r="M18">
-        <v>1.04</v>
-      </c>
-      <c r="N18">
-        <v>4.9</v>
-      </c>
-      <c r="O18">
-        <v>1.24</v>
-      </c>
-      <c r="P18">
+      <c r="BD18">
+        <v>55</v>
+      </c>
+      <c r="BE18">
+        <v>100</v>
+      </c>
+      <c r="BF18">
+        <v>19</v>
+      </c>
+      <c r="BG18">
+        <v>100</v>
+      </c>
+      <c r="BH18">
+        <v>11.5</v>
+      </c>
+      <c r="BI18">
+        <v>2.2</v>
+      </c>
+      <c r="BJ18">
+        <v>18</v>
+      </c>
+      <c r="BK18">
+        <v>3.8</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.94</v>
+      </c>
+      <c r="BN18">
+        <v>5.9</v>
+      </c>
+      <c r="BO18">
+        <v>3.3</v>
+      </c>
+      <c r="BP18">
+        <v>23</v>
+      </c>
+      <c r="BQ18">
+        <v>4</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
         <v>1.89</v>
       </c>
-      <c r="Q18">
-        <v>1.64</v>
-      </c>
-      <c r="R18">
-        <v>1.35</v>
-      </c>
-      <c r="S18">
-        <v>2.66</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.4</v>
-      </c>
-      <c r="W18">
-        <v>1.47</v>
-      </c>
-      <c r="X18">
-        <v>95</v>
-      </c>
-      <c r="Y18">
-        <v>80</v>
-      </c>
-      <c r="Z18">
-        <v>90</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>80</v>
-      </c>
-      <c r="AC18">
-        <v>46</v>
-      </c>
-      <c r="AD18">
-        <v>70</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>90</v>
-      </c>
-      <c r="AG18">
-        <v>70</v>
-      </c>
-      <c r="AH18">
-        <v>90</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>4</v>
-      </c>
-      <c r="AQ18">
-        <v>3.75</v>
-      </c>
-      <c r="AR18">
-        <v>1.12</v>
-      </c>
-      <c r="AS18">
-        <v>1.13</v>
-      </c>
-      <c r="AT18">
-        <v>3.4</v>
-      </c>
-      <c r="AU18">
-        <v>1.11</v>
-      </c>
-      <c r="AV18">
-        <v>3.15</v>
-      </c>
-      <c r="AW18">
-        <v>1.13</v>
-      </c>
-      <c r="AX18">
-        <v>1.12</v>
-      </c>
-      <c r="AY18">
-        <v>3.15</v>
-      </c>
-      <c r="AZ18">
-        <v>3.75</v>
-      </c>
-      <c r="BA18">
-        <v>1.13</v>
-      </c>
-      <c r="BB18">
-        <v>1.13</v>
-      </c>
-      <c r="BC18">
-        <v>1.13</v>
-      </c>
-      <c r="BD18">
-        <v>1.13</v>
-      </c>
-      <c r="BE18">
-        <v>1.13</v>
-      </c>
-      <c r="BF18">
-        <v>1.13</v>
-      </c>
-      <c r="BG18">
-        <v>1.13</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.01</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.01</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.01</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.01</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.01</v>
-      </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="CB18" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F19">
-        <v>2.66</v>
+        <v>1.75</v>
       </c>
       <c r="G19">
-        <v>4.2</v>
+        <v>1.81</v>
       </c>
       <c r="H19">
-        <v>2.36</v>
+        <v>5.6</v>
       </c>
       <c r="I19">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>2.82</v>
+        <v>3.65</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="CB19" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20">
+        <v>2.72</v>
+      </c>
+      <c r="G20">
+        <v>3.15</v>
+      </c>
+      <c r="H20">
+        <v>2.44</v>
+      </c>
+      <c r="I20">
+        <v>2.8</v>
+      </c>
+      <c r="J20">
+        <v>3.45</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>1.2</v>
+      </c>
+      <c r="M20">
+        <v>1.06</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>1.26</v>
+      </c>
+      <c r="P20">
+        <v>2.02</v>
+      </c>
+      <c r="Q20">
+        <v>1.79</v>
+      </c>
+      <c r="R20">
+        <v>1.41</v>
+      </c>
+      <c r="S20">
+        <v>2.98</v>
+      </c>
+      <c r="T20">
+        <v>1.65</v>
+      </c>
+      <c r="U20">
+        <v>2.26</v>
+      </c>
+      <c r="V20">
+        <v>1.55</v>
+      </c>
+      <c r="W20">
+        <v>1.46</v>
+      </c>
+      <c r="X20">
+        <v>22</v>
+      </c>
+      <c r="Y20">
+        <v>14</v>
+      </c>
+      <c r="Z20">
+        <v>19</v>
+      </c>
+      <c r="AA20">
+        <v>40</v>
+      </c>
+      <c r="AB20">
+        <v>15.5</v>
+      </c>
+      <c r="AC20">
+        <v>9</v>
+      </c>
+      <c r="AD20">
+        <v>13</v>
+      </c>
+      <c r="AE20">
+        <v>29</v>
+      </c>
+      <c r="AF20">
+        <v>22</v>
+      </c>
+      <c r="AG20">
+        <v>13.5</v>
+      </c>
+      <c r="AH20">
+        <v>17</v>
+      </c>
+      <c r="AI20">
+        <v>38</v>
+      </c>
+      <c r="AJ20">
+        <v>48</v>
+      </c>
+      <c r="AK20">
+        <v>38</v>
+      </c>
+      <c r="AL20">
+        <v>42</v>
+      </c>
+      <c r="AM20">
         <v>90</v>
       </c>
-      <c r="B20" t="s">
+      <c r="AN20">
+        <v>26</v>
+      </c>
+      <c r="AO20">
+        <v>24</v>
+      </c>
+      <c r="AP20">
+        <v>14</v>
+      </c>
+      <c r="AQ20">
+        <v>10.5</v>
+      </c>
+      <c r="AR20">
+        <v>15</v>
+      </c>
+      <c r="AS20">
+        <v>5.8</v>
+      </c>
+      <c r="AT20">
+        <v>11.5</v>
+      </c>
+      <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
+        <v>9.6</v>
+      </c>
+      <c r="AW20">
+        <v>20</v>
+      </c>
+      <c r="AX20">
+        <v>17</v>
+      </c>
+      <c r="AY20">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20">
+        <v>13.5</v>
+      </c>
+      <c r="BA20">
+        <v>5.7</v>
+      </c>
+      <c r="BB20">
+        <v>29</v>
+      </c>
+      <c r="BC20">
+        <v>5.7</v>
+      </c>
+      <c r="BD20">
+        <v>5.7</v>
+      </c>
+      <c r="BE20">
+        <v>6</v>
+      </c>
+      <c r="BF20">
+        <v>20</v>
+      </c>
+      <c r="BG20">
+        <v>16.5</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
         <v>91</v>
       </c>
-      <c r="C20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F20">
-        <v>2.16</v>
-      </c>
-      <c r="G20">
-        <v>2.42</v>
-      </c>
-      <c r="H20">
-        <v>3.05</v>
-      </c>
-      <c r="I20">
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21">
+        <v>2.66</v>
+      </c>
+      <c r="G21">
+        <v>4.2</v>
+      </c>
+      <c r="H21">
+        <v>2.36</v>
+      </c>
+      <c r="I21">
+        <v>3.55</v>
+      </c>
+      <c r="J21">
+        <v>2.76</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22">
+        <v>1.56</v>
+      </c>
+      <c r="G22">
+        <v>1.65</v>
+      </c>
+      <c r="H22">
+        <v>6.8</v>
+      </c>
+      <c r="I22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J22">
+        <v>3.85</v>
+      </c>
+      <c r="K22">
+        <v>4.4</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.08</v>
+      </c>
+      <c r="N22">
+        <v>3.25</v>
+      </c>
+      <c r="O22">
+        <v>1.35</v>
+      </c>
+      <c r="P22">
+        <v>1.79</v>
+      </c>
+      <c r="Q22">
+        <v>2.08</v>
+      </c>
+      <c r="R22">
+        <v>1.26</v>
+      </c>
+      <c r="S22">
+        <v>3.6</v>
+      </c>
+      <c r="T22">
+        <v>2.14</v>
+      </c>
+      <c r="U22">
+        <v>1.67</v>
+      </c>
+      <c r="V22">
+        <v>1.14</v>
+      </c>
+      <c r="W22">
+        <v>2.52</v>
+      </c>
+      <c r="X22">
+        <v>25</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>970</v>
+      </c>
+      <c r="AC22">
+        <v>970</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>970</v>
+      </c>
+      <c r="AG22">
+        <v>23</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>970</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22">
+        <v>1.01</v>
+      </c>
+      <c r="AR22">
+        <v>1.03</v>
+      </c>
+      <c r="AS22">
+        <v>1.03</v>
+      </c>
+      <c r="AT22">
+        <v>1.03</v>
+      </c>
+      <c r="AU22">
+        <v>1.03</v>
+      </c>
+      <c r="AV22">
+        <v>1.03</v>
+      </c>
+      <c r="AW22">
+        <v>1.03</v>
+      </c>
+      <c r="AX22">
+        <v>1.03</v>
+      </c>
+      <c r="AY22">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22">
+        <v>1.03</v>
+      </c>
+      <c r="BA22">
+        <v>1.03</v>
+      </c>
+      <c r="BB22">
+        <v>1.01</v>
+      </c>
+      <c r="BC22">
+        <v>1.01</v>
+      </c>
+      <c r="BD22">
+        <v>1.03</v>
+      </c>
+      <c r="BE22">
+        <v>1.03</v>
+      </c>
+      <c r="BF22">
+        <v>1.01</v>
+      </c>
+      <c r="BG22">
+        <v>1.01</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.01</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.01</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23">
+        <v>2.18</v>
+      </c>
+      <c r="G23">
+        <v>2.38</v>
+      </c>
+      <c r="H23">
+        <v>3.25</v>
+      </c>
+      <c r="I23">
         <v>3.75</v>
       </c>
-      <c r="J20">
-        <v>3.3</v>
-      </c>
-      <c r="K20">
-        <v>4.2</v>
-      </c>
-      <c r="L20">
+      <c r="J23">
+        <v>3.55</v>
+      </c>
+      <c r="K23">
+        <v>3.9</v>
+      </c>
+      <c r="L23">
         <v>1.34</v>
       </c>
-      <c r="M20">
+      <c r="M23">
         <v>1.04</v>
       </c>
-      <c r="N20">
-        <v>3.5</v>
-      </c>
-      <c r="O20">
-        <v>1.28</v>
-      </c>
-      <c r="P20">
-        <v>1.92</v>
-      </c>
-      <c r="Q20">
-        <v>1.83</v>
-      </c>
-      <c r="R20">
+      <c r="N23">
+        <v>3.8</v>
+      </c>
+      <c r="O23">
+        <v>1.3</v>
+      </c>
+      <c r="P23">
+        <v>1.95</v>
+      </c>
+      <c r="Q23">
+        <v>1.86</v>
+      </c>
+      <c r="R23">
         <v>1.34</v>
       </c>
-      <c r="S20">
-        <v>3.1</v>
-      </c>
-      <c r="T20">
+      <c r="S23">
+        <v>3.2</v>
+      </c>
+      <c r="T23">
         <v>1.68</v>
       </c>
-      <c r="U20">
-        <v>2.04</v>
-      </c>
-      <c r="V20">
-        <v>1.37</v>
-      </c>
-      <c r="W20">
-        <v>1.71</v>
-      </c>
-      <c r="X20">
-        <v>970</v>
-      </c>
-      <c r="Y20">
-        <v>890</v>
-      </c>
-      <c r="Z20">
-        <v>1000</v>
-      </c>
-      <c r="AA20">
-        <v>90</v>
-      </c>
-      <c r="AB20">
-        <v>970</v>
-      </c>
-      <c r="AC20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD20">
-        <v>970</v>
-      </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>900</v>
-      </c>
-      <c r="AG20">
-        <v>550</v>
-      </c>
-      <c r="AH20">
-        <v>19</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>1000</v>
-      </c>
-      <c r="AK20">
-        <v>1000</v>
-      </c>
-      <c r="AL20">
-        <v>1000</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>970</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>10.5</v>
-      </c>
-      <c r="AQ20">
-        <v>1.85</v>
-      </c>
-      <c r="AR20">
+      <c r="U23">
+        <v>2.06</v>
+      </c>
+      <c r="V23">
+        <v>1.36</v>
+      </c>
+      <c r="W23">
+        <v>1.72</v>
+      </c>
+      <c r="X23">
+        <v>16</v>
+      </c>
+      <c r="Y23">
+        <v>14.5</v>
+      </c>
+      <c r="Z23">
+        <v>32</v>
+      </c>
+      <c r="AA23">
+        <v>75</v>
+      </c>
+      <c r="AB23">
+        <v>11</v>
+      </c>
+      <c r="AC23">
+        <v>8.6</v>
+      </c>
+      <c r="AD23">
+        <v>15.5</v>
+      </c>
+      <c r="AE23">
+        <v>42</v>
+      </c>
+      <c r="AF23">
+        <v>15.5</v>
+      </c>
+      <c r="AG23">
+        <v>11.5</v>
+      </c>
+      <c r="AH23">
         <v>18</v>
       </c>
-      <c r="AS20">
-        <v>1.56</v>
-      </c>
-      <c r="AT20">
-        <v>8.6</v>
-      </c>
-      <c r="AU20">
-        <v>7.4</v>
-      </c>
-      <c r="AV20">
-        <v>1.95</v>
-      </c>
-      <c r="AW20">
-        <v>1.52</v>
-      </c>
-      <c r="AX20">
-        <v>1.86</v>
-      </c>
-      <c r="AY20">
-        <v>1.79</v>
-      </c>
-      <c r="AZ20">
-        <v>1.77</v>
-      </c>
-      <c r="BA20">
-        <v>1.95</v>
-      </c>
-      <c r="BB20">
-        <v>19</v>
-      </c>
-      <c r="BC20">
-        <v>1.52</v>
-      </c>
-      <c r="BD20">
-        <v>1.52</v>
-      </c>
-      <c r="BE20">
-        <v>1.52</v>
-      </c>
-      <c r="BF20">
-        <v>1.76</v>
-      </c>
-      <c r="BG20">
-        <v>1.52</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
+      <c r="AI23">
+        <v>60</v>
+      </c>
+      <c r="AJ23">
+        <v>32</v>
+      </c>
+      <c r="AK23">
+        <v>25</v>
+      </c>
+      <c r="AL23">
+        <v>38</v>
+      </c>
+      <c r="AM23">
+        <v>110</v>
+      </c>
+      <c r="AN23">
+        <v>17.5</v>
+      </c>
+      <c r="AO23">
+        <v>40</v>
+      </c>
+      <c r="AP23">
+        <v>13</v>
+      </c>
+      <c r="AQ23">
+        <v>12</v>
+      </c>
+      <c r="AR23">
+        <v>21</v>
+      </c>
+      <c r="AS23">
+        <v>22</v>
+      </c>
+      <c r="AT23">
+        <v>9</v>
+      </c>
+      <c r="AU23">
+        <v>7.2</v>
+      </c>
+      <c r="AV23">
+        <v>12.5</v>
+      </c>
+      <c r="AW23">
+        <v>7.8</v>
+      </c>
+      <c r="AX23">
+        <v>12.5</v>
+      </c>
+      <c r="AY23">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23">
+        <v>14.5</v>
+      </c>
+      <c r="BA23">
+        <v>17.5</v>
+      </c>
+      <c r="BB23">
+        <v>7.2</v>
+      </c>
+      <c r="BC23">
+        <v>20</v>
+      </c>
+      <c r="BD23">
+        <v>7.6</v>
+      </c>
+      <c r="BE23">
+        <v>27</v>
+      </c>
+      <c r="BF23">
+        <v>14.5</v>
+      </c>
+      <c r="BG23">
+        <v>7.8</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
         <v>2.8</v>
       </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
         <v>1.17</v>
       </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
         <v>1.17</v>
       </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
         <v>1.35</v>
       </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
         <v>1.17</v>
       </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
         <v>1.17</v>
       </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
         <v>1.17</v>
       </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
         <v>1.17</v>
       </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
         <v>1.17</v>
       </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
         <v>1.17</v>
       </c>
-      <c r="CB20" t="s">
-        <v>144</v>
+      <c r="CB23" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -481,7 +481,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 12:43:03</t>
+    <t>2026-10-04 14:53:23</t>
   </si>
 </sst>
 </file>
@@ -1075,19 +1075,19 @@
         <v>133</v>
       </c>
       <c r="F2">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H2">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I2">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
         <v>4.1</v>
@@ -1102,31 +1102,31 @@
         <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
         <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
         <v>2.44</v>
       </c>
       <c r="V2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X2">
         <v>20</v>
@@ -1135,16 +1135,16 @@
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>13</v>
@@ -1159,7 +1159,7 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI2">
         <v>36</v>
@@ -1171,31 +1171,31 @@
         <v>28</v>
       </c>
       <c r="AL2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP2">
         <v>17.5</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS2">
         <v>30</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU2">
         <v>8.4</v>
@@ -1204,28 +1204,28 @@
         <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX2">
         <v>16.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE2">
         <v>55</v>
@@ -1234,43 +1234,43 @@
         <v>15.5</v>
       </c>
       <c r="BG2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH2">
         <v>3.95</v>
       </c>
       <c r="BI2">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2">
+        <v>5.7</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>13.5</v>
+      </c>
+      <c r="BN2">
         <v>5.9</v>
       </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>15</v>
-      </c>
-      <c r="BN2">
-        <v>5.7</v>
-      </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
         <v>27</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
@@ -1279,22 +1279,22 @@
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>19.5</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>155</v>
@@ -1317,7 +1317,7 @@
         <v>134</v>
       </c>
       <c r="F3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G3">
         <v>4.7</v>
@@ -1326,70 +1326,70 @@
         <v>2.12</v>
       </c>
       <c r="I3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W3">
         <v>1.27</v>
       </c>
       <c r="X3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z3">
         <v>11</v>
       </c>
       <c r="AA3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
         <v>32</v>
@@ -1398,34 +1398,34 @@
         <v>32</v>
       </c>
       <c r="AG3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM3">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="AN3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
         <v>6</v>
@@ -1434,7 +1434,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT3">
         <v>10</v>
@@ -1446,73 +1446,73 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY3">
         <v>18.5</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB3">
         <v>40</v>
       </c>
       <c r="BC3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF3">
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO3">
         <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
         <v>80</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
         <v>4.5</v>
@@ -1521,19 +1521,19 @@
         <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW3">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY3">
         <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="CA3">
         <v>12</v>
@@ -1559,7 +1559,7 @@
         <v>135</v>
       </c>
       <c r="F4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1571,10 +1571,10 @@
         <v>2.26</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -1586,7 +1586,7 @@
         <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
         <v>1.77</v>
@@ -1619,28 +1619,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA4">
         <v>28</v>
       </c>
       <c r="AB4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4">
         <v>26</v>
       </c>
       <c r="AG4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH4">
         <v>23</v>
@@ -1655,16 +1655,16 @@
         <v>65</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AN4">
         <v>75</v>
       </c>
       <c r="AO4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1724,7 +1724,7 @@
         <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4">
         <v>10</v>
@@ -1801,58 +1801,58 @@
         <v>136</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="G5">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="H5">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="I5">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.32</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="W5">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
         <v>23</v>
@@ -1861,94 +1861,94 @@
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AG5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>130</v>
+        <v>610</v>
       </c>
       <c r="AK5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL5">
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AN5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
         <v>9</v>
       </c>
       <c r="AW5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX5">
         <v>32</v>
       </c>
       <c r="AY5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
         <v>23</v>
       </c>
       <c r="BB5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BC5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BD5">
         <v>40</v>
@@ -1957,10 +1957,10 @@
         <v>60</v>
       </c>
       <c r="BF5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG5">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>4.3</v>
@@ -1972,55 +1972,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP5">
         <v>42</v>
       </c>
       <c r="BQ5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV5">
         <v>11</v>
       </c>
       <c r="BW5">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX5">
         <v>23</v>
       </c>
       <c r="BY5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
         <v>15.5</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
         <v>155</v>
@@ -2052,10 +2052,10 @@
         <v>3.05</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2064,7 +2064,7 @@
         <v>1.35</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
         <v>2.82</v>
@@ -2091,7 +2091,7 @@
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
         <v>1.86</v>
@@ -2384,7 +2384,7 @@
         <v>1000</v>
       </c>
       <c r="AM7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
         <v>1000</v>
@@ -2393,31 +2393,31 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AQ7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AR7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AS7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AT7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AU7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AV7">
         <v>2.44</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="AX7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AY7">
         <v>3</v>
@@ -2426,22 +2426,22 @@
         <v>2.02</v>
       </c>
       <c r="BA7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BB7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BC7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BD7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BE7">
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG7">
         <v>3.95</v>
@@ -2548,7 +2548,7 @@
         <v>1.35</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
         <v>2.68</v>
@@ -2557,16 +2557,16 @@
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q8">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R8">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T8">
         <v>1.87</v>
@@ -2769,22 +2769,22 @@
         <v>140</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H9">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I9">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2808,19 +2808,19 @@
         <v>1.51</v>
       </c>
       <c r="S9">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="T9">
         <v>1.53</v>
       </c>
       <c r="U9">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2892,7 +2892,7 @@
         <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
         <v>1.03</v>
@@ -2934,61 +2934,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>155</v>
@@ -3026,7 +3026,7 @@
         <v>5.2</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>19.5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3035,13 +3035,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="O10">
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
         <v>1.4</v>
@@ -3050,7 +3050,7 @@
         <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3176,61 +3176,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>155</v>
@@ -3256,13 +3256,13 @@
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J11">
         <v>1.12</v>
@@ -3277,13 +3277,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
       <c r="O11">
         <v>1.02</v>
       </c>
       <c r="P11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q11">
         <v>1.02</v>
@@ -3292,13 +3292,13 @@
         <v>1.08</v>
       </c>
       <c r="S11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.03</v>
@@ -3498,7 +3498,7 @@
         <v>3.75</v>
       </c>
       <c r="G12">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H12">
         <v>1.73</v>
@@ -3510,10 +3510,10 @@
         <v>4.3</v>
       </c>
       <c r="K12">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M12">
         <v>1.01</v>
@@ -3534,19 +3534,19 @@
         <v>2.38</v>
       </c>
       <c r="S12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="U12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V12">
         <v>2.14</v>
       </c>
       <c r="W12">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3555,34 +3555,34 @@
         <v>1000</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD12">
         <v>34</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH12">
         <v>48</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ12">
         <v>1000</v>
@@ -3597,40 +3597,40 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO12">
         <v>970</v>
       </c>
       <c r="AP12">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="AQ12">
-        <v>1.32</v>
+        <v>17.5</v>
       </c>
       <c r="AR12">
-        <v>1.32</v>
+        <v>16.5</v>
       </c>
       <c r="AS12">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="AT12">
-        <v>1.32</v>
+        <v>25</v>
       </c>
       <c r="AU12">
         <v>8.4</v>
       </c>
       <c r="AV12">
-        <v>1.27</v>
+        <v>9.4</v>
       </c>
       <c r="AW12">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="AX12">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AY12">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="AZ12">
         <v>8</v>
@@ -3639,16 +3639,16 @@
         <v>9.6</v>
       </c>
       <c r="BB12">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="BC12">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="BD12">
-        <v>1.32</v>
+        <v>16.5</v>
       </c>
       <c r="BE12">
-        <v>1.32</v>
+        <v>18.5</v>
       </c>
       <c r="BF12">
         <v>8.4</v>
@@ -3737,28 +3737,28 @@
         <v>144</v>
       </c>
       <c r="F13">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G13">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H13">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
         <v>3.2</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L13">
         <v>1.43</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N13">
         <v>2.38</v>
@@ -3767,88 +3767,88 @@
         <v>1.44</v>
       </c>
       <c r="P13">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Q13">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S13">
-        <v>2.74</v>
+        <v>5.1</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="V13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W13">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR13">
         <v>1.03</v>
@@ -3857,10 +3857,10 @@
         <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV13">
         <v>1.03</v>
@@ -3869,10 +3869,10 @@
         <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
         <v>1.03</v>
@@ -3881,10 +3881,10 @@
         <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD13">
         <v>1.03</v>
@@ -3893,70 +3893,70 @@
         <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>230</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>155</v>
@@ -3979,7 +3979,7 @@
         <v>145</v>
       </c>
       <c r="F14">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G14">
         <v>2.04</v>
@@ -3994,7 +3994,7 @@
         <v>3.55</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
         <v>1.38</v>
@@ -4003,25 +4003,25 @@
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O14">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P14">
         <v>1.99</v>
       </c>
       <c r="Q14">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R14">
         <v>1.38</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T14">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
         <v>2.16</v>
@@ -4030,10 +4030,10 @@
         <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y14">
         <v>18.5</v>
@@ -4042,43 +4042,43 @@
         <v>36</v>
       </c>
       <c r="AA14">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB14">
         <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AE14">
         <v>110</v>
       </c>
       <c r="AF14">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI14">
         <v>130</v>
       </c>
       <c r="AJ14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL14">
         <v>44</v>
       </c>
       <c r="AM14">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN14">
         <v>970</v>
@@ -4093,22 +4093,22 @@
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT14">
         <v>7</v>
       </c>
       <c r="AU14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4120,25 +4120,25 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BB14">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE14">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="BF14">
         <v>8.6</v>
       </c>
       <c r="BG14">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4221,67 +4221,67 @@
         <v>146</v>
       </c>
       <c r="F15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G15">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H15">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="I15">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
         <v>4.6</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
+        <v>2.24</v>
+      </c>
+      <c r="Q15">
+        <v>1.64</v>
+      </c>
+      <c r="R15">
+        <v>1.49</v>
+      </c>
+      <c r="S15">
+        <v>2.6</v>
+      </c>
+      <c r="T15">
+        <v>1.64</v>
+      </c>
+      <c r="U15">
         <v>2.3</v>
       </c>
-      <c r="Q15">
-        <v>1.58</v>
-      </c>
-      <c r="R15">
-        <v>1.52</v>
-      </c>
-      <c r="S15">
-        <v>2.54</v>
-      </c>
-      <c r="T15">
-        <v>1.61</v>
-      </c>
-      <c r="U15">
-        <v>2.28</v>
-      </c>
       <c r="V15">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="W15">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X15">
         <v>27</v>
       </c>
       <c r="Y15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA15">
         <v>25</v>
@@ -4290,7 +4290,7 @@
         <v>21</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD15">
         <v>11.5</v>
@@ -4299,7 +4299,7 @@
         <v>21</v>
       </c>
       <c r="AF15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG15">
         <v>17.5</v>
@@ -4314,7 +4314,7 @@
         <v>85</v>
       </c>
       <c r="AK15">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL15">
         <v>48</v>
@@ -4323,34 +4323,34 @@
         <v>85</v>
       </c>
       <c r="AN15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AP15">
         <v>18</v>
       </c>
       <c r="AQ15">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AR15">
         <v>11.5</v>
       </c>
       <c r="AS15">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV15">
         <v>8.800000000000001</v>
       </c>
       <c r="AW15">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX15">
         <v>5.7</v>
@@ -4359,37 +4359,37 @@
         <v>13.5</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC15">
         <v>5.9</v>
       </c>
       <c r="BD15">
+        <v>5.9</v>
+      </c>
+      <c r="BE15">
+        <v>6</v>
+      </c>
+      <c r="BF15">
         <v>5.8</v>
       </c>
-      <c r="BE15">
-        <v>5.8</v>
-      </c>
-      <c r="BF15">
-        <v>5.7</v>
-      </c>
       <c r="BG15">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI15">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK15">
         <v>7.2</v>
@@ -4401,7 +4401,7 @@
         <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO15">
         <v>6.2</v>
@@ -4425,10 +4425,10 @@
         <v>3.9</v>
       </c>
       <c r="BV15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW15">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX15">
         <v>24</v>
@@ -4437,7 +4437,7 @@
         <v>14.5</v>
       </c>
       <c r="BZ15">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA15">
         <v>12</v>
@@ -4466,163 +4466,163 @@
         <v>1.92</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5.5</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L16">
         <v>1.61</v>
       </c>
       <c r="M16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O16">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="P16">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q16">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U16">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V16">
         <v>1.22</v>
       </c>
       <c r="W16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X16">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y16">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z16">
         <v>48</v>
       </c>
       <c r="AA16">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF16">
         <v>10.5</v>
       </c>
       <c r="AG16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AI16">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AJ16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK16">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL16">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM16">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AN16">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO16">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AP16">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16">
         <v>11</v>
       </c>
       <c r="AR16">
+        <v>23</v>
+      </c>
+      <c r="AS16">
+        <v>11.5</v>
+      </c>
+      <c r="AT16">
+        <v>6</v>
+      </c>
+      <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
         <v>18.5</v>
       </c>
-      <c r="AS16">
-        <v>10.5</v>
-      </c>
-      <c r="AT16">
-        <v>5.6</v>
-      </c>
-      <c r="AU16">
-        <v>6.8</v>
-      </c>
-      <c r="AV16">
-        <v>20</v>
-      </c>
       <c r="AW16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BA16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB16">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC16">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD16">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BE16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF16">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH16">
         <v>2.64</v>
@@ -4909,7 +4909,7 @@
         <v>5.3</v>
       </c>
       <c r="BV17">
-        <v>740</v>
+        <v>620</v>
       </c>
       <c r="BW17">
         <v>1.83</v>
@@ -4947,10 +4947,10 @@
         <v>149</v>
       </c>
       <c r="F18">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G18">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>5.2</v>
@@ -4980,7 +4980,7 @@
         <v>1.45</v>
       </c>
       <c r="Q18">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R18">
         <v>1.15</v>
@@ -4992,13 +4992,13 @@
         <v>2.58</v>
       </c>
       <c r="U18">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V18">
         <v>1.22</v>
       </c>
       <c r="W18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X18">
         <v>7.6</v>
@@ -5034,7 +5034,7 @@
         <v>34</v>
       </c>
       <c r="AI18">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AJ18">
         <v>25</v>
@@ -5061,7 +5061,7 @@
         <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS18">
         <v>44</v>
@@ -5097,7 +5097,7 @@
         <v>23</v>
       </c>
       <c r="BD18">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BE18">
         <v>100</v>
@@ -5198,7 +5198,7 @@
         <v>5.6</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J19">
         <v>3.65</v>
@@ -5219,7 +5219,7 @@
         <v>1.42</v>
       </c>
       <c r="P19">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q19">
         <v>2.26</v>
@@ -5237,7 +5237,7 @@
         <v>1.8</v>
       </c>
       <c r="V19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W19">
         <v>2.22</v>
@@ -5306,7 +5306,7 @@
         <v>32</v>
       </c>
       <c r="AS19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT19">
         <v>6.6</v>
@@ -5431,22 +5431,22 @@
         <v>151</v>
       </c>
       <c r="F20">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G20">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="I20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J20">
         <v>3.45</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L20">
         <v>1.2</v>
@@ -5455,40 +5455,40 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q20">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R20">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S20">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="T20">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="U20">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V20">
         <v>1.55</v>
       </c>
       <c r="W20">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z20">
         <v>19</v>
@@ -5500,7 +5500,7 @@
         <v>15.5</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD20">
         <v>13</v>
@@ -5509,19 +5509,19 @@
         <v>29</v>
       </c>
       <c r="AF20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH20">
         <v>17</v>
       </c>
       <c r="AI20">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AJ20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK20">
         <v>38</v>
@@ -5533,13 +5533,13 @@
         <v>90</v>
       </c>
       <c r="AN20">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AO20">
         <v>24</v>
       </c>
       <c r="AP20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ20">
         <v>10.5</v>
@@ -5548,13 +5548,13 @@
         <v>15</v>
       </c>
       <c r="AS20">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV20">
         <v>9.6</v>
@@ -5566,25 +5566,25 @@
         <v>17</v>
       </c>
       <c r="AY20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB20">
         <v>29</v>
       </c>
       <c r="BC20">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD20">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE20">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BF20">
         <v>20</v>
@@ -5673,7 +5673,7 @@
         <v>152</v>
       </c>
       <c r="F21">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G21">
         <v>4.2</v>
@@ -5682,13 +5682,13 @@
         <v>2.36</v>
       </c>
       <c r="I21">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="J21">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>153</v>
       </c>
       <c r="F22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G22">
         <v>1.65</v>
@@ -5924,7 +5924,7 @@
         <v>6.8</v>
       </c>
       <c r="I22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
         <v>3.85</v>
@@ -5933,7 +5933,7 @@
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M22">
         <v>1.08</v>
@@ -5942,7 +5942,7 @@
         <v>3.25</v>
       </c>
       <c r="O22">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P22">
         <v>1.79</v>
@@ -5960,7 +5960,7 @@
         <v>2.14</v>
       </c>
       <c r="U22">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V22">
         <v>1.14</v>
@@ -6166,19 +6166,19 @@
         <v>3.25</v>
       </c>
       <c r="I23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
         <v>3.9</v>
       </c>
       <c r="L23">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
         <v>3.8</v>
@@ -6190,22 +6190,22 @@
         <v>1.95</v>
       </c>
       <c r="Q23">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S23">
         <v>3.2</v>
       </c>
       <c r="T23">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U23">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
         <v>1.72</v>
@@ -6286,7 +6286,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AX23">
         <v>12.5</v>
@@ -6319,64 +6319,64 @@
         <v>7.8</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI23">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK23">
-        <v>1.17</v>
+        <v>6.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ23">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS23">
-        <v>1.17</v>
+        <v>8</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU23">
-        <v>1.17</v>
+        <v>5.7</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW23">
-        <v>1.17</v>
+        <v>8</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY23">
-        <v>1.17</v>
+        <v>8.6</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA23">
-        <v>1.17</v>
+        <v>7.8</v>
       </c>
       <c r="CB23" t="s">
         <v>155</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -481,7 +481,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 14:53:23</t>
+    <t>2026-10-04 17:04:42</t>
   </si>
 </sst>
 </file>
@@ -1075,22 +1075,22 @@
         <v>133</v>
       </c>
       <c r="F2">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="I2">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -1102,58 +1102,58 @@
         <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
         <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
         <v>20</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AB2">
+        <v>12.5</v>
+      </c>
+      <c r="AC2">
+        <v>9.6</v>
+      </c>
+      <c r="AD2">
         <v>13.5</v>
       </c>
-      <c r="AC2">
-        <v>9</v>
-      </c>
-      <c r="AD2">
-        <v>13</v>
-      </c>
       <c r="AE2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1162,43 +1162,43 @@
         <v>16.5</v>
       </c>
       <c r="AI2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>28</v>
       </c>
       <c r="AL2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN2">
+        <v>15.5</v>
+      </c>
+      <c r="AO2">
+        <v>23</v>
+      </c>
+      <c r="AP2">
         <v>18</v>
-      </c>
-      <c r="AO2">
-        <v>18</v>
-      </c>
-      <c r="AP2">
-        <v>17.5</v>
       </c>
       <c r="AQ2">
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT2">
         <v>12</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV2">
         <v>11.5</v>
@@ -1207,91 +1207,91 @@
         <v>24</v>
       </c>
       <c r="AX2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD2">
         <v>29</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BF2">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
         <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BS2">
         <v>10</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV2">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA2">
         <v>8.800000000000001</v>
@@ -1320,13 +1320,13 @@
         <v>4.5</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
         <v>2.12</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1338,34 +1338,34 @@
         <v>1.62</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P3">
         <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
         <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W3">
         <v>1.27</v>
@@ -1392,7 +1392,7 @@
         <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF3">
         <v>32</v>
@@ -1407,22 +1407,22 @@
         <v>70</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL3">
         <v>120</v>
       </c>
       <c r="AM3">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP3">
         <v>7.6</v>
@@ -1431,37 +1431,37 @@
         <v>6</v>
       </c>
       <c r="AR3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT3">
         <v>10</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX3">
         <v>28</v>
       </c>
       <c r="AY3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
         <v>25</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BC3">
         <v>60</v>
@@ -1476,10 +1476,10 @@
         <v>44</v>
       </c>
       <c r="BG3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI3">
         <v>2.48</v>
@@ -1488,13 +1488,13 @@
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN3">
         <v>7.6</v>
@@ -1506,13 +1506,13 @@
         <v>50</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR3">
         <v>80</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
         <v>4.5</v>
@@ -1524,7 +1524,7 @@
         <v>20</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
         <v>42</v>
@@ -1536,7 +1536,7 @@
         <v>46</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>155</v>
@@ -1559,7 +1559,7 @@
         <v>135</v>
       </c>
       <c r="F4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1568,13 +1568,13 @@
         <v>2.22</v>
       </c>
       <c r="I4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -1586,10 +1586,10 @@
         <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
         <v>2.24</v>
@@ -1601,13 +1601,13 @@
         <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U4">
         <v>2.02</v>
       </c>
       <c r="V4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W4">
         <v>1.33</v>
@@ -1619,13 +1619,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z4">
+        <v>13.5</v>
+      </c>
+      <c r="AA4">
+        <v>29</v>
+      </c>
+      <c r="AB4">
         <v>13</v>
-      </c>
-      <c r="AA4">
-        <v>28</v>
-      </c>
-      <c r="AB4">
-        <v>13.5</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1640,7 +1640,7 @@
         <v>26</v>
       </c>
       <c r="AG4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH4">
         <v>23</v>
@@ -1649,13 +1649,13 @@
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>200</v>
@@ -1664,13 +1664,13 @@
         <v>75</v>
       </c>
       <c r="AO4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
         <v>11.5</v>
@@ -1682,10 +1682,10 @@
         <v>11.5</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4">
         <v>21</v>
@@ -1697,10 +1697,10 @@
         <v>14.5</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB4">
         <v>55</v>
@@ -1712,10 +1712,10 @@
         <v>48</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BG4">
         <v>18.5</v>
@@ -1801,22 +1801,22 @@
         <v>136</v>
       </c>
       <c r="F5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H5">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="I5">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1828,31 +1828,31 @@
         <v>5.1</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
         <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V5">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
         <v>23</v>
@@ -1861,52 +1861,52 @@
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC5">
         <v>11</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AG5">
         <v>21</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5">
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>610</v>
+        <v>130</v>
       </c>
       <c r="AK5">
         <v>75</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP5">
         <v>18.5</v>
@@ -1915,25 +1915,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR5">
+        <v>10</v>
+      </c>
+      <c r="AS5">
+        <v>14.5</v>
+      </c>
+      <c r="AT5">
+        <v>20</v>
+      </c>
+      <c r="AU5">
         <v>9.6</v>
-      </c>
-      <c r="AS5">
-        <v>13.5</v>
-      </c>
-      <c r="AT5">
-        <v>19</v>
-      </c>
-      <c r="AU5">
-        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
         <v>9</v>
       </c>
       <c r="AW5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AY5">
         <v>17.5</v>
@@ -1951,76 +1951,76 @@
         <v>44</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BO5">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP5">
         <v>42</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU5">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BV5">
         <v>11</v>
       </c>
       <c r="BW5">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BX5">
         <v>23</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>15.5</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>155</v>
@@ -2043,22 +2043,22 @@
         <v>137</v>
       </c>
       <c r="F6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G6">
         <v>2.18</v>
       </c>
       <c r="H6">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.35</v>
@@ -2067,7 +2067,7 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
         <v>1.37</v>
@@ -2082,7 +2082,7 @@
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
         <v>1.76</v>
@@ -2091,10 +2091,10 @@
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2566,7 +2566,7 @@
         <v>1.23</v>
       </c>
       <c r="S8">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T8">
         <v>1.87</v>
@@ -2784,7 +2784,7 @@
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2877,52 +2877,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
         <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3020,10 +3020,10 @@
         <v>8.6</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
         <v>19.5</v>
@@ -3035,19 +3035,19 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="O10">
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q10">
         <v>1.4</v>
       </c>
       <c r="R10">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S10">
         <v>1.66</v>
@@ -3119,52 +3119,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3277,22 +3277,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.94</v>
+        <v>1.13</v>
       </c>
       <c r="O11">
         <v>1.02</v>
       </c>
       <c r="P11">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="Q11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R11">
         <v>1.08</v>
       </c>
       <c r="S11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3301,10 +3301,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3361,52 +3361,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3418,61 +3418,61 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>155</v>
@@ -3510,16 +3510,16 @@
         <v>4.3</v>
       </c>
       <c r="K12">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="M12">
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
         <v>1.05</v>
@@ -3537,7 +3537,7 @@
         <v>1.53</v>
       </c>
       <c r="T12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U12">
         <v>3.6</v>
@@ -3546,13 +3546,13 @@
         <v>2.14</v>
       </c>
       <c r="W12">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X12">
         <v>1000</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12">
         <v>34</v>
@@ -3561,13 +3561,13 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
         <v>970</v>
       </c>
       <c r="AD12">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AE12">
         <v>23</v>
@@ -3576,10 +3576,10 @@
         <v>75</v>
       </c>
       <c r="AG12">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AH12">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AI12">
         <v>50</v>
@@ -3597,22 +3597,22 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
         <v>970</v>
       </c>
       <c r="AP12">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AQ12">
         <v>17.5</v>
       </c>
       <c r="AR12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AT12">
         <v>25</v>
@@ -3624,13 +3624,13 @@
         <v>9.4</v>
       </c>
       <c r="AW12">
+        <v>1.7</v>
+      </c>
+      <c r="AX12">
+        <v>1.8</v>
+      </c>
+      <c r="AY12">
         <v>1.73</v>
-      </c>
-      <c r="AX12">
-        <v>1.83</v>
-      </c>
-      <c r="AY12">
-        <v>1.76</v>
       </c>
       <c r="AZ12">
         <v>8</v>
@@ -3639,10 +3639,10 @@
         <v>9.6</v>
       </c>
       <c r="BB12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BC12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BD12">
         <v>16.5</v>
@@ -3660,61 +3660,61 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>155</v>
@@ -3737,22 +3737,22 @@
         <v>144</v>
       </c>
       <c r="F13">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="G13">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="H13">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.43</v>
@@ -3761,10 +3761,10 @@
         <v>1.11</v>
       </c>
       <c r="N13">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="P13">
         <v>1.54</v>
@@ -3782,13 +3782,13 @@
         <v>2.34</v>
       </c>
       <c r="U13">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="V13">
         <v>1.13</v>
       </c>
       <c r="W13">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X13">
         <v>11.5</v>
@@ -3851,10 +3851,10 @@
         <v>12</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
         <v>4.4</v>
@@ -3866,7 +3866,7 @@
         <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
         <v>6.4</v>
@@ -3878,7 +3878,7 @@
         <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
@@ -3887,16 +3887,16 @@
         <v>17</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
         <v>12.5</v>
       </c>
       <c r="BG13">
-        <v>230</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3982,16 +3982,16 @@
         <v>1.97</v>
       </c>
       <c r="G14">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I14">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J14">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
         <v>3.85</v>
@@ -4009,16 +4009,16 @@
         <v>1.31</v>
       </c>
       <c r="P14">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R14">
         <v>1.38</v>
       </c>
       <c r="S14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T14">
         <v>1.8</v>
@@ -4027,10 +4027,10 @@
         <v>2.16</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X14">
         <v>19</v>
@@ -4039,7 +4039,7 @@
         <v>18.5</v>
       </c>
       <c r="Z14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA14">
         <v>200</v>
@@ -4048,16 +4048,16 @@
         <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE14">
         <v>110</v>
       </c>
       <c r="AF14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AG14">
         <v>13</v>
@@ -4066,19 +4066,19 @@
         <v>23</v>
       </c>
       <c r="AI14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AK14">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AL14">
         <v>44</v>
       </c>
       <c r="AM14">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN14">
         <v>970</v>
@@ -4087,64 +4087,64 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ14">
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AS14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT14">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW14">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
       </c>
       <c r="AY14">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>3.85</v>
+        <v>25</v>
       </c>
       <c r="BB14">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC14">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD14">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BE14">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BF14">
         <v>8.6</v>
       </c>
       <c r="BG14">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
@@ -4156,49 +4156,49 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="CB14" t="s">
         <v>155</v>
@@ -4224,10 +4224,10 @@
         <v>3.7</v>
       </c>
       <c r="G15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="I15">
         <v>2.02</v>
@@ -4236,7 +4236,7 @@
         <v>4.1</v>
       </c>
       <c r="K15">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.29</v>
@@ -4251,7 +4251,7 @@
         <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
         <v>1.64</v>
@@ -4260,19 +4260,19 @@
         <v>1.49</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
         <v>1.64</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X15">
         <v>27</v>
@@ -4332,13 +4332,13 @@
         <v>18</v>
       </c>
       <c r="AQ15">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AR15">
         <v>11.5</v>
       </c>
       <c r="AS15">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="AT15">
         <v>15</v>
@@ -4350,10 +4350,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY15">
         <v>13.5</v>
@@ -4362,22 +4362,22 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB15">
         <v>6</v>
       </c>
       <c r="BC15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE15">
         <v>6</v>
       </c>
       <c r="BF15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG15">
         <v>8.4</v>
@@ -4392,55 +4392,55 @@
         <v>9.6</v>
       </c>
       <c r="BK15">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN15">
         <v>7.8</v>
       </c>
       <c r="BO15">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP15">
         <v>32</v>
       </c>
       <c r="BQ15">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15">
         <v>5.1</v>
       </c>
       <c r="BU15">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BV15">
         <v>13.5</v>
       </c>
       <c r="BW15">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="BX15">
         <v>24</v>
       </c>
       <c r="BY15">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ15">
         <v>18.5</v>
       </c>
       <c r="CA15">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="CB15" t="s">
         <v>155</v>
@@ -4463,166 +4463,166 @@
         <v>147</v>
       </c>
       <c r="F16">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G16">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I16">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J16">
         <v>3.3</v>
       </c>
       <c r="K16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L16">
         <v>1.61</v>
       </c>
       <c r="M16">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N16">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="O16">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="P16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q16">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="R16">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="T16">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="U16">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W16">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X16">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y16">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z16">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA16">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI16">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
         <v>23</v>
       </c>
       <c r="AK16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL16">
         <v>65</v>
       </c>
       <c r="AM16">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AN16">
         <v>24</v>
       </c>
       <c r="AO16">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16">
         <v>11</v>
       </c>
       <c r="AR16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS16">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AT16">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU16">
         <v>7.4</v>
       </c>
       <c r="AV16">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW16">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="AX16">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA16">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BB16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC16">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE16">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BF16">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BH16">
         <v>2.64</v>
@@ -4652,7 +4652,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR16">
         <v>55</v>
@@ -4667,7 +4667,7 @@
         <v>7.6</v>
       </c>
       <c r="BV16">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW16">
         <v>11</v>
@@ -4909,7 +4909,7 @@
         <v>5.3</v>
       </c>
       <c r="BV17">
-        <v>620</v>
+        <v>570</v>
       </c>
       <c r="BW17">
         <v>1.83</v>
@@ -4947,16 +4947,16 @@
         <v>149</v>
       </c>
       <c r="F18">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J18">
         <v>3.2</v>
@@ -4968,31 +4968,31 @@
         <v>1.59</v>
       </c>
       <c r="M18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N18">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O18">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P18">
         <v>1.45</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S18">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="T18">
         <v>2.58</v>
       </c>
       <c r="U18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V18">
         <v>1.22</v>
@@ -5001,10 +5001,10 @@
         <v>2</v>
       </c>
       <c r="X18">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z18">
         <v>38</v>
@@ -5019,43 +5019,43 @@
         <v>8</v>
       </c>
       <c r="AD18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE18">
         <v>1000</v>
       </c>
       <c r="AF18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18">
         <v>12.5</v>
       </c>
       <c r="AH18">
+        <v>36</v>
+      </c>
+      <c r="AI18">
+        <v>150</v>
+      </c>
+      <c r="AJ18">
+        <v>24</v>
+      </c>
+      <c r="AK18">
         <v>34</v>
       </c>
-      <c r="AI18">
-        <v>840</v>
-      </c>
-      <c r="AJ18">
-        <v>25</v>
-      </c>
-      <c r="AK18">
-        <v>36</v>
-      </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM18">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AN18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO18">
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ18">
         <v>10.5</v>
@@ -5067,37 +5067,37 @@
         <v>44</v>
       </c>
       <c r="AT18">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU18">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV18">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD18">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BE18">
         <v>100</v>
@@ -5201,7 +5201,7 @@
         <v>6.2</v>
       </c>
       <c r="J19">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K19">
         <v>3.85</v>
@@ -5228,7 +5228,7 @@
         <v>1.27</v>
       </c>
       <c r="S19">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T19">
         <v>2.14</v>
@@ -5249,7 +5249,7 @@
         <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA19">
         <v>1000</v>
@@ -5261,10 +5261,10 @@
         <v>8.4</v>
       </c>
       <c r="AD19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE19">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
         <v>9.4</v>
@@ -5297,7 +5297,7 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ19">
         <v>14</v>
@@ -5431,16 +5431,16 @@
         <v>151</v>
       </c>
       <c r="F20">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H20">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="I20">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="J20">
         <v>3.45</v>
@@ -5455,22 +5455,22 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P20">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R20">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T20">
         <v>1.69</v>
@@ -5479,10 +5479,10 @@
         <v>2.24</v>
       </c>
       <c r="V20">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X20">
         <v>21</v>
@@ -5491,13 +5491,13 @@
         <v>13.5</v>
       </c>
       <c r="Z20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA20">
         <v>40</v>
       </c>
       <c r="AB20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC20">
         <v>8.4</v>
@@ -5506,10 +5506,10 @@
         <v>13</v>
       </c>
       <c r="AE20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF20">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG20">
         <v>13</v>
@@ -5518,10 +5518,10 @@
         <v>17</v>
       </c>
       <c r="AI20">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ20">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK20">
         <v>38</v>
@@ -5536,34 +5536,34 @@
         <v>32</v>
       </c>
       <c r="AO20">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR20">
         <v>15</v>
       </c>
       <c r="AS20">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW20">
         <v>20</v>
       </c>
       <c r="AX20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY20">
         <v>11</v>
@@ -5572,85 +5572,85 @@
         <v>14</v>
       </c>
       <c r="BA20">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB20">
         <v>29</v>
       </c>
       <c r="BC20">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD20">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE20">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BF20">
         <v>20</v>
       </c>
       <c r="BG20">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>155</v>
@@ -5676,7 +5676,7 @@
         <v>2.64</v>
       </c>
       <c r="G21">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="H21">
         <v>2.36</v>
@@ -5945,22 +5945,22 @@
         <v>1.37</v>
       </c>
       <c r="P22">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q22">
         <v>2.08</v>
       </c>
       <c r="R22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S22">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T22">
         <v>2.14</v>
       </c>
       <c r="U22">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V22">
         <v>1.14</v>
@@ -5969,172 +5969,172 @@
         <v>2.52</v>
       </c>
       <c r="X22">
+        <v>13.5</v>
+      </c>
+      <c r="Y22">
         <v>25</v>
       </c>
-      <c r="Y22">
-        <v>1000</v>
-      </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB22">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC22">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE22">
         <v>1000</v>
       </c>
       <c r="AF22">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG22">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI22">
         <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK22">
         <v>1000</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AN22">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AO22">
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>155</v>
@@ -6328,7 +6328,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK23">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL23">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -481,7 +481,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 17:04:42</t>
+    <t>2026-10-04 19:16:20</t>
   </si>
 </sst>
 </file>
@@ -1075,25 +1075,25 @@
         <v>133</v>
       </c>
       <c r="F2">
+        <v>2.28</v>
+      </c>
+      <c r="G2">
         <v>2.34</v>
       </c>
-      <c r="G2">
-        <v>2.38</v>
-      </c>
       <c r="H2">
+        <v>2.86</v>
+      </c>
+      <c r="I2">
         <v>2.92</v>
       </c>
-      <c r="I2">
-        <v>3.1</v>
-      </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M2">
         <v>1.05</v>
@@ -1108,13 +1108,13 @@
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T2">
         <v>1.66</v>
@@ -1123,13 +1123,13 @@
         <v>2.34</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y2">
         <v>15</v>
@@ -1138,106 +1138,106 @@
         <v>23</v>
       </c>
       <c r="AA2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF2">
         <v>17</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI2">
         <v>38</v>
       </c>
       <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>27</v>
+      </c>
+      <c r="AL2">
         <v>32</v>
       </c>
-      <c r="AK2">
-        <v>28</v>
-      </c>
-      <c r="AL2">
+      <c r="AM2">
+        <v>80</v>
+      </c>
+      <c r="AN2">
+        <v>16</v>
+      </c>
+      <c r="AO2">
+        <v>20</v>
+      </c>
+      <c r="AP2">
+        <v>19</v>
+      </c>
+      <c r="AQ2">
+        <v>14</v>
+      </c>
+      <c r="AR2">
+        <v>18.5</v>
+      </c>
+      <c r="AS2">
         <v>34</v>
       </c>
-      <c r="AM2">
-        <v>75</v>
-      </c>
-      <c r="AN2">
+      <c r="AT2">
+        <v>11.5</v>
+      </c>
+      <c r="AU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>12</v>
+      </c>
+      <c r="AW2">
+        <v>26</v>
+      </c>
+      <c r="AX2">
         <v>15.5</v>
       </c>
-      <c r="AO2">
-        <v>23</v>
-      </c>
-      <c r="AP2">
-        <v>18</v>
-      </c>
-      <c r="AQ2">
-        <v>13</v>
-      </c>
-      <c r="AR2">
-        <v>19</v>
-      </c>
-      <c r="AS2">
-        <v>32</v>
-      </c>
-      <c r="AT2">
-        <v>12</v>
-      </c>
-      <c r="AU2">
-        <v>8.6</v>
-      </c>
-      <c r="AV2">
-        <v>11.5</v>
-      </c>
-      <c r="AW2">
-        <v>24</v>
-      </c>
-      <c r="AX2">
-        <v>15</v>
-      </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BF2">
         <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI2">
         <v>3.6</v>
@@ -1246,55 +1246,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
         <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BR2">
         <v>25</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>23</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
         <v>155</v>
@@ -1317,55 +1317,55 @@
         <v>134</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
         <v>2.12</v>
       </c>
       <c r="I3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
         <v>1.58</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>1.19</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W3">
         <v>1.27</v>
@@ -1389,7 +1389,7 @@
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
         <v>30</v>
@@ -1401,16 +1401,16 @@
         <v>20</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL3">
         <v>120</v>
@@ -1440,16 +1440,16 @@
         <v>10</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
         <v>27</v>
       </c>
       <c r="AX3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY3">
         <v>18</v>
@@ -1458,22 +1458,22 @@
         <v>25</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BB3">
+        <v>40</v>
+      </c>
+      <c r="BC3">
         <v>65</v>
       </c>
-      <c r="BC3">
-        <v>60</v>
-      </c>
       <c r="BD3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG3">
         <v>25</v>
@@ -1488,13 +1488,13 @@
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
         <v>7.6</v>
@@ -1503,40 +1503,40 @@
         <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
         <v>80</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BT3">
         <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
         <v>46</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
         <v>155</v>
@@ -1559,22 +1559,22 @@
         <v>135</v>
       </c>
       <c r="F4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -1586,7 +1586,7 @@
         <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
         <v>1.79</v>
@@ -1604,13 +1604,13 @@
         <v>1.93</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1619,7 +1619,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA4">
         <v>29</v>
@@ -1652,7 +1652,7 @@
         <v>90</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL4">
         <v>75</v>
@@ -1661,10 +1661,10 @@
         <v>200</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP4">
         <v>10</v>
@@ -1676,7 +1676,7 @@
         <v>11.5</v>
       </c>
       <c r="AS4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT4">
         <v>11.5</v>
@@ -1688,7 +1688,7 @@
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX4">
         <v>23</v>
@@ -1751,7 +1751,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS4">
         <v>10</v>
@@ -1801,22 +1801,22 @@
         <v>136</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H5">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="I5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1825,46 +1825,46 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
         <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="T5">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U5">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB5">
         <v>23</v>
@@ -1882,46 +1882,46 @@
         <v>42</v>
       </c>
       <c r="AG5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL5">
         <v>65</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AO5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AP5">
         <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU5">
         <v>9.6</v>
@@ -1936,10 +1936,10 @@
         <v>34</v>
       </c>
       <c r="AY5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>23</v>
@@ -1951,76 +1951,76 @@
         <v>44</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BO5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BQ5">
         <v>10</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BV5">
         <v>11</v>
       </c>
       <c r="BW5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>155</v>
@@ -2052,13 +2052,13 @@
         <v>3.7</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>1.35</v>
@@ -2067,13 +2067,13 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
         <v>1.37</v>
       </c>
       <c r="P6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
         <v>2.04</v>
@@ -2082,16 +2082,16 @@
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="U6">
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
         <v>1.84</v>
@@ -2527,7 +2527,7 @@
         <v>139</v>
       </c>
       <c r="F8">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G8">
         <v>2.72</v>
@@ -2539,40 +2539,40 @@
         <v>3.65</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
         <v>1.35</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="R8">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
         <v>1.37</v>
@@ -2581,7 +2581,7 @@
         <v>1.58</v>
       </c>
       <c r="X8">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y8">
         <v>12.5</v>
@@ -2590,103 +2590,103 @@
         <v>26</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB8">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF8">
         <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
         <v>40</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM8">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO8">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AP8">
+        <v>4.2</v>
+      </c>
+      <c r="AQ8">
+        <v>3.95</v>
+      </c>
+      <c r="AR8">
+        <v>4.7</v>
+      </c>
+      <c r="AS8">
+        <v>5.3</v>
+      </c>
+      <c r="AT8">
+        <v>3.9</v>
+      </c>
+      <c r="AU8">
+        <v>3.5</v>
+      </c>
+      <c r="AV8">
+        <v>4.2</v>
+      </c>
+      <c r="AW8">
+        <v>5</v>
+      </c>
+      <c r="AX8">
+        <v>4.2</v>
+      </c>
+      <c r="AY8">
         <v>4</v>
       </c>
-      <c r="AQ8">
-        <v>4</v>
-      </c>
-      <c r="AR8">
-        <v>4.8</v>
-      </c>
-      <c r="AS8">
-        <v>5.5</v>
-      </c>
-      <c r="AT8">
-        <v>3.8</v>
-      </c>
-      <c r="AU8">
-        <v>3.35</v>
-      </c>
-      <c r="AV8">
+      <c r="AZ8">
         <v>4.4</v>
       </c>
-      <c r="AW8">
-        <v>5.3</v>
-      </c>
-      <c r="AX8">
-        <v>4.3</v>
-      </c>
-      <c r="AY8">
-        <v>4.1</v>
-      </c>
-      <c r="AZ8">
-        <v>4.6</v>
-      </c>
       <c r="BA8">
+        <v>5.2</v>
+      </c>
+      <c r="BB8">
+        <v>5</v>
+      </c>
+      <c r="BC8">
+        <v>4.9</v>
+      </c>
+      <c r="BD8">
+        <v>5.1</v>
+      </c>
+      <c r="BE8">
         <v>5.4</v>
       </c>
-      <c r="BB8">
-        <v>5.2</v>
-      </c>
-      <c r="BC8">
-        <v>5</v>
-      </c>
-      <c r="BD8">
-        <v>5.4</v>
-      </c>
-      <c r="BE8">
-        <v>5.7</v>
-      </c>
       <c r="BF8">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG8">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2772,19 +2772,19 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H9">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I9">
-        <v>4.1</v>
+        <v>110</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2814,13 +2814,13 @@
         <v>1.53</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3011,22 +3011,22 @@
         <v>141</v>
       </c>
       <c r="F10">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="G10">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="H10">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I10">
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>5.7</v>
       </c>
       <c r="K10">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3035,22 +3035,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.92</v>
+        <v>6.4</v>
       </c>
       <c r="O10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q10">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="R10">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="S10">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3062,7 +3062,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3253,19 +3253,19 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3283,16 +3283,16 @@
         <v>1.02</v>
       </c>
       <c r="P11">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="Q11">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="R11">
         <v>1.08</v>
       </c>
       <c r="S11">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3301,10 +3301,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3498,13 +3498,13 @@
         <v>3.75</v>
       </c>
       <c r="G12">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H12">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I12">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="J12">
         <v>4.3</v>
@@ -3513,7 +3513,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
         <v>1.01</v>
@@ -3531,22 +3531,22 @@
         <v>1.2</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S12">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="U12">
         <v>3.6</v>
       </c>
       <c r="V12">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="W12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3561,7 +3561,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC12">
         <v>970</v>
@@ -3582,7 +3582,7 @@
         <v>950</v>
       </c>
       <c r="AI12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ12">
         <v>1000</v>
@@ -3603,7 +3603,7 @@
         <v>970</v>
       </c>
       <c r="AP12">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AQ12">
         <v>17.5</v>
@@ -3612,10 +3612,10 @@
         <v>16</v>
       </c>
       <c r="AS12">
+        <v>15.5</v>
+      </c>
+      <c r="AT12">
         <v>1.85</v>
-      </c>
-      <c r="AT12">
-        <v>25</v>
       </c>
       <c r="AU12">
         <v>8.4</v>
@@ -3624,13 +3624,13 @@
         <v>9.4</v>
       </c>
       <c r="AW12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AX12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AY12">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AZ12">
         <v>8</v>
@@ -3639,10 +3639,10 @@
         <v>9.6</v>
       </c>
       <c r="BB12">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BC12">
-        <v>1.85</v>
+        <v>21</v>
       </c>
       <c r="BD12">
         <v>16.5</v>
@@ -3761,7 +3761,7 @@
         <v>1.11</v>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O13">
         <v>1.5</v>
@@ -3782,7 +3782,7 @@
         <v>2.34</v>
       </c>
       <c r="U13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
         <v>1.13</v>
@@ -3851,10 +3851,10 @@
         <v>12</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT13">
         <v>4.4</v>
@@ -3863,10 +3863,10 @@
         <v>6.4</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX13">
         <v>6.4</v>
@@ -3875,10 +3875,10 @@
         <v>8</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
@@ -3887,16 +3887,16 @@
         <v>17</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF13">
         <v>12.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3982,16 +3982,16 @@
         <v>1.97</v>
       </c>
       <c r="G14">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>4.2</v>
       </c>
       <c r="I14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
         <v>3.85</v>
@@ -4000,145 +4000,145 @@
         <v>1.38</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O14">
         <v>1.31</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q14">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T14">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U14">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
         <v>2</v>
       </c>
       <c r="X14">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB14">
         <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE14">
+        <v>60</v>
+      </c>
+      <c r="AF14">
+        <v>12.5</v>
+      </c>
+      <c r="AG14">
+        <v>11</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>70</v>
+      </c>
+      <c r="AJ14">
+        <v>24</v>
+      </c>
+      <c r="AK14">
+        <v>22</v>
+      </c>
+      <c r="AL14">
+        <v>40</v>
+      </c>
+      <c r="AM14">
         <v>110</v>
       </c>
-      <c r="AF14">
-        <v>19</v>
-      </c>
-      <c r="AG14">
-        <v>13</v>
-      </c>
-      <c r="AH14">
-        <v>23</v>
-      </c>
-      <c r="AI14">
-        <v>120</v>
-      </c>
-      <c r="AJ14">
-        <v>42</v>
-      </c>
-      <c r="AK14">
-        <v>26</v>
-      </c>
-      <c r="AL14">
-        <v>44</v>
-      </c>
-      <c r="AM14">
-        <v>220</v>
-      </c>
       <c r="AN14">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14">
+        <v>14.5</v>
+      </c>
+      <c r="AR14">
+        <v>24</v>
+      </c>
+      <c r="AS14">
+        <v>7.4</v>
+      </c>
+      <c r="AT14">
+        <v>7.6</v>
+      </c>
+      <c r="AU14">
+        <v>7.6</v>
+      </c>
+      <c r="AV14">
+        <v>15.5</v>
+      </c>
+      <c r="AW14">
+        <v>40</v>
+      </c>
+      <c r="AX14">
+        <v>9.4</v>
+      </c>
+      <c r="AY14">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14">
+        <v>16</v>
+      </c>
+      <c r="BA14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB14">
+        <v>11</v>
+      </c>
+      <c r="BC14">
+        <v>17</v>
+      </c>
+      <c r="BD14">
+        <v>27</v>
+      </c>
+      <c r="BE14">
+        <v>7.4</v>
+      </c>
+      <c r="BF14">
         <v>11.5</v>
       </c>
-      <c r="AR14">
-        <v>13.5</v>
-      </c>
-      <c r="AS14">
-        <v>42</v>
-      </c>
-      <c r="AT14">
-        <v>7.8</v>
-      </c>
-      <c r="AU14">
-        <v>6.8</v>
-      </c>
-      <c r="AV14">
-        <v>12.5</v>
-      </c>
-      <c r="AW14">
-        <v>23</v>
-      </c>
-      <c r="AX14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY14">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14">
-        <v>15</v>
-      </c>
-      <c r="BA14">
-        <v>25</v>
-      </c>
-      <c r="BB14">
-        <v>10.5</v>
-      </c>
-      <c r="BC14">
-        <v>15.5</v>
-      </c>
-      <c r="BD14">
-        <v>15</v>
-      </c>
-      <c r="BE14">
-        <v>3.5</v>
-      </c>
-      <c r="BF14">
-        <v>8.6</v>
-      </c>
       <c r="BG14">
-        <v>3.55</v>
+        <v>38</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4221,22 +4221,22 @@
         <v>146</v>
       </c>
       <c r="F15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G15">
         <v>4</v>
       </c>
       <c r="H15">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="I15">
         <v>2.02</v>
       </c>
       <c r="J15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>1.29</v>
@@ -4248,25 +4248,25 @@
         <v>4.6</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q15">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S15">
         <v>2.62</v>
       </c>
       <c r="T15">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
         <v>1.98</v>
@@ -4287,7 +4287,7 @@
         <v>25</v>
       </c>
       <c r="AB15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC15">
         <v>11</v>
@@ -4296,7 +4296,7 @@
         <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF15">
         <v>38</v>
@@ -4305,7 +4305,7 @@
         <v>17.5</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI15">
         <v>34</v>
@@ -4335,7 +4335,7 @@
         <v>9.6</v>
       </c>
       <c r="AR15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS15">
         <v>17.5</v>
@@ -4365,7 +4365,7 @@
         <v>5.7</v>
       </c>
       <c r="BB15">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC15">
         <v>6</v>
@@ -4374,13 +4374,13 @@
         <v>6</v>
       </c>
       <c r="BE15">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF15">
         <v>5.9</v>
       </c>
       <c r="BG15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15">
         <v>4.2</v>
@@ -4428,7 +4428,7 @@
         <v>13.5</v>
       </c>
       <c r="BW15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX15">
         <v>24</v>
@@ -4463,7 +4463,7 @@
         <v>147</v>
       </c>
       <c r="F16">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G16">
         <v>2.02</v>
@@ -4472,13 +4472,13 @@
         <v>4.9</v>
       </c>
       <c r="I16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L16">
         <v>1.61</v>
@@ -4487,55 +4487,55 @@
         <v>1.14</v>
       </c>
       <c r="N16">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q16">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S16">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T16">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U16">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W16">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>12</v>
       </c>
       <c r="Z16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC16">
         <v>8.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -4544,46 +4544,46 @@
         <v>10</v>
       </c>
       <c r="AG16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH16">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ16">
         <v>23</v>
       </c>
       <c r="AK16">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
         <v>290</v>
       </c>
       <c r="AN16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS16">
         <v>42</v>
       </c>
       <c r="AT16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU16">
         <v>7.4</v>
@@ -4595,13 +4595,13 @@
         <v>60</v>
       </c>
       <c r="AX16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA16">
         <v>65</v>
@@ -4610,10 +4610,10 @@
         <v>20</v>
       </c>
       <c r="BC16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD16">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE16">
         <v>50</v>
@@ -4634,13 +4634,13 @@
         <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN16">
         <v>4.3</v>
@@ -4649,7 +4649,7 @@
         <v>3.95</v>
       </c>
       <c r="BP16">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ16">
         <v>7.8</v>
@@ -4658,7 +4658,7 @@
         <v>55</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
         <v>8.6</v>
@@ -4670,19 +4670,19 @@
         <v>70</v>
       </c>
       <c r="BW16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX16">
         <v>100</v>
       </c>
       <c r="BY16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16">
         <v>55</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB16" t="s">
         <v>155</v>
@@ -4720,7 +4720,7 @@
         <v>3.55</v>
       </c>
       <c r="K17">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4729,7 +4729,7 @@
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
         <v>1.36</v>
@@ -4738,13 +4738,13 @@
         <v>1.84</v>
       </c>
       <c r="Q17">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R17">
         <v>1.32</v>
       </c>
       <c r="S17">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T17">
         <v>1.88</v>
@@ -4909,7 +4909,7 @@
         <v>5.3</v>
       </c>
       <c r="BV17">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="BW17">
         <v>1.83</v>
@@ -4947,22 +4947,22 @@
         <v>149</v>
       </c>
       <c r="F18">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J18">
+        <v>3.15</v>
+      </c>
+      <c r="K18">
         <v>3.2</v>
-      </c>
-      <c r="K18">
-        <v>3.35</v>
       </c>
       <c r="L18">
         <v>1.59</v>
@@ -4971,34 +4971,34 @@
         <v>1.16</v>
       </c>
       <c r="N18">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O18">
         <v>1.69</v>
       </c>
       <c r="P18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q18">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S18">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>2.58</v>
       </c>
       <c r="U18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V18">
         <v>1.22</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X18">
         <v>7.2</v>
@@ -5013,13 +5013,13 @@
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AC18">
         <v>8</v>
       </c>
       <c r="AD18">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE18">
         <v>1000</v>
@@ -5031,25 +5031,25 @@
         <v>12.5</v>
       </c>
       <c r="AH18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI18">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK18">
         <v>34</v>
       </c>
       <c r="AL18">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
         <v>360</v>
       </c>
       <c r="AN18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO18">
         <v>1000</v>
@@ -5061,19 +5061,19 @@
         <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AS18">
         <v>44</v>
       </c>
       <c r="AT18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU18">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW18">
         <v>60</v>
@@ -5082,22 +5082,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BA18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB18">
         <v>20</v>
       </c>
       <c r="BC18">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BD18">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BE18">
         <v>100</v>
@@ -5109,22 +5109,22 @@
         <v>100</v>
       </c>
       <c r="BH18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
         <v>2.2</v>
       </c>
       <c r="BJ18">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="BN18">
         <v>5.9</v>
@@ -5133,19 +5133,19 @@
         <v>3.3</v>
       </c>
       <c r="BP18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="BT18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
         <v>5.3</v>
@@ -5154,19 +5154,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="CB18" t="s">
         <v>155</v>
@@ -5189,16 +5189,16 @@
         <v>150</v>
       </c>
       <c r="F19">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G19">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H19">
         <v>5.6</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>3.6</v>
@@ -5213,16 +5213,16 @@
         <v>1.09</v>
       </c>
       <c r="N19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O19">
         <v>1.42</v>
       </c>
       <c r="P19">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R19">
         <v>1.27</v>
@@ -5231,22 +5231,22 @@
         <v>4.4</v>
       </c>
       <c r="T19">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U19">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W19">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X19">
         <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z19">
         <v>46</v>
@@ -5267,7 +5267,7 @@
         <v>1000</v>
       </c>
       <c r="AF19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG19">
         <v>11</v>
@@ -5279,7 +5279,7 @@
         <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK19">
         <v>22</v>
@@ -5291,7 +5291,7 @@
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO19">
         <v>1000</v>
@@ -5306,7 +5306,7 @@
         <v>32</v>
       </c>
       <c r="AS19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT19">
         <v>6.6</v>
@@ -5321,7 +5321,7 @@
         <v>36</v>
       </c>
       <c r="AX19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY19">
         <v>9.6</v>
@@ -5336,7 +5336,7 @@
         <v>15.5</v>
       </c>
       <c r="BC19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD19">
         <v>38</v>
@@ -5431,22 +5431,22 @@
         <v>151</v>
       </c>
       <c r="F20">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="G20">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="H20">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I20">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="J20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L20">
         <v>1.2</v>
@@ -5461,28 +5461,28 @@
         <v>1.29</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R20">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S20">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
         <v>1.69</v>
       </c>
       <c r="U20">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="X20">
         <v>21</v>
@@ -5491,7 +5491,7 @@
         <v>13.5</v>
       </c>
       <c r="Z20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA20">
         <v>40</v>
@@ -5509,7 +5509,7 @@
         <v>28</v>
       </c>
       <c r="AF20">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AG20">
         <v>13</v>
@@ -5521,10 +5521,10 @@
         <v>40</v>
       </c>
       <c r="AJ20">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AK20">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL20">
         <v>42</v>
@@ -5533,64 +5533,64 @@
         <v>90</v>
       </c>
       <c r="AN20">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ20">
         <v>10</v>
       </c>
       <c r="AR20">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU20">
         <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX20">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AY20">
         <v>11</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BB20">
         <v>29</v>
       </c>
       <c r="BC20">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD20">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BE20">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BF20">
         <v>20</v>
       </c>
       <c r="BG20">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5924,13 +5924,13 @@
         <v>6.8</v>
       </c>
       <c r="I22">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
         <v>3.85</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
         <v>1.35</v>
@@ -5954,7 +5954,7 @@
         <v>1.3</v>
       </c>
       <c r="S22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T22">
         <v>2.14</v>
@@ -5978,7 +5978,7 @@
         <v>80</v>
       </c>
       <c r="AA22">
-        <v>990</v>
+        <v>900</v>
       </c>
       <c r="AB22">
         <v>7.2</v>
@@ -5990,7 +5990,7 @@
         <v>36</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AF22">
         <v>9</v>
@@ -6002,25 +6002,25 @@
         <v>32</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AJ22">
         <v>18.5</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL22">
         <v>55</v>
       </c>
       <c r="AM22">
-        <v>990</v>
+        <v>900</v>
       </c>
       <c r="AN22">
         <v>11.5</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AP22">
         <v>11</v>
@@ -6029,7 +6029,7 @@
         <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS22">
         <v>7.4</v>
@@ -6044,7 +6044,7 @@
         <v>21</v>
       </c>
       <c r="AW22">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22">
         <v>7.4</v>
@@ -6056,7 +6056,7 @@
         <v>19</v>
       </c>
       <c r="BA22">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB22">
         <v>12.5</v>
@@ -6068,7 +6068,7 @@
         <v>36</v>
       </c>
       <c r="BE22">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22">
         <v>9.6</v>
@@ -6187,10 +6187,10 @@
         <v>1.3</v>
       </c>
       <c r="P23">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q23">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R23">
         <v>1.37</v>
@@ -6286,7 +6286,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX23">
         <v>12.5</v>
@@ -6310,7 +6310,7 @@
         <v>7.6</v>
       </c>
       <c r="BE23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF23">
         <v>14.5</v>
@@ -6328,7 +6328,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK23">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -481,7 +481,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 19:16:20</t>
+    <t>2026-10-04 21:27:43</t>
   </si>
 </sst>
 </file>
@@ -1075,214 +1075,214 @@
         <v>133</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>1.14</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>1.15</v>
       </c>
       <c r="H2">
-        <v>2.86</v>
+        <v>24</v>
       </c>
       <c r="I2">
-        <v>2.92</v>
+        <v>28</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.13</v>
       </c>
       <c r="R2">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="S2">
-        <v>2.82</v>
+        <v>1.67</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="V2">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>7.6</v>
       </c>
       <c r="X2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>8.4</v>
+      </c>
+      <c r="AG2">
+        <v>8</v>
+      </c>
+      <c r="AH2">
+        <v>17</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>7</v>
+      </c>
+      <c r="AK2">
+        <v>7.6</v>
+      </c>
+      <c r="AL2">
+        <v>16.5</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>3.8</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2">
+        <v>14.5</v>
+      </c>
+      <c r="AR2">
+        <v>14.5</v>
+      </c>
+      <c r="AS2">
+        <v>14.5</v>
+      </c>
+      <c r="AT2">
+        <v>14.5</v>
+      </c>
+      <c r="AU2">
+        <v>14.5</v>
+      </c>
+      <c r="AV2">
         <v>29</v>
       </c>
-      <c r="AF2">
-        <v>17</v>
-      </c>
-      <c r="AG2">
+      <c r="AW2">
+        <v>29</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>42</v>
+      </c>
+      <c r="BB2">
+        <v>6.6</v>
+      </c>
+      <c r="BC2">
+        <v>7.2</v>
+      </c>
+      <c r="BD2">
+        <v>14.5</v>
+      </c>
+      <c r="BE2">
+        <v>44</v>
+      </c>
+      <c r="BF2">
+        <v>3.4</v>
+      </c>
+      <c r="BG2">
+        <v>55</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>10</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>10</v>
+      </c>
+      <c r="BL2">
+        <v>960</v>
+      </c>
+      <c r="BM2">
         <v>11</v>
       </c>
-      <c r="AH2">
-        <v>18</v>
-      </c>
-      <c r="AI2">
-        <v>38</v>
-      </c>
-      <c r="AJ2">
-        <v>34</v>
-      </c>
-      <c r="AK2">
-        <v>27</v>
-      </c>
-      <c r="AL2">
-        <v>32</v>
-      </c>
-      <c r="AM2">
-        <v>80</v>
-      </c>
-      <c r="AN2">
-        <v>16</v>
-      </c>
-      <c r="AO2">
-        <v>20</v>
-      </c>
-      <c r="AP2">
-        <v>19</v>
-      </c>
-      <c r="AQ2">
-        <v>14</v>
-      </c>
-      <c r="AR2">
-        <v>18.5</v>
-      </c>
-      <c r="AS2">
-        <v>34</v>
-      </c>
-      <c r="AT2">
-        <v>11.5</v>
-      </c>
-      <c r="AU2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>26</v>
-      </c>
-      <c r="AX2">
-        <v>15.5</v>
-      </c>
-      <c r="AY2">
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
         <v>10</v>
       </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>32</v>
-      </c>
-      <c r="BB2">
-        <v>29</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>27</v>
-      </c>
-      <c r="BE2">
-        <v>60</v>
-      </c>
-      <c r="BF2">
-        <v>13.5</v>
-      </c>
-      <c r="BG2">
-        <v>17</v>
-      </c>
-      <c r="BH2">
-        <v>4.1</v>
-      </c>
-      <c r="BI2">
-        <v>3.6</v>
-      </c>
-      <c r="BJ2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK2">
-        <v>6.8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>13.5</v>
-      </c>
-      <c r="BN2">
+      <c r="BP2">
+        <v>1.87</v>
+      </c>
+      <c r="BQ2">
+        <v>1.82</v>
+      </c>
+      <c r="BR2">
+        <v>6.6</v>
+      </c>
+      <c r="BS2">
         <v>5.5</v>
       </c>
-      <c r="BO2">
-        <v>5</v>
-      </c>
-      <c r="BP2">
-        <v>15.5</v>
-      </c>
-      <c r="BQ2">
-        <v>12</v>
-      </c>
-      <c r="BR2">
-        <v>25</v>
-      </c>
-      <c r="BS2">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BV2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1291,10 +1291,10 @@
         <v>10</v>
       </c>
       <c r="BZ2">
-        <v>18.5</v>
+        <v>3.9</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>3.35</v>
       </c>
       <c r="CB2" t="s">
         <v>155</v>
@@ -1317,19 +1317,19 @@
         <v>134</v>
       </c>
       <c r="F3">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="G3">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H3">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.3</v>
@@ -1341,202 +1341,202 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="W3">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="Z3">
+        <v>11.5</v>
+      </c>
+      <c r="AA3">
+        <v>30</v>
+      </c>
+      <c r="AB3">
         <v>11</v>
-      </c>
-      <c r="AA3">
-        <v>27</v>
-      </c>
-      <c r="AB3">
-        <v>11.5</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE3">
         <v>30</v>
       </c>
       <c r="AF3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
+        <v>25</v>
+      </c>
+      <c r="AI3">
+        <v>60</v>
+      </c>
+      <c r="AJ3">
+        <v>110</v>
+      </c>
+      <c r="AK3">
+        <v>75</v>
+      </c>
+      <c r="AL3">
+        <v>95</v>
+      </c>
+      <c r="AM3">
+        <v>200</v>
+      </c>
+      <c r="AN3">
+        <v>110</v>
+      </c>
+      <c r="AO3">
+        <v>30</v>
+      </c>
+      <c r="AP3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>6.8</v>
+      </c>
+      <c r="AR3">
+        <v>10.5</v>
+      </c>
+      <c r="AS3">
         <v>26</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>85</v>
-      </c>
-      <c r="AL3">
-        <v>120</v>
-      </c>
-      <c r="AM3">
-        <v>260</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>28</v>
-      </c>
-      <c r="AP3">
-        <v>7.6</v>
-      </c>
-      <c r="AQ3">
-        <v>6</v>
-      </c>
-      <c r="AR3">
-        <v>10</v>
-      </c>
-      <c r="AS3">
-        <v>24</v>
       </c>
       <c r="AT3">
         <v>10</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AY3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AZ3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA3">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BB3">
+        <v>80</v>
+      </c>
+      <c r="BC3">
+        <v>60</v>
+      </c>
+      <c r="BD3">
+        <v>50</v>
+      </c>
+      <c r="BE3">
+        <v>140</v>
+      </c>
+      <c r="BF3">
         <v>40</v>
       </c>
-      <c r="BC3">
+      <c r="BG3">
+        <v>26</v>
+      </c>
+      <c r="BH3">
+        <v>2.66</v>
+      </c>
+      <c r="BI3">
+        <v>2.54</v>
+      </c>
+      <c r="BJ3">
+        <v>11.5</v>
+      </c>
+      <c r="BK3">
+        <v>9.6</v>
+      </c>
+      <c r="BL3">
+        <v>250</v>
+      </c>
+      <c r="BM3">
+        <v>180</v>
+      </c>
+      <c r="BN3">
+        <v>7.2</v>
+      </c>
+      <c r="BO3">
+        <v>6.4</v>
+      </c>
+      <c r="BP3">
+        <v>42</v>
+      </c>
+      <c r="BQ3">
+        <v>15</v>
+      </c>
+      <c r="BR3">
         <v>65</v>
       </c>
-      <c r="BD3">
-        <v>65</v>
-      </c>
-      <c r="BE3">
-        <v>50</v>
-      </c>
-      <c r="BF3">
-        <v>46</v>
-      </c>
-      <c r="BG3">
-        <v>25</v>
-      </c>
-      <c r="BH3">
-        <v>2.64</v>
-      </c>
-      <c r="BI3">
-        <v>2.48</v>
-      </c>
-      <c r="BJ3">
-        <v>13.5</v>
-      </c>
-      <c r="BK3">
-        <v>7.8</v>
-      </c>
-      <c r="BL3">
-        <v>260</v>
-      </c>
-      <c r="BM3">
-        <v>15.5</v>
-      </c>
-      <c r="BN3">
-        <v>7.6</v>
-      </c>
-      <c r="BO3">
-        <v>6.8</v>
-      </c>
-      <c r="BP3">
-        <v>48</v>
-      </c>
-      <c r="BQ3">
-        <v>12.5</v>
-      </c>
-      <c r="BR3">
-        <v>80</v>
-      </c>
       <c r="BS3">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BT3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BW3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BZ3">
         <v>46</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="CB3" t="s">
         <v>155</v>
@@ -1559,16 +1559,16 @@
         <v>135</v>
       </c>
       <c r="F4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H4">
         <v>2.18</v>
       </c>
       <c r="I4">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J4">
         <v>3.3</v>
@@ -1583,31 +1583,31 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.24</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
         <v>2</v>
       </c>
       <c r="V4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W4">
         <v>1.32</v>
@@ -1622,7 +1622,7 @@
         <v>13</v>
       </c>
       <c r="AA4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AB4">
         <v>13</v>
@@ -1637,28 +1637,28 @@
         <v>25</v>
       </c>
       <c r="AF4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG4">
         <v>16.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
+        <v>46</v>
+      </c>
+      <c r="AJ4">
+        <v>85</v>
+      </c>
+      <c r="AK4">
         <v>55</v>
-      </c>
-      <c r="AJ4">
-        <v>90</v>
-      </c>
-      <c r="AK4">
-        <v>65</v>
       </c>
       <c r="AL4">
         <v>75</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AN4">
         <v>70</v>
@@ -1670,19 +1670,19 @@
         <v>10</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR4">
         <v>11.5</v>
       </c>
       <c r="AS4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>10</v>
@@ -1691,37 +1691,37 @@
         <v>22</v>
       </c>
       <c r="AX4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BC4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD4">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="BE4">
         <v>85</v>
       </c>
       <c r="BF4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BG4">
         <v>18.5</v>
       </c>
       <c r="BH4">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
         <v>2.86</v>
@@ -1736,7 +1736,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1748,13 +1748,13 @@
         <v>34</v>
       </c>
       <c r="BQ4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BT4">
         <v>4.9</v>
@@ -1766,19 +1766,19 @@
         <v>17</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BX4">
         <v>34</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>155</v>
@@ -1801,22 +1801,22 @@
         <v>136</v>
       </c>
       <c r="F5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="I5">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1825,37 +1825,37 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
         <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
         <v>1.71</v>
       </c>
       <c r="U5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="W5">
         <v>1.23</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5">
         <v>11.5</v>
@@ -1864,7 +1864,7 @@
         <v>12</v>
       </c>
       <c r="AA5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AB5">
         <v>23</v>
@@ -1876,49 +1876,49 @@
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH5">
         <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK5">
         <v>60</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN5">
         <v>55</v>
       </c>
       <c r="AO5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
         <v>10.5</v>
       </c>
       <c r="AS5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT5">
         <v>19.5</v>
@@ -1927,28 +1927,28 @@
         <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW5">
         <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AY5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BD5">
         <v>36</v>
@@ -1957,13 +1957,13 @@
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BG5">
         <v>7</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>3.9</v>
@@ -1972,19 +1972,19 @@
         <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN5">
         <v>9</v>
       </c>
       <c r="BO5">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BP5">
         <v>38</v>
@@ -1996,7 +1996,7 @@
         <v>40</v>
       </c>
       <c r="BS5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>4.6</v>
@@ -2008,19 +2008,19 @@
         <v>11</v>
       </c>
       <c r="BW5">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
         <v>22</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
         <v>155</v>
@@ -2043,7 +2043,7 @@
         <v>137</v>
       </c>
       <c r="F6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G6">
         <v>2.18</v>
@@ -2067,7 +2067,7 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>2.98</v>
       </c>
       <c r="O6">
         <v>1.37</v>
@@ -2082,19 +2082,19 @@
         <v>1.25</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U6">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="V6">
         <v>1.21</v>
       </c>
       <c r="W6">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2530,7 +2530,7 @@
         <v>2.3</v>
       </c>
       <c r="G8">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H8">
         <v>3.05</v>
@@ -2539,10 +2539,10 @@
         <v>3.65</v>
       </c>
       <c r="J8">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
         <v>1.35</v>
@@ -2551,22 +2551,22 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
         <v>1.32</v>
       </c>
       <c r="P8">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
         <v>1.96</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T8">
         <v>1.74</v>
@@ -2578,7 +2578,7 @@
         <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
         <v>15.5</v>
@@ -2611,7 +2611,7 @@
         <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
         <v>55</v>
@@ -2623,7 +2623,7 @@
         <v>32</v>
       </c>
       <c r="AL8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM8">
         <v>110</v>
@@ -2632,61 +2632,61 @@
         <v>26</v>
       </c>
       <c r="AO8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR8">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="AS8">
+        <v>5.5</v>
+      </c>
+      <c r="AT8">
+        <v>7.8</v>
+      </c>
+      <c r="AU8">
+        <v>3.6</v>
+      </c>
+      <c r="AV8">
+        <v>11</v>
+      </c>
+      <c r="AW8">
         <v>5.3</v>
       </c>
-      <c r="AT8">
-        <v>3.9</v>
-      </c>
-      <c r="AU8">
-        <v>3.5</v>
-      </c>
-      <c r="AV8">
-        <v>4.2</v>
-      </c>
-      <c r="AW8">
-        <v>5</v>
-      </c>
       <c r="AX8">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ8">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
+        <v>5.4</v>
+      </c>
+      <c r="BB8">
         <v>5.2</v>
       </c>
-      <c r="BB8">
-        <v>5</v>
-      </c>
       <c r="BC8">
+        <v>5.7</v>
+      </c>
+      <c r="BD8">
+        <v>5.3</v>
+      </c>
+      <c r="BE8">
+        <v>5.7</v>
+      </c>
+      <c r="BF8">
         <v>4.9</v>
       </c>
-      <c r="BD8">
-        <v>5.1</v>
-      </c>
-      <c r="BE8">
-        <v>5.4</v>
-      </c>
-      <c r="BF8">
-        <v>4.7</v>
-      </c>
       <c r="BG8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2772,19 +2772,19 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H9">
         <v>2.96</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2817,10 +2817,10 @@
         <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3011,22 +3011,22 @@
         <v>141</v>
       </c>
       <c r="F10">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="G10">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="H10">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
         <v>990</v>
       </c>
       <c r="J10">
-        <v>5.7</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3038,16 +3038,16 @@
         <v>6.4</v>
       </c>
       <c r="O10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
         <v>1.49</v>
@@ -3062,7 +3062,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3253,19 +3253,19 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3286,13 +3286,13 @@
         <v>1.13</v>
       </c>
       <c r="Q11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R11">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3301,10 +3301,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3495,16 +3495,16 @@
         <v>143</v>
       </c>
       <c r="F12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G12">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H12">
         <v>1.75</v>
       </c>
       <c r="I12">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="J12">
         <v>4.3</v>
@@ -3519,7 +3519,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O12">
         <v>1.05</v>
@@ -3531,7 +3531,7 @@
         <v>1.2</v>
       </c>
       <c r="R12">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
         <v>1.56</v>
@@ -3540,13 +3540,13 @@
         <v>1.27</v>
       </c>
       <c r="U12">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V12">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="W12">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3573,16 +3573,16 @@
         <v>23</v>
       </c>
       <c r="AF12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG12">
         <v>950</v>
       </c>
       <c r="AH12">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI12">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ12">
         <v>1000</v>
@@ -3603,7 +3603,7 @@
         <v>970</v>
       </c>
       <c r="AP12">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AQ12">
         <v>17.5</v>
@@ -3612,10 +3612,10 @@
         <v>16</v>
       </c>
       <c r="AS12">
-        <v>15.5</v>
+        <v>1.99</v>
       </c>
       <c r="AT12">
-        <v>1.85</v>
+        <v>26</v>
       </c>
       <c r="AU12">
         <v>8.4</v>
@@ -3624,13 +3624,13 @@
         <v>9.4</v>
       </c>
       <c r="AW12">
-        <v>1.73</v>
+        <v>11</v>
       </c>
       <c r="AX12">
-        <v>1.83</v>
+        <v>25</v>
       </c>
       <c r="AY12">
-        <v>1.76</v>
+        <v>14.5</v>
       </c>
       <c r="AZ12">
         <v>8</v>
@@ -3639,19 +3639,19 @@
         <v>9.6</v>
       </c>
       <c r="BB12">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>1.99</v>
       </c>
       <c r="BD12">
-        <v>16.5</v>
+        <v>1.99</v>
       </c>
       <c r="BE12">
-        <v>18.5</v>
+        <v>1.99</v>
       </c>
       <c r="BF12">
-        <v>8.4</v>
+        <v>1.99</v>
       </c>
       <c r="BG12">
         <v>3.65</v>
@@ -3782,7 +3782,7 @@
         <v>2.34</v>
       </c>
       <c r="U13">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V13">
         <v>1.13</v>
@@ -3979,10 +3979,10 @@
         <v>145</v>
       </c>
       <c r="F14">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H14">
         <v>4.2</v>
@@ -3991,7 +3991,7 @@
         <v>4.5</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
         <v>3.85</v>
@@ -4003,40 +4003,40 @@
         <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O14">
         <v>1.31</v>
       </c>
       <c r="P14">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q14">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T14">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V14">
         <v>1.29</v>
       </c>
       <c r="W14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X14">
         <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="Z14">
         <v>36</v>
@@ -4048,7 +4048,7 @@
         <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD14">
         <v>18</v>
@@ -4069,7 +4069,7 @@
         <v>70</v>
       </c>
       <c r="AJ14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK14">
         <v>22</v>
@@ -4081,13 +4081,13 @@
         <v>110</v>
       </c>
       <c r="AN14">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO14">
         <v>60</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14">
         <v>14.5</v>
@@ -4096,49 +4096,49 @@
         <v>24</v>
       </c>
       <c r="AS14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT14">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU14">
         <v>7.6</v>
       </c>
       <c r="AV14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX14">
         <v>9.4</v>
       </c>
       <c r="AY14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC14">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
         <v>11.5</v>
       </c>
       <c r="BG14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4230,16 +4230,16 @@
         <v>1.81</v>
       </c>
       <c r="I15">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.04</v>
@@ -4269,7 +4269,7 @@
         <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="W15">
         <v>1.33</v>
@@ -4296,7 +4296,7 @@
         <v>11.5</v>
       </c>
       <c r="AE15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF15">
         <v>38</v>
@@ -4353,7 +4353,7 @@
         <v>15</v>
       </c>
       <c r="AX15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY15">
         <v>13.5</v>
@@ -4362,7 +4362,7 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB15">
         <v>6.4</v>
@@ -4377,70 +4377,70 @@
         <v>6.4</v>
       </c>
       <c r="BF15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG15">
         <v>8.199999999999999</v>
       </c>
       <c r="BH15">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>155</v>
@@ -4463,40 +4463,40 @@
         <v>147</v>
       </c>
       <c r="F16">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G16">
         <v>2.02</v>
       </c>
       <c r="H16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J16">
         <v>3.25</v>
       </c>
       <c r="K16">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L16">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="M16">
         <v>1.14</v>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
         <v>1.17</v>
@@ -4505,10 +4505,10 @@
         <v>6.2</v>
       </c>
       <c r="T16">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U16">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V16">
         <v>1.24</v>
@@ -4532,7 +4532,7 @@
         <v>5.9</v>
       </c>
       <c r="AC16">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
         <v>24</v>
@@ -4544,7 +4544,7 @@
         <v>10</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
         <v>32</v>
@@ -4577,40 +4577,40 @@
         <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AS16">
         <v>42</v>
       </c>
       <c r="AT16">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU16">
         <v>7.4</v>
       </c>
       <c r="AV16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW16">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AX16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BA16">
         <v>65</v>
       </c>
       <c r="BB16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD16">
         <v>34</v>
@@ -4622,10 +4622,10 @@
         <v>20</v>
       </c>
       <c r="BG16">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH16">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="BI16">
         <v>2.46</v>
@@ -4634,13 +4634,13 @@
         <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN16">
         <v>4.3</v>
@@ -4652,13 +4652,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ16">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR16">
         <v>55</v>
       </c>
       <c r="BS16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT16">
         <v>8.6</v>
@@ -4670,19 +4670,19 @@
         <v>70</v>
       </c>
       <c r="BW16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX16">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BY16">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ16">
         <v>55</v>
       </c>
       <c r="CA16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB16" t="s">
         <v>155</v>
@@ -4705,13 +4705,13 @@
         <v>148</v>
       </c>
       <c r="F17">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I17">
         <v>4.9</v>
@@ -4726,10 +4726,10 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
         <v>1.36</v>
@@ -4756,7 +4756,7 @@
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X17">
         <v>13.5</v>
@@ -4768,7 +4768,7 @@
         <v>40</v>
       </c>
       <c r="AA17">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB17">
         <v>8.800000000000001</v>
@@ -4807,7 +4807,7 @@
         <v>140</v>
       </c>
       <c r="AN17">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO17">
         <v>90</v>
@@ -4819,10 +4819,10 @@
         <v>13</v>
       </c>
       <c r="AR17">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17">
         <v>7.4</v>
@@ -4834,19 +4834,19 @@
         <v>15.5</v>
       </c>
       <c r="AW17">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX17">
         <v>10</v>
       </c>
       <c r="AY17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ17">
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB17">
         <v>17</v>
@@ -4855,16 +4855,16 @@
         <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE17">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF17">
         <v>12.5</v>
       </c>
       <c r="BG17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>5.3</v>
       </c>
       <c r="BV17">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="BW17">
         <v>1.83</v>
@@ -4947,19 +4947,19 @@
         <v>149</v>
       </c>
       <c r="F18">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G18">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="H18">
+        <v>4.7</v>
+      </c>
+      <c r="I18">
         <v>5.1</v>
       </c>
-      <c r="I18">
-        <v>5.5</v>
-      </c>
       <c r="J18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K18">
         <v>3.2</v>
@@ -4971,16 +4971,16 @@
         <v>1.16</v>
       </c>
       <c r="N18">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O18">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R18">
         <v>1.15</v>
@@ -4989,67 +4989,67 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U18">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V18">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W18">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="X18">
         <v>7.2</v>
       </c>
       <c r="Y18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA18">
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD18">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE18">
         <v>1000</v>
       </c>
       <c r="AF18">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG18">
         <v>12.5</v>
       </c>
       <c r="AH18">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI18">
         <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK18">
         <v>34</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM18">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AN18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO18">
         <v>1000</v>
@@ -5058,19 +5058,19 @@
         <v>6.6</v>
       </c>
       <c r="AQ18">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR18">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AS18">
         <v>44</v>
       </c>
       <c r="AT18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV18">
         <v>20</v>
@@ -5079,37 +5079,37 @@
         <v>60</v>
       </c>
       <c r="AX18">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY18">
         <v>11</v>
       </c>
       <c r="AZ18">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BA18">
+        <v>44</v>
+      </c>
+      <c r="BB18">
+        <v>23</v>
+      </c>
+      <c r="BC18">
+        <v>23</v>
+      </c>
+      <c r="BD18">
+        <v>55</v>
+      </c>
+      <c r="BE18">
+        <v>95</v>
+      </c>
+      <c r="BF18">
+        <v>19.5</v>
+      </c>
+      <c r="BG18">
         <v>46</v>
       </c>
-      <c r="BB18">
-        <v>20</v>
-      </c>
-      <c r="BC18">
-        <v>19.5</v>
-      </c>
-      <c r="BD18">
-        <v>48</v>
-      </c>
-      <c r="BE18">
-        <v>100</v>
-      </c>
-      <c r="BF18">
-        <v>19</v>
-      </c>
-      <c r="BG18">
-        <v>100</v>
-      </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI18">
         <v>2.2</v>
@@ -5118,13 +5118,13 @@
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="BN18">
         <v>5.9</v>
@@ -5136,13 +5136,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="BT18">
         <v>1000</v>
@@ -5154,19 +5154,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="CB18" t="s">
         <v>155</v>
@@ -5204,37 +5204,37 @@
         <v>3.6</v>
       </c>
       <c r="K19">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L19">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O19">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P19">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R19">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T19">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V19">
         <v>1.2</v>
@@ -5243,7 +5243,7 @@
         <v>2.2</v>
       </c>
       <c r="X19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y19">
         <v>16</v>
@@ -5255,7 +5255,7 @@
         <v>1000</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC19">
         <v>8.4</v>
@@ -5285,7 +5285,7 @@
         <v>22</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM19">
         <v>1000</v>
@@ -5297,7 +5297,7 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19">
         <v>14</v>
@@ -5306,10 +5306,10 @@
         <v>32</v>
       </c>
       <c r="AS19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT19">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU19">
         <v>7.6</v>
@@ -5324,7 +5324,7 @@
         <v>8.6</v>
       </c>
       <c r="AY19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
         <v>21</v>
@@ -5548,7 +5548,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT20">
         <v>11</v>
@@ -5560,7 +5560,7 @@
         <v>10.5</v>
       </c>
       <c r="AW20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX20">
         <v>16.5</v>
@@ -5581,7 +5581,7 @@
         <v>13.5</v>
       </c>
       <c r="BD20">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE20">
         <v>30</v>
@@ -5682,13 +5682,13 @@
         <v>2.36</v>
       </c>
       <c r="I21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J21">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K21">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5921,10 +5921,10 @@
         <v>1.65</v>
       </c>
       <c r="H22">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>3.85</v>
@@ -5939,7 +5939,7 @@
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O22">
         <v>1.37</v>
@@ -5957,7 +5957,7 @@
         <v>3.8</v>
       </c>
       <c r="T22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U22">
         <v>1.76</v>
@@ -5966,19 +5966,19 @@
         <v>1.14</v>
       </c>
       <c r="W22">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X22">
         <v>13.5</v>
       </c>
       <c r="Y22">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z22">
         <v>80</v>
       </c>
       <c r="AA22">
-        <v>900</v>
+        <v>780</v>
       </c>
       <c r="AB22">
         <v>7.2</v>
@@ -5987,13 +5987,13 @@
         <v>9.6</v>
       </c>
       <c r="AD22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE22">
-        <v>910</v>
+        <v>790</v>
       </c>
       <c r="AF22">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG22">
         <v>10.5</v>
@@ -6002,10 +6002,10 @@
         <v>32</v>
       </c>
       <c r="AI22">
-        <v>910</v>
+        <v>790</v>
       </c>
       <c r="AJ22">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK22">
         <v>19.5</v>
@@ -6014,13 +6014,13 @@
         <v>55</v>
       </c>
       <c r="AM22">
-        <v>900</v>
+        <v>780</v>
       </c>
       <c r="AN22">
         <v>11.5</v>
       </c>
       <c r="AO22">
-        <v>910</v>
+        <v>790</v>
       </c>
       <c r="AP22">
         <v>11</v>
@@ -6029,34 +6029,34 @@
         <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS22">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22">
         <v>6</v>
       </c>
       <c r="AU22">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22">
         <v>21</v>
       </c>
       <c r="AW22">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX22">
         <v>7.4</v>
       </c>
       <c r="AY22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22">
         <v>19</v>
       </c>
       <c r="BA22">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB22">
         <v>12.5</v>
@@ -6068,13 +6068,13 @@
         <v>36</v>
       </c>
       <c r="BE22">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22">
         <v>9.6</v>
       </c>
       <c r="BG22">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6160,19 +6160,19 @@
         <v>2.18</v>
       </c>
       <c r="G23">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H23">
         <v>3.25</v>
       </c>
       <c r="I23">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J23">
         <v>3.6</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L23">
         <v>1.38</v>
@@ -6181,13 +6181,13 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O23">
         <v>1.3</v>
       </c>
       <c r="P23">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q23">
         <v>1.89</v>
@@ -6199,16 +6199,16 @@
         <v>3.2</v>
       </c>
       <c r="T23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U23">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V23">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X23">
         <v>16</v>
@@ -6217,19 +6217,19 @@
         <v>14.5</v>
       </c>
       <c r="Z23">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AA23">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB23">
         <v>11</v>
       </c>
       <c r="AC23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE23">
         <v>42</v>
@@ -6247,7 +6247,7 @@
         <v>60</v>
       </c>
       <c r="AJ23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK23">
         <v>25</v>
@@ -6262,7 +6262,7 @@
         <v>17.5</v>
       </c>
       <c r="AO23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP23">
         <v>13</v>
@@ -6277,7 +6277,7 @@
         <v>22</v>
       </c>
       <c r="AT23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU23">
         <v>7.2</v>
@@ -6286,37 +6286,37 @@
         <v>12.5</v>
       </c>
       <c r="AW23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX23">
         <v>12.5</v>
       </c>
       <c r="AY23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23">
         <v>14.5</v>
       </c>
       <c r="BA23">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB23">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BC23">
         <v>20</v>
       </c>
       <c r="BD23">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BE23">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF23">
         <v>14.5</v>
       </c>
       <c r="BG23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH23">
         <v>3.6</v>
@@ -6340,19 +6340,19 @@
         <v>5.3</v>
       </c>
       <c r="BO23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP23">
         <v>17</v>
       </c>
       <c r="BQ23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR23">
         <v>30</v>
       </c>
       <c r="BS23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23">
         <v>7</v>
@@ -6367,7 +6367,7 @@
         <v>8</v>
       </c>
       <c r="BX23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY23">
         <v>8.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="150">
   <si>
     <t>League</t>
   </si>
@@ -256,39 +256,39 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>CONCACAF Nations League A</t>
   </si>
   <si>
+    <t>Serbian First League</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Turkish 2 Lig</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Argentinian Primera B Metropolitana</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
-    <t>Serbian First League</t>
-  </si>
-  <si>
-    <t>Paraguayan Primera Division</t>
-  </si>
-  <si>
-    <t>Slovakian 2 Liga</t>
-  </si>
-  <si>
-    <t>Turkish 2 Lig</t>
-  </si>
-  <si>
-    <t>Norwegian 1st Division</t>
-  </si>
-  <si>
-    <t>Argentinian Primera B Metropolitana</t>
-  </si>
-  <si>
-    <t>Spanish Segunda Division</t>
-  </si>
-  <si>
-    <t>CONCACAF Nations League B</t>
-  </si>
-  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -298,12 +298,6 @@
     <t>2026-10-05</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
-    <t>00:30:00</t>
-  </si>
-  <si>
     <t>01:15:00</t>
   </si>
   <si>
@@ -349,12 +343,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
-    <t>Estudiantes Rio Cuarto</t>
-  </si>
-  <si>
     <t>Llaneros FC</t>
   </si>
   <si>
@@ -415,12 +403,6 @@
     <t>Nacional (Uru)</t>
   </si>
   <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
     <t>America de Cali S.A</t>
   </si>
   <si>
@@ -481,7 +463,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 21:27:43</t>
+    <t>2026-10-04 23:37:12</t>
   </si>
 </sst>
 </file>
@@ -813,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1069,235 +1051,235 @@
         <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="G2">
-        <v>1.15</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
+        <v>3.6</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.94</v>
+      </c>
+      <c r="O2">
+        <v>1.51</v>
+      </c>
+      <c r="P2">
+        <v>1.41</v>
+      </c>
+      <c r="Q2">
+        <v>3.3</v>
+      </c>
+      <c r="R2">
+        <v>1.09</v>
+      </c>
+      <c r="S2">
+        <v>11</v>
+      </c>
+      <c r="T2">
+        <v>1.92</v>
+      </c>
+      <c r="U2">
+        <v>1.96</v>
+      </c>
+      <c r="V2">
+        <v>1.13</v>
+      </c>
+      <c r="W2">
+        <v>2.46</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>3.05</v>
+      </c>
+      <c r="AC2">
+        <v>4.1</v>
+      </c>
+      <c r="AD2">
         <v>11.5</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>8</v>
-      </c>
-      <c r="Q2">
-        <v>1.13</v>
-      </c>
-      <c r="R2">
-        <v>2.36</v>
-      </c>
-      <c r="S2">
-        <v>1.67</v>
-      </c>
-      <c r="T2">
-        <v>1.59</v>
-      </c>
-      <c r="U2">
-        <v>2.54</v>
-      </c>
-      <c r="V2">
-        <v>1.03</v>
-      </c>
-      <c r="W2">
-        <v>7.6</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>1000</v>
-      </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF2">
         <v>8.4</v>
       </c>
       <c r="AG2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AJ2">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="AK2">
+        <v>75</v>
+      </c>
+      <c r="AL2">
+        <v>260</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>250</v>
+      </c>
+      <c r="AO2">
+        <v>330</v>
+      </c>
+      <c r="AP2">
+        <v>17.5</v>
+      </c>
+      <c r="AQ2">
+        <v>17.5</v>
+      </c>
+      <c r="AR2">
+        <v>17.5</v>
+      </c>
+      <c r="AS2">
+        <v>17.5</v>
+      </c>
+      <c r="AT2">
+        <v>2.96</v>
+      </c>
+      <c r="AU2">
+        <v>3.8</v>
+      </c>
+      <c r="AV2">
+        <v>10.5</v>
+      </c>
+      <c r="AW2">
+        <v>50</v>
+      </c>
+      <c r="AX2">
         <v>7.6</v>
       </c>
-      <c r="AL2">
-        <v>16.5</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>3.8</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2">
-        <v>14.5</v>
-      </c>
-      <c r="AR2">
-        <v>14.5</v>
-      </c>
-      <c r="AS2">
-        <v>14.5</v>
-      </c>
-      <c r="AT2">
-        <v>14.5</v>
-      </c>
-      <c r="AU2">
-        <v>14.5</v>
-      </c>
-      <c r="AV2">
+      <c r="AY2">
+        <v>11</v>
+      </c>
+      <c r="AZ2">
         <v>29</v>
       </c>
-      <c r="AW2">
-        <v>29</v>
-      </c>
-      <c r="AX2">
-        <v>7.8</v>
-      </c>
-      <c r="AY2">
-        <v>7.4</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
       <c r="BA2">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="BB2">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BC2">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="BD2">
-        <v>14.5</v>
+        <v>130</v>
       </c>
       <c r="BE2">
-        <v>44</v>
+        <v>290</v>
       </c>
       <c r="BF2">
-        <v>3.4</v>
+        <v>140</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1311,235 +1293,235 @@
         <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F3">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
+        <v>3.85</v>
+      </c>
+      <c r="M3">
+        <v>1.21</v>
+      </c>
+      <c r="N3">
+        <v>1.92</v>
+      </c>
+      <c r="O3">
+        <v>2.02</v>
+      </c>
+      <c r="P3">
+        <v>1.29</v>
+      </c>
+      <c r="Q3">
+        <v>4.2</v>
+      </c>
+      <c r="R3">
+        <v>1.09</v>
+      </c>
+      <c r="S3">
+        <v>11</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>1.41</v>
+      </c>
+      <c r="V3">
         <v>1.61</v>
       </c>
-      <c r="M3">
-        <v>1.13</v>
-      </c>
-      <c r="N3">
-        <v>2.74</v>
-      </c>
-      <c r="O3">
-        <v>1.56</v>
-      </c>
-      <c r="P3">
-        <v>1.56</v>
-      </c>
-      <c r="Q3">
-        <v>2.72</v>
-      </c>
-      <c r="R3">
-        <v>1.2</v>
-      </c>
-      <c r="S3">
-        <v>5.7</v>
-      </c>
-      <c r="T3">
-        <v>2.2</v>
-      </c>
-      <c r="U3">
-        <v>1.79</v>
-      </c>
-      <c r="V3">
-        <v>1.81</v>
-      </c>
       <c r="W3">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="X3">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="Y3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="Z3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA3">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AB3">
+        <v>7.6</v>
+      </c>
+      <c r="AC3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>60</v>
+      </c>
+      <c r="AF3">
+        <v>22</v>
+      </c>
+      <c r="AG3">
+        <v>21</v>
+      </c>
+      <c r="AH3">
+        <v>46</v>
+      </c>
+      <c r="AI3">
+        <v>160</v>
+      </c>
+      <c r="AJ3">
+        <v>100</v>
+      </c>
+      <c r="AK3">
+        <v>110</v>
+      </c>
+      <c r="AL3">
+        <v>180</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>200</v>
+      </c>
+      <c r="AO3">
+        <v>85</v>
+      </c>
+      <c r="AP3">
+        <v>6</v>
+      </c>
+      <c r="AQ3">
+        <v>5.5</v>
+      </c>
+      <c r="AR3">
         <v>11</v>
       </c>
-      <c r="AC3">
+      <c r="AS3">
+        <v>38</v>
+      </c>
+      <c r="AT3">
+        <v>6.8</v>
+      </c>
+      <c r="AU3">
         <v>7.4</v>
       </c>
-      <c r="AD3">
+      <c r="AV3">
+        <v>15</v>
+      </c>
+      <c r="AW3">
+        <v>44</v>
+      </c>
+      <c r="AX3">
+        <v>18</v>
+      </c>
+      <c r="AY3">
+        <v>18</v>
+      </c>
+      <c r="AZ3">
+        <v>34</v>
+      </c>
+      <c r="BA3">
+        <v>100</v>
+      </c>
+      <c r="BB3">
+        <v>75</v>
+      </c>
+      <c r="BC3">
+        <v>70</v>
+      </c>
+      <c r="BD3">
+        <v>130</v>
+      </c>
+      <c r="BE3">
+        <v>230</v>
+      </c>
+      <c r="BF3">
+        <v>100</v>
+      </c>
+      <c r="BG3">
+        <v>60</v>
+      </c>
+      <c r="BH3">
+        <v>1.32</v>
+      </c>
+      <c r="BI3">
+        <v>1.23</v>
+      </c>
+      <c r="BJ3">
+        <v>970</v>
+      </c>
+      <c r="BK3">
+        <v>65</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>9.4</v>
+      </c>
+      <c r="BN3">
+        <v>25</v>
+      </c>
+      <c r="BO3">
         <v>11</v>
       </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>27</v>
-      </c>
-      <c r="AG3">
-        <v>17.5</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>60</v>
-      </c>
-      <c r="AJ3">
-        <v>110</v>
-      </c>
-      <c r="AK3">
-        <v>75</v>
-      </c>
-      <c r="AL3">
-        <v>95</v>
-      </c>
-      <c r="AM3">
-        <v>200</v>
-      </c>
-      <c r="AN3">
-        <v>110</v>
-      </c>
-      <c r="AO3">
-        <v>30</v>
-      </c>
-      <c r="AP3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ3">
-        <v>6.8</v>
-      </c>
-      <c r="AR3">
-        <v>10.5</v>
-      </c>
-      <c r="AS3">
-        <v>26</v>
-      </c>
-      <c r="AT3">
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
         <v>10</v>
       </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>10.5</v>
-      </c>
-      <c r="AW3">
-        <v>28</v>
-      </c>
-      <c r="AX3">
-        <v>24</v>
-      </c>
-      <c r="AY3">
-        <v>16.5</v>
-      </c>
-      <c r="AZ3">
-        <v>23</v>
-      </c>
-      <c r="BA3">
-        <v>50</v>
-      </c>
-      <c r="BB3">
-        <v>80</v>
-      </c>
-      <c r="BC3">
-        <v>60</v>
-      </c>
-      <c r="BD3">
-        <v>50</v>
-      </c>
-      <c r="BE3">
-        <v>140</v>
-      </c>
-      <c r="BF3">
-        <v>40</v>
-      </c>
-      <c r="BG3">
-        <v>26</v>
-      </c>
-      <c r="BH3">
-        <v>2.66</v>
-      </c>
-      <c r="BI3">
-        <v>2.54</v>
-      </c>
-      <c r="BJ3">
-        <v>11.5</v>
-      </c>
-      <c r="BK3">
-        <v>9.6</v>
-      </c>
-      <c r="BL3">
-        <v>250</v>
-      </c>
-      <c r="BM3">
-        <v>180</v>
-      </c>
-      <c r="BN3">
-        <v>7.2</v>
-      </c>
-      <c r="BO3">
-        <v>6.4</v>
-      </c>
-      <c r="BP3">
-        <v>42</v>
-      </c>
-      <c r="BQ3">
-        <v>15</v>
-      </c>
       <c r="BR3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BV3">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1553,240 +1535,240 @@
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F4">
+        <v>1.89</v>
+      </c>
+      <c r="G4">
+        <v>2.12</v>
+      </c>
+      <c r="H4">
+        <v>4.2</v>
+      </c>
+      <c r="I4">
+        <v>5.1</v>
+      </c>
+      <c r="J4">
+        <v>3.25</v>
+      </c>
+      <c r="K4">
+        <v>4.2</v>
+      </c>
+      <c r="L4">
+        <v>1.41</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>3.1</v>
+      </c>
+      <c r="O4">
+        <v>1.38</v>
+      </c>
+      <c r="P4">
+        <v>1.72</v>
+      </c>
+      <c r="Q4">
+        <v>2.08</v>
+      </c>
+      <c r="R4">
+        <v>1.27</v>
+      </c>
+      <c r="S4">
+        <v>3.95</v>
+      </c>
+      <c r="T4">
+        <v>1.89</v>
+      </c>
+      <c r="U4">
+        <v>1.89</v>
+      </c>
+      <c r="V4">
+        <v>1.24</v>
+      </c>
+      <c r="W4">
+        <v>1.91</v>
+      </c>
+      <c r="X4">
+        <v>14</v>
+      </c>
+      <c r="Y4">
+        <v>16.5</v>
+      </c>
+      <c r="Z4">
+        <v>40</v>
+      </c>
+      <c r="AA4">
+        <v>130</v>
+      </c>
+      <c r="AB4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4">
+        <v>8.4</v>
+      </c>
+      <c r="AD4">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>80</v>
+      </c>
+      <c r="AF4">
+        <v>13.5</v>
+      </c>
+      <c r="AG4">
+        <v>12</v>
+      </c>
+      <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>90</v>
+      </c>
+      <c r="AJ4">
+        <v>28</v>
+      </c>
+      <c r="AK4">
+        <v>27</v>
+      </c>
+      <c r="AL4">
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>160</v>
+      </c>
+      <c r="AN4">
+        <v>21</v>
+      </c>
+      <c r="AO4">
+        <v>100</v>
+      </c>
+      <c r="AP4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>11</v>
+      </c>
+      <c r="AR4">
+        <v>4.8</v>
+      </c>
+      <c r="AS4">
+        <v>5.2</v>
+      </c>
+      <c r="AT4">
+        <v>6.2</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>14</v>
+      </c>
+      <c r="AW4">
+        <v>5.1</v>
+      </c>
+      <c r="AX4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>15.5</v>
+      </c>
+      <c r="BA4">
+        <v>5.1</v>
+      </c>
+      <c r="BB4">
+        <v>18</v>
+      </c>
+      <c r="BC4">
+        <v>19</v>
+      </c>
+      <c r="BD4">
+        <v>4.9</v>
+      </c>
+      <c r="BE4">
+        <v>5.3</v>
+      </c>
+      <c r="BF4">
+        <v>13.5</v>
+      </c>
+      <c r="BG4">
+        <v>5.2</v>
+      </c>
+      <c r="BH4">
+        <v>3.5</v>
+      </c>
+      <c r="BI4">
+        <v>2.6</v>
+      </c>
+      <c r="BJ4">
+        <v>12</v>
+      </c>
+      <c r="BK4">
+        <v>4</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>5.8</v>
+      </c>
+      <c r="BN4">
+        <v>5.1</v>
+      </c>
+      <c r="BO4">
         <v>3.9</v>
       </c>
-      <c r="G4">
-        <v>4.1</v>
-      </c>
-      <c r="H4">
-        <v>2.18</v>
-      </c>
-      <c r="I4">
-        <v>2.22</v>
-      </c>
-      <c r="J4">
-        <v>3.3</v>
-      </c>
-      <c r="K4">
-        <v>3.45</v>
-      </c>
-      <c r="L4">
-        <v>1.47</v>
-      </c>
-      <c r="M4">
-        <v>1.09</v>
-      </c>
-      <c r="N4">
-        <v>3.4</v>
-      </c>
-      <c r="O4">
-        <v>1.4</v>
-      </c>
-      <c r="P4">
-        <v>1.77</v>
-      </c>
-      <c r="Q4">
-        <v>2.24</v>
-      </c>
-      <c r="R4">
-        <v>1.3</v>
-      </c>
-      <c r="S4">
-        <v>4.1</v>
-      </c>
-      <c r="T4">
-        <v>1.94</v>
-      </c>
-      <c r="U4">
-        <v>2</v>
-      </c>
-      <c r="V4">
-        <v>1.81</v>
-      </c>
-      <c r="W4">
-        <v>1.32</v>
-      </c>
-      <c r="X4">
-        <v>12</v>
-      </c>
-      <c r="Y4">
+      <c r="BP4">
+        <v>17</v>
+      </c>
+      <c r="BQ4">
+        <v>4.4</v>
+      </c>
+      <c r="BR4">
+        <v>38</v>
+      </c>
+      <c r="BS4">
+        <v>5.1</v>
+      </c>
+      <c r="BT4">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z4">
-        <v>13</v>
-      </c>
-      <c r="AA4">
-        <v>34</v>
-      </c>
-      <c r="AB4">
-        <v>13</v>
-      </c>
-      <c r="AC4">
-        <v>7.6</v>
-      </c>
-      <c r="AD4">
-        <v>11</v>
-      </c>
-      <c r="AE4">
-        <v>25</v>
-      </c>
-      <c r="AF4">
-        <v>29</v>
-      </c>
-      <c r="AG4">
-        <v>16.5</v>
-      </c>
-      <c r="AH4">
-        <v>22</v>
-      </c>
-      <c r="AI4">
-        <v>46</v>
-      </c>
-      <c r="AJ4">
-        <v>85</v>
-      </c>
-      <c r="AK4">
-        <v>55</v>
-      </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
-      <c r="AM4">
-        <v>140</v>
-      </c>
-      <c r="AN4">
-        <v>70</v>
-      </c>
-      <c r="AO4">
-        <v>22</v>
-      </c>
-      <c r="AP4">
-        <v>10</v>
-      </c>
-      <c r="AQ4">
-        <v>8</v>
-      </c>
-      <c r="AR4">
-        <v>11.5</v>
-      </c>
-      <c r="AS4">
-        <v>24</v>
-      </c>
-      <c r="AT4">
-        <v>12</v>
-      </c>
-      <c r="AU4">
-        <v>6.8</v>
-      </c>
-      <c r="AV4">
-        <v>10</v>
-      </c>
-      <c r="AW4">
-        <v>22</v>
-      </c>
-      <c r="AX4">
-        <v>24</v>
-      </c>
-      <c r="AY4">
-        <v>14</v>
-      </c>
-      <c r="AZ4">
-        <v>18</v>
-      </c>
-      <c r="BA4">
-        <v>38</v>
-      </c>
-      <c r="BB4">
-        <v>44</v>
-      </c>
-      <c r="BC4">
-        <v>38</v>
-      </c>
-      <c r="BD4">
-        <v>15</v>
-      </c>
-      <c r="BE4">
-        <v>85</v>
-      </c>
-      <c r="BF4">
-        <v>40</v>
-      </c>
-      <c r="BG4">
-        <v>18.5</v>
-      </c>
-      <c r="BH4">
-        <v>3.15</v>
-      </c>
-      <c r="BI4">
-        <v>2.86</v>
-      </c>
-      <c r="BJ4">
-        <v>10</v>
-      </c>
-      <c r="BK4">
-        <v>8</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>110</v>
-      </c>
-      <c r="BN4">
-        <v>6.8</v>
-      </c>
-      <c r="BO4">
-        <v>6</v>
-      </c>
-      <c r="BP4">
-        <v>34</v>
-      </c>
-      <c r="BQ4">
-        <v>11.5</v>
-      </c>
-      <c r="BR4">
-        <v>50</v>
-      </c>
-      <c r="BS4">
-        <v>13</v>
-      </c>
-      <c r="BT4">
-        <v>4.9</v>
-      </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BV4">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="BW4">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>93</v>
@@ -1795,477 +1777,477 @@
         <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="G5">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H5">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="I5">
-        <v>1.7</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="R5">
+        <v>1.75</v>
+      </c>
+      <c r="S5">
+        <v>1.03</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>1.01</v>
+      </c>
+      <c r="W5">
+        <v>1.01</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>18</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>990</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.05</v>
+      </c>
+      <c r="AQ5">
+        <v>1.05</v>
+      </c>
+      <c r="AR5">
+        <v>1.05</v>
+      </c>
+      <c r="AS5">
+        <v>1.05</v>
+      </c>
+      <c r="AT5">
+        <v>1.05</v>
+      </c>
+      <c r="AU5">
+        <v>1.05</v>
+      </c>
+      <c r="AV5">
+        <v>2.44</v>
+      </c>
+      <c r="AW5">
         <v>1.59</v>
       </c>
-      <c r="S5">
-        <v>2.62</v>
-      </c>
-      <c r="T5">
-        <v>1.71</v>
-      </c>
-      <c r="U5">
-        <v>2.28</v>
-      </c>
-      <c r="V5">
-        <v>2.4</v>
-      </c>
-      <c r="W5">
-        <v>1.23</v>
-      </c>
-      <c r="X5">
-        <v>23</v>
-      </c>
-      <c r="Y5">
-        <v>11.5</v>
-      </c>
-      <c r="Z5">
-        <v>12</v>
-      </c>
-      <c r="AA5">
-        <v>17.5</v>
-      </c>
-      <c r="AB5">
-        <v>23</v>
-      </c>
-      <c r="AC5">
-        <v>11</v>
-      </c>
-      <c r="AD5">
-        <v>10.5</v>
-      </c>
-      <c r="AE5">
-        <v>16.5</v>
-      </c>
-      <c r="AF5">
-        <v>44</v>
-      </c>
-      <c r="AG5">
-        <v>20</v>
-      </c>
-      <c r="AH5">
-        <v>18.5</v>
-      </c>
-      <c r="AI5">
-        <v>29</v>
-      </c>
-      <c r="AJ5">
-        <v>130</v>
-      </c>
-      <c r="AK5">
-        <v>60</v>
-      </c>
-      <c r="AL5">
-        <v>60</v>
-      </c>
-      <c r="AM5">
-        <v>95</v>
-      </c>
-      <c r="AN5">
-        <v>55</v>
-      </c>
-      <c r="AO5">
-        <v>7.6</v>
-      </c>
-      <c r="AP5">
-        <v>19.5</v>
-      </c>
-      <c r="AQ5">
-        <v>10.5</v>
-      </c>
-      <c r="AR5">
-        <v>10.5</v>
-      </c>
-      <c r="AS5">
-        <v>16</v>
-      </c>
-      <c r="AT5">
-        <v>19.5</v>
-      </c>
-      <c r="AU5">
-        <v>9.6</v>
-      </c>
-      <c r="AV5">
-        <v>9.4</v>
-      </c>
-      <c r="AW5">
-        <v>14.5</v>
-      </c>
       <c r="AX5">
-        <v>38</v>
+        <v>1.05</v>
       </c>
       <c r="AY5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>2.02</v>
       </c>
       <c r="BA5">
-        <v>24</v>
+        <v>1.05</v>
       </c>
       <c r="BB5">
-        <v>70</v>
+        <v>1.05</v>
       </c>
       <c r="BC5">
-        <v>40</v>
+        <v>1.05</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>1.05</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>38</v>
+        <v>1.05</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
         <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F6">
+        <v>2.3</v>
+      </c>
+      <c r="G6">
+        <v>2.62</v>
+      </c>
+      <c r="H6">
+        <v>3.05</v>
+      </c>
+      <c r="I6">
+        <v>3.55</v>
+      </c>
+      <c r="J6">
+        <v>3.2</v>
+      </c>
+      <c r="K6">
+        <v>3.65</v>
+      </c>
+      <c r="L6">
+        <v>1.42</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
+        <v>3.4</v>
+      </c>
+      <c r="O6">
+        <v>1.33</v>
+      </c>
+      <c r="P6">
         <v>1.83</v>
       </c>
-      <c r="G6">
-        <v>2.18</v>
-      </c>
-      <c r="H6">
-        <v>3.7</v>
-      </c>
-      <c r="I6">
+      <c r="Q6">
+        <v>1.97</v>
+      </c>
+      <c r="R6">
+        <v>1.33</v>
+      </c>
+      <c r="S6">
+        <v>3.45</v>
+      </c>
+      <c r="T6">
+        <v>1.74</v>
+      </c>
+      <c r="U6">
+        <v>2.08</v>
+      </c>
+      <c r="V6">
+        <v>1.4</v>
+      </c>
+      <c r="W6">
+        <v>1.61</v>
+      </c>
+      <c r="X6">
+        <v>15.5</v>
+      </c>
+      <c r="Y6">
+        <v>12.5</v>
+      </c>
+      <c r="Z6">
+        <v>26</v>
+      </c>
+      <c r="AA6">
+        <v>70</v>
+      </c>
+      <c r="AB6">
+        <v>12</v>
+      </c>
+      <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>16.5</v>
+      </c>
+      <c r="AE6">
+        <v>42</v>
+      </c>
+      <c r="AF6">
+        <v>16.5</v>
+      </c>
+      <c r="AG6">
+        <v>13.5</v>
+      </c>
+      <c r="AH6">
+        <v>18.5</v>
+      </c>
+      <c r="AI6">
+        <v>55</v>
+      </c>
+      <c r="AJ6">
+        <v>38</v>
+      </c>
+      <c r="AK6">
+        <v>32</v>
+      </c>
+      <c r="AL6">
+        <v>42</v>
+      </c>
+      <c r="AM6">
+        <v>110</v>
+      </c>
+      <c r="AN6">
+        <v>26</v>
+      </c>
+      <c r="AO6">
+        <v>40</v>
+      </c>
+      <c r="AP6">
+        <v>4.3</v>
+      </c>
+      <c r="AQ6">
+        <v>4.1</v>
+      </c>
+      <c r="AR6">
+        <v>19</v>
+      </c>
+      <c r="AS6">
+        <v>5.6</v>
+      </c>
+      <c r="AT6">
+        <v>7.8</v>
+      </c>
+      <c r="AU6">
+        <v>3.6</v>
+      </c>
+      <c r="AV6">
+        <v>11</v>
+      </c>
+      <c r="AW6">
+        <v>5.3</v>
+      </c>
+      <c r="AX6">
+        <v>4.4</v>
+      </c>
+      <c r="AY6">
+        <v>4.2</v>
+      </c>
+      <c r="AZ6">
+        <v>14.5</v>
+      </c>
+      <c r="BA6">
+        <v>5.5</v>
+      </c>
+      <c r="BB6">
+        <v>5.2</v>
+      </c>
+      <c r="BC6">
+        <v>5.1</v>
+      </c>
+      <c r="BD6">
+        <v>5.3</v>
+      </c>
+      <c r="BE6">
         <v>5.8</v>
       </c>
-      <c r="J6">
-        <v>3.1</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>1.35</v>
-      </c>
-      <c r="M6">
-        <v>1.08</v>
-      </c>
-      <c r="N6">
-        <v>2.98</v>
-      </c>
-      <c r="O6">
-        <v>1.37</v>
-      </c>
-      <c r="P6">
-        <v>1.67</v>
-      </c>
-      <c r="Q6">
-        <v>2.04</v>
-      </c>
-      <c r="R6">
-        <v>1.25</v>
-      </c>
-      <c r="S6">
-        <v>3.7</v>
-      </c>
-      <c r="T6">
-        <v>1.88</v>
-      </c>
-      <c r="U6">
-        <v>1.89</v>
-      </c>
-      <c r="V6">
-        <v>1.21</v>
-      </c>
-      <c r="W6">
-        <v>1.85</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>1000</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6">
-        <v>1.01</v>
-      </c>
-      <c r="AR6">
-        <v>1.01</v>
-      </c>
-      <c r="AS6">
-        <v>1.01</v>
-      </c>
-      <c r="AT6">
-        <v>1.01</v>
-      </c>
-      <c r="AU6">
-        <v>1.01</v>
-      </c>
-      <c r="AV6">
-        <v>1.01</v>
-      </c>
-      <c r="AW6">
-        <v>1.01</v>
-      </c>
-      <c r="AX6">
-        <v>1.01</v>
-      </c>
-      <c r="AY6">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6">
-        <v>1.01</v>
-      </c>
-      <c r="BA6">
-        <v>1.01</v>
-      </c>
-      <c r="BB6">
-        <v>1.01</v>
-      </c>
-      <c r="BC6">
-        <v>1.01</v>
-      </c>
-      <c r="BD6">
-        <v>1.01</v>
-      </c>
-      <c r="BE6">
-        <v>1.01</v>
-      </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2276,67 +2258,67 @@
         <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="H7">
-        <v>1.08</v>
+        <v>2.96</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="R7">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2360,7 +2342,7 @@
         <v>1000</v>
       </c>
       <c r="AE7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
         <v>1000</v>
@@ -2369,7 +2351,7 @@
         <v>1000</v>
       </c>
       <c r="AH7">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
         <v>1000</v>
@@ -2393,126 +2375,126 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>93</v>
@@ -2521,172 +2503,172 @@
         <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F8">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="G8">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
-        <v>3.65</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S8">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="X8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2749,7 +2731,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2760,28 +2742,28 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="G9">
-        <v>2.54</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>2.96</v>
+        <v>1.33</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>1.18</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2793,34 +2775,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q9">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="R9">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="T9">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="W9">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2991,114 +2973,114 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
         <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F10">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="G10">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>1.76</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>1.84</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>4.4</v>
       </c>
       <c r="K10">
+        <v>5.1</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>4.3</v>
+      </c>
+      <c r="O10">
+        <v>1.07</v>
+      </c>
+      <c r="P10">
+        <v>4.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.23</v>
+      </c>
+      <c r="R10">
+        <v>2.38</v>
+      </c>
+      <c r="S10">
+        <v>1.56</v>
+      </c>
+      <c r="T10">
+        <v>1.27</v>
+      </c>
+      <c r="U10">
+        <v>3.55</v>
+      </c>
+      <c r="V10">
+        <v>2.2</v>
+      </c>
+      <c r="W10">
+        <v>1.3</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
         <v>950</v>
       </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>6.4</v>
-      </c>
-      <c r="O10">
-        <v>1.16</v>
-      </c>
-      <c r="P10">
-        <v>2.5</v>
-      </c>
-      <c r="Q10">
-        <v>1.49</v>
-      </c>
-      <c r="R10">
-        <v>1.55</v>
-      </c>
-      <c r="S10">
-        <v>1.49</v>
-      </c>
-      <c r="T10">
-        <v>1.11</v>
-      </c>
-      <c r="U10">
-        <v>1.11</v>
-      </c>
-      <c r="V10">
-        <v>1.02</v>
-      </c>
-      <c r="W10">
-        <v>1.01</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ10">
         <v>1000</v>
@@ -3116,61 +3098,61 @@
         <v>1000</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3233,12 +3215,12 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
@@ -3247,172 +3229,172 @@
         <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F11">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>1.78</v>
       </c>
       <c r="H11">
-        <v>1.31</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>1.15</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>1.13</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P11">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="Q11">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>1.19</v>
+        <v>5.1</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V11">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>2.28</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3475,12 +3457,12 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
         <v>93</v>
@@ -3489,240 +3471,240 @@
         <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F12">
+        <v>1.98</v>
+      </c>
+      <c r="G12">
+        <v>2.02</v>
+      </c>
+      <c r="H12">
+        <v>4.2</v>
+      </c>
+      <c r="I12">
+        <v>4.4</v>
+      </c>
+      <c r="J12">
         <v>3.7</v>
       </c>
-      <c r="G12">
-        <v>4.3</v>
-      </c>
-      <c r="H12">
-        <v>1.75</v>
-      </c>
-      <c r="I12">
-        <v>1.89</v>
-      </c>
-      <c r="J12">
-        <v>4.3</v>
-      </c>
       <c r="K12">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="O12">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="P12">
-        <v>4.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q12">
-        <v>1.2</v>
+        <v>1.94</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="S12">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="T12">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="U12">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
-        <v>2.12</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y12">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z12">
+        <v>36</v>
+      </c>
+      <c r="AA12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
+        <v>9.6</v>
+      </c>
+      <c r="AC12">
+        <v>8.6</v>
+      </c>
+      <c r="AD12">
+        <v>18.5</v>
+      </c>
+      <c r="AE12">
+        <v>60</v>
+      </c>
+      <c r="AF12">
+        <v>12.5</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>70</v>
+      </c>
+      <c r="AJ12">
+        <v>24</v>
+      </c>
+      <c r="AK12">
+        <v>22</v>
+      </c>
+      <c r="AL12">
+        <v>40</v>
+      </c>
+      <c r="AM12">
+        <v>110</v>
+      </c>
+      <c r="AN12">
+        <v>14.5</v>
+      </c>
+      <c r="AO12">
+        <v>60</v>
+      </c>
+      <c r="AP12">
+        <v>13</v>
+      </c>
+      <c r="AQ12">
+        <v>13.5</v>
+      </c>
+      <c r="AR12">
+        <v>24</v>
+      </c>
+      <c r="AS12">
+        <v>7.8</v>
+      </c>
+      <c r="AT12">
+        <v>7</v>
+      </c>
+      <c r="AU12">
+        <v>7.4</v>
+      </c>
+      <c r="AV12">
+        <v>15</v>
+      </c>
+      <c r="AW12">
         <v>34</v>
       </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>950</v>
-      </c>
-      <c r="AC12">
-        <v>970</v>
-      </c>
-      <c r="AD12">
-        <v>950</v>
-      </c>
-      <c r="AE12">
-        <v>23</v>
-      </c>
-      <c r="AF12">
-        <v>80</v>
-      </c>
-      <c r="AG12">
-        <v>950</v>
-      </c>
-      <c r="AH12">
-        <v>970</v>
-      </c>
-      <c r="AI12">
-        <v>40</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>970</v>
-      </c>
-      <c r="AP12">
-        <v>1.99</v>
-      </c>
-      <c r="AQ12">
-        <v>17.5</v>
-      </c>
-      <c r="AR12">
+      <c r="AX12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY12">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12">
         <v>16</v>
       </c>
-      <c r="AS12">
-        <v>1.99</v>
-      </c>
-      <c r="AT12">
-        <v>26</v>
-      </c>
-      <c r="AU12">
-        <v>8.4</v>
-      </c>
-      <c r="AV12">
-        <v>9.4</v>
-      </c>
-      <c r="AW12">
+      <c r="BA12">
+        <v>7.6</v>
+      </c>
+      <c r="BB12">
         <v>11</v>
       </c>
-      <c r="AX12">
-        <v>25</v>
-      </c>
-      <c r="AY12">
-        <v>14.5</v>
-      </c>
-      <c r="AZ12">
-        <v>8</v>
-      </c>
-      <c r="BA12">
-        <v>9.6</v>
-      </c>
-      <c r="BB12">
-        <v>1.99</v>
-      </c>
       <c r="BC12">
-        <v>1.99</v>
+        <v>18.5</v>
       </c>
       <c r="BD12">
-        <v>1.99</v>
+        <v>29</v>
       </c>
       <c r="BE12">
-        <v>1.99</v>
+        <v>7.8</v>
       </c>
       <c r="BF12">
-        <v>1.99</v>
+        <v>12.5</v>
       </c>
       <c r="BG12">
-        <v>3.65</v>
+        <v>32</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
         <v>93</v>
@@ -3731,172 +3713,172 @@
         <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F13">
+        <v>3.65</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>1.83</v>
+      </c>
+      <c r="I13">
+        <v>1.93</v>
+      </c>
+      <c r="J13">
+        <v>4.3</v>
+      </c>
+      <c r="K13">
+        <v>5</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.04</v>
+      </c>
+      <c r="N13">
+        <v>4.6</v>
+      </c>
+      <c r="O13">
+        <v>1.21</v>
+      </c>
+      <c r="P13">
+        <v>2.24</v>
+      </c>
+      <c r="Q13">
+        <v>1.62</v>
+      </c>
+      <c r="R13">
+        <v>1.48</v>
+      </c>
+      <c r="S13">
+        <v>2.62</v>
+      </c>
+      <c r="T13">
         <v>1.63</v>
       </c>
-      <c r="G13">
-        <v>1.78</v>
-      </c>
-      <c r="H13">
-        <v>6.6</v>
-      </c>
-      <c r="I13">
-        <v>8.4</v>
-      </c>
-      <c r="J13">
-        <v>3.35</v>
-      </c>
-      <c r="K13">
-        <v>4.3</v>
-      </c>
-      <c r="L13">
-        <v>1.43</v>
-      </c>
-      <c r="M13">
-        <v>1.11</v>
-      </c>
-      <c r="N13">
-        <v>2.62</v>
-      </c>
-      <c r="O13">
-        <v>1.5</v>
-      </c>
-      <c r="P13">
-        <v>1.54</v>
-      </c>
-      <c r="Q13">
-        <v>2.5</v>
-      </c>
-      <c r="R13">
-        <v>1.19</v>
-      </c>
-      <c r="S13">
-        <v>5.1</v>
-      </c>
-      <c r="T13">
-        <v>2.34</v>
-      </c>
       <c r="U13">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="W13">
-        <v>2.28</v>
+        <v>1.33</v>
       </c>
       <c r="X13">
+        <v>27</v>
+      </c>
+      <c r="Y13">
+        <v>12.5</v>
+      </c>
+      <c r="Z13">
+        <v>14</v>
+      </c>
+      <c r="AA13">
+        <v>25</v>
+      </c>
+      <c r="AB13">
+        <v>19.5</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
         <v>11.5</v>
       </c>
-      <c r="Y13">
-        <v>21</v>
-      </c>
-      <c r="Z13">
-        <v>75</v>
-      </c>
-      <c r="AA13">
-        <v>360</v>
-      </c>
-      <c r="AB13">
-        <v>7</v>
-      </c>
-      <c r="AC13">
+      <c r="AE13">
+        <v>19</v>
+      </c>
+      <c r="AF13">
+        <v>38</v>
+      </c>
+      <c r="AG13">
+        <v>17.5</v>
+      </c>
+      <c r="AH13">
+        <v>19.5</v>
+      </c>
+      <c r="AI13">
+        <v>34</v>
+      </c>
+      <c r="AJ13">
+        <v>85</v>
+      </c>
+      <c r="AK13">
+        <v>50</v>
+      </c>
+      <c r="AL13">
+        <v>48</v>
+      </c>
+      <c r="AM13">
+        <v>85</v>
+      </c>
+      <c r="AN13">
+        <v>42</v>
+      </c>
+      <c r="AO13">
         <v>10.5</v>
       </c>
-      <c r="AD13">
-        <v>38</v>
-      </c>
-      <c r="AE13">
-        <v>200</v>
-      </c>
-      <c r="AF13">
-        <v>10.5</v>
-      </c>
-      <c r="AG13">
-        <v>13</v>
-      </c>
-      <c r="AH13">
-        <v>38</v>
-      </c>
-      <c r="AI13">
-        <v>210</v>
-      </c>
-      <c r="AJ13">
-        <v>21</v>
-      </c>
-      <c r="AK13">
-        <v>29</v>
-      </c>
-      <c r="AL13">
-        <v>80</v>
-      </c>
-      <c r="AM13">
-        <v>340</v>
-      </c>
-      <c r="AN13">
-        <v>21</v>
-      </c>
-      <c r="AO13">
-        <v>400</v>
-      </c>
       <c r="AP13">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AR13">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AS13">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AT13">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AU13">
+        <v>8.6</v>
+      </c>
+      <c r="AV13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW13">
+        <v>15</v>
+      </c>
+      <c r="AX13">
+        <v>5.9</v>
+      </c>
+      <c r="AY13">
+        <v>13.5</v>
+      </c>
+      <c r="AZ13">
+        <v>15</v>
+      </c>
+      <c r="BA13">
+        <v>5.8</v>
+      </c>
+      <c r="BB13">
         <v>6.4</v>
       </c>
-      <c r="AV13">
-        <v>3.9</v>
-      </c>
-      <c r="AW13">
-        <v>4.2</v>
-      </c>
-      <c r="AX13">
+      <c r="BC13">
+        <v>6</v>
+      </c>
+      <c r="BD13">
+        <v>6</v>
+      </c>
+      <c r="BE13">
         <v>6.4</v>
       </c>
-      <c r="AY13">
-        <v>8</v>
-      </c>
-      <c r="AZ13">
-        <v>3.9</v>
-      </c>
-      <c r="BA13">
-        <v>4.2</v>
-      </c>
-      <c r="BB13">
-        <v>12.5</v>
-      </c>
-      <c r="BC13">
-        <v>17</v>
-      </c>
-      <c r="BD13">
-        <v>4.1</v>
-      </c>
-      <c r="BE13">
-        <v>4.3</v>
-      </c>
       <c r="BF13">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BG13">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3959,12 +3941,12 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
         <v>93</v>
@@ -3973,240 +3955,240 @@
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G14">
         <v>2.02</v>
       </c>
       <c r="H14">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L14">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="P14">
+        <v>1.5</v>
+      </c>
+      <c r="Q14">
+        <v>2.94</v>
+      </c>
+      <c r="R14">
+        <v>1.17</v>
+      </c>
+      <c r="S14">
+        <v>6.2</v>
+      </c>
+      <c r="T14">
+        <v>2.46</v>
+      </c>
+      <c r="U14">
+        <v>1.63</v>
+      </c>
+      <c r="V14">
+        <v>1.24</v>
+      </c>
+      <c r="W14">
         <v>1.98</v>
       </c>
-      <c r="Q14">
-        <v>1.91</v>
-      </c>
-      <c r="R14">
-        <v>1.38</v>
-      </c>
-      <c r="S14">
-        <v>3.25</v>
-      </c>
-      <c r="T14">
-        <v>1.8</v>
-      </c>
-      <c r="U14">
-        <v>2.16</v>
-      </c>
-      <c r="V14">
-        <v>1.29</v>
-      </c>
-      <c r="W14">
-        <v>1.99</v>
-      </c>
       <c r="X14">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
+        <v>10</v>
+      </c>
+      <c r="AG14">
         <v>12.5</v>
       </c>
-      <c r="AG14">
-        <v>11</v>
-      </c>
       <c r="AH14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="AN14">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AO14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ14">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR14">
         <v>24</v>
       </c>
       <c r="AS14">
+        <v>42</v>
+      </c>
+      <c r="AT14">
+        <v>5.5</v>
+      </c>
+      <c r="AU14">
+        <v>7.4</v>
+      </c>
+      <c r="AV14">
+        <v>21</v>
+      </c>
+      <c r="AW14">
+        <v>38</v>
+      </c>
+      <c r="AX14">
+        <v>9</v>
+      </c>
+      <c r="AY14">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14">
+        <v>27</v>
+      </c>
+      <c r="BA14">
+        <v>44</v>
+      </c>
+      <c r="BB14">
+        <v>21</v>
+      </c>
+      <c r="BC14">
+        <v>24</v>
+      </c>
+      <c r="BD14">
+        <v>34</v>
+      </c>
+      <c r="BE14">
+        <v>50</v>
+      </c>
+      <c r="BF14">
+        <v>20</v>
+      </c>
+      <c r="BG14">
+        <v>46</v>
+      </c>
+      <c r="BH14">
+        <v>2.56</v>
+      </c>
+      <c r="BI14">
+        <v>2.46</v>
+      </c>
+      <c r="BJ14">
+        <v>12.5</v>
+      </c>
+      <c r="BK14">
         <v>7.2</v>
       </c>
-      <c r="AT14">
-        <v>8.4</v>
-      </c>
-      <c r="AU14">
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>15.5</v>
+      </c>
+      <c r="BN14">
+        <v>4.3</v>
+      </c>
+      <c r="BO14">
+        <v>3.95</v>
+      </c>
+      <c r="BP14">
+        <v>16.5</v>
+      </c>
+      <c r="BQ14">
+        <v>8.6</v>
+      </c>
+      <c r="BR14">
+        <v>55</v>
+      </c>
+      <c r="BS14">
+        <v>12.5</v>
+      </c>
+      <c r="BT14">
+        <v>8.6</v>
+      </c>
+      <c r="BU14">
         <v>7.6</v>
       </c>
-      <c r="AV14">
-        <v>15</v>
-      </c>
-      <c r="AW14">
-        <v>34</v>
-      </c>
-      <c r="AX14">
-        <v>9.4</v>
-      </c>
-      <c r="AY14">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14">
-        <v>15.5</v>
-      </c>
-      <c r="BA14">
-        <v>9.4</v>
-      </c>
-      <c r="BB14">
-        <v>11.5</v>
-      </c>
-      <c r="BC14">
-        <v>18.5</v>
-      </c>
-      <c r="BD14">
-        <v>29</v>
-      </c>
-      <c r="BE14">
-        <v>7.2</v>
-      </c>
-      <c r="BF14">
-        <v>11.5</v>
-      </c>
-      <c r="BG14">
-        <v>32</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.5</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>6.2</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.5</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.71</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>2.48</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.5</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>2.02</v>
-      </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW14">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY14">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA14">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
         <v>93</v>
@@ -4215,240 +4197,240 @@
         <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F15">
-        <v>3.65</v>
+        <v>1.86</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>1.96</v>
       </c>
       <c r="H15">
-        <v>1.81</v>
+        <v>4.5</v>
       </c>
       <c r="I15">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q15">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="T15">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="U15">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="V15">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="X15">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="Y15">
+        <v>16</v>
+      </c>
+      <c r="Z15">
+        <v>40</v>
+      </c>
+      <c r="AA15">
+        <v>140</v>
+      </c>
+      <c r="AB15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>19.5</v>
+      </c>
+      <c r="AE15">
+        <v>75</v>
+      </c>
+      <c r="AF15">
+        <v>12</v>
+      </c>
+      <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
+        <v>21</v>
+      </c>
+      <c r="AI15">
+        <v>80</v>
+      </c>
+      <c r="AJ15">
+        <v>24</v>
+      </c>
+      <c r="AK15">
+        <v>23</v>
+      </c>
+      <c r="AL15">
+        <v>46</v>
+      </c>
+      <c r="AM15">
+        <v>140</v>
+      </c>
+      <c r="AN15">
+        <v>14.5</v>
+      </c>
+      <c r="AO15">
+        <v>90</v>
+      </c>
+      <c r="AP15">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15">
+        <v>13</v>
+      </c>
+      <c r="AR15">
+        <v>7.8</v>
+      </c>
+      <c r="AS15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT15">
+        <v>7.4</v>
+      </c>
+      <c r="AU15">
+        <v>7.2</v>
+      </c>
+      <c r="AV15">
+        <v>15.5</v>
+      </c>
+      <c r="AW15">
+        <v>8.6</v>
+      </c>
+      <c r="AX15">
+        <v>10</v>
+      </c>
+      <c r="AY15">
+        <v>9</v>
+      </c>
+      <c r="AZ15">
+        <v>17</v>
+      </c>
+      <c r="BA15">
+        <v>8.6</v>
+      </c>
+      <c r="BB15">
+        <v>17</v>
+      </c>
+      <c r="BC15">
+        <v>16.5</v>
+      </c>
+      <c r="BD15">
+        <v>8</v>
+      </c>
+      <c r="BE15">
+        <v>9</v>
+      </c>
+      <c r="BF15">
         <v>12.5</v>
       </c>
-      <c r="Z15">
-        <v>14</v>
-      </c>
-      <c r="AA15">
-        <v>25</v>
-      </c>
-      <c r="AB15">
-        <v>19.5</v>
-      </c>
-      <c r="AC15">
-        <v>11</v>
-      </c>
-      <c r="AD15">
-        <v>11.5</v>
-      </c>
-      <c r="AE15">
+      <c r="BG15">
+        <v>8.6</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.88</v>
+      </c>
+      <c r="BJ15">
+        <v>14.5</v>
+      </c>
+      <c r="BK15">
+        <v>1.66</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.88</v>
+      </c>
+      <c r="BN15">
+        <v>6</v>
+      </c>
+      <c r="BO15">
+        <v>3.2</v>
+      </c>
+      <c r="BP15">
         <v>19</v>
       </c>
-      <c r="AF15">
+      <c r="BQ15">
+        <v>1.71</v>
+      </c>
+      <c r="BR15">
+        <v>40</v>
+      </c>
+      <c r="BS15">
+        <v>1.79</v>
+      </c>
+      <c r="BT15">
+        <v>10.5</v>
+      </c>
+      <c r="BU15">
+        <v>5.3</v>
+      </c>
+      <c r="BV15">
+        <v>260</v>
+      </c>
+      <c r="BW15">
+        <v>1.83</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.84</v>
+      </c>
+      <c r="BZ15">
         <v>38</v>
       </c>
-      <c r="AG15">
-        <v>17.5</v>
-      </c>
-      <c r="AH15">
-        <v>19.5</v>
-      </c>
-      <c r="AI15">
-        <v>34</v>
-      </c>
-      <c r="AJ15">
-        <v>85</v>
-      </c>
-      <c r="AK15">
-        <v>50</v>
-      </c>
-      <c r="AL15">
-        <v>48</v>
-      </c>
-      <c r="AM15">
-        <v>85</v>
-      </c>
-      <c r="AN15">
-        <v>42</v>
-      </c>
-      <c r="AO15">
-        <v>10.5</v>
-      </c>
-      <c r="AP15">
-        <v>18</v>
-      </c>
-      <c r="AQ15">
-        <v>9.6</v>
-      </c>
-      <c r="AR15">
-        <v>11</v>
-      </c>
-      <c r="AS15">
-        <v>17.5</v>
-      </c>
-      <c r="AT15">
-        <v>15</v>
-      </c>
-      <c r="AU15">
-        <v>8.6</v>
-      </c>
-      <c r="AV15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW15">
-        <v>15</v>
-      </c>
-      <c r="AX15">
-        <v>5.9</v>
-      </c>
-      <c r="AY15">
-        <v>13.5</v>
-      </c>
-      <c r="AZ15">
-        <v>15</v>
-      </c>
-      <c r="BA15">
-        <v>5.8</v>
-      </c>
-      <c r="BB15">
-        <v>6.4</v>
-      </c>
-      <c r="BC15">
-        <v>6</v>
-      </c>
-      <c r="BD15">
-        <v>6</v>
-      </c>
-      <c r="BE15">
-        <v>6.4</v>
-      </c>
-      <c r="BF15">
-        <v>6</v>
-      </c>
-      <c r="BG15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.04</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.04</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.04</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.04</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.04</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.04</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>1.04</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.04</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="CB15" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
         <v>93</v>
@@ -4457,145 +4439,145 @@
         <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F16">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G16">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H16">
+        <v>4.7</v>
+      </c>
+      <c r="I16">
         <v>5</v>
       </c>
-      <c r="I16">
-        <v>5.3</v>
-      </c>
       <c r="J16">
+        <v>3.1</v>
+      </c>
+      <c r="K16">
         <v>3.25</v>
       </c>
-      <c r="K16">
-        <v>3.35</v>
-      </c>
       <c r="L16">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M16">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O16">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="P16">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S16">
+        <v>6.8</v>
+      </c>
+      <c r="T16">
+        <v>2.46</v>
+      </c>
+      <c r="U16">
+        <v>1.65</v>
+      </c>
+      <c r="V16">
+        <v>1.25</v>
+      </c>
+      <c r="W16">
+        <v>1.89</v>
+      </c>
+      <c r="X16">
+        <v>7.4</v>
+      </c>
+      <c r="Y16">
+        <v>11</v>
+      </c>
+      <c r="Z16">
+        <v>36</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
         <v>6.2</v>
-      </c>
-      <c r="T16">
-        <v>2.48</v>
-      </c>
-      <c r="U16">
-        <v>1.62</v>
-      </c>
-      <c r="V16">
-        <v>1.24</v>
-      </c>
-      <c r="W16">
-        <v>1.98</v>
-      </c>
-      <c r="X16">
-        <v>8</v>
-      </c>
-      <c r="Y16">
-        <v>12</v>
-      </c>
-      <c r="Z16">
-        <v>38</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>5.9</v>
       </c>
       <c r="AC16">
         <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH16">
         <v>32</v>
       </c>
       <c r="AI16">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AK16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL16">
         <v>1000</v>
       </c>
       <c r="AM16">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AN16">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS16">
         <v>42</v>
       </c>
       <c r="AT16">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU16">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX16">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4604,330 +4586,330 @@
         <v>27</v>
       </c>
       <c r="BA16">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC16">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BE16">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG16">
         <v>46</v>
       </c>
       <c r="BH16">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BI16">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="BJ16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>15.5</v>
+        <v>1.37</v>
       </c>
       <c r="BN16">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BO16">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="BP16">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="BR16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="BT16">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="BX16">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>14</v>
+        <v>1.37</v>
       </c>
       <c r="BZ16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="CB16" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
         <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F17">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G17">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="H17">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="I17">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
         <v>3.85</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M17">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="P17">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="Q17">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="R17">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S17">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="T17">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W17">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="X17">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA17">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AC17">
         <v>8.4</v>
       </c>
       <c r="AD17">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE17">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AG17">
         <v>11</v>
       </c>
       <c r="AH17">
+        <v>26</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>18.5</v>
+      </c>
+      <c r="AK17">
+        <v>22</v>
+      </c>
+      <c r="AL17">
+        <v>65</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>15</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>9.6</v>
+      </c>
+      <c r="AQ17">
+        <v>14</v>
+      </c>
+      <c r="AR17">
+        <v>32</v>
+      </c>
+      <c r="AS17">
+        <v>44</v>
+      </c>
+      <c r="AT17">
+        <v>6.2</v>
+      </c>
+      <c r="AU17">
+        <v>7.6</v>
+      </c>
+      <c r="AV17">
         <v>21</v>
       </c>
-      <c r="AI17">
-        <v>80</v>
-      </c>
-      <c r="AJ17">
-        <v>24</v>
-      </c>
-      <c r="AK17">
-        <v>23</v>
-      </c>
-      <c r="AL17">
+      <c r="AW17">
+        <v>36</v>
+      </c>
+      <c r="AX17">
+        <v>8.4</v>
+      </c>
+      <c r="AY17">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17">
+        <v>22</v>
+      </c>
+      <c r="BA17">
+        <v>60</v>
+      </c>
+      <c r="BB17">
+        <v>15.5</v>
+      </c>
+      <c r="BC17">
+        <v>19</v>
+      </c>
+      <c r="BD17">
+        <v>38</v>
+      </c>
+      <c r="BE17">
         <v>46</v>
       </c>
-      <c r="AM17">
-        <v>140</v>
-      </c>
-      <c r="AN17">
-        <v>14.5</v>
-      </c>
-      <c r="AO17">
-        <v>90</v>
-      </c>
-      <c r="AP17">
-        <v>11.5</v>
-      </c>
-      <c r="AQ17">
+      <c r="BF17">
         <v>13</v>
       </c>
-      <c r="AR17">
-        <v>7.8</v>
-      </c>
-      <c r="AS17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT17">
-        <v>7.4</v>
-      </c>
-      <c r="AU17">
-        <v>7.2</v>
-      </c>
-      <c r="AV17">
-        <v>15.5</v>
-      </c>
-      <c r="AW17">
-        <v>8.6</v>
-      </c>
-      <c r="AX17">
-        <v>10</v>
-      </c>
-      <c r="AY17">
-        <v>9</v>
-      </c>
-      <c r="AZ17">
-        <v>17</v>
-      </c>
-      <c r="BA17">
-        <v>8.6</v>
-      </c>
-      <c r="BB17">
-        <v>17</v>
-      </c>
-      <c r="BC17">
-        <v>16.5</v>
-      </c>
-      <c r="BD17">
-        <v>8</v>
-      </c>
-      <c r="BE17">
-        <v>9</v>
-      </c>
-      <c r="BF17">
-        <v>12.5</v>
-      </c>
       <c r="BG17">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI17">
-        <v>1.88</v>
+        <v>2.66</v>
       </c>
       <c r="BJ17">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="BN17">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BP17">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="BR17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="BT17">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>5.3</v>
+        <v>2.06</v>
       </c>
       <c r="BV17">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="BZ17">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="CB17" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4938,659 +4920,659 @@
         <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18">
+        <v>2.6</v>
+      </c>
+      <c r="G18">
+        <v>2.86</v>
+      </c>
+      <c r="H18">
+        <v>2.62</v>
+      </c>
+      <c r="I18">
+        <v>2.86</v>
+      </c>
+      <c r="J18">
+        <v>3.55</v>
+      </c>
+      <c r="K18">
+        <v>3.9</v>
+      </c>
+      <c r="L18">
+        <v>1.2</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>4</v>
+      </c>
+      <c r="O18">
+        <v>1.28</v>
+      </c>
+      <c r="P18">
+        <v>2.02</v>
+      </c>
+      <c r="Q18">
+        <v>1.86</v>
+      </c>
+      <c r="R18">
+        <v>1.4</v>
+      </c>
+      <c r="S18">
+        <v>3.15</v>
+      </c>
+      <c r="T18">
+        <v>1.69</v>
+      </c>
+      <c r="U18">
+        <v>2.24</v>
+      </c>
+      <c r="V18">
+        <v>1.54</v>
+      </c>
+      <c r="W18">
+        <v>1.54</v>
+      </c>
+      <c r="X18">
+        <v>21</v>
+      </c>
+      <c r="Y18">
+        <v>13.5</v>
+      </c>
+      <c r="Z18">
+        <v>19.5</v>
+      </c>
+      <c r="AA18">
+        <v>40</v>
+      </c>
+      <c r="AB18">
+        <v>15</v>
+      </c>
+      <c r="AC18">
+        <v>8.6</v>
+      </c>
+      <c r="AD18">
+        <v>13</v>
+      </c>
+      <c r="AE18">
+        <v>30</v>
+      </c>
+      <c r="AF18">
+        <v>20</v>
+      </c>
+      <c r="AG18">
+        <v>13</v>
+      </c>
+      <c r="AH18">
+        <v>17</v>
+      </c>
+      <c r="AI18">
+        <v>40</v>
+      </c>
+      <c r="AJ18">
+        <v>44</v>
+      </c>
+      <c r="AK18">
+        <v>30</v>
+      </c>
+      <c r="AL18">
+        <v>42</v>
+      </c>
+      <c r="AM18">
+        <v>90</v>
+      </c>
+      <c r="AN18">
+        <v>26</v>
+      </c>
+      <c r="AO18">
+        <v>23</v>
+      </c>
+      <c r="AP18">
+        <v>14</v>
+      </c>
+      <c r="AQ18">
+        <v>10</v>
+      </c>
+      <c r="AR18">
+        <v>15.5</v>
+      </c>
+      <c r="AS18">
+        <v>27</v>
+      </c>
+      <c r="AT18">
+        <v>11</v>
+      </c>
+      <c r="AU18">
+        <v>7.2</v>
+      </c>
+      <c r="AV18">
+        <v>10.5</v>
+      </c>
+      <c r="AW18">
+        <v>20</v>
+      </c>
+      <c r="AX18">
+        <v>16.5</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>14.5</v>
+      </c>
+      <c r="BA18">
+        <v>27</v>
+      </c>
+      <c r="BB18">
+        <v>29</v>
+      </c>
+      <c r="BC18">
+        <v>6.6</v>
+      </c>
+      <c r="BD18">
+        <v>17</v>
+      </c>
+      <c r="BE18">
+        <v>30</v>
+      </c>
+      <c r="BF18">
+        <v>20</v>
+      </c>
+      <c r="BG18">
+        <v>19</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.04</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.04</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.04</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.04</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.04</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.04</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.04</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.04</v>
+      </c>
+      <c r="CB18" t="s">
         <v>149</v>
-      </c>
-      <c r="F18">
-        <v>2.06</v>
-      </c>
-      <c r="G18">
-        <v>2.14</v>
-      </c>
-      <c r="H18">
-        <v>4.7</v>
-      </c>
-      <c r="I18">
-        <v>5.1</v>
-      </c>
-      <c r="J18">
-        <v>3.1</v>
-      </c>
-      <c r="K18">
-        <v>3.2</v>
-      </c>
-      <c r="L18">
-        <v>1.59</v>
-      </c>
-      <c r="M18">
-        <v>1.16</v>
-      </c>
-      <c r="N18">
-        <v>2.36</v>
-      </c>
-      <c r="O18">
-        <v>1.68</v>
-      </c>
-      <c r="P18">
-        <v>1.45</v>
-      </c>
-      <c r="Q18">
-        <v>3.05</v>
-      </c>
-      <c r="R18">
-        <v>1.15</v>
-      </c>
-      <c r="S18">
-        <v>7</v>
-      </c>
-      <c r="T18">
-        <v>2.52</v>
-      </c>
-      <c r="U18">
-        <v>1.62</v>
-      </c>
-      <c r="V18">
-        <v>1.24</v>
-      </c>
-      <c r="W18">
-        <v>1.88</v>
-      </c>
-      <c r="X18">
-        <v>7.2</v>
-      </c>
-      <c r="Y18">
-        <v>11</v>
-      </c>
-      <c r="Z18">
-        <v>36</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>5.9</v>
-      </c>
-      <c r="AC18">
-        <v>7.8</v>
-      </c>
-      <c r="AD18">
-        <v>24</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>10.5</v>
-      </c>
-      <c r="AG18">
-        <v>12.5</v>
-      </c>
-      <c r="AH18">
-        <v>34</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>29</v>
-      </c>
-      <c r="AK18">
-        <v>34</v>
-      </c>
-      <c r="AL18">
-        <v>80</v>
-      </c>
-      <c r="AM18">
-        <v>340</v>
-      </c>
-      <c r="AN18">
-        <v>34</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>6.6</v>
-      </c>
-      <c r="AQ18">
-        <v>9.6</v>
-      </c>
-      <c r="AR18">
-        <v>27</v>
-      </c>
-      <c r="AS18">
-        <v>44</v>
-      </c>
-      <c r="AT18">
-        <v>5.5</v>
-      </c>
-      <c r="AU18">
-        <v>7</v>
-      </c>
-      <c r="AV18">
-        <v>20</v>
-      </c>
-      <c r="AW18">
-        <v>60</v>
-      </c>
-      <c r="AX18">
-        <v>9.6</v>
-      </c>
-      <c r="AY18">
-        <v>11</v>
-      </c>
-      <c r="AZ18">
-        <v>24</v>
-      </c>
-      <c r="BA18">
-        <v>44</v>
-      </c>
-      <c r="BB18">
-        <v>23</v>
-      </c>
-      <c r="BC18">
-        <v>23</v>
-      </c>
-      <c r="BD18">
-        <v>55</v>
-      </c>
-      <c r="BE18">
-        <v>95</v>
-      </c>
-      <c r="BF18">
-        <v>19.5</v>
-      </c>
-      <c r="BG18">
-        <v>46</v>
-      </c>
-      <c r="BH18">
-        <v>2.6</v>
-      </c>
-      <c r="BI18">
-        <v>2.2</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>3.6</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.37</v>
-      </c>
-      <c r="BN18">
-        <v>5.9</v>
-      </c>
-      <c r="BO18">
-        <v>3.3</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>3.8</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>2.9</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
-      <c r="BU18">
-        <v>5.3</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>2.9</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>1.37</v>
-      </c>
-      <c r="BZ18">
-        <v>1000</v>
-      </c>
-      <c r="CA18">
-        <v>2.9</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
         <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F19">
-        <v>1.77</v>
+        <v>2.64</v>
       </c>
       <c r="G19">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="H19">
-        <v>5.6</v>
+        <v>2.36</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="J19">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="L19">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH19">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL19">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AQ19">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AS19">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AU19">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX19">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ19">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB19">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BC19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BD19">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BE19">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH19">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BI19">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK19">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BL19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO19">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ19">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU19">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
         <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F20">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="G20">
-        <v>2.94</v>
+        <v>1.65</v>
       </c>
       <c r="H20">
-        <v>2.52</v>
+        <v>7</v>
       </c>
       <c r="I20">
-        <v>2.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O20">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q20">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="T20">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="U20">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="W20">
-        <v>1.51</v>
+        <v>2.54</v>
       </c>
       <c r="X20">
+        <v>13.5</v>
+      </c>
+      <c r="Y20">
+        <v>22</v>
+      </c>
+      <c r="Z20">
+        <v>80</v>
+      </c>
+      <c r="AA20">
+        <v>680</v>
+      </c>
+      <c r="AB20">
+        <v>7.2</v>
+      </c>
+      <c r="AC20">
+        <v>9.6</v>
+      </c>
+      <c r="AD20">
+        <v>32</v>
+      </c>
+      <c r="AE20">
+        <v>690</v>
+      </c>
+      <c r="AF20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG20">
+        <v>10.5</v>
+      </c>
+      <c r="AH20">
+        <v>32</v>
+      </c>
+      <c r="AI20">
+        <v>690</v>
+      </c>
+      <c r="AJ20">
+        <v>15.5</v>
+      </c>
+      <c r="AK20">
+        <v>19.5</v>
+      </c>
+      <c r="AL20">
+        <v>55</v>
+      </c>
+      <c r="AM20">
+        <v>680</v>
+      </c>
+      <c r="AN20">
+        <v>11.5</v>
+      </c>
+      <c r="AO20">
+        <v>690</v>
+      </c>
+      <c r="AP20">
+        <v>11</v>
+      </c>
+      <c r="AQ20">
+        <v>17.5</v>
+      </c>
+      <c r="AR20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT20">
+        <v>6</v>
+      </c>
+      <c r="AU20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20">
         <v>21</v>
       </c>
-      <c r="Y20">
-        <v>13.5</v>
-      </c>
-      <c r="Z20">
+      <c r="AW20">
+        <v>8.6</v>
+      </c>
+      <c r="AX20">
+        <v>7.4</v>
+      </c>
+      <c r="AY20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ20">
         <v>19</v>
       </c>
-      <c r="AA20">
-        <v>40</v>
-      </c>
-      <c r="AB20">
-        <v>15</v>
-      </c>
-      <c r="AC20">
-        <v>8.4</v>
-      </c>
-      <c r="AD20">
-        <v>13</v>
-      </c>
-      <c r="AE20">
-        <v>28</v>
-      </c>
-      <c r="AF20">
-        <v>21</v>
-      </c>
-      <c r="AG20">
-        <v>13</v>
-      </c>
-      <c r="AH20">
-        <v>17</v>
-      </c>
-      <c r="AI20">
-        <v>40</v>
-      </c>
-      <c r="AJ20">
-        <v>44</v>
-      </c>
-      <c r="AK20">
-        <v>32</v>
-      </c>
-      <c r="AL20">
-        <v>42</v>
-      </c>
-      <c r="AM20">
-        <v>90</v>
-      </c>
-      <c r="AN20">
-        <v>26</v>
-      </c>
-      <c r="AO20">
-        <v>23</v>
-      </c>
-      <c r="AP20">
-        <v>14</v>
-      </c>
-      <c r="AQ20">
-        <v>10</v>
-      </c>
-      <c r="AR20">
-        <v>15.5</v>
-      </c>
-      <c r="AS20">
-        <v>15</v>
-      </c>
-      <c r="AT20">
-        <v>11</v>
-      </c>
-      <c r="AU20">
-        <v>7.2</v>
-      </c>
-      <c r="AV20">
-        <v>10.5</v>
-      </c>
-      <c r="AW20">
-        <v>20</v>
-      </c>
-      <c r="AX20">
-        <v>16.5</v>
-      </c>
-      <c r="AY20">
-        <v>11</v>
-      </c>
-      <c r="AZ20">
-        <v>14.5</v>
-      </c>
       <c r="BA20">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="BB20">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="BC20">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BD20">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BE20">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BG20">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5653,12 +5635,12 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
         <v>93</v>
@@ -5667,719 +5649,235 @@
         <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F21">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="G21">
+        <v>2.3</v>
+      </c>
+      <c r="H21">
         <v>3.3</v>
       </c>
-      <c r="H21">
-        <v>2.36</v>
-      </c>
       <c r="I21">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J21">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CB21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:80">
-      <c r="A22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22">
-        <v>1.57</v>
-      </c>
-      <c r="G22">
-        <v>1.65</v>
-      </c>
-      <c r="H22">
-        <v>7</v>
-      </c>
-      <c r="I22">
-        <v>8</v>
-      </c>
-      <c r="J22">
-        <v>3.85</v>
-      </c>
-      <c r="K22">
-        <v>4.3</v>
-      </c>
-      <c r="L22">
-        <v>1.35</v>
-      </c>
-      <c r="M22">
-        <v>1.08</v>
-      </c>
-      <c r="N22">
-        <v>3.3</v>
-      </c>
-      <c r="O22">
-        <v>1.37</v>
-      </c>
-      <c r="P22">
-        <v>1.77</v>
-      </c>
-      <c r="Q22">
-        <v>2.08</v>
-      </c>
-      <c r="R22">
-        <v>1.3</v>
-      </c>
-      <c r="S22">
-        <v>3.8</v>
-      </c>
-      <c r="T22">
-        <v>2.12</v>
-      </c>
-      <c r="U22">
-        <v>1.76</v>
-      </c>
-      <c r="V22">
-        <v>1.14</v>
-      </c>
-      <c r="W22">
-        <v>2.54</v>
-      </c>
-      <c r="X22">
-        <v>13.5</v>
-      </c>
-      <c r="Y22">
-        <v>22</v>
-      </c>
-      <c r="Z22">
-        <v>80</v>
-      </c>
-      <c r="AA22">
-        <v>780</v>
-      </c>
-      <c r="AB22">
-        <v>7.2</v>
-      </c>
-      <c r="AC22">
-        <v>9.6</v>
-      </c>
-      <c r="AD22">
-        <v>32</v>
-      </c>
-      <c r="AE22">
-        <v>790</v>
-      </c>
-      <c r="AF22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG22">
-        <v>10.5</v>
-      </c>
-      <c r="AH22">
-        <v>32</v>
-      </c>
-      <c r="AI22">
-        <v>790</v>
-      </c>
-      <c r="AJ22">
-        <v>15.5</v>
-      </c>
-      <c r="AK22">
-        <v>19.5</v>
-      </c>
-      <c r="AL22">
-        <v>55</v>
-      </c>
-      <c r="AM22">
-        <v>780</v>
-      </c>
-      <c r="AN22">
-        <v>11.5</v>
-      </c>
-      <c r="AO22">
-        <v>790</v>
-      </c>
-      <c r="AP22">
-        <v>11</v>
-      </c>
-      <c r="AQ22">
-        <v>17.5</v>
-      </c>
-      <c r="AR22">
-        <v>9</v>
-      </c>
-      <c r="AS22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT22">
-        <v>6</v>
-      </c>
-      <c r="AU22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV22">
-        <v>21</v>
-      </c>
-      <c r="AW22">
-        <v>8.6</v>
-      </c>
-      <c r="AX22">
-        <v>7.4</v>
-      </c>
-      <c r="AY22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ22">
-        <v>19</v>
-      </c>
-      <c r="BA22">
-        <v>8.6</v>
-      </c>
-      <c r="BB22">
-        <v>12.5</v>
-      </c>
-      <c r="BC22">
-        <v>16</v>
-      </c>
-      <c r="BD22">
-        <v>36</v>
-      </c>
-      <c r="BE22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF22">
-        <v>9.6</v>
-      </c>
-      <c r="BG22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.04</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>1.04</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.04</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
-        <v>1.04</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>1.04</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>1.04</v>
-      </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
-      <c r="BU22">
-        <v>1.04</v>
-      </c>
-      <c r="BV22">
-        <v>1000</v>
-      </c>
-      <c r="BW22">
-        <v>1.04</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>1.04</v>
-      </c>
-      <c r="BZ22">
-        <v>1000</v>
-      </c>
-      <c r="CA22">
-        <v>1.04</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" t="s">
-        <v>154</v>
-      </c>
-      <c r="F23">
-        <v>2.18</v>
-      </c>
-      <c r="G23">
-        <v>2.3</v>
-      </c>
-      <c r="H23">
-        <v>3.25</v>
-      </c>
-      <c r="I23">
-        <v>3.55</v>
-      </c>
-      <c r="J23">
-        <v>3.6</v>
-      </c>
-      <c r="K23">
-        <v>3.85</v>
-      </c>
-      <c r="L23">
-        <v>1.38</v>
-      </c>
-      <c r="M23">
-        <v>1.06</v>
-      </c>
-      <c r="N23">
-        <v>3.95</v>
-      </c>
-      <c r="O23">
-        <v>1.3</v>
-      </c>
-      <c r="P23">
-        <v>1.95</v>
-      </c>
-      <c r="Q23">
-        <v>1.89</v>
-      </c>
-      <c r="R23">
-        <v>1.37</v>
-      </c>
-      <c r="S23">
-        <v>3.2</v>
-      </c>
-      <c r="T23">
-        <v>1.73</v>
-      </c>
-      <c r="U23">
-        <v>2.18</v>
-      </c>
-      <c r="V23">
-        <v>1.39</v>
-      </c>
-      <c r="W23">
-        <v>1.76</v>
-      </c>
-      <c r="X23">
-        <v>16</v>
-      </c>
-      <c r="Y23">
-        <v>14.5</v>
-      </c>
-      <c r="Z23">
-        <v>26</v>
-      </c>
-      <c r="AA23">
-        <v>65</v>
-      </c>
-      <c r="AB23">
-        <v>11</v>
-      </c>
-      <c r="AC23">
-        <v>8.4</v>
-      </c>
-      <c r="AD23">
-        <v>15</v>
-      </c>
-      <c r="AE23">
-        <v>42</v>
-      </c>
-      <c r="AF23">
-        <v>15.5</v>
-      </c>
-      <c r="AG23">
-        <v>11.5</v>
-      </c>
-      <c r="AH23">
-        <v>18</v>
-      </c>
-      <c r="AI23">
-        <v>60</v>
-      </c>
-      <c r="AJ23">
-        <v>30</v>
-      </c>
-      <c r="AK23">
-        <v>25</v>
-      </c>
-      <c r="AL23">
-        <v>38</v>
-      </c>
-      <c r="AM23">
-        <v>110</v>
-      </c>
-      <c r="AN23">
-        <v>17.5</v>
-      </c>
-      <c r="AO23">
-        <v>38</v>
-      </c>
-      <c r="AP23">
-        <v>13</v>
-      </c>
-      <c r="AQ23">
-        <v>12</v>
-      </c>
-      <c r="AR23">
-        <v>21</v>
-      </c>
-      <c r="AS23">
-        <v>22</v>
-      </c>
-      <c r="AT23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU23">
-        <v>7.2</v>
-      </c>
-      <c r="AV23">
-        <v>12.5</v>
-      </c>
-      <c r="AW23">
-        <v>14.5</v>
-      </c>
-      <c r="AX23">
-        <v>12.5</v>
-      </c>
-      <c r="AY23">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ23">
-        <v>14.5</v>
-      </c>
-      <c r="BA23">
-        <v>18.5</v>
-      </c>
-      <c r="BB23">
-        <v>11</v>
-      </c>
-      <c r="BC23">
-        <v>20</v>
-      </c>
-      <c r="BD23">
-        <v>12.5</v>
-      </c>
-      <c r="BE23">
-        <v>30</v>
-      </c>
-      <c r="BF23">
-        <v>14.5</v>
-      </c>
-      <c r="BG23">
-        <v>8</v>
-      </c>
-      <c r="BH23">
-        <v>3.6</v>
-      </c>
-      <c r="BI23">
-        <v>3.15</v>
-      </c>
-      <c r="BJ23">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK23">
-        <v>6.8</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>10</v>
-      </c>
-      <c r="BN23">
-        <v>5.3</v>
-      </c>
-      <c r="BO23">
-        <v>4.6</v>
-      </c>
-      <c r="BP23">
-        <v>17</v>
-      </c>
-      <c r="BQ23">
-        <v>6.8</v>
-      </c>
-      <c r="BR23">
-        <v>30</v>
-      </c>
-      <c r="BS23">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT23">
-        <v>7</v>
-      </c>
-      <c r="BU23">
-        <v>5.7</v>
-      </c>
-      <c r="BV23">
-        <v>28</v>
-      </c>
-      <c r="BW23">
-        <v>8</v>
-      </c>
-      <c r="BX23">
-        <v>38</v>
-      </c>
-      <c r="BY23">
-        <v>8.6</v>
-      </c>
-      <c r="BZ23">
-        <v>26</v>
-      </c>
-      <c r="CA23">
-        <v>7.8</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="143">
   <si>
     <t>League</t>
   </si>
@@ -256,39 +256,36 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
+    <t>Serbian First League</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Turkish 2 Lig</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Argentinian Primera B Metropolitana</t>
+  </si>
+  <si>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
   </si>
   <si>
     <t>CONCACAF Nations League A</t>
   </si>
   <si>
-    <t>Serbian First League</t>
-  </si>
-  <si>
-    <t>Paraguayan Primera Division</t>
-  </si>
-  <si>
-    <t>Slovakian 2 Liga</t>
-  </si>
-  <si>
-    <t>Turkish 2 Lig</t>
-  </si>
-  <si>
-    <t>Norwegian 1st Division</t>
-  </si>
-  <si>
-    <t>Argentinian Primera B Metropolitana</t>
-  </si>
-  <si>
-    <t>Spanish Segunda Division</t>
-  </si>
-  <si>
-    <t>CONCACAF Nations League B</t>
-  </si>
-  <si>
-    <t>Argentinian Primera Division</t>
-  </si>
-  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -298,12 +295,6 @@
     <t>2026-10-05</t>
   </si>
   <si>
-    <t>01:15:00</t>
-  </si>
-  <si>
-    <t>02:00:00</t>
-  </si>
-  <si>
     <t>13:00:00</t>
   </si>
   <si>
@@ -343,12 +334,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Llaneros FC</t>
-  </si>
-  <si>
-    <t>Nicaragua</t>
-  </si>
-  <si>
     <t>Fk Smederevo</t>
   </si>
   <si>
@@ -403,12 +388,6 @@
     <t>Nacional (Uru)</t>
   </si>
   <si>
-    <t>America de Cali S.A</t>
-  </si>
-  <si>
-    <t>Dominican Republic</t>
-  </si>
-  <si>
     <t>Vozdovac</t>
   </si>
   <si>
@@ -463,7 +442,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-04 23:37:12</t>
+    <t>2026-10-05 01:46:57</t>
   </si>
 </sst>
 </file>
@@ -795,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1045,241 +1024,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
         <v>93</v>
       </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>3.4</v>
+      </c>
+      <c r="K2">
+        <v>3.65</v>
+      </c>
+      <c r="L2">
+        <v>1.47</v>
+      </c>
+      <c r="M2">
+        <v>1.09</v>
+      </c>
+      <c r="N2">
+        <v>3.25</v>
+      </c>
+      <c r="O2">
+        <v>1.38</v>
+      </c>
+      <c r="P2">
+        <v>1.76</v>
+      </c>
+      <c r="Q2">
+        <v>2.16</v>
+      </c>
+      <c r="R2">
+        <v>1.27</v>
+      </c>
+      <c r="S2">
+        <v>4</v>
+      </c>
+      <c r="T2">
+        <v>1.93</v>
+      </c>
+      <c r="U2">
+        <v>1.89</v>
+      </c>
+      <c r="V2">
+        <v>1.27</v>
+      </c>
+      <c r="W2">
+        <v>1.94</v>
+      </c>
+      <c r="X2">
+        <v>13.5</v>
+      </c>
+      <c r="Y2">
+        <v>16.5</v>
+      </c>
+      <c r="Z2">
+        <v>40</v>
+      </c>
+      <c r="AA2">
+        <v>130</v>
+      </c>
+      <c r="AB2">
         <v>9</v>
       </c>
-      <c r="J2">
-        <v>3.5</v>
-      </c>
-      <c r="K2">
-        <v>3.6</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>2.94</v>
-      </c>
-      <c r="O2">
-        <v>1.51</v>
-      </c>
-      <c r="P2">
-        <v>1.41</v>
-      </c>
-      <c r="Q2">
-        <v>3.3</v>
-      </c>
-      <c r="R2">
-        <v>1.09</v>
-      </c>
-      <c r="S2">
-        <v>11</v>
-      </c>
-      <c r="T2">
-        <v>1.92</v>
-      </c>
-      <c r="U2">
-        <v>1.96</v>
-      </c>
-      <c r="V2">
-        <v>1.13</v>
-      </c>
-      <c r="W2">
-        <v>2.46</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>3.05</v>
-      </c>
       <c r="AC2">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AK2">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AL2">
-        <v>260</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AO2">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
+        <v>10.5</v>
+      </c>
+      <c r="AR2">
+        <v>5</v>
+      </c>
+      <c r="AS2">
+        <v>5.5</v>
+      </c>
+      <c r="AT2">
+        <v>6.2</v>
+      </c>
+      <c r="AU2">
+        <v>6.2</v>
+      </c>
+      <c r="AV2">
+        <v>14</v>
+      </c>
+      <c r="AW2">
+        <v>5.3</v>
+      </c>
+      <c r="AX2">
+        <v>9</v>
+      </c>
+      <c r="AY2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>5.3</v>
+      </c>
+      <c r="BB2">
+        <v>18</v>
+      </c>
+      <c r="BC2">
         <v>17.5</v>
       </c>
-      <c r="AQ2">
-        <v>17.5</v>
-      </c>
-      <c r="AR2">
-        <v>17.5</v>
-      </c>
-      <c r="AS2">
-        <v>17.5</v>
-      </c>
-      <c r="AT2">
-        <v>2.96</v>
-      </c>
-      <c r="AU2">
-        <v>3.8</v>
-      </c>
-      <c r="AV2">
-        <v>10.5</v>
-      </c>
-      <c r="AW2">
-        <v>50</v>
-      </c>
-      <c r="AX2">
-        <v>7.6</v>
-      </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>29</v>
-      </c>
-      <c r="BA2">
-        <v>120</v>
-      </c>
-      <c r="BB2">
-        <v>40</v>
-      </c>
-      <c r="BC2">
-        <v>60</v>
-      </c>
       <c r="BD2">
-        <v>130</v>
+        <v>5.1</v>
       </c>
       <c r="BE2">
-        <v>290</v>
+        <v>5.5</v>
       </c>
       <c r="BF2">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>130</v>
+        <v>5.4</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1287,1038 +1266,1038 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>1.08</v>
       </c>
       <c r="I3">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L3">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>4.1</v>
+      </c>
+      <c r="Q3">
+        <v>1.27</v>
+      </c>
+      <c r="R3">
+        <v>1.75</v>
+      </c>
+      <c r="S3">
+        <v>1.03</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+      <c r="W3">
+        <v>1.01</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>18</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.05</v>
+      </c>
+      <c r="AQ3">
+        <v>1.05</v>
+      </c>
+      <c r="AR3">
+        <v>1.05</v>
+      </c>
+      <c r="AS3">
+        <v>1.05</v>
+      </c>
+      <c r="AT3">
+        <v>1.05</v>
+      </c>
+      <c r="AU3">
+        <v>1.05</v>
+      </c>
+      <c r="AV3">
+        <v>2.44</v>
+      </c>
+      <c r="AW3">
+        <v>1.59</v>
+      </c>
+      <c r="AX3">
+        <v>1.05</v>
+      </c>
+      <c r="AY3">
+        <v>3</v>
+      </c>
+      <c r="AZ3">
         <v>2.02</v>
       </c>
-      <c r="P3">
-        <v>1.29</v>
-      </c>
-      <c r="Q3">
-        <v>4.2</v>
-      </c>
-      <c r="R3">
-        <v>1.09</v>
-      </c>
-      <c r="S3">
-        <v>11</v>
-      </c>
-      <c r="T3">
-        <v>3</v>
-      </c>
-      <c r="U3">
-        <v>1.41</v>
-      </c>
-      <c r="V3">
-        <v>1.61</v>
-      </c>
-      <c r="W3">
-        <v>1.38</v>
-      </c>
-      <c r="X3">
-        <v>6.4</v>
-      </c>
-      <c r="Y3">
-        <v>6.2</v>
-      </c>
-      <c r="Z3">
-        <v>12.5</v>
-      </c>
-      <c r="AA3">
-        <v>46</v>
-      </c>
-      <c r="AB3">
-        <v>7.6</v>
-      </c>
-      <c r="AC3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>17</v>
-      </c>
-      <c r="AE3">
-        <v>60</v>
-      </c>
-      <c r="AF3">
-        <v>22</v>
-      </c>
-      <c r="AG3">
-        <v>21</v>
-      </c>
-      <c r="AH3">
-        <v>46</v>
-      </c>
-      <c r="AI3">
-        <v>160</v>
-      </c>
-      <c r="AJ3">
-        <v>100</v>
-      </c>
-      <c r="AK3">
-        <v>110</v>
-      </c>
-      <c r="AL3">
-        <v>180</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>200</v>
-      </c>
-      <c r="AO3">
-        <v>85</v>
-      </c>
-      <c r="AP3">
-        <v>6</v>
-      </c>
-      <c r="AQ3">
-        <v>5.5</v>
-      </c>
-      <c r="AR3">
-        <v>11</v>
-      </c>
-      <c r="AS3">
-        <v>38</v>
-      </c>
-      <c r="AT3">
-        <v>6.8</v>
-      </c>
-      <c r="AU3">
-        <v>7.4</v>
-      </c>
-      <c r="AV3">
-        <v>15</v>
-      </c>
-      <c r="AW3">
-        <v>44</v>
-      </c>
-      <c r="AX3">
-        <v>18</v>
-      </c>
-      <c r="AY3">
-        <v>18</v>
-      </c>
-      <c r="AZ3">
-        <v>34</v>
-      </c>
       <c r="BA3">
-        <v>100</v>
+        <v>1.05</v>
       </c>
       <c r="BB3">
-        <v>75</v>
+        <v>1.05</v>
       </c>
       <c r="BC3">
-        <v>70</v>
+        <v>1.05</v>
       </c>
       <c r="BD3">
-        <v>130</v>
+        <v>1.05</v>
       </c>
       <c r="BE3">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>100</v>
+        <v>1.05</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>3.95</v>
       </c>
       <c r="BH3">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J4">
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
+        <v>2.06</v>
+      </c>
+      <c r="R4">
+        <v>1.32</v>
+      </c>
+      <c r="S4">
+        <v>3.65</v>
+      </c>
+      <c r="T4">
+        <v>1.79</v>
+      </c>
+      <c r="U4">
         <v>2.08</v>
       </c>
-      <c r="R4">
-        <v>1.27</v>
-      </c>
-      <c r="S4">
-        <v>3.95</v>
-      </c>
-      <c r="T4">
-        <v>1.89</v>
-      </c>
-      <c r="U4">
-        <v>1.89</v>
-      </c>
       <c r="V4">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y4">
+        <v>12.5</v>
+      </c>
+      <c r="Z4">
+        <v>24</v>
+      </c>
+      <c r="AA4">
+        <v>75</v>
+      </c>
+      <c r="AB4">
+        <v>10</v>
+      </c>
+      <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
         <v>16.5</v>
       </c>
-      <c r="Z4">
-        <v>40</v>
-      </c>
-      <c r="AA4">
-        <v>130</v>
-      </c>
-      <c r="AB4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC4">
-        <v>8.4</v>
-      </c>
-      <c r="AD4">
-        <v>22</v>
-      </c>
       <c r="AE4">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AF4">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG4">
         <v>12</v>
       </c>
       <c r="AH4">
+        <v>18</v>
+      </c>
+      <c r="AI4">
+        <v>55</v>
+      </c>
+      <c r="AJ4">
+        <v>36</v>
+      </c>
+      <c r="AK4">
+        <v>28</v>
+      </c>
+      <c r="AL4">
+        <v>42</v>
+      </c>
+      <c r="AM4">
+        <v>130</v>
+      </c>
+      <c r="AN4">
+        <v>25</v>
+      </c>
+      <c r="AO4">
+        <v>46</v>
+      </c>
+      <c r="AP4">
+        <v>10</v>
+      </c>
+      <c r="AQ4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR4">
+        <v>19</v>
+      </c>
+      <c r="AS4">
+        <v>25</v>
+      </c>
+      <c r="AT4">
+        <v>7.8</v>
+      </c>
+      <c r="AU4">
+        <v>5.7</v>
+      </c>
+      <c r="AV4">
+        <v>11</v>
+      </c>
+      <c r="AW4">
         <v>24</v>
       </c>
-      <c r="AI4">
-        <v>90</v>
-      </c>
-      <c r="AJ4">
-        <v>28</v>
-      </c>
-      <c r="AK4">
+      <c r="AX4">
+        <v>11.5</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>14.5</v>
+      </c>
+      <c r="BA4">
+        <v>32</v>
+      </c>
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>18</v>
+      </c>
+      <c r="BD4">
+        <v>17</v>
+      </c>
+      <c r="BE4">
+        <v>70</v>
+      </c>
+      <c r="BF4">
+        <v>19</v>
+      </c>
+      <c r="BG4">
+        <v>23</v>
+      </c>
+      <c r="BH4">
+        <v>3.25</v>
+      </c>
+      <c r="BI4">
+        <v>2.72</v>
+      </c>
+      <c r="BJ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4">
+        <v>5.8</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>12.5</v>
+      </c>
+      <c r="BN4">
+        <v>5.3</v>
+      </c>
+      <c r="BO4">
+        <v>4.6</v>
+      </c>
+      <c r="BP4">
+        <v>18.5</v>
+      </c>
+      <c r="BQ4">
+        <v>8</v>
+      </c>
+      <c r="BR4">
+        <v>34</v>
+      </c>
+      <c r="BS4">
+        <v>10</v>
+      </c>
+      <c r="BT4">
+        <v>6.4</v>
+      </c>
+      <c r="BU4">
+        <v>5.4</v>
+      </c>
+      <c r="BV4">
         <v>27</v>
       </c>
-      <c r="AL4">
-        <v>50</v>
-      </c>
-      <c r="AM4">
-        <v>160</v>
-      </c>
-      <c r="AN4">
-        <v>21</v>
-      </c>
-      <c r="AO4">
-        <v>100</v>
-      </c>
-      <c r="AP4">
+      <c r="BW4">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ4">
-        <v>11</v>
-      </c>
-      <c r="AR4">
-        <v>4.8</v>
-      </c>
-      <c r="AS4">
-        <v>5.2</v>
-      </c>
-      <c r="AT4">
-        <v>6.2</v>
-      </c>
-      <c r="AU4">
-        <v>6.6</v>
-      </c>
-      <c r="AV4">
-        <v>14</v>
-      </c>
-      <c r="AW4">
-        <v>5.1</v>
-      </c>
-      <c r="AX4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4">
-        <v>15.5</v>
-      </c>
-      <c r="BA4">
-        <v>5.1</v>
-      </c>
-      <c r="BB4">
-        <v>18</v>
-      </c>
-      <c r="BC4">
-        <v>19</v>
-      </c>
-      <c r="BD4">
-        <v>4.9</v>
-      </c>
-      <c r="BE4">
-        <v>5.3</v>
-      </c>
-      <c r="BF4">
-        <v>13.5</v>
-      </c>
-      <c r="BG4">
-        <v>5.2</v>
-      </c>
-      <c r="BH4">
-        <v>3.5</v>
-      </c>
-      <c r="BI4">
-        <v>2.6</v>
-      </c>
-      <c r="BJ4">
-        <v>12</v>
-      </c>
-      <c r="BK4">
-        <v>4</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>5.8</v>
-      </c>
-      <c r="BN4">
-        <v>5.1</v>
-      </c>
-      <c r="BO4">
-        <v>3.9</v>
-      </c>
-      <c r="BP4">
-        <v>17</v>
-      </c>
-      <c r="BQ4">
-        <v>4.4</v>
-      </c>
-      <c r="BR4">
-        <v>38</v>
-      </c>
-      <c r="BS4">
-        <v>5.1</v>
-      </c>
-      <c r="BT4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU4">
-        <v>3.55</v>
-      </c>
-      <c r="BV4">
-        <v>48</v>
-      </c>
-      <c r="BW4">
-        <v>5.3</v>
-      </c>
       <c r="BX4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CA4">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G5">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="H5">
-        <v>1.08</v>
+        <v>2.94</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
+        <v>2.36</v>
+      </c>
+      <c r="Q5">
+        <v>1.6</v>
+      </c>
+      <c r="R5">
+        <v>1.54</v>
+      </c>
+      <c r="S5">
+        <v>2.6</v>
+      </c>
+      <c r="T5">
+        <v>1.57</v>
+      </c>
+      <c r="U5">
+        <v>2.5</v>
+      </c>
+      <c r="V5">
+        <v>1.39</v>
+      </c>
+      <c r="W5">
+        <v>1.69</v>
+      </c>
+      <c r="X5">
+        <v>28</v>
+      </c>
+      <c r="Y5">
+        <v>21</v>
+      </c>
+      <c r="Z5">
+        <v>32</v>
+      </c>
+      <c r="AA5">
+        <v>65</v>
+      </c>
+      <c r="AB5">
+        <v>17</v>
+      </c>
+      <c r="AC5">
+        <v>11.5</v>
+      </c>
+      <c r="AD5">
+        <v>17</v>
+      </c>
+      <c r="AE5">
+        <v>38</v>
+      </c>
+      <c r="AF5">
+        <v>21</v>
+      </c>
+      <c r="AG5">
+        <v>14</v>
+      </c>
+      <c r="AH5">
+        <v>18.5</v>
+      </c>
+      <c r="AI5">
+        <v>44</v>
+      </c>
+      <c r="AJ5">
+        <v>36</v>
+      </c>
+      <c r="AK5">
+        <v>26</v>
+      </c>
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>75</v>
+      </c>
+      <c r="AN5">
+        <v>15</v>
+      </c>
+      <c r="AO5">
+        <v>26</v>
+      </c>
+      <c r="AP5">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5">
+        <v>14.5</v>
+      </c>
+      <c r="AR5">
+        <v>18</v>
+      </c>
+      <c r="AS5">
+        <v>4.2</v>
+      </c>
+      <c r="AT5">
+        <v>11.5</v>
+      </c>
+      <c r="AU5">
+        <v>8</v>
+      </c>
+      <c r="AV5">
+        <v>11.5</v>
+      </c>
+      <c r="AW5">
+        <v>4</v>
+      </c>
+      <c r="AX5">
+        <v>14.5</v>
+      </c>
+      <c r="AY5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>12.5</v>
+      </c>
+      <c r="BA5">
         <v>4.1</v>
       </c>
-      <c r="Q5">
-        <v>1.27</v>
-      </c>
-      <c r="R5">
-        <v>1.75</v>
-      </c>
-      <c r="S5">
-        <v>1.03</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>1.01</v>
-      </c>
-      <c r="W5">
-        <v>1.01</v>
-      </c>
-      <c r="X5">
-        <v>1000</v>
-      </c>
-      <c r="Y5">
-        <v>1000</v>
-      </c>
-      <c r="Z5">
-        <v>1000</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>1000</v>
-      </c>
-      <c r="AC5">
-        <v>1000</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>18</v>
-      </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>1000</v>
-      </c>
-      <c r="AH5">
-        <v>990</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>1.05</v>
-      </c>
-      <c r="AQ5">
-        <v>1.05</v>
-      </c>
-      <c r="AR5">
-        <v>1.05</v>
-      </c>
-      <c r="AS5">
-        <v>1.05</v>
-      </c>
-      <c r="AT5">
-        <v>1.05</v>
-      </c>
-      <c r="AU5">
-        <v>1.05</v>
-      </c>
-      <c r="AV5">
-        <v>2.44</v>
-      </c>
-      <c r="AW5">
-        <v>1.59</v>
-      </c>
-      <c r="AX5">
-        <v>1.05</v>
-      </c>
-      <c r="AY5">
-        <v>3</v>
-      </c>
-      <c r="AZ5">
-        <v>2.02</v>
-      </c>
-      <c r="BA5">
-        <v>1.05</v>
-      </c>
       <c r="BB5">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="BC5">
-        <v>1.05</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>1.05</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="CB5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F6">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="G6">
+        <v>1.36</v>
+      </c>
+      <c r="H6">
+        <v>8.6</v>
+      </c>
+      <c r="I6">
+        <v>13.5</v>
+      </c>
+      <c r="J6">
+        <v>5.1</v>
+      </c>
+      <c r="K6">
+        <v>6.6</v>
+      </c>
+      <c r="L6">
+        <v>1.27</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>5.6</v>
+      </c>
+      <c r="O6">
+        <v>1.18</v>
+      </c>
+      <c r="P6">
         <v>2.62</v>
       </c>
-      <c r="H6">
-        <v>3.05</v>
-      </c>
-      <c r="I6">
-        <v>3.55</v>
-      </c>
-      <c r="J6">
-        <v>3.2</v>
-      </c>
-      <c r="K6">
-        <v>3.65</v>
-      </c>
-      <c r="L6">
-        <v>1.42</v>
-      </c>
-      <c r="M6">
-        <v>1.07</v>
-      </c>
-      <c r="N6">
-        <v>3.4</v>
-      </c>
-      <c r="O6">
-        <v>1.33</v>
-      </c>
-      <c r="P6">
-        <v>1.83</v>
-      </c>
       <c r="Q6">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="S6">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
-        <v>1.61</v>
+        <v>3.7</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="Y6">
+        <v>44</v>
+      </c>
+      <c r="Z6">
+        <v>170</v>
+      </c>
+      <c r="AA6">
+        <v>390</v>
+      </c>
+      <c r="AB6">
         <v>12.5</v>
       </c>
-      <c r="Z6">
-        <v>26</v>
-      </c>
-      <c r="AA6">
+      <c r="AC6">
+        <v>16</v>
+      </c>
+      <c r="AD6">
+        <v>42</v>
+      </c>
+      <c r="AE6">
+        <v>300</v>
+      </c>
+      <c r="AF6">
+        <v>10.5</v>
+      </c>
+      <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
+        <v>27</v>
+      </c>
+      <c r="AI6">
+        <v>190</v>
+      </c>
+      <c r="AJ6">
+        <v>12.5</v>
+      </c>
+      <c r="AK6">
+        <v>16</v>
+      </c>
+      <c r="AL6">
+        <v>34</v>
+      </c>
+      <c r="AM6">
+        <v>140</v>
+      </c>
+      <c r="AN6">
+        <v>4.6</v>
+      </c>
+      <c r="AO6">
+        <v>260</v>
+      </c>
+      <c r="AP6">
+        <v>21</v>
+      </c>
+      <c r="AQ6">
+        <v>30</v>
+      </c>
+      <c r="AR6">
         <v>70</v>
       </c>
-      <c r="AB6">
-        <v>12</v>
-      </c>
-      <c r="AC6">
-        <v>9</v>
-      </c>
-      <c r="AD6">
-        <v>16.5</v>
-      </c>
-      <c r="AE6">
-        <v>42</v>
-      </c>
-      <c r="AF6">
-        <v>16.5</v>
-      </c>
-      <c r="AG6">
+      <c r="AS6">
+        <v>7</v>
+      </c>
+      <c r="AT6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6">
+        <v>10.5</v>
+      </c>
+      <c r="AV6">
+        <v>29</v>
+      </c>
+      <c r="AW6">
+        <v>6.8</v>
+      </c>
+      <c r="AX6">
+        <v>7.4</v>
+      </c>
+      <c r="AY6">
+        <v>8.4</v>
+      </c>
+      <c r="AZ6">
+        <v>20</v>
+      </c>
+      <c r="BA6">
+        <v>50</v>
+      </c>
+      <c r="BB6">
+        <v>8.6</v>
+      </c>
+      <c r="BC6">
+        <v>11</v>
+      </c>
+      <c r="BD6">
+        <v>20</v>
+      </c>
+      <c r="BE6">
+        <v>65</v>
+      </c>
+      <c r="BF6">
+        <v>4</v>
+      </c>
+      <c r="BG6">
+        <v>70</v>
+      </c>
+      <c r="BH6">
+        <v>4.7</v>
+      </c>
+      <c r="BI6">
+        <v>3.75</v>
+      </c>
+      <c r="BJ6">
+        <v>11.5</v>
+      </c>
+      <c r="BK6">
+        <v>6.6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>14.5</v>
+      </c>
+      <c r="BN6">
+        <v>4</v>
+      </c>
+      <c r="BO6">
+        <v>3.25</v>
+      </c>
+      <c r="BP6">
+        <v>7.4</v>
+      </c>
+      <c r="BQ6">
+        <v>5.7</v>
+      </c>
+      <c r="BR6">
+        <v>21</v>
+      </c>
+      <c r="BS6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT6">
+        <v>14</v>
+      </c>
+      <c r="BU6">
+        <v>7.4</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
         <v>13.5</v>
       </c>
-      <c r="AH6">
-        <v>18.5</v>
-      </c>
-      <c r="AI6">
-        <v>55</v>
-      </c>
-      <c r="AJ6">
-        <v>38</v>
-      </c>
-      <c r="AK6">
-        <v>32</v>
-      </c>
-      <c r="AL6">
-        <v>42</v>
-      </c>
-      <c r="AM6">
-        <v>110</v>
-      </c>
-      <c r="AN6">
-        <v>26</v>
-      </c>
-      <c r="AO6">
-        <v>40</v>
-      </c>
-      <c r="AP6">
-        <v>4.3</v>
-      </c>
-      <c r="AQ6">
-        <v>4.1</v>
-      </c>
-      <c r="AR6">
-        <v>19</v>
-      </c>
-      <c r="AS6">
-        <v>5.6</v>
-      </c>
-      <c r="AT6">
-        <v>7.8</v>
-      </c>
-      <c r="AU6">
-        <v>3.6</v>
-      </c>
-      <c r="AV6">
-        <v>11</v>
-      </c>
-      <c r="AW6">
-        <v>5.3</v>
-      </c>
-      <c r="AX6">
-        <v>4.4</v>
-      </c>
-      <c r="AY6">
-        <v>4.2</v>
-      </c>
-      <c r="AZ6">
-        <v>14.5</v>
-      </c>
-      <c r="BA6">
-        <v>5.5</v>
-      </c>
-      <c r="BB6">
-        <v>5.2</v>
-      </c>
-      <c r="BC6">
-        <v>5.1</v>
-      </c>
-      <c r="BD6">
-        <v>5.3</v>
-      </c>
-      <c r="BE6">
-        <v>5.8</v>
-      </c>
-      <c r="BF6">
-        <v>4.9</v>
-      </c>
-      <c r="BG6">
-        <v>5.3</v>
-      </c>
-      <c r="BH6">
-        <v>3.4</v>
-      </c>
-      <c r="BI6">
-        <v>2.7</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>5</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>9</v>
-      </c>
-      <c r="BN6">
-        <v>5.6</v>
-      </c>
-      <c r="BO6">
-        <v>4.6</v>
-      </c>
-      <c r="BP6">
-        <v>19.5</v>
-      </c>
-      <c r="BQ6">
-        <v>6.4</v>
-      </c>
-      <c r="BR6">
-        <v>36</v>
-      </c>
-      <c r="BS6">
-        <v>7.6</v>
-      </c>
-      <c r="BT6">
-        <v>6.6</v>
-      </c>
-      <c r="BU6">
-        <v>5.4</v>
-      </c>
-      <c r="BV6">
-        <v>28</v>
-      </c>
-      <c r="BW6">
-        <v>7.2</v>
-      </c>
       <c r="BX6">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BZ6">
-        <v>32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA6">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F7">
+        <v>1.8</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="G7">
-        <v>2.54</v>
-      </c>
       <c r="H7">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="O7">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R7">
         <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="T7">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2489,114 +2468,114 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F8">
-        <v>1.22</v>
+        <v>3.95</v>
       </c>
       <c r="G8">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>1.81</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q8">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="R8">
-        <v>1.55</v>
+        <v>2.46</v>
       </c>
       <c r="S8">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>3.55</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="W8">
-        <v>3.3</v>
+        <v>1.31</v>
       </c>
       <c r="X8">
         <v>1000</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ8">
         <v>1000</v>
@@ -2614,61 +2593,61 @@
         <v>1000</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2731,7 +2710,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2739,178 +2718,178 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F9">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>1.77</v>
       </c>
       <c r="H9">
-        <v>1.33</v>
+        <v>6.2</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>1.18</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N9">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
       <c r="O9">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
+        <v>1.51</v>
+      </c>
+      <c r="Q9">
+        <v>2.62</v>
+      </c>
+      <c r="R9">
+        <v>1.17</v>
+      </c>
+      <c r="S9">
+        <v>5.4</v>
+      </c>
+      <c r="T9">
+        <v>2.42</v>
+      </c>
+      <c r="U9">
+        <v>1.57</v>
+      </c>
+      <c r="V9">
         <v>1.13</v>
       </c>
-      <c r="Q9">
-        <v>1.23</v>
-      </c>
-      <c r="R9">
-        <v>1.08</v>
-      </c>
-      <c r="S9">
-        <v>1.24</v>
-      </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>1.11</v>
-      </c>
-      <c r="V9">
-        <v>1.08</v>
-      </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2973,7 +2952,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2981,241 +2960,241 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10">
+        <v>1.97</v>
+      </c>
+      <c r="G10">
+        <v>1.99</v>
+      </c>
+      <c r="H10">
+        <v>4.3</v>
+      </c>
+      <c r="I10">
+        <v>4.5</v>
+      </c>
+      <c r="J10">
+        <v>3.7</v>
+      </c>
+      <c r="K10">
+        <v>3.8</v>
+      </c>
+      <c r="L10">
+        <v>1.41</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
+        <v>3.9</v>
+      </c>
+      <c r="O10">
+        <v>1.33</v>
+      </c>
+      <c r="P10">
+        <v>1.97</v>
+      </c>
+      <c r="Q10">
+        <v>1.98</v>
+      </c>
+      <c r="R10">
+        <v>1.37</v>
+      </c>
+      <c r="S10">
+        <v>3.5</v>
+      </c>
+      <c r="T10">
+        <v>1.83</v>
+      </c>
+      <c r="U10">
+        <v>2.12</v>
+      </c>
+      <c r="V10">
+        <v>1.29</v>
+      </c>
+      <c r="W10">
+        <v>2</v>
+      </c>
+      <c r="X10">
+        <v>15</v>
+      </c>
+      <c r="Y10">
+        <v>38</v>
+      </c>
+      <c r="Z10">
+        <v>36</v>
+      </c>
+      <c r="AA10">
         <v>100</v>
       </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10">
-        <v>3.8</v>
-      </c>
-      <c r="G10">
-        <v>4.3</v>
-      </c>
-      <c r="H10">
-        <v>1.76</v>
-      </c>
-      <c r="I10">
-        <v>1.84</v>
-      </c>
-      <c r="J10">
-        <v>4.4</v>
-      </c>
-      <c r="K10">
-        <v>5.1</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>4.3</v>
-      </c>
-      <c r="O10">
-        <v>1.07</v>
-      </c>
-      <c r="P10">
-        <v>4.2</v>
-      </c>
-      <c r="Q10">
-        <v>1.23</v>
-      </c>
-      <c r="R10">
-        <v>2.38</v>
-      </c>
-      <c r="S10">
-        <v>1.56</v>
-      </c>
-      <c r="T10">
-        <v>1.27</v>
-      </c>
-      <c r="U10">
-        <v>3.55</v>
-      </c>
-      <c r="V10">
-        <v>2.2</v>
-      </c>
-      <c r="W10">
-        <v>1.3</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>950</v>
-      </c>
-      <c r="Z10">
+      <c r="AB10">
+        <v>15.5</v>
+      </c>
+      <c r="AC10">
+        <v>12.5</v>
+      </c>
+      <c r="AD10">
+        <v>18.5</v>
+      </c>
+      <c r="AE10">
+        <v>60</v>
+      </c>
+      <c r="AF10">
+        <v>12.5</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>19</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>23</v>
+      </c>
+      <c r="AK10">
+        <v>23</v>
+      </c>
+      <c r="AL10">
+        <v>40</v>
+      </c>
+      <c r="AM10">
+        <v>110</v>
+      </c>
+      <c r="AN10">
+        <v>970</v>
+      </c>
+      <c r="AO10">
+        <v>60</v>
+      </c>
+      <c r="AP10">
+        <v>12.5</v>
+      </c>
+      <c r="AQ10">
+        <v>14</v>
+      </c>
+      <c r="AR10">
+        <v>25</v>
+      </c>
+      <c r="AS10">
+        <v>4</v>
+      </c>
+      <c r="AT10">
+        <v>8.4</v>
+      </c>
+      <c r="AU10">
+        <v>7.4</v>
+      </c>
+      <c r="AV10">
+        <v>15.5</v>
+      </c>
+      <c r="AW10">
         <v>34</v>
       </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>950</v>
-      </c>
-      <c r="AC10">
-        <v>970</v>
-      </c>
-      <c r="AD10">
-        <v>950</v>
-      </c>
-      <c r="AE10">
-        <v>23</v>
-      </c>
-      <c r="AF10">
-        <v>80</v>
-      </c>
-      <c r="AG10">
-        <v>950</v>
-      </c>
-      <c r="AH10">
-        <v>970</v>
-      </c>
-      <c r="AI10">
-        <v>40</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>970</v>
-      </c>
-      <c r="AP10">
-        <v>1.99</v>
-      </c>
-      <c r="AQ10">
+      <c r="AX10">
+        <v>8.4</v>
+      </c>
+      <c r="AY10">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10">
+        <v>17</v>
+      </c>
+      <c r="BA10">
+        <v>7.8</v>
+      </c>
+      <c r="BB10">
+        <v>11</v>
+      </c>
+      <c r="BC10">
         <v>17.5</v>
       </c>
-      <c r="AR10">
-        <v>16</v>
-      </c>
-      <c r="AS10">
-        <v>2</v>
-      </c>
-      <c r="AT10">
-        <v>26</v>
-      </c>
-      <c r="AU10">
-        <v>8.4</v>
-      </c>
-      <c r="AV10">
-        <v>9.4</v>
-      </c>
-      <c r="AW10">
-        <v>1.83</v>
-      </c>
-      <c r="AX10">
-        <v>1.95</v>
-      </c>
-      <c r="AY10">
-        <v>14.5</v>
-      </c>
-      <c r="AZ10">
-        <v>8</v>
-      </c>
-      <c r="BA10">
-        <v>9.6</v>
-      </c>
-      <c r="BB10">
-        <v>2</v>
-      </c>
-      <c r="BC10">
-        <v>22</v>
-      </c>
       <c r="BD10">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="BE10">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="BF10">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="BG10">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3223,178 +3202,178 @@
         <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F11">
-        <v>1.66</v>
+        <v>3.6</v>
       </c>
       <c r="G11">
-        <v>1.78</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
-        <v>6.6</v>
+        <v>1.92</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="M11">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>4.7</v>
       </c>
       <c r="O11">
+        <v>1.24</v>
+      </c>
+      <c r="P11">
+        <v>2.32</v>
+      </c>
+      <c r="Q11">
+        <v>1.68</v>
+      </c>
+      <c r="R11">
         <v>1.5</v>
       </c>
-      <c r="P11">
-        <v>1.55</v>
-      </c>
-      <c r="Q11">
-        <v>2.5</v>
-      </c>
-      <c r="R11">
-        <v>1.2</v>
-      </c>
       <c r="S11">
-        <v>5.1</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="U11">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="V11">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>1.33</v>
       </c>
       <c r="X11">
+        <v>26</v>
+      </c>
+      <c r="Y11">
+        <v>12</v>
+      </c>
+      <c r="Z11">
+        <v>13.5</v>
+      </c>
+      <c r="AA11">
+        <v>25</v>
+      </c>
+      <c r="AB11">
+        <v>18</v>
+      </c>
+      <c r="AC11">
+        <v>11</v>
+      </c>
+      <c r="AD11">
         <v>11.5</v>
       </c>
-      <c r="Y11">
+      <c r="AE11">
+        <v>19</v>
+      </c>
+      <c r="AF11">
+        <v>36</v>
+      </c>
+      <c r="AG11">
+        <v>16.5</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
+        <v>34</v>
+      </c>
+      <c r="AJ11">
+        <v>85</v>
+      </c>
+      <c r="AK11">
+        <v>50</v>
+      </c>
+      <c r="AL11">
+        <v>48</v>
+      </c>
+      <c r="AM11">
+        <v>85</v>
+      </c>
+      <c r="AN11">
+        <v>42</v>
+      </c>
+      <c r="AO11">
+        <v>13.5</v>
+      </c>
+      <c r="AP11">
+        <v>18</v>
+      </c>
+      <c r="AQ11">
+        <v>9.6</v>
+      </c>
+      <c r="AR11">
+        <v>11</v>
+      </c>
+      <c r="AS11">
+        <v>17.5</v>
+      </c>
+      <c r="AT11">
+        <v>15</v>
+      </c>
+      <c r="AU11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW11">
+        <v>15</v>
+      </c>
+      <c r="AX11">
+        <v>5.5</v>
+      </c>
+      <c r="AY11">
+        <v>13.5</v>
+      </c>
+      <c r="AZ11">
+        <v>15</v>
+      </c>
+      <c r="BA11">
+        <v>5.4</v>
+      </c>
+      <c r="BB11">
+        <v>22</v>
+      </c>
+      <c r="BC11">
+        <v>5.7</v>
+      </c>
+      <c r="BD11">
+        <v>5.7</v>
+      </c>
+      <c r="BE11">
         <v>20</v>
       </c>
-      <c r="Z11">
-        <v>70</v>
-      </c>
-      <c r="AA11">
-        <v>330</v>
-      </c>
-      <c r="AB11">
-        <v>7</v>
-      </c>
-      <c r="AC11">
-        <v>10.5</v>
-      </c>
-      <c r="AD11">
-        <v>36</v>
-      </c>
-      <c r="AE11">
-        <v>190</v>
-      </c>
-      <c r="AF11">
-        <v>10.5</v>
-      </c>
-      <c r="AG11">
-        <v>13</v>
-      </c>
-      <c r="AH11">
-        <v>38</v>
-      </c>
-      <c r="AI11">
-        <v>200</v>
-      </c>
-      <c r="AJ11">
-        <v>21</v>
-      </c>
-      <c r="AK11">
-        <v>29</v>
-      </c>
-      <c r="AL11">
-        <v>75</v>
-      </c>
-      <c r="AM11">
-        <v>330</v>
-      </c>
-      <c r="AN11">
-        <v>21</v>
-      </c>
-      <c r="AO11">
-        <v>370</v>
-      </c>
-      <c r="AP11">
-        <v>6.8</v>
-      </c>
-      <c r="AQ11">
-        <v>12</v>
-      </c>
-      <c r="AR11">
-        <v>4.2</v>
-      </c>
-      <c r="AS11">
-        <v>4.4</v>
-      </c>
-      <c r="AT11">
-        <v>4.5</v>
-      </c>
-      <c r="AU11">
-        <v>6.4</v>
-      </c>
-      <c r="AV11">
-        <v>3.95</v>
-      </c>
-      <c r="AW11">
-        <v>4.3</v>
-      </c>
-      <c r="AX11">
-        <v>6.4</v>
-      </c>
-      <c r="AY11">
-        <v>8</v>
-      </c>
-      <c r="AZ11">
-        <v>4</v>
-      </c>
-      <c r="BA11">
-        <v>4.3</v>
-      </c>
-      <c r="BB11">
-        <v>12.5</v>
-      </c>
-      <c r="BC11">
-        <v>17</v>
-      </c>
-      <c r="BD11">
-        <v>4.2</v>
-      </c>
-      <c r="BE11">
-        <v>4.4</v>
-      </c>
       <c r="BF11">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG11">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3457,7 +3436,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3465,554 +3444,554 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F12">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H12">
+        <v>5.1</v>
+      </c>
+      <c r="I12">
+        <v>5.4</v>
+      </c>
+      <c r="J12">
+        <v>3.25</v>
+      </c>
+      <c r="K12">
+        <v>3.35</v>
+      </c>
+      <c r="L12">
+        <v>1.64</v>
+      </c>
+      <c r="M12">
+        <v>1.14</v>
+      </c>
+      <c r="N12">
+        <v>2.52</v>
+      </c>
+      <c r="O12">
+        <v>1.63</v>
+      </c>
+      <c r="P12">
+        <v>1.49</v>
+      </c>
+      <c r="Q12">
+        <v>2.96</v>
+      </c>
+      <c r="R12">
+        <v>1.17</v>
+      </c>
+      <c r="S12">
+        <v>6.6</v>
+      </c>
+      <c r="T12">
+        <v>2.46</v>
+      </c>
+      <c r="U12">
+        <v>1.64</v>
+      </c>
+      <c r="V12">
+        <v>1.22</v>
+      </c>
+      <c r="W12">
+        <v>2</v>
+      </c>
+      <c r="X12">
+        <v>8</v>
+      </c>
+      <c r="Y12">
+        <v>12</v>
+      </c>
+      <c r="Z12">
+        <v>40</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>5.9</v>
+      </c>
+      <c r="AC12">
+        <v>7.8</v>
+      </c>
+      <c r="AD12">
+        <v>24</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG12">
+        <v>11.5</v>
+      </c>
+      <c r="AH12">
+        <v>32</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>25</v>
+      </c>
+      <c r="AK12">
+        <v>34</v>
+      </c>
+      <c r="AL12">
+        <v>110</v>
+      </c>
+      <c r="AM12">
+        <v>290</v>
+      </c>
+      <c r="AN12">
+        <v>28</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12">
+        <v>10.5</v>
+      </c>
+      <c r="AR12">
+        <v>29</v>
+      </c>
+      <c r="AS12">
+        <v>44</v>
+      </c>
+      <c r="AT12">
+        <v>5.5</v>
+      </c>
+      <c r="AU12">
+        <v>7.2</v>
+      </c>
+      <c r="AV12">
+        <v>21</v>
+      </c>
+      <c r="AW12">
+        <v>38</v>
+      </c>
+      <c r="AX12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>27</v>
+      </c>
+      <c r="BA12">
+        <v>75</v>
+      </c>
+      <c r="BB12">
+        <v>20</v>
+      </c>
+      <c r="BC12">
+        <v>21</v>
+      </c>
+      <c r="BD12">
+        <v>50</v>
+      </c>
+      <c r="BE12">
+        <v>50</v>
+      </c>
+      <c r="BF12">
+        <v>20</v>
+      </c>
+      <c r="BG12">
+        <v>46</v>
+      </c>
+      <c r="BH12">
+        <v>2.56</v>
+      </c>
+      <c r="BI12">
+        <v>2.42</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>6.8</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>12.5</v>
+      </c>
+      <c r="BN12">
         <v>4.2</v>
       </c>
-      <c r="I12">
-        <v>4.4</v>
-      </c>
-      <c r="J12">
-        <v>3.7</v>
-      </c>
-      <c r="K12">
-        <v>3.8</v>
-      </c>
-      <c r="L12">
-        <v>1.38</v>
-      </c>
-      <c r="M12">
-        <v>1.07</v>
-      </c>
-      <c r="N12">
-        <v>3.95</v>
-      </c>
-      <c r="O12">
-        <v>1.31</v>
-      </c>
-      <c r="P12">
-        <v>1.99</v>
-      </c>
-      <c r="Q12">
-        <v>1.94</v>
-      </c>
-      <c r="R12">
-        <v>1.38</v>
-      </c>
-      <c r="S12">
-        <v>3.3</v>
-      </c>
-      <c r="T12">
-        <v>1.82</v>
-      </c>
-      <c r="U12">
-        <v>2.1</v>
-      </c>
-      <c r="V12">
-        <v>1.29</v>
-      </c>
-      <c r="W12">
-        <v>1.98</v>
-      </c>
-      <c r="X12">
-        <v>14.5</v>
-      </c>
-      <c r="Y12">
-        <v>34</v>
-      </c>
-      <c r="Z12">
-        <v>36</v>
-      </c>
-      <c r="AA12">
-        <v>100</v>
-      </c>
-      <c r="AB12">
-        <v>9.6</v>
-      </c>
-      <c r="AC12">
-        <v>8.6</v>
-      </c>
-      <c r="AD12">
-        <v>18.5</v>
-      </c>
-      <c r="AE12">
-        <v>60</v>
-      </c>
-      <c r="AF12">
-        <v>12.5</v>
-      </c>
-      <c r="AG12">
+      <c r="BO12">
+        <v>3.9</v>
+      </c>
+      <c r="BP12">
+        <v>16.5</v>
+      </c>
+      <c r="BQ12">
+        <v>7.8</v>
+      </c>
+      <c r="BR12">
+        <v>55</v>
+      </c>
+      <c r="BS12">
+        <v>10.5</v>
+      </c>
+      <c r="BT12">
+        <v>10.5</v>
+      </c>
+      <c r="BU12">
+        <v>7.6</v>
+      </c>
+      <c r="BV12">
+        <v>70</v>
+      </c>
+      <c r="BW12">
         <v>11</v>
       </c>
-      <c r="AH12">
-        <v>20</v>
-      </c>
-      <c r="AI12">
-        <v>70</v>
-      </c>
-      <c r="AJ12">
-        <v>24</v>
-      </c>
-      <c r="AK12">
-        <v>22</v>
-      </c>
-      <c r="AL12">
-        <v>40</v>
-      </c>
-      <c r="AM12">
+      <c r="BX12">
         <v>110</v>
       </c>
-      <c r="AN12">
-        <v>14.5</v>
-      </c>
-      <c r="AO12">
-        <v>60</v>
-      </c>
-      <c r="AP12">
-        <v>13</v>
-      </c>
-      <c r="AQ12">
-        <v>13.5</v>
-      </c>
-      <c r="AR12">
-        <v>24</v>
-      </c>
-      <c r="AS12">
-        <v>7.8</v>
-      </c>
-      <c r="AT12">
-        <v>7</v>
-      </c>
-      <c r="AU12">
-        <v>7.4</v>
-      </c>
-      <c r="AV12">
-        <v>15</v>
-      </c>
-      <c r="AW12">
-        <v>34</v>
-      </c>
-      <c r="AX12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY12">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12">
-        <v>16</v>
-      </c>
-      <c r="BA12">
-        <v>7.6</v>
-      </c>
-      <c r="BB12">
-        <v>11</v>
-      </c>
-      <c r="BC12">
-        <v>18.5</v>
-      </c>
-      <c r="BD12">
-        <v>29</v>
-      </c>
-      <c r="BE12">
-        <v>7.8</v>
-      </c>
-      <c r="BF12">
-        <v>12.5</v>
-      </c>
-      <c r="BG12">
-        <v>32</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.5</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>6.2</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.5</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.71</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>2.48</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.5</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>2.02</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.5</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
       <c r="BY12">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA12">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13">
+        <v>1.88</v>
+      </c>
+      <c r="G13">
+        <v>1.96</v>
+      </c>
+      <c r="H13">
+        <v>4.6</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>3.6</v>
+      </c>
+      <c r="K13">
+        <v>3.85</v>
+      </c>
+      <c r="L13">
+        <v>1.42</v>
+      </c>
+      <c r="M13">
+        <v>1.07</v>
+      </c>
+      <c r="N13">
+        <v>3.6</v>
+      </c>
+      <c r="O13">
+        <v>1.35</v>
+      </c>
+      <c r="P13">
+        <v>1.87</v>
+      </c>
+      <c r="Q13">
+        <v>2.06</v>
+      </c>
+      <c r="R13">
+        <v>1.33</v>
+      </c>
+      <c r="S13">
+        <v>3.75</v>
+      </c>
+      <c r="T13">
+        <v>1.89</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>1.25</v>
+      </c>
+      <c r="W13">
+        <v>2.04</v>
+      </c>
+      <c r="X13">
+        <v>13.5</v>
+      </c>
+      <c r="Y13">
+        <v>16</v>
+      </c>
+      <c r="Z13">
+        <v>38</v>
+      </c>
+      <c r="AA13">
         <v>140</v>
       </c>
-      <c r="F13">
-        <v>3.65</v>
-      </c>
-      <c r="G13">
-        <v>4</v>
-      </c>
-      <c r="H13">
+      <c r="AB13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC13">
+        <v>8.4</v>
+      </c>
+      <c r="AD13">
+        <v>19.5</v>
+      </c>
+      <c r="AE13">
+        <v>75</v>
+      </c>
+      <c r="AF13">
+        <v>12</v>
+      </c>
+      <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>21</v>
+      </c>
+      <c r="AI13">
+        <v>75</v>
+      </c>
+      <c r="AJ13">
+        <v>23</v>
+      </c>
+      <c r="AK13">
+        <v>22</v>
+      </c>
+      <c r="AL13">
+        <v>42</v>
+      </c>
+      <c r="AM13">
+        <v>140</v>
+      </c>
+      <c r="AN13">
+        <v>14.5</v>
+      </c>
+      <c r="AO13">
+        <v>90</v>
+      </c>
+      <c r="AP13">
+        <v>11.5</v>
+      </c>
+      <c r="AQ13">
+        <v>13</v>
+      </c>
+      <c r="AR13">
+        <v>8.4</v>
+      </c>
+      <c r="AS13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT13">
+        <v>7.4</v>
+      </c>
+      <c r="AU13">
+        <v>7.2</v>
+      </c>
+      <c r="AV13">
+        <v>15.5</v>
+      </c>
+      <c r="AW13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>9</v>
+      </c>
+      <c r="AZ13">
+        <v>17</v>
+      </c>
+      <c r="BA13">
+        <v>9.4</v>
+      </c>
+      <c r="BB13">
+        <v>18</v>
+      </c>
+      <c r="BC13">
+        <v>16.5</v>
+      </c>
+      <c r="BD13">
+        <v>8.4</v>
+      </c>
+      <c r="BE13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF13">
+        <v>12.5</v>
+      </c>
+      <c r="BG13">
+        <v>9.4</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.88</v>
+      </c>
+      <c r="BJ13">
+        <v>14.5</v>
+      </c>
+      <c r="BK13">
+        <v>1.67</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.88</v>
+      </c>
+      <c r="BN13">
+        <v>6</v>
+      </c>
+      <c r="BO13">
+        <v>3.3</v>
+      </c>
+      <c r="BP13">
+        <v>19</v>
+      </c>
+      <c r="BQ13">
+        <v>1.71</v>
+      </c>
+      <c r="BR13">
+        <v>40</v>
+      </c>
+      <c r="BS13">
+        <v>1.8</v>
+      </c>
+      <c r="BT13">
+        <v>10.5</v>
+      </c>
+      <c r="BU13">
+        <v>5.3</v>
+      </c>
+      <c r="BV13">
+        <v>190</v>
+      </c>
+      <c r="BW13">
         <v>1.83</v>
       </c>
-      <c r="I13">
-        <v>1.93</v>
-      </c>
-      <c r="J13">
-        <v>4.3</v>
-      </c>
-      <c r="K13">
-        <v>5</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.04</v>
-      </c>
-      <c r="N13">
-        <v>4.6</v>
-      </c>
-      <c r="O13">
-        <v>1.21</v>
-      </c>
-      <c r="P13">
-        <v>2.24</v>
-      </c>
-      <c r="Q13">
-        <v>1.62</v>
-      </c>
-      <c r="R13">
-        <v>1.48</v>
-      </c>
-      <c r="S13">
-        <v>2.62</v>
-      </c>
-      <c r="T13">
-        <v>1.63</v>
-      </c>
-      <c r="U13">
-        <v>2.26</v>
-      </c>
-      <c r="V13">
-        <v>2.06</v>
-      </c>
-      <c r="W13">
-        <v>1.33</v>
-      </c>
-      <c r="X13">
-        <v>27</v>
-      </c>
-      <c r="Y13">
-        <v>12.5</v>
-      </c>
-      <c r="Z13">
-        <v>14</v>
-      </c>
-      <c r="AA13">
-        <v>25</v>
-      </c>
-      <c r="AB13">
-        <v>19.5</v>
-      </c>
-      <c r="AC13">
-        <v>11</v>
-      </c>
-      <c r="AD13">
-        <v>11.5</v>
-      </c>
-      <c r="AE13">
-        <v>19</v>
-      </c>
-      <c r="AF13">
-        <v>38</v>
-      </c>
-      <c r="AG13">
-        <v>17.5</v>
-      </c>
-      <c r="AH13">
-        <v>19.5</v>
-      </c>
-      <c r="AI13">
-        <v>34</v>
-      </c>
-      <c r="AJ13">
-        <v>85</v>
-      </c>
-      <c r="AK13">
-        <v>50</v>
-      </c>
-      <c r="AL13">
-        <v>48</v>
-      </c>
-      <c r="AM13">
-        <v>85</v>
-      </c>
-      <c r="AN13">
-        <v>42</v>
-      </c>
-      <c r="AO13">
-        <v>10.5</v>
-      </c>
-      <c r="AP13">
-        <v>18</v>
-      </c>
-      <c r="AQ13">
-        <v>9.6</v>
-      </c>
-      <c r="AR13">
-        <v>11</v>
-      </c>
-      <c r="AS13">
-        <v>17.5</v>
-      </c>
-      <c r="AT13">
-        <v>15</v>
-      </c>
-      <c r="AU13">
-        <v>8.6</v>
-      </c>
-      <c r="AV13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW13">
-        <v>15</v>
-      </c>
-      <c r="AX13">
-        <v>5.9</v>
-      </c>
-      <c r="AY13">
-        <v>13.5</v>
-      </c>
-      <c r="AZ13">
-        <v>15</v>
-      </c>
-      <c r="BA13">
-        <v>5.8</v>
-      </c>
-      <c r="BB13">
-        <v>6.4</v>
-      </c>
-      <c r="BC13">
-        <v>6</v>
-      </c>
-      <c r="BD13">
-        <v>6</v>
-      </c>
-      <c r="BE13">
-        <v>6.4</v>
-      </c>
-      <c r="BF13">
-        <v>6</v>
-      </c>
-      <c r="BG13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.04</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.04</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.04</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.04</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.04</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.04</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.04</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.04</v>
-      </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="CB13" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G14">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L14">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="M14">
         <v>1.14</v>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P14">
         <v>1.5</v>
       </c>
       <c r="Q14">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R14">
         <v>1.17</v>
       </c>
       <c r="S14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U14">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -4021,49 +4000,49 @@
         <v>12</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AC14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD14">
+        <v>25</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG14">
+        <v>11.5</v>
+      </c>
+      <c r="AH14">
+        <v>34</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
         <v>24</v>
       </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>10</v>
-      </c>
-      <c r="AG14">
-        <v>12.5</v>
-      </c>
-      <c r="AH14">
-        <v>32</v>
-      </c>
-      <c r="AI14">
-        <v>160</v>
-      </c>
-      <c r="AJ14">
-        <v>23</v>
-      </c>
       <c r="AK14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM14">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AN14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO14">
         <v>1000</v>
@@ -4075,599 +4054,599 @@
         <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU14">
         <v>7.4</v>
       </c>
       <c r="AV14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW14">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AX14">
         <v>9</v>
       </c>
       <c r="AY14">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
         <v>27</v>
       </c>
       <c r="BA14">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BB14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE14">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BF14">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH14">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BI14">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="BJ14">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>15.5</v>
+        <v>1.37</v>
       </c>
       <c r="BN14">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BO14">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="BP14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>12.5</v>
+        <v>2.78</v>
       </c>
       <c r="BT14">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>13</v>
+        <v>2.78</v>
       </c>
       <c r="BX14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>14</v>
+        <v>1.37</v>
       </c>
       <c r="BZ14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>12.5</v>
+        <v>2.78</v>
       </c>
       <c r="CB14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F15">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="G15">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="H15">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
         <v>3.85</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N15">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O15">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="P15">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="Q15">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S15">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="T15">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W15">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="X15">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA15">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AC15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD15">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AE15">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AK15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM15">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
         <v>14.5</v>
       </c>
       <c r="AO15">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR15">
+        <v>36</v>
+      </c>
+      <c r="AS15">
+        <v>44</v>
+      </c>
+      <c r="AT15">
+        <v>6.2</v>
+      </c>
+      <c r="AU15">
         <v>7.8</v>
       </c>
-      <c r="AS15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT15">
-        <v>7.4</v>
-      </c>
-      <c r="AU15">
-        <v>7.2</v>
-      </c>
       <c r="AV15">
+        <v>21</v>
+      </c>
+      <c r="AW15">
+        <v>38</v>
+      </c>
+      <c r="AX15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY15">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15">
+        <v>19.5</v>
+      </c>
+      <c r="BA15">
+        <v>40</v>
+      </c>
+      <c r="BB15">
         <v>15.5</v>
       </c>
-      <c r="AW15">
-        <v>8.6</v>
-      </c>
-      <c r="AX15">
-        <v>10</v>
-      </c>
-      <c r="AY15">
-        <v>9</v>
-      </c>
-      <c r="AZ15">
-        <v>17</v>
-      </c>
-      <c r="BA15">
-        <v>8.6</v>
-      </c>
-      <c r="BB15">
-        <v>17</v>
-      </c>
       <c r="BC15">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD15">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BE15">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BF15">
         <v>12.5</v>
       </c>
       <c r="BG15">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI15">
-        <v>1.88</v>
+        <v>2.66</v>
       </c>
       <c r="BJ15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="BN15">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BP15">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="BR15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="BT15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.3</v>
+        <v>2.06</v>
       </c>
       <c r="BV15">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="BZ15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="CB15" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F16">
+        <v>2.48</v>
+      </c>
+      <c r="G16">
+        <v>2.56</v>
+      </c>
+      <c r="H16">
+        <v>2.88</v>
+      </c>
+      <c r="I16">
+        <v>2.98</v>
+      </c>
+      <c r="J16">
+        <v>3.7</v>
+      </c>
+      <c r="K16">
+        <v>3.9</v>
+      </c>
+      <c r="L16">
+        <v>1.38</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>4.1</v>
+      </c>
+      <c r="O16">
+        <v>1.29</v>
+      </c>
+      <c r="P16">
         <v>2.06</v>
       </c>
-      <c r="G16">
-        <v>2.12</v>
-      </c>
-      <c r="H16">
-        <v>4.7</v>
-      </c>
-      <c r="I16">
-        <v>5</v>
-      </c>
-      <c r="J16">
-        <v>3.1</v>
-      </c>
-      <c r="K16">
+      <c r="Q16">
+        <v>1.88</v>
+      </c>
+      <c r="R16">
+        <v>1.41</v>
+      </c>
+      <c r="S16">
         <v>3.25</v>
       </c>
-      <c r="L16">
-        <v>1.59</v>
-      </c>
-      <c r="M16">
-        <v>1.15</v>
-      </c>
-      <c r="N16">
-        <v>2.44</v>
-      </c>
-      <c r="O16">
-        <v>1.66</v>
-      </c>
-      <c r="P16">
-        <v>1.47</v>
-      </c>
-      <c r="Q16">
-        <v>2.96</v>
-      </c>
-      <c r="R16">
-        <v>1.16</v>
-      </c>
-      <c r="S16">
-        <v>6.8</v>
-      </c>
       <c r="T16">
-        <v>2.46</v>
+        <v>1.68</v>
       </c>
       <c r="U16">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="X16">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Z16">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AE16">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AF16">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AG16">
         <v>12</v>
       </c>
       <c r="AH16">
+        <v>17.5</v>
+      </c>
+      <c r="AI16">
+        <v>50</v>
+      </c>
+      <c r="AJ16">
+        <v>38</v>
+      </c>
+      <c r="AK16">
+        <v>26</v>
+      </c>
+      <c r="AL16">
+        <v>36</v>
+      </c>
+      <c r="AM16">
+        <v>90</v>
+      </c>
+      <c r="AN16">
+        <v>23</v>
+      </c>
+      <c r="AO16">
         <v>32</v>
       </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
+      <c r="AP16">
+        <v>14.5</v>
+      </c>
+      <c r="AQ16">
+        <v>11.5</v>
+      </c>
+      <c r="AR16">
+        <v>17.5</v>
+      </c>
+      <c r="AS16">
+        <v>29</v>
+      </c>
+      <c r="AT16">
+        <v>10</v>
+      </c>
+      <c r="AU16">
+        <v>7.6</v>
+      </c>
+      <c r="AV16">
+        <v>11.5</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>14.5</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>15</v>
+      </c>
+      <c r="BA16">
         <v>28</v>
       </c>
-      <c r="AK16">
-        <v>34</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>320</v>
-      </c>
-      <c r="AN16">
-        <v>34</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>7</v>
-      </c>
-      <c r="AQ16">
-        <v>9.6</v>
-      </c>
-      <c r="AR16">
+      <c r="BB16">
         <v>27</v>
-      </c>
-      <c r="AS16">
-        <v>42</v>
-      </c>
-      <c r="AT16">
-        <v>5.7</v>
-      </c>
-      <c r="AU16">
-        <v>7</v>
-      </c>
-      <c r="AV16">
-        <v>19</v>
-      </c>
-      <c r="AW16">
-        <v>36</v>
-      </c>
-      <c r="AX16">
-        <v>9.6</v>
-      </c>
-      <c r="AY16">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16">
-        <v>27</v>
-      </c>
-      <c r="BA16">
-        <v>70</v>
-      </c>
-      <c r="BB16">
-        <v>23</v>
       </c>
       <c r="BC16">
         <v>20</v>
       </c>
       <c r="BD16">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="BE16">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="BF16">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BG16">
-        <v>46</v>
+        <v>18.5</v>
       </c>
       <c r="BH16">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4675,241 +4654,241 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F17">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="G17">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="H17">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="K17">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="L17">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH17">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BI17">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK17">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO17">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ17">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU17">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4917,178 +4896,178 @@
         <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F18">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="G18">
-        <v>2.86</v>
+        <v>1.63</v>
       </c>
       <c r="H18">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>2.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K18">
+        <v>4.3</v>
+      </c>
+      <c r="L18">
+        <v>1.44</v>
+      </c>
+      <c r="M18">
+        <v>1.08</v>
+      </c>
+      <c r="N18">
+        <v>3.45</v>
+      </c>
+      <c r="O18">
+        <v>1.37</v>
+      </c>
+      <c r="P18">
+        <v>1.83</v>
+      </c>
+      <c r="Q18">
+        <v>2.1</v>
+      </c>
+      <c r="R18">
+        <v>1.33</v>
+      </c>
+      <c r="S18">
         <v>3.9</v>
       </c>
-      <c r="L18">
-        <v>1.2</v>
-      </c>
-      <c r="M18">
-        <v>1.06</v>
-      </c>
-      <c r="N18">
-        <v>4</v>
-      </c>
-      <c r="O18">
-        <v>1.28</v>
-      </c>
-      <c r="P18">
-        <v>2.02</v>
-      </c>
-      <c r="Q18">
-        <v>1.86</v>
-      </c>
-      <c r="R18">
-        <v>1.4</v>
-      </c>
-      <c r="S18">
-        <v>3.15</v>
-      </c>
       <c r="T18">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="U18">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="V18">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="W18">
-        <v>1.54</v>
+        <v>2.58</v>
       </c>
       <c r="X18">
+        <v>13.5</v>
+      </c>
+      <c r="Y18">
+        <v>22</v>
+      </c>
+      <c r="Z18">
+        <v>80</v>
+      </c>
+      <c r="AA18">
+        <v>600</v>
+      </c>
+      <c r="AB18">
+        <v>7.2</v>
+      </c>
+      <c r="AC18">
+        <v>9.6</v>
+      </c>
+      <c r="AD18">
+        <v>32</v>
+      </c>
+      <c r="AE18">
+        <v>610</v>
+      </c>
+      <c r="AF18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG18">
+        <v>10.5</v>
+      </c>
+      <c r="AH18">
+        <v>32</v>
+      </c>
+      <c r="AI18">
+        <v>610</v>
+      </c>
+      <c r="AJ18">
+        <v>15.5</v>
+      </c>
+      <c r="AK18">
+        <v>19.5</v>
+      </c>
+      <c r="AL18">
+        <v>55</v>
+      </c>
+      <c r="AM18">
+        <v>600</v>
+      </c>
+      <c r="AN18">
+        <v>11.5</v>
+      </c>
+      <c r="AO18">
+        <v>610</v>
+      </c>
+      <c r="AP18">
+        <v>11</v>
+      </c>
+      <c r="AQ18">
+        <v>17.5</v>
+      </c>
+      <c r="AR18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT18">
+        <v>6</v>
+      </c>
+      <c r="AU18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV18">
         <v>21</v>
       </c>
-      <c r="Y18">
-        <v>13.5</v>
-      </c>
-      <c r="Z18">
-        <v>19.5</v>
-      </c>
-      <c r="AA18">
-        <v>40</v>
-      </c>
-      <c r="AB18">
-        <v>15</v>
-      </c>
-      <c r="AC18">
+      <c r="AW18">
         <v>8.6</v>
       </c>
-      <c r="AD18">
-        <v>13</v>
-      </c>
-      <c r="AE18">
-        <v>30</v>
-      </c>
-      <c r="AF18">
-        <v>20</v>
-      </c>
-      <c r="AG18">
-        <v>13</v>
-      </c>
-      <c r="AH18">
-        <v>17</v>
-      </c>
-      <c r="AI18">
-        <v>40</v>
-      </c>
-      <c r="AJ18">
-        <v>44</v>
-      </c>
-      <c r="AK18">
-        <v>30</v>
-      </c>
-      <c r="AL18">
-        <v>42</v>
-      </c>
-      <c r="AM18">
-        <v>90</v>
-      </c>
-      <c r="AN18">
-        <v>26</v>
-      </c>
-      <c r="AO18">
-        <v>23</v>
-      </c>
-      <c r="AP18">
-        <v>14</v>
-      </c>
-      <c r="AQ18">
-        <v>10</v>
-      </c>
-      <c r="AR18">
-        <v>15.5</v>
-      </c>
-      <c r="AS18">
-        <v>27</v>
-      </c>
-      <c r="AT18">
-        <v>11</v>
-      </c>
-      <c r="AU18">
-        <v>7.2</v>
-      </c>
-      <c r="AV18">
-        <v>10.5</v>
-      </c>
-      <c r="AW18">
-        <v>20</v>
-      </c>
       <c r="AX18">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY18">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BA18">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="BB18">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="BC18">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BD18">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BE18">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BG18">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5151,7 +5130,7 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5159,725 +5138,241 @@
         <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F19">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="G19">
+        <v>2.32</v>
+      </c>
+      <c r="H19">
         <v>3.3</v>
       </c>
-      <c r="H19">
-        <v>2.36</v>
-      </c>
       <c r="I19">
+        <v>3.55</v>
+      </c>
+      <c r="J19">
+        <v>3.65</v>
+      </c>
+      <c r="K19">
         <v>3.85</v>
       </c>
-      <c r="J19">
-        <v>2.78</v>
-      </c>
-      <c r="K19">
-        <v>3.4</v>
-      </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB19" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:80">
-      <c r="A20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20">
-        <v>1.57</v>
-      </c>
-      <c r="G20">
-        <v>1.65</v>
-      </c>
-      <c r="H20">
-        <v>7</v>
-      </c>
-      <c r="I20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J20">
-        <v>3.85</v>
-      </c>
-      <c r="K20">
-        <v>4.3</v>
-      </c>
-      <c r="L20">
-        <v>1.35</v>
-      </c>
-      <c r="M20">
-        <v>1.08</v>
-      </c>
-      <c r="N20">
-        <v>3.3</v>
-      </c>
-      <c r="O20">
-        <v>1.37</v>
-      </c>
-      <c r="P20">
-        <v>1.77</v>
-      </c>
-      <c r="Q20">
-        <v>2.08</v>
-      </c>
-      <c r="R20">
-        <v>1.33</v>
-      </c>
-      <c r="S20">
-        <v>3.8</v>
-      </c>
-      <c r="T20">
-        <v>2.12</v>
-      </c>
-      <c r="U20">
-        <v>1.76</v>
-      </c>
-      <c r="V20">
-        <v>1.14</v>
-      </c>
-      <c r="W20">
-        <v>2.54</v>
-      </c>
-      <c r="X20">
-        <v>13.5</v>
-      </c>
-      <c r="Y20">
-        <v>22</v>
-      </c>
-      <c r="Z20">
-        <v>80</v>
-      </c>
-      <c r="AA20">
-        <v>680</v>
-      </c>
-      <c r="AB20">
-        <v>7.2</v>
-      </c>
-      <c r="AC20">
-        <v>9.6</v>
-      </c>
-      <c r="AD20">
-        <v>32</v>
-      </c>
-      <c r="AE20">
-        <v>690</v>
-      </c>
-      <c r="AF20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG20">
-        <v>10.5</v>
-      </c>
-      <c r="AH20">
-        <v>32</v>
-      </c>
-      <c r="AI20">
-        <v>690</v>
-      </c>
-      <c r="AJ20">
-        <v>15.5</v>
-      </c>
-      <c r="AK20">
-        <v>19.5</v>
-      </c>
-      <c r="AL20">
-        <v>55</v>
-      </c>
-      <c r="AM20">
-        <v>680</v>
-      </c>
-      <c r="AN20">
-        <v>11.5</v>
-      </c>
-      <c r="AO20">
-        <v>690</v>
-      </c>
-      <c r="AP20">
-        <v>11</v>
-      </c>
-      <c r="AQ20">
-        <v>17.5</v>
-      </c>
-      <c r="AR20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT20">
-        <v>6</v>
-      </c>
-      <c r="AU20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>21</v>
-      </c>
-      <c r="AW20">
-        <v>8.6</v>
-      </c>
-      <c r="AX20">
-        <v>7.4</v>
-      </c>
-      <c r="AY20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20">
-        <v>19</v>
-      </c>
-      <c r="BA20">
-        <v>9.4</v>
-      </c>
-      <c r="BB20">
-        <v>12.5</v>
-      </c>
-      <c r="BC20">
-        <v>16</v>
-      </c>
-      <c r="BD20">
-        <v>36</v>
-      </c>
-      <c r="BE20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF20">
-        <v>9.6</v>
-      </c>
-      <c r="BG20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.04</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.04</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.04</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.04</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.04</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="21" spans="1:80">
-      <c r="A21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21">
-        <v>2.18</v>
-      </c>
-      <c r="G21">
-        <v>2.3</v>
-      </c>
-      <c r="H21">
-        <v>3.3</v>
-      </c>
-      <c r="I21">
-        <v>3.55</v>
-      </c>
-      <c r="J21">
-        <v>3.6</v>
-      </c>
-      <c r="K21">
-        <v>3.85</v>
-      </c>
-      <c r="L21">
-        <v>1.38</v>
-      </c>
-      <c r="M21">
-        <v>1.06</v>
-      </c>
-      <c r="N21">
-        <v>3.85</v>
-      </c>
-      <c r="O21">
-        <v>1.3</v>
-      </c>
-      <c r="P21">
-        <v>1.95</v>
-      </c>
-      <c r="Q21">
-        <v>1.89</v>
-      </c>
-      <c r="R21">
-        <v>1.37</v>
-      </c>
-      <c r="S21">
-        <v>3.25</v>
-      </c>
-      <c r="T21">
-        <v>1.76</v>
-      </c>
-      <c r="U21">
-        <v>2.18</v>
-      </c>
-      <c r="V21">
-        <v>1.39</v>
-      </c>
-      <c r="W21">
-        <v>1.76</v>
-      </c>
-      <c r="X21">
-        <v>16</v>
-      </c>
-      <c r="Y21">
-        <v>14.5</v>
-      </c>
-      <c r="Z21">
-        <v>26</v>
-      </c>
-      <c r="AA21">
-        <v>65</v>
-      </c>
-      <c r="AB21">
-        <v>11</v>
-      </c>
-      <c r="AC21">
-        <v>8.4</v>
-      </c>
-      <c r="AD21">
-        <v>15</v>
-      </c>
-      <c r="AE21">
-        <v>42</v>
-      </c>
-      <c r="AF21">
-        <v>15.5</v>
-      </c>
-      <c r="AG21">
-        <v>11.5</v>
-      </c>
-      <c r="AH21">
-        <v>18</v>
-      </c>
-      <c r="AI21">
-        <v>60</v>
-      </c>
-      <c r="AJ21">
-        <v>30</v>
-      </c>
-      <c r="AK21">
-        <v>25</v>
-      </c>
-      <c r="AL21">
-        <v>38</v>
-      </c>
-      <c r="AM21">
-        <v>110</v>
-      </c>
-      <c r="AN21">
-        <v>17.5</v>
-      </c>
-      <c r="AO21">
-        <v>38</v>
-      </c>
-      <c r="AP21">
-        <v>13</v>
-      </c>
-      <c r="AQ21">
-        <v>12</v>
-      </c>
-      <c r="AR21">
-        <v>21</v>
-      </c>
-      <c r="AS21">
-        <v>22</v>
-      </c>
-      <c r="AT21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21">
-        <v>7.2</v>
-      </c>
-      <c r="AV21">
-        <v>12.5</v>
-      </c>
-      <c r="AW21">
-        <v>14.5</v>
-      </c>
-      <c r="AX21">
-        <v>12.5</v>
-      </c>
-      <c r="AY21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ21">
-        <v>14.5</v>
-      </c>
-      <c r="BA21">
-        <v>18.5</v>
-      </c>
-      <c r="BB21">
-        <v>11</v>
-      </c>
-      <c r="BC21">
-        <v>20</v>
-      </c>
-      <c r="BD21">
-        <v>12.5</v>
-      </c>
-      <c r="BE21">
-        <v>30</v>
-      </c>
-      <c r="BF21">
-        <v>14.5</v>
-      </c>
-      <c r="BG21">
-        <v>8</v>
-      </c>
-      <c r="BH21">
-        <v>3.6</v>
-      </c>
-      <c r="BI21">
-        <v>3.15</v>
-      </c>
-      <c r="BJ21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK21">
-        <v>5.2</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>10</v>
-      </c>
-      <c r="BN21">
-        <v>5.3</v>
-      </c>
-      <c r="BO21">
-        <v>4.6</v>
-      </c>
-      <c r="BP21">
-        <v>17</v>
-      </c>
-      <c r="BQ21">
-        <v>6.8</v>
-      </c>
-      <c r="BR21">
-        <v>30</v>
-      </c>
-      <c r="BS21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT21">
-        <v>7</v>
-      </c>
-      <c r="BU21">
-        <v>5.7</v>
-      </c>
-      <c r="BV21">
-        <v>28</v>
-      </c>
-      <c r="BW21">
-        <v>8</v>
-      </c>
-      <c r="BX21">
-        <v>38</v>
-      </c>
-      <c r="BY21">
-        <v>8.6</v>
-      </c>
-      <c r="BZ21">
-        <v>26</v>
-      </c>
-      <c r="CA21">
-        <v>7.8</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
   <si>
     <t>League</t>
   </si>
@@ -370,6 +370,9 @@
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Deportivo Merlo</t>
+  </si>
+  <si>
     <t>Velez Sarsfield</t>
   </si>
   <si>
@@ -424,6 +427,9 @@
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>Brown de Adrogue</t>
+  </si>
+  <si>
     <t>CA Platense</t>
   </si>
   <si>
@@ -436,13 +442,13 @@
     <t>Envigado</t>
   </si>
   <si>
-    <t>Club 2 de Mayo</t>
+    <t>Club 2 de Mayo de Pedro Juan Cab</t>
   </si>
   <si>
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-05 01:46:57</t>
+    <t>2026-10-05 03:56:16</t>
   </si>
 </sst>
 </file>
@@ -774,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1033,10 +1039,10 @@
         <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
         <v>2.06</v>
@@ -1051,7 +1057,7 @@
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1063,7 +1069,7 @@
         <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
         <v>1.76</v>
@@ -1075,19 +1081,19 @@
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
         <v>13.5</v>
@@ -1258,7 +1264,7 @@
         <v>5.3</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1275,7 +1281,7 @@
         <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>1.04</v>
@@ -1500,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1517,7 +1523,7 @@
         <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>2.36</v>
@@ -1535,13 +1541,13 @@
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
         <v>1.44</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.5</v>
@@ -1562,7 +1568,7 @@
         <v>3.65</v>
       </c>
       <c r="T4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
         <v>2.08</v>
@@ -1571,7 +1577,7 @@
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X4">
         <v>15.5</v>
@@ -1634,22 +1640,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS4">
         <v>25</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>5.7</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
@@ -1658,7 +1664,7 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA4">
         <v>32</v>
@@ -1667,16 +1673,16 @@
         <v>15</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BE4">
         <v>70</v>
       </c>
       <c r="BF4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BG4">
         <v>23</v>
@@ -1691,13 +1697,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
         <v>5.3</v>
@@ -1709,13 +1715,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
@@ -1727,22 +1733,22 @@
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="CA4">
         <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1759,25 +1765,25 @@
         <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F5">
         <v>2.16</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
         <v>2.94</v>
       </c>
       <c r="I5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.28</v>
@@ -1786,31 +1792,31 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
         <v>2.36</v>
       </c>
       <c r="Q5">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R5">
         <v>1.54</v>
       </c>
       <c r="S5">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U5">
         <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
         <v>1.69</v>
@@ -1819,7 +1825,7 @@
         <v>28</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -1828,25 +1834,25 @@
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>17</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI5">
         <v>44</v>
@@ -1864,7 +1870,7 @@
         <v>75</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO5">
         <v>26</v>
@@ -1876,10 +1882,10 @@
         <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
@@ -1891,7 +1897,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -1903,7 +1909,7 @@
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="BB5">
         <v>21</v>
@@ -1915,7 +1921,7 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="BF5">
         <v>10.5</v>
@@ -1984,7 +1990,7 @@
         <v>3.85</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2001,232 +2007,232 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="K6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O6">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q6">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="R6">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="S6">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Y6">
         <v>44</v>
       </c>
       <c r="Z6">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AA6">
-        <v>390</v>
+        <v>530</v>
       </c>
       <c r="AB6">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD6">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AE6">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="AF6">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI6">
+        <v>170</v>
+      </c>
+      <c r="AJ6">
+        <v>12</v>
+      </c>
+      <c r="AK6">
+        <v>17</v>
+      </c>
+      <c r="AL6">
+        <v>44</v>
+      </c>
+      <c r="AM6">
         <v>190</v>
       </c>
-      <c r="AJ6">
-        <v>12.5</v>
-      </c>
-      <c r="AK6">
-        <v>16</v>
-      </c>
-      <c r="AL6">
-        <v>34</v>
-      </c>
-      <c r="AM6">
-        <v>140</v>
-      </c>
       <c r="AN6">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO6">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="AR6">
-        <v>70</v>
+        <v>5.5</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AU6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV6">
-        <v>29</v>
+        <v>5.2</v>
       </c>
       <c r="AW6">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX6">
         <v>7.4</v>
       </c>
       <c r="AY6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BA6">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="BB6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6">
         <v>11</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>5.6</v>
       </c>
       <c r="BF6">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BG6">
-        <v>70</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
+        <v>12.5</v>
+      </c>
+      <c r="BK6">
+        <v>6.4</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>12.5</v>
+      </c>
+      <c r="BN6">
+        <v>3.85</v>
+      </c>
+      <c r="BO6">
+        <v>3.1</v>
+      </c>
+      <c r="BP6">
+        <v>7.6</v>
+      </c>
+      <c r="BQ6">
+        <v>5.8</v>
+      </c>
+      <c r="BR6">
+        <v>24</v>
+      </c>
+      <c r="BS6">
+        <v>8.6</v>
+      </c>
+      <c r="BT6">
+        <v>14.5</v>
+      </c>
+      <c r="BU6">
+        <v>7</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>12</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
         <v>11.5</v>
       </c>
-      <c r="BK6">
-        <v>6.6</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>14.5</v>
-      </c>
-      <c r="BN6">
-        <v>4</v>
-      </c>
-      <c r="BO6">
-        <v>3.25</v>
-      </c>
-      <c r="BP6">
-        <v>7.4</v>
-      </c>
-      <c r="BQ6">
-        <v>5.7</v>
-      </c>
-      <c r="BR6">
-        <v>21</v>
-      </c>
-      <c r="BS6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT6">
-        <v>14</v>
-      </c>
-      <c r="BU6">
-        <v>7.4</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>13.5</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>13</v>
-      </c>
       <c r="BZ6">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="CA6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2243,13 +2249,13 @@
         <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H7">
         <v>3.8</v>
@@ -2258,34 +2264,34 @@
         <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
+        <v>1.4</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
+        <v>3.7</v>
+      </c>
+      <c r="O7">
         <v>1.31</v>
       </c>
-      <c r="M7">
-        <v>1.03</v>
-      </c>
-      <c r="N7">
-        <v>4.8</v>
-      </c>
-      <c r="O7">
-        <v>1.2</v>
-      </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2297,7 +2303,7 @@
         <v>1.27</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2468,7 +2474,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2485,25 +2491,25 @@
         <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G8">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H8">
+        <v>1.74</v>
+      </c>
+      <c r="I8">
         <v>1.77</v>
-      </c>
-      <c r="I8">
-        <v>1.81</v>
       </c>
       <c r="J8">
         <v>4.8</v>
       </c>
       <c r="K8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L8">
         <v>1.16</v>
@@ -2512,205 +2518,205 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="O8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R8">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S8">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="T8">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U8">
         <v>3.55</v>
       </c>
       <c r="V8">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="W8">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB8">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AD8">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AE8">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AF8">
         <v>80</v>
       </c>
       <c r="AG8">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AH8">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO8">
-        <v>970</v>
+        <v>4.5</v>
       </c>
       <c r="AP8">
-        <v>1.99</v>
+        <v>46</v>
       </c>
       <c r="AQ8">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AR8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AT8">
+        <v>36</v>
+      </c>
+      <c r="AU8">
+        <v>13.5</v>
+      </c>
+      <c r="AV8">
+        <v>11</v>
+      </c>
+      <c r="AW8">
+        <v>14</v>
+      </c>
+      <c r="AX8">
+        <v>46</v>
+      </c>
+      <c r="AY8">
+        <v>18</v>
+      </c>
+      <c r="AZ8">
+        <v>13</v>
+      </c>
+      <c r="BA8">
+        <v>16.5</v>
+      </c>
+      <c r="BB8">
+        <v>55</v>
+      </c>
+      <c r="BC8">
+        <v>30</v>
+      </c>
+      <c r="BD8">
+        <v>23</v>
+      </c>
+      <c r="BE8">
+        <v>27</v>
+      </c>
+      <c r="BF8">
+        <v>15</v>
+      </c>
+      <c r="BG8">
+        <v>3.95</v>
+      </c>
+      <c r="BH8">
+        <v>7.8</v>
+      </c>
+      <c r="BI8">
+        <v>5.5</v>
+      </c>
+      <c r="BJ8">
+        <v>9.4</v>
+      </c>
+      <c r="BK8">
+        <v>3.55</v>
+      </c>
+      <c r="BL8">
+        <v>48</v>
+      </c>
+      <c r="BM8">
+        <v>5.1</v>
+      </c>
+      <c r="BN8">
+        <v>10.5</v>
+      </c>
+      <c r="BO8">
+        <v>3.7</v>
+      </c>
+      <c r="BP8">
+        <v>28</v>
+      </c>
+      <c r="BQ8">
+        <v>4.7</v>
+      </c>
+      <c r="BR8">
         <v>26</v>
       </c>
-      <c r="AU8">
-        <v>8.4</v>
-      </c>
-      <c r="AV8">
-        <v>9.4</v>
-      </c>
-      <c r="AW8">
-        <v>11</v>
-      </c>
-      <c r="AX8">
-        <v>1.95</v>
-      </c>
-      <c r="AY8">
-        <v>14.5</v>
-      </c>
-      <c r="AZ8">
-        <v>8</v>
-      </c>
-      <c r="BA8">
-        <v>9.6</v>
-      </c>
-      <c r="BB8">
-        <v>2</v>
-      </c>
-      <c r="BC8">
-        <v>22</v>
-      </c>
-      <c r="BD8">
-        <v>2</v>
-      </c>
-      <c r="BE8">
-        <v>2</v>
-      </c>
-      <c r="BF8">
-        <v>2</v>
-      </c>
-      <c r="BG8">
-        <v>3.9</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2727,61 +2733,61 @@
         <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G9">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H9">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
         <v>8.4</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P9">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V9">
         <v>1.13</v>
       </c>
       <c r="W9">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X9">
         <v>11</v>
@@ -2796,10 +2802,10 @@
         <v>330</v>
       </c>
       <c r="AB9">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD9">
         <v>36</v>
@@ -2820,10 +2826,10 @@
         <v>200</v>
       </c>
       <c r="AJ9">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL9">
         <v>75</v>
@@ -2832,34 +2838,34 @@
         <v>330</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO9">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="AP9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
         <v>12</v>
       </c>
       <c r="AR9">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS9">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT9">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AW9">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX9">
         <v>6.2</v>
@@ -2868,91 +2874,91 @@
         <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BA9">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB9">
         <v>12.5</v>
       </c>
       <c r="BC9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD9">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE9">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF9">
         <v>13</v>
       </c>
       <c r="BG9">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2969,55 +2975,55 @@
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
         <v>4.5</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O10">
         <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R10">
         <v>1.37</v>
       </c>
       <c r="S10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
         <v>1.29</v>
@@ -3026,37 +3032,37 @@
         <v>2</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y10">
-        <v>38</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA10">
         <v>100</v>
       </c>
       <c r="AB10">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD10">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF10">
         <v>12.5</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
         <v>65</v>
@@ -3065,16 +3071,16 @@
         <v>23</v>
       </c>
       <c r="AK10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM10">
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO10">
         <v>60</v>
@@ -3086,25 +3092,25 @@
         <v>14</v>
       </c>
       <c r="AR10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AS10">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="AT10">
         <v>8.4</v>
       </c>
       <c r="AU10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV10">
         <v>15.5</v>
       </c>
       <c r="AW10">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AX10">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AY10">
         <v>9.6</v>
@@ -3113,25 +3119,25 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BB10">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BC10">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE10">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="BF10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG10">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3194,7 +3200,7 @@
         <v>1.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3211,232 +3217,232 @@
         <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H11">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J11">
         <v>4.2</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q11">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S11">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T11">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U11">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y11">
         <v>12</v>
       </c>
       <c r="Z11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE11">
         <v>19</v>
       </c>
       <c r="AF11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL11">
         <v>48</v>
       </c>
       <c r="AM11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN11">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO11">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
+        <v>10.5</v>
+      </c>
+      <c r="AR11">
+        <v>12</v>
+      </c>
+      <c r="AS11">
+        <v>20</v>
+      </c>
+      <c r="AT11">
+        <v>16</v>
+      </c>
+      <c r="AU11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV11">
+        <v>9.4</v>
+      </c>
+      <c r="AW11">
+        <v>16.5</v>
+      </c>
+      <c r="AX11">
+        <v>26</v>
+      </c>
+      <c r="AY11">
+        <v>14</v>
+      </c>
+      <c r="AZ11">
+        <v>16</v>
+      </c>
+      <c r="BA11">
+        <v>25</v>
+      </c>
+      <c r="BB11">
+        <v>32</v>
+      </c>
+      <c r="BC11">
+        <v>34</v>
+      </c>
+      <c r="BD11">
+        <v>38</v>
+      </c>
+      <c r="BE11">
+        <v>12</v>
+      </c>
+      <c r="BF11">
+        <v>26</v>
+      </c>
+      <c r="BG11">
+        <v>9.4</v>
+      </c>
+      <c r="BH11">
+        <v>4.1</v>
+      </c>
+      <c r="BI11">
+        <v>3.15</v>
+      </c>
+      <c r="BJ11">
+        <v>9.4</v>
+      </c>
+      <c r="BK11">
+        <v>5</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
         <v>9.6</v>
       </c>
-      <c r="AR11">
-        <v>11</v>
-      </c>
-      <c r="AS11">
-        <v>17.5</v>
-      </c>
-      <c r="AT11">
-        <v>15</v>
-      </c>
-      <c r="AU11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW11">
-        <v>15</v>
-      </c>
-      <c r="AX11">
-        <v>5.5</v>
-      </c>
-      <c r="AY11">
-        <v>13.5</v>
-      </c>
-      <c r="AZ11">
-        <v>15</v>
-      </c>
-      <c r="BA11">
-        <v>5.4</v>
-      </c>
-      <c r="BB11">
-        <v>22</v>
-      </c>
-      <c r="BC11">
-        <v>5.7</v>
-      </c>
-      <c r="BD11">
-        <v>5.7</v>
-      </c>
-      <c r="BE11">
-        <v>20</v>
-      </c>
-      <c r="BF11">
+      <c r="BN11">
+        <v>7.8</v>
+      </c>
+      <c r="BO11">
         <v>5.6</v>
       </c>
-      <c r="BG11">
-        <v>8.4</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.04</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.04</v>
-      </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3453,19 +3459,19 @@
         <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G12">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
         <v>3.25</v>
@@ -3501,13 +3507,13 @@
         <v>2.46</v>
       </c>
       <c r="U12">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -3552,7 +3558,7 @@
         <v>34</v>
       </c>
       <c r="AL12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
         <v>290</v>
@@ -3567,25 +3573,25 @@
         <v>7.2</v>
       </c>
       <c r="AQ12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AS12">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT12">
         <v>5.5</v>
       </c>
       <c r="AU12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AW12">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX12">
         <v>8.800000000000001</v>
@@ -3597,16 +3603,16 @@
         <v>27</v>
       </c>
       <c r="BA12">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="BB12">
         <v>20</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE12">
         <v>50</v>
@@ -3615,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="BG12">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BH12">
         <v>2.56</v>
@@ -3633,7 +3639,7 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN12">
         <v>4.2</v>
@@ -3651,7 +3657,7 @@
         <v>55</v>
       </c>
       <c r="BS12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT12">
         <v>10.5</v>
@@ -3663,22 +3669,22 @@
         <v>70</v>
       </c>
       <c r="BW12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX12">
         <v>110</v>
       </c>
       <c r="BY12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ12">
         <v>55</v>
       </c>
       <c r="CA12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3695,7 +3701,7 @@
         <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F13">
         <v>1.88</v>
@@ -3704,7 +3710,7 @@
         <v>1.96</v>
       </c>
       <c r="H13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -3716,7 +3722,7 @@
         <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M13">
         <v>1.07</v>
@@ -3761,7 +3767,7 @@
         <v>38</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB13">
         <v>8.800000000000001</v>
@@ -3860,72 +3866,72 @@
         <v>9.4</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI13">
-        <v>1.88</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK13">
-        <v>1.67</v>
+        <v>5.3</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.88</v>
+        <v>9.6</v>
       </c>
       <c r="BN13">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO13">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP13">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BQ13">
-        <v>1.71</v>
+        <v>5.9</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BS13">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="BT13">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BU13">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV13">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="BW13">
-        <v>1.83</v>
+        <v>8.4</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13">
-        <v>1.84</v>
+        <v>8.6</v>
       </c>
       <c r="BZ13">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="CA13">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
         <v>92</v>
@@ -3937,232 +3943,232 @@
         <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>1.94</v>
+        <v>2.96</v>
       </c>
       <c r="G14">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="H14">
-        <v>5.1</v>
+        <v>2.64</v>
       </c>
       <c r="I14">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="K14">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L14">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="M14">
         <v>1.14</v>
       </c>
       <c r="N14">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="O14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P14">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Q14">
         <v>2.98</v>
       </c>
       <c r="R14">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T14">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="U14">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="V14">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="Z14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AC14">
         <v>8</v>
       </c>
       <c r="AD14">
+        <v>17</v>
+      </c>
+      <c r="AE14">
+        <v>60</v>
+      </c>
+      <c r="AF14">
+        <v>24</v>
+      </c>
+      <c r="AG14">
+        <v>18.5</v>
+      </c>
+      <c r="AH14">
+        <v>32</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>80</v>
+      </c>
+      <c r="AK14">
+        <v>70</v>
+      </c>
+      <c r="AL14">
+        <v>120</v>
+      </c>
+      <c r="AM14">
+        <v>310</v>
+      </c>
+      <c r="AN14">
+        <v>110</v>
+      </c>
+      <c r="AO14">
+        <v>80</v>
+      </c>
+      <c r="AP14">
+        <v>5.5</v>
+      </c>
+      <c r="AQ14">
+        <v>5.8</v>
+      </c>
+      <c r="AR14">
+        <v>13</v>
+      </c>
+      <c r="AS14">
+        <v>40</v>
+      </c>
+      <c r="AT14">
+        <v>6.4</v>
+      </c>
+      <c r="AU14">
+        <v>5.5</v>
+      </c>
+      <c r="AV14">
+        <v>11</v>
+      </c>
+      <c r="AW14">
+        <v>38</v>
+      </c>
+      <c r="AX14">
+        <v>15</v>
+      </c>
+      <c r="AY14">
+        <v>12</v>
+      </c>
+      <c r="AZ14">
+        <v>20</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>50</v>
+      </c>
+      <c r="BC14">
+        <v>44</v>
+      </c>
+      <c r="BD14">
+        <v>70</v>
+      </c>
+      <c r="BE14">
+        <v>200</v>
+      </c>
+      <c r="BF14">
+        <v>65</v>
+      </c>
+      <c r="BG14">
+        <v>50</v>
+      </c>
+      <c r="BH14">
+        <v>2.68</v>
+      </c>
+      <c r="BI14">
+        <v>2.08</v>
+      </c>
+      <c r="BJ14">
+        <v>14</v>
+      </c>
+      <c r="BK14">
+        <v>9.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>7</v>
+      </c>
+      <c r="BO14">
+        <v>4.8</v>
+      </c>
+      <c r="BP14">
+        <v>40</v>
+      </c>
+      <c r="BQ14">
         <v>25</v>
       </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG14">
-        <v>11.5</v>
-      </c>
-      <c r="AH14">
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>48</v>
+      </c>
+      <c r="BT14">
+        <v>6.4</v>
+      </c>
+      <c r="BU14">
+        <v>4.4</v>
+      </c>
+      <c r="BV14">
         <v>34</v>
       </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>24</v>
-      </c>
-      <c r="AK14">
-        <v>30</v>
-      </c>
-      <c r="AL14">
-        <v>80</v>
-      </c>
-      <c r="AM14">
-        <v>340</v>
-      </c>
-      <c r="AN14">
-        <v>29</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>7.4</v>
-      </c>
-      <c r="AQ14">
-        <v>10.5</v>
-      </c>
-      <c r="AR14">
-        <v>28</v>
-      </c>
-      <c r="AS14">
+      <c r="BW14">
+        <v>21</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
         <v>44</v>
       </c>
-      <c r="AT14">
-        <v>5.4</v>
-      </c>
-      <c r="AU14">
-        <v>7.4</v>
-      </c>
-      <c r="AV14">
-        <v>20</v>
-      </c>
-      <c r="AW14">
-        <v>60</v>
-      </c>
-      <c r="AX14">
-        <v>9</v>
-      </c>
-      <c r="AY14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14">
-        <v>27</v>
-      </c>
-      <c r="BA14">
-        <v>75</v>
-      </c>
-      <c r="BB14">
-        <v>20</v>
-      </c>
-      <c r="BC14">
-        <v>25</v>
-      </c>
-      <c r="BD14">
-        <v>42</v>
-      </c>
-      <c r="BE14">
-        <v>95</v>
-      </c>
-      <c r="BF14">
-        <v>18.5</v>
-      </c>
-      <c r="BG14">
-        <v>48</v>
-      </c>
-      <c r="BH14">
-        <v>2.74</v>
-      </c>
-      <c r="BI14">
-        <v>2.2</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>3.35</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.37</v>
-      </c>
-      <c r="BN14">
-        <v>5.9</v>
-      </c>
-      <c r="BO14">
-        <v>3.3</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>8.4</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>2.78</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>5.3</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>2.78</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.37</v>
-      </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>2.78</v>
+        <v>50</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4179,133 +4185,133 @@
         <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="G15">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="I15">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J15">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L15">
+        <v>1.66</v>
+      </c>
+      <c r="M15">
+        <v>1.15</v>
+      </c>
+      <c r="N15">
+        <v>2.48</v>
+      </c>
+      <c r="O15">
+        <v>1.65</v>
+      </c>
+      <c r="P15">
         <v>1.5</v>
       </c>
-      <c r="M15">
-        <v>1.09</v>
-      </c>
-      <c r="N15">
-        <v>3.2</v>
-      </c>
-      <c r="O15">
-        <v>1.44</v>
-      </c>
-      <c r="P15">
-        <v>1.73</v>
-      </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="R15">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="S15">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="T15">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="U15">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="V15">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="X15">
+        <v>7.8</v>
+      </c>
+      <c r="Y15">
+        <v>12</v>
+      </c>
+      <c r="Z15">
+        <v>40</v>
+      </c>
+      <c r="AA15">
+        <v>180</v>
+      </c>
+      <c r="AB15">
+        <v>5.8</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>24</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG15">
         <v>11.5</v>
       </c>
-      <c r="Y15">
-        <v>17</v>
-      </c>
-      <c r="Z15">
-        <v>55</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>6.8</v>
-      </c>
-      <c r="AC15">
-        <v>8.6</v>
-      </c>
-      <c r="AD15">
-        <v>26</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG15">
-        <v>10.5</v>
-      </c>
       <c r="AH15">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AK15">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AL15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN15">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP15">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AQ15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AS15">
         <v>44</v>
       </c>
       <c r="AT15">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU15">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV15">
         <v>21</v>
@@ -4314,102 +4320,102 @@
         <v>38</v>
       </c>
       <c r="AX15">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="BA15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BC15">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BD15">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BE15">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="BF15">
+        <v>24</v>
+      </c>
+      <c r="BG15">
+        <v>48</v>
+      </c>
+      <c r="BH15">
+        <v>2.54</v>
+      </c>
+      <c r="BI15">
+        <v>2.4</v>
+      </c>
+      <c r="BJ15">
+        <v>13.5</v>
+      </c>
+      <c r="BK15">
+        <v>8</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>13.5</v>
+      </c>
+      <c r="BN15">
+        <v>4.2</v>
+      </c>
+      <c r="BO15">
+        <v>3.9</v>
+      </c>
+      <c r="BP15">
+        <v>17</v>
+      </c>
+      <c r="BQ15">
+        <v>8.4</v>
+      </c>
+      <c r="BR15">
+        <v>48</v>
+      </c>
+      <c r="BS15">
+        <v>11</v>
+      </c>
+      <c r="BT15">
+        <v>10</v>
+      </c>
+      <c r="BU15">
+        <v>7.6</v>
+      </c>
+      <c r="BV15">
+        <v>75</v>
+      </c>
+      <c r="BW15">
+        <v>12</v>
+      </c>
+      <c r="BX15">
+        <v>110</v>
+      </c>
+      <c r="BY15">
         <v>12.5</v>
       </c>
-      <c r="BG15">
-        <v>42</v>
-      </c>
-      <c r="BH15">
-        <v>3.35</v>
-      </c>
-      <c r="BI15">
-        <v>2.66</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>2.4</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>2.26</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>2.92</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>2.4</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>2.26</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>2.06</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>2.26</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>2.26</v>
-      </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA15">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
         <v>92</v>
@@ -4421,237 +4427,237 @@
         <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>6.4</v>
       </c>
       <c r="J16">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
+        <v>3.2</v>
+      </c>
+      <c r="O16">
+        <v>1.43</v>
+      </c>
+      <c r="P16">
+        <v>1.73</v>
+      </c>
+      <c r="Q16">
+        <v>2.3</v>
+      </c>
+      <c r="R16">
+        <v>1.26</v>
+      </c>
+      <c r="S16">
+        <v>4.5</v>
+      </c>
+      <c r="T16">
+        <v>2.18</v>
+      </c>
+      <c r="U16">
+        <v>1.8</v>
+      </c>
+      <c r="V16">
+        <v>1.19</v>
+      </c>
+      <c r="W16">
+        <v>2.32</v>
+      </c>
+      <c r="X16">
+        <v>11.5</v>
+      </c>
+      <c r="Y16">
+        <v>17</v>
+      </c>
+      <c r="Z16">
+        <v>55</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>6.8</v>
+      </c>
+      <c r="AC16">
+        <v>8.6</v>
+      </c>
+      <c r="AD16">
+        <v>26</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG16">
+        <v>10.5</v>
+      </c>
+      <c r="AH16">
+        <v>26</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>18</v>
+      </c>
+      <c r="AK16">
+        <v>22</v>
+      </c>
+      <c r="AL16">
+        <v>50</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>14.5</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>10</v>
+      </c>
+      <c r="AQ16">
+        <v>14</v>
+      </c>
+      <c r="AR16">
+        <v>36</v>
+      </c>
+      <c r="AS16">
+        <v>44</v>
+      </c>
+      <c r="AT16">
+        <v>6.2</v>
+      </c>
+      <c r="AU16">
+        <v>7.8</v>
+      </c>
+      <c r="AV16">
+        <v>21</v>
+      </c>
+      <c r="AW16">
+        <v>38</v>
+      </c>
+      <c r="AX16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY16">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16">
+        <v>21</v>
+      </c>
+      <c r="BA16">
+        <v>65</v>
+      </c>
+      <c r="BB16">
+        <v>15.5</v>
+      </c>
+      <c r="BC16">
+        <v>18</v>
+      </c>
+      <c r="BD16">
+        <v>38</v>
+      </c>
+      <c r="BE16">
+        <v>46</v>
+      </c>
+      <c r="BF16">
+        <v>12.5</v>
+      </c>
+      <c r="BG16">
+        <v>42</v>
+      </c>
+      <c r="BH16">
+        <v>3.05</v>
+      </c>
+      <c r="BI16">
+        <v>2.82</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>6.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>13</v>
+      </c>
+      <c r="BN16">
         <v>4.1</v>
       </c>
-      <c r="O16">
-        <v>1.29</v>
-      </c>
-      <c r="P16">
-        <v>2.06</v>
-      </c>
-      <c r="Q16">
-        <v>1.88</v>
-      </c>
-      <c r="R16">
-        <v>1.41</v>
-      </c>
-      <c r="S16">
-        <v>3.25</v>
-      </c>
-      <c r="T16">
-        <v>1.68</v>
-      </c>
-      <c r="U16">
-        <v>2.24</v>
-      </c>
-      <c r="V16">
-        <v>1.5</v>
-      </c>
-      <c r="W16">
-        <v>1.64</v>
-      </c>
-      <c r="X16">
-        <v>20</v>
-      </c>
-      <c r="Y16">
-        <v>14.5</v>
-      </c>
-      <c r="Z16">
-        <v>22</v>
-      </c>
-      <c r="AA16">
-        <v>55</v>
-      </c>
-      <c r="AB16">
-        <v>13</v>
-      </c>
-      <c r="AC16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD16">
-        <v>14</v>
-      </c>
-      <c r="AE16">
+      <c r="BO16">
+        <v>3.65</v>
+      </c>
+      <c r="BP16">
+        <v>12.5</v>
+      </c>
+      <c r="BQ16">
+        <v>7.2</v>
+      </c>
+      <c r="BR16">
         <v>34</v>
       </c>
-      <c r="AF16">
-        <v>17.5</v>
-      </c>
-      <c r="AG16">
+      <c r="BS16">
+        <v>10</v>
+      </c>
+      <c r="BT16">
+        <v>10</v>
+      </c>
+      <c r="BU16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV16">
+        <v>70</v>
+      </c>
+      <c r="BW16">
+        <v>11.5</v>
+      </c>
+      <c r="BX16">
+        <v>85</v>
+      </c>
+      <c r="BY16">
         <v>12</v>
       </c>
-      <c r="AH16">
-        <v>17.5</v>
-      </c>
-      <c r="AI16">
-        <v>50</v>
-      </c>
-      <c r="AJ16">
-        <v>38</v>
-      </c>
-      <c r="AK16">
-        <v>26</v>
-      </c>
-      <c r="AL16">
-        <v>36</v>
-      </c>
-      <c r="AM16">
-        <v>90</v>
-      </c>
-      <c r="AN16">
-        <v>23</v>
-      </c>
-      <c r="AO16">
-        <v>32</v>
-      </c>
-      <c r="AP16">
-        <v>14.5</v>
-      </c>
-      <c r="AQ16">
-        <v>11.5</v>
-      </c>
-      <c r="AR16">
-        <v>17.5</v>
-      </c>
-      <c r="AS16">
+      <c r="BZ16">
         <v>29</v>
       </c>
-      <c r="AT16">
-        <v>10</v>
-      </c>
-      <c r="AU16">
-        <v>7.6</v>
-      </c>
-      <c r="AV16">
-        <v>11.5</v>
-      </c>
-      <c r="AW16">
-        <v>21</v>
-      </c>
-      <c r="AX16">
-        <v>14.5</v>
-      </c>
-      <c r="AY16">
-        <v>10</v>
-      </c>
-      <c r="AZ16">
-        <v>15</v>
-      </c>
-      <c r="BA16">
-        <v>28</v>
-      </c>
-      <c r="BB16">
-        <v>27</v>
-      </c>
-      <c r="BC16">
-        <v>20</v>
-      </c>
-      <c r="BD16">
-        <v>14.5</v>
-      </c>
-      <c r="BE16">
-        <v>42</v>
-      </c>
-      <c r="BF16">
-        <v>16</v>
-      </c>
-      <c r="BG16">
-        <v>18.5</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.04</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.04</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.04</v>
-      </c>
-      <c r="BZ16">
-        <v>1000</v>
-      </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>92</v>
@@ -4663,716 +4669,958 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="H17">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I17">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="J17">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
         <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F18">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="G18">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="H18">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="I18">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J18">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="L18">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA18">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BB18">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD18">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE18">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BF18">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BG18">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F19">
+        <v>1.59</v>
+      </c>
+      <c r="G19">
+        <v>1.63</v>
+      </c>
+      <c r="H19">
+        <v>7</v>
+      </c>
+      <c r="I19">
+        <v>8</v>
+      </c>
+      <c r="J19">
+        <v>3.95</v>
+      </c>
+      <c r="K19">
+        <v>4.3</v>
+      </c>
+      <c r="L19">
+        <v>1.44</v>
+      </c>
+      <c r="M19">
+        <v>1.08</v>
+      </c>
+      <c r="N19">
+        <v>3.45</v>
+      </c>
+      <c r="O19">
+        <v>1.37</v>
+      </c>
+      <c r="P19">
+        <v>1.83</v>
+      </c>
+      <c r="Q19">
+        <v>2.12</v>
+      </c>
+      <c r="R19">
+        <v>1.31</v>
+      </c>
+      <c r="S19">
+        <v>3.95</v>
+      </c>
+      <c r="T19">
+        <v>2.14</v>
+      </c>
+      <c r="U19">
+        <v>1.78</v>
+      </c>
+      <c r="V19">
+        <v>1.15</v>
+      </c>
+      <c r="W19">
+        <v>2.6</v>
+      </c>
+      <c r="X19">
+        <v>13.5</v>
+      </c>
+      <c r="Y19">
+        <v>21</v>
+      </c>
+      <c r="Z19">
+        <v>65</v>
+      </c>
+      <c r="AA19">
+        <v>510</v>
+      </c>
+      <c r="AB19">
+        <v>7.2</v>
+      </c>
+      <c r="AC19">
+        <v>9.6</v>
+      </c>
+      <c r="AD19">
+        <v>29</v>
+      </c>
+      <c r="AE19">
+        <v>520</v>
+      </c>
+      <c r="AF19">
+        <v>9</v>
+      </c>
+      <c r="AG19">
+        <v>10.5</v>
+      </c>
+      <c r="AH19">
+        <v>32</v>
+      </c>
+      <c r="AI19">
+        <v>520</v>
+      </c>
+      <c r="AJ19">
+        <v>15.5</v>
+      </c>
+      <c r="AK19">
+        <v>19.5</v>
+      </c>
+      <c r="AL19">
+        <v>55</v>
+      </c>
+      <c r="AM19">
+        <v>510</v>
+      </c>
+      <c r="AN19">
+        <v>11.5</v>
+      </c>
+      <c r="AO19">
+        <v>520</v>
+      </c>
+      <c r="AP19">
+        <v>11</v>
+      </c>
+      <c r="AQ19">
+        <v>17.5</v>
+      </c>
+      <c r="AR19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS19">
+        <v>9.4</v>
+      </c>
+      <c r="AT19">
+        <v>6</v>
+      </c>
+      <c r="AU19">
+        <v>8</v>
+      </c>
+      <c r="AV19">
+        <v>21</v>
+      </c>
+      <c r="AW19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX19">
+        <v>7.6</v>
+      </c>
+      <c r="AY19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ19">
+        <v>19</v>
+      </c>
+      <c r="BA19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB19">
+        <v>12.5</v>
+      </c>
+      <c r="BC19">
+        <v>16</v>
+      </c>
+      <c r="BD19">
+        <v>36</v>
+      </c>
+      <c r="BE19">
+        <v>9.4</v>
+      </c>
+      <c r="BF19">
+        <v>9.6</v>
+      </c>
+      <c r="BG19">
+        <v>9.4</v>
+      </c>
+      <c r="BH19">
+        <v>3.35</v>
+      </c>
+      <c r="BI19">
+        <v>2.92</v>
+      </c>
+      <c r="BJ19">
+        <v>12</v>
+      </c>
+      <c r="BK19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>11</v>
+      </c>
+      <c r="BN19">
+        <v>4</v>
+      </c>
+      <c r="BO19">
+        <v>3.45</v>
+      </c>
+      <c r="BP19">
+        <v>11</v>
+      </c>
+      <c r="BQ19">
+        <v>8</v>
+      </c>
+      <c r="BR19">
+        <v>32</v>
+      </c>
+      <c r="BS19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT19">
+        <v>11</v>
+      </c>
+      <c r="BU19">
+        <v>7.6</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>10</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>10.5</v>
+      </c>
+      <c r="BZ19">
+        <v>24</v>
+      </c>
+      <c r="CA19">
+        <v>8</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20">
         <v>2.2</v>
       </c>
-      <c r="G19">
-        <v>2.32</v>
-      </c>
-      <c r="H19">
-        <v>3.3</v>
-      </c>
-      <c r="I19">
-        <v>3.55</v>
-      </c>
-      <c r="J19">
+      <c r="G20">
+        <v>2.3</v>
+      </c>
+      <c r="H20">
+        <v>3.35</v>
+      </c>
+      <c r="I20">
+        <v>3.6</v>
+      </c>
+      <c r="J20">
         <v>3.65</v>
       </c>
-      <c r="K19">
+      <c r="K20">
         <v>3.85</v>
       </c>
-      <c r="L19">
+      <c r="L20">
         <v>1.39</v>
       </c>
-      <c r="M19">
+      <c r="M20">
         <v>1.06</v>
       </c>
-      <c r="N19">
-        <v>3.95</v>
-      </c>
-      <c r="O19">
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
         <v>1.3</v>
       </c>
-      <c r="P19">
+      <c r="P20">
         <v>2.02</v>
       </c>
-      <c r="Q19">
+      <c r="Q20">
         <v>1.91</v>
       </c>
-      <c r="R19">
+      <c r="R20">
         <v>1.4</v>
       </c>
-      <c r="S19">
+      <c r="S20">
         <v>3.35</v>
       </c>
-      <c r="T19">
+      <c r="T20">
         <v>1.73</v>
       </c>
-      <c r="U19">
+      <c r="U20">
         <v>2.18</v>
       </c>
-      <c r="V19">
-        <v>1.39</v>
-      </c>
-      <c r="W19">
-        <v>1.75</v>
-      </c>
-      <c r="X19">
+      <c r="V20">
+        <v>1.38</v>
+      </c>
+      <c r="W20">
+        <v>1.76</v>
+      </c>
+      <c r="X20">
         <v>16</v>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <v>14.5</v>
       </c>
-      <c r="Z19">
+      <c r="Z20">
         <v>26</v>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <v>65</v>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <v>11</v>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <v>8.4</v>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <v>15</v>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <v>42</v>
       </c>
-      <c r="AF19">
+      <c r="AF20">
         <v>15.5</v>
       </c>
-      <c r="AG19">
+      <c r="AG20">
         <v>11.5</v>
       </c>
-      <c r="AH19">
+      <c r="AH20">
         <v>18</v>
       </c>
-      <c r="AI19">
+      <c r="AI20">
         <v>60</v>
       </c>
-      <c r="AJ19">
+      <c r="AJ20">
         <v>30</v>
       </c>
-      <c r="AK19">
+      <c r="AK20">
+        <v>24</v>
+      </c>
+      <c r="AL20">
+        <v>38</v>
+      </c>
+      <c r="AM20">
+        <v>110</v>
+      </c>
+      <c r="AN20">
+        <v>17</v>
+      </c>
+      <c r="AO20">
+        <v>38</v>
+      </c>
+      <c r="AP20">
+        <v>13</v>
+      </c>
+      <c r="AQ20">
+        <v>12</v>
+      </c>
+      <c r="AR20">
+        <v>21</v>
+      </c>
+      <c r="AS20">
+        <v>22</v>
+      </c>
+      <c r="AT20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU20">
+        <v>7.2</v>
+      </c>
+      <c r="AV20">
+        <v>12.5</v>
+      </c>
+      <c r="AW20">
+        <v>14.5</v>
+      </c>
+      <c r="AX20">
+        <v>12.5</v>
+      </c>
+      <c r="AY20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ20">
+        <v>14.5</v>
+      </c>
+      <c r="BA20">
+        <v>18.5</v>
+      </c>
+      <c r="BB20">
+        <v>11</v>
+      </c>
+      <c r="BC20">
+        <v>20</v>
+      </c>
+      <c r="BD20">
+        <v>12.5</v>
+      </c>
+      <c r="BE20">
+        <v>30</v>
+      </c>
+      <c r="BF20">
+        <v>14</v>
+      </c>
+      <c r="BG20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH20">
+        <v>3.6</v>
+      </c>
+      <c r="BI20">
+        <v>3.15</v>
+      </c>
+      <c r="BJ20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK20">
+        <v>5.3</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>10</v>
+      </c>
+      <c r="BN20">
+        <v>5.3</v>
+      </c>
+      <c r="BO20">
+        <v>4.5</v>
+      </c>
+      <c r="BP20">
+        <v>17</v>
+      </c>
+      <c r="BQ20">
+        <v>6.8</v>
+      </c>
+      <c r="BR20">
+        <v>30</v>
+      </c>
+      <c r="BS20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT20">
+        <v>7</v>
+      </c>
+      <c r="BU20">
+        <v>5.8</v>
+      </c>
+      <c r="BV20">
+        <v>28</v>
+      </c>
+      <c r="BW20">
+        <v>8</v>
+      </c>
+      <c r="BX20">
+        <v>40</v>
+      </c>
+      <c r="BY20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ20">
         <v>25</v>
       </c>
-      <c r="AL19">
-        <v>38</v>
-      </c>
-      <c r="AM19">
-        <v>110</v>
-      </c>
-      <c r="AN19">
-        <v>17.5</v>
-      </c>
-      <c r="AO19">
-        <v>38</v>
-      </c>
-      <c r="AP19">
-        <v>13</v>
-      </c>
-      <c r="AQ19">
-        <v>12</v>
-      </c>
-      <c r="AR19">
-        <v>21</v>
-      </c>
-      <c r="AS19">
-        <v>22</v>
-      </c>
-      <c r="AT19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU19">
-        <v>7.2</v>
-      </c>
-      <c r="AV19">
-        <v>12.5</v>
-      </c>
-      <c r="AW19">
-        <v>14.5</v>
-      </c>
-      <c r="AX19">
-        <v>12.5</v>
-      </c>
-      <c r="AY19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ19">
-        <v>14.5</v>
-      </c>
-      <c r="BA19">
-        <v>18.5</v>
-      </c>
-      <c r="BB19">
-        <v>11</v>
-      </c>
-      <c r="BC19">
-        <v>20</v>
-      </c>
-      <c r="BD19">
-        <v>12.5</v>
-      </c>
-      <c r="BE19">
-        <v>30</v>
-      </c>
-      <c r="BF19">
-        <v>14.5</v>
-      </c>
-      <c r="BG19">
-        <v>8</v>
-      </c>
-      <c r="BH19">
-        <v>3.6</v>
-      </c>
-      <c r="BI19">
-        <v>3.15</v>
-      </c>
-      <c r="BJ19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK19">
-        <v>5.2</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>10</v>
-      </c>
-      <c r="BN19">
-        <v>5.3</v>
-      </c>
-      <c r="BO19">
-        <v>4.5</v>
-      </c>
-      <c r="BP19">
-        <v>17</v>
-      </c>
-      <c r="BQ19">
-        <v>6.6</v>
-      </c>
-      <c r="BR19">
-        <v>30</v>
-      </c>
-      <c r="BS19">
-        <v>8</v>
-      </c>
-      <c r="BT19">
-        <v>7</v>
-      </c>
-      <c r="BU19">
-        <v>5.8</v>
-      </c>
-      <c r="BV19">
-        <v>29</v>
-      </c>
-      <c r="BW19">
-        <v>8</v>
-      </c>
-      <c r="BX19">
-        <v>40</v>
-      </c>
-      <c r="BY19">
-        <v>8.6</v>
-      </c>
-      <c r="BZ19">
-        <v>26</v>
-      </c>
-      <c r="CA19">
-        <v>7.6</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>142</v>
+      <c r="CA20">
+        <v>7.8</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -448,7 +448,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-05 03:56:16</t>
+    <t>2026-10-05 06:05:49</t>
   </si>
 </sst>
 </file>
@@ -1042,22 +1042,22 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G2">
         <v>2.06</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1066,13 +1066,13 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1081,46 +1081,46 @@
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X2">
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA2">
         <v>130</v>
       </c>
       <c r="AB2">
+        <v>11</v>
+      </c>
+      <c r="AC2">
         <v>9</v>
       </c>
-      <c r="AC2">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1132,10 +1132,10 @@
         <v>90</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL2">
         <v>50</v>
@@ -1150,85 +1150,85 @@
         <v>100</v>
       </c>
       <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>12</v>
+      </c>
+      <c r="AR2">
+        <v>4.5</v>
+      </c>
+      <c r="AS2">
+        <v>4.9</v>
+      </c>
+      <c r="AT2">
+        <v>7.6</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>15.5</v>
+      </c>
+      <c r="AW2">
+        <v>4.8</v>
+      </c>
+      <c r="AX2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2">
         <v>9</v>
       </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
-      <c r="AR2">
+      <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
+        <v>4.8</v>
+      </c>
+      <c r="BB2">
+        <v>4.3</v>
+      </c>
+      <c r="BC2">
+        <v>4.3</v>
+      </c>
+      <c r="BD2">
+        <v>4.7</v>
+      </c>
+      <c r="BE2">
         <v>5</v>
       </c>
-      <c r="AS2">
-        <v>5.5</v>
-      </c>
-      <c r="AT2">
-        <v>6.2</v>
-      </c>
-      <c r="AU2">
-        <v>6.2</v>
-      </c>
-      <c r="AV2">
-        <v>14</v>
-      </c>
-      <c r="AW2">
-        <v>5.3</v>
-      </c>
-      <c r="AX2">
-        <v>9</v>
-      </c>
-      <c r="AY2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2">
+      <c r="BF2">
         <v>15.5</v>
       </c>
-      <c r="BA2">
-        <v>5.3</v>
-      </c>
-      <c r="BB2">
-        <v>18</v>
-      </c>
-      <c r="BC2">
-        <v>17.5</v>
-      </c>
-      <c r="BD2">
-        <v>5.1</v>
-      </c>
-      <c r="BE2">
-        <v>5.5</v>
-      </c>
-      <c r="BF2">
-        <v>14</v>
-      </c>
       <c r="BG2">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ2">
         <v>4.5</v>
@@ -1237,31 +1237,31 @@
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT2">
         <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="BV2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ2">
         <v>36</v>
       </c>
       <c r="CA2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="s">
         <v>144</v>
@@ -1526,22 +1526,22 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J4">
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.44</v>
@@ -1550,43 +1550,43 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
         <v>1.82</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
         <v>1.32</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA4">
         <v>75</v>
@@ -1598,13 +1598,13 @@
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG4">
         <v>12</v>
@@ -1613,13 +1613,13 @@
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1628,34 +1628,34 @@
         <v>130</v>
       </c>
       <c r="AN4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO4">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP4">
+        <v>11</v>
+      </c>
+      <c r="AQ4">
         <v>10</v>
       </c>
-      <c r="AQ4">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
@@ -1670,19 +1670,19 @@
         <v>32</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BG4">
         <v>23</v>
@@ -1691,61 +1691,61 @@
         <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>144</v>
@@ -1768,64 +1768,64 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="H5">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
+        <v>2.58</v>
+      </c>
+      <c r="T5">
+        <v>1.57</v>
+      </c>
+      <c r="U5">
         <v>2.48</v>
       </c>
-      <c r="T5">
-        <v>1.56</v>
-      </c>
-      <c r="U5">
-        <v>2.5</v>
-      </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X5">
         <v>28</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -1834,7 +1834,7 @@
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1846,10 +1846,10 @@
         <v>34</v>
       </c>
       <c r="AF5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
         <v>16</v>
@@ -1861,22 +1861,22 @@
         <v>36</v>
       </c>
       <c r="AK5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL5">
         <v>36</v>
       </c>
       <c r="AM5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>26</v>
       </c>
       <c r="AP5">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ5">
         <v>14.5</v>
@@ -1885,19 +1885,19 @@
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT5">
         <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -1906,31 +1906,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB5">
         <v>21</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE5">
         <v>46</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG5">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BH5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI5">
         <v>3.3</v>
@@ -1939,13 +1939,13 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BN5">
         <v>6.6</v>
@@ -1954,40 +1954,40 @@
         <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BR5">
         <v>29</v>
       </c>
       <c r="BS5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5">
         <v>5.1</v>
       </c>
       <c r="BV5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW5">
+        <v>3.9</v>
+      </c>
+      <c r="BX5">
+        <v>36</v>
+      </c>
+      <c r="BY5">
         <v>4</v>
-      </c>
-      <c r="BX5">
-        <v>34</v>
-      </c>
-      <c r="BY5">
-        <v>4.1</v>
       </c>
       <c r="BZ5">
         <v>21</v>
       </c>
       <c r="CA5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="CB5" t="s">
         <v>144</v>
@@ -2025,7 +2025,7 @@
         <v>5.5</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -2037,13 +2037,13 @@
         <v>4.9</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
         <v>2.4</v>
       </c>
       <c r="Q6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R6">
         <v>1.55</v>
@@ -2070,10 +2070,10 @@
         <v>44</v>
       </c>
       <c r="Z6">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA6">
-        <v>530</v>
+        <v>600</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -2082,43 +2082,43 @@
         <v>15.5</v>
       </c>
       <c r="AD6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AE6">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AF6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
         <v>12</v>
       </c>
       <c r="AK6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AO6">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="AP6">
-        <v>17.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6">
         <v>5.1</v>
@@ -2130,22 +2130,22 @@
         <v>5.7</v>
       </c>
       <c r="AT6">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AV6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW6">
         <v>5.6</v>
       </c>
       <c r="AX6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY6">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
         <v>4.9</v>
@@ -2154,10 +2154,10 @@
         <v>5.6</v>
       </c>
       <c r="BB6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD6">
         <v>5.1</v>
@@ -2166,7 +2166,7 @@
         <v>5.6</v>
       </c>
       <c r="BF6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG6">
         <v>5.7</v>
@@ -2175,61 +2175,61 @@
         <v>4.2</v>
       </c>
       <c r="BI6">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BO6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BP6">
         <v>7.6</v>
       </c>
       <c r="BQ6">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BR6">
         <v>24</v>
       </c>
       <c r="BS6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
+        <v>13</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>12.5</v>
+      </c>
+      <c r="BZ6">
         <v>12</v>
       </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>11.5</v>
-      </c>
-      <c r="BZ6">
-        <v>12.5</v>
-      </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="s">
         <v>144</v>
@@ -2261,13 +2261,13 @@
         <v>3.8</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2336,7 +2336,7 @@
         <v>1000</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI7">
         <v>1000</v>
@@ -2360,58 +2360,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ7">
         <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2494,22 +2494,22 @@
         <v>131</v>
       </c>
       <c r="F8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H8">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="I8">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L8">
         <v>1.16</v>
@@ -2518,28 +2518,28 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="O8">
         <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R8">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="V8">
         <v>2.28</v>
@@ -2551,13 +2551,13 @@
         <v>950</v>
       </c>
       <c r="Y8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z8">
         <v>23</v>
       </c>
       <c r="AA8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB8">
         <v>48</v>
@@ -2566,7 +2566,7 @@
         <v>16</v>
       </c>
       <c r="AD8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE8">
         <v>16.5</v>
@@ -2575,31 +2575,31 @@
         <v>80</v>
       </c>
       <c r="AG8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
         <v>20</v>
       </c>
       <c r="AJ8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK8">
         <v>44</v>
       </c>
       <c r="AL8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM8">
         <v>46</v>
       </c>
       <c r="AN8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AP8">
         <v>46</v>
@@ -2608,7 +2608,7 @@
         <v>22</v>
       </c>
       <c r="AR8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS8">
         <v>20</v>
@@ -2632,10 +2632,10 @@
         <v>18</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BB8">
         <v>55</v>
@@ -2650,70 +2650,70 @@
         <v>27</v>
       </c>
       <c r="BF8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH8">
         <v>7.8</v>
       </c>
       <c r="BI8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BJ8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BL8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BM8">
+        <v>6.2</v>
+      </c>
+      <c r="BN8">
+        <v>9.6</v>
+      </c>
+      <c r="BO8">
+        <v>4.1</v>
+      </c>
+      <c r="BP8">
+        <v>27</v>
+      </c>
+      <c r="BQ8">
+        <v>5.7</v>
+      </c>
+      <c r="BR8">
+        <v>24</v>
+      </c>
+      <c r="BS8">
+        <v>5.6</v>
+      </c>
+      <c r="BT8">
+        <v>6.2</v>
+      </c>
+      <c r="BU8">
         <v>5.1</v>
       </c>
-      <c r="BN8">
-        <v>10.5</v>
-      </c>
-      <c r="BO8">
-        <v>3.7</v>
-      </c>
-      <c r="BP8">
-        <v>28</v>
-      </c>
-      <c r="BQ8">
-        <v>4.7</v>
-      </c>
-      <c r="BR8">
-        <v>26</v>
-      </c>
-      <c r="BS8">
-        <v>4.7</v>
-      </c>
-      <c r="BT8">
-        <v>6.8</v>
-      </c>
-      <c r="BU8">
-        <v>4.8</v>
-      </c>
       <c r="BV8">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BW8">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
         <v>17</v>
       </c>
       <c r="BY8">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BZ8">
         <v>8.6</v>
       </c>
       <c r="CA8">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="CB8" t="s">
         <v>144</v>
@@ -2736,22 +2736,22 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>3.4</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
         <v>1.56</v>
@@ -2760,40 +2760,40 @@
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P9">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S9">
         <v>5.2</v>
       </c>
       <c r="T9">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="X9">
         <v>11</v>
       </c>
       <c r="Y9">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z9">
         <v>70</v>
@@ -2802,10 +2802,10 @@
         <v>330</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
         <v>36</v>
@@ -2817,67 +2817,67 @@
         <v>10</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI9">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ9">
         <v>18.5</v>
       </c>
       <c r="AK9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM9">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN9">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO9">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="AP9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR9">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS9">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT9">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AW9">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX9">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA9">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB9">
         <v>12.5</v>
@@ -2886,16 +2886,16 @@
         <v>20</v>
       </c>
       <c r="BD9">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE9">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF9">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG9">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9">
         <v>3.2</v>
@@ -2904,58 +2904,58 @@
         <v>2.28</v>
       </c>
       <c r="BJ9">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BK9">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BN9">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="BP9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="BR9">
         <v>48</v>
       </c>
       <c r="BS9">
+        <v>5.1</v>
+      </c>
+      <c r="BT9">
+        <v>11</v>
+      </c>
+      <c r="BU9">
+        <v>7.8</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
         <v>5.4</v>
       </c>
-      <c r="BT9">
-        <v>13</v>
-      </c>
-      <c r="BU9">
-        <v>8</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>5.8</v>
-      </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9">
         <v>42</v>
       </c>
       <c r="CA9">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="s">
         <v>144</v>
@@ -2978,10 +2978,10 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H10">
         <v>4.2</v>
@@ -2990,10 +2990,10 @@
         <v>4.5</v>
       </c>
       <c r="J10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
         <v>1.42</v>
@@ -3011,7 +3011,7 @@
         <v>1.96</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R10">
         <v>1.37</v>
@@ -3020,19 +3020,19 @@
         <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
         <v>1.29</v>
       </c>
       <c r="W10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y10">
         <v>15.5</v>
@@ -3041,13 +3041,13 @@
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB10">
         <v>9.199999999999999</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
         <v>17.5</v>
@@ -3074,7 +3074,7 @@
         <v>21</v>
       </c>
       <c r="AL10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM10">
         <v>110</v>
@@ -3086,7 +3086,7 @@
         <v>60</v>
       </c>
       <c r="AP10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ10">
         <v>14</v>
@@ -3095,19 +3095,19 @@
         <v>28</v>
       </c>
       <c r="AS10">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AT10">
         <v>8.4</v>
       </c>
       <c r="AU10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV10">
         <v>15.5</v>
       </c>
       <c r="AW10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX10">
         <v>11</v>
@@ -3119,10 +3119,10 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC10">
         <v>19</v>
@@ -3131,73 +3131,73 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG10">
+        <v>40</v>
+      </c>
+      <c r="BH10">
+        <v>3.8</v>
+      </c>
+      <c r="BI10">
+        <v>3.1</v>
+      </c>
+      <c r="BJ10">
+        <v>11.5</v>
+      </c>
+      <c r="BK10">
+        <v>4.6</v>
+      </c>
+      <c r="BL10">
+        <v>150</v>
+      </c>
+      <c r="BM10">
+        <v>7.2</v>
+      </c>
+      <c r="BN10">
+        <v>4.7</v>
+      </c>
+      <c r="BO10">
+        <v>4.2</v>
+      </c>
+      <c r="BP10">
+        <v>16</v>
+      </c>
+      <c r="BQ10">
+        <v>5.4</v>
+      </c>
+      <c r="BR10">
+        <v>34</v>
+      </c>
+      <c r="BS10">
+        <v>6.2</v>
+      </c>
+      <c r="BT10">
+        <v>7.6</v>
+      </c>
+      <c r="BU10">
+        <v>6.8</v>
+      </c>
+      <c r="BV10">
         <v>42</v>
       </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.5</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>6.2</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.5</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.71</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>2.48</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>1.5</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>2.02</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
       <c r="BW10">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA10">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="s">
         <v>144</v>
@@ -3220,25 +3220,25 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="G11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
+        <v>1.9</v>
+      </c>
+      <c r="I11">
         <v>1.93</v>
       </c>
-      <c r="I11">
-        <v>1.98</v>
-      </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M11">
         <v>1.04</v>
@@ -3250,28 +3250,28 @@
         <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q11">
         <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S11">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U11">
         <v>2.3</v>
       </c>
       <c r="V11">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X11">
         <v>23</v>
@@ -3313,7 +3313,7 @@
         <v>80</v>
       </c>
       <c r="AK11">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL11">
         <v>48</v>
@@ -3340,7 +3340,7 @@
         <v>20</v>
       </c>
       <c r="AT11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU11">
         <v>9.199999999999999</v>
@@ -3349,7 +3349,7 @@
         <v>9.4</v>
       </c>
       <c r="AW11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX11">
         <v>26</v>
@@ -3364,25 +3364,25 @@
         <v>25</v>
       </c>
       <c r="BB11">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BC11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD11">
         <v>38</v>
       </c>
       <c r="BE11">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI11">
         <v>3.15</v>
@@ -3391,13 +3391,13 @@
         <v>9.4</v>
       </c>
       <c r="BK11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
         <v>7.8</v>
@@ -3409,13 +3409,13 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
+        <v>7.6</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
         <v>7.8</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
         <v>5.2</v>
@@ -3427,19 +3427,19 @@
         <v>14</v>
       </c>
       <c r="BW11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX11">
         <v>25</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11">
         <v>18.5</v>
       </c>
       <c r="CA11">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB11" t="s">
         <v>144</v>
@@ -3462,52 +3462,52 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H12">
         <v>5.2</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
         <v>1.64</v>
       </c>
       <c r="M12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O12">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P12">
         <v>1.49</v>
       </c>
       <c r="Q12">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S12">
         <v>6.6</v>
       </c>
       <c r="T12">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U12">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V12">
         <v>1.22</v>
@@ -3528,10 +3528,10 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
         <v>24</v>
@@ -3540,22 +3540,22 @@
         <v>1000</v>
       </c>
       <c r="AF12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI12">
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK12">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL12">
         <v>1000</v>
@@ -3564,13 +3564,13 @@
         <v>290</v>
       </c>
       <c r="AN12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12">
         <v>11</v>
@@ -3579,37 +3579,37 @@
         <v>32</v>
       </c>
       <c r="AS12">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AT12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU12">
         <v>7</v>
       </c>
       <c r="AV12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW12">
         <v>50</v>
       </c>
       <c r="AX12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA12">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BB12">
         <v>20</v>
       </c>
       <c r="BC12">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD12">
         <v>46</v>
@@ -3621,25 +3621,25 @@
         <v>20</v>
       </c>
       <c r="BG12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BH12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BI12">
         <v>2.42</v>
       </c>
       <c r="BJ12">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
         <v>4.2</v>
@@ -3648,7 +3648,7 @@
         <v>3.9</v>
       </c>
       <c r="BP12">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ12">
         <v>7.8</v>
@@ -3657,31 +3657,31 @@
         <v>55</v>
       </c>
       <c r="BS12">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12">
         <v>7.6</v>
       </c>
       <c r="BV12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BW12">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BX12">
         <v>110</v>
       </c>
       <c r="BY12">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="CB12" t="s">
         <v>144</v>
@@ -3707,10 +3707,10 @@
         <v>1.88</v>
       </c>
       <c r="G13">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -3725,16 +3725,16 @@
         <v>1.43</v>
       </c>
       <c r="M13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
         <v>3.6</v>
       </c>
       <c r="O13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P13">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q13">
         <v>2.06</v>
@@ -3767,7 +3767,7 @@
         <v>38</v>
       </c>
       <c r="AA13">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB13">
         <v>8.800000000000001</v>
@@ -3779,7 +3779,7 @@
         <v>19.5</v>
       </c>
       <c r="AE13">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF13">
         <v>12</v>
@@ -3812,7 +3812,7 @@
         <v>90</v>
       </c>
       <c r="AP13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
         <v>13</v>
@@ -3827,19 +3827,19 @@
         <v>7.4</v>
       </c>
       <c r="AU13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW13">
         <v>9.199999999999999</v>
       </c>
       <c r="AX13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
         <v>17</v>
@@ -3851,7 +3851,7 @@
         <v>18</v>
       </c>
       <c r="BC13">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD13">
         <v>8.4</v>
@@ -3860,7 +3860,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BF13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG13">
         <v>9.4</v>
@@ -3887,7 +3887,7 @@
         <v>4.7</v>
       </c>
       <c r="BO13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP13">
         <v>14</v>
@@ -3946,79 +3946,79 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H14">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="I14">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="K14">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="L14">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="M14">
+        <v>1.17</v>
+      </c>
+      <c r="N14">
+        <v>2.26</v>
+      </c>
+      <c r="O14">
+        <v>1.72</v>
+      </c>
+      <c r="P14">
+        <v>1.4</v>
+      </c>
+      <c r="Q14">
+        <v>3.25</v>
+      </c>
+      <c r="R14">
         <v>1.14</v>
       </c>
-      <c r="N14">
-        <v>2.16</v>
-      </c>
-      <c r="O14">
-        <v>1.64</v>
-      </c>
-      <c r="P14">
-        <v>1.35</v>
-      </c>
-      <c r="Q14">
-        <v>2.98</v>
-      </c>
-      <c r="R14">
-        <v>1.12</v>
-      </c>
       <c r="S14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T14">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="U14">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X14">
         <v>7.8</v>
       </c>
       <c r="Y14">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA14">
         <v>65</v>
       </c>
       <c r="AB14">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE14">
         <v>60</v>
@@ -4027,13 +4027,13 @@
         <v>24</v>
       </c>
       <c r="AG14">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH14">
         <v>32</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
         <v>80</v>
@@ -4045,37 +4045,37 @@
         <v>120</v>
       </c>
       <c r="AM14">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO14">
         <v>80</v>
       </c>
       <c r="AP14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR14">
         <v>13</v>
       </c>
       <c r="AS14">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU14">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
         <v>11</v>
       </c>
       <c r="AW14">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
         <v>15</v>
@@ -4084,88 +4084,88 @@
         <v>12</v>
       </c>
       <c r="AZ14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA14">
         <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>200</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI14">
         <v>2.08</v>
       </c>
       <c r="BJ14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK14">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BN14">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP14">
         <v>40</v>
       </c>
       <c r="BQ14">
-        <v>25</v>
+        <v>5.7</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BT14">
         <v>6.4</v>
       </c>
       <c r="BU14">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV14">
         <v>34</v>
       </c>
       <c r="BW14">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="CB14" t="s">
         <v>144</v>
@@ -4188,40 +4188,40 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G15">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H15">
         <v>5.1</v>
       </c>
       <c r="I15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J15">
         <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L15">
         <v>1.66</v>
       </c>
       <c r="M15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N15">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
         <v>1.65</v>
       </c>
       <c r="P15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q15">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="R15">
         <v>1.16</v>
@@ -4230,7 +4230,7 @@
         <v>6.4</v>
       </c>
       <c r="T15">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
         <v>1.63</v>
@@ -4239,19 +4239,19 @@
         <v>1.22</v>
       </c>
       <c r="W15">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X15">
         <v>7.8</v>
       </c>
       <c r="Y15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA15">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
         <v>5.8</v>
@@ -4263,10 +4263,10 @@
         <v>24</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF15">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -4275,7 +4275,7 @@
         <v>32</v>
       </c>
       <c r="AI15">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
         <v>24</v>
@@ -4287,19 +4287,19 @@
         <v>75</v>
       </c>
       <c r="AM15">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN15">
         <v>28</v>
       </c>
       <c r="AO15">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR15">
         <v>32</v>
@@ -4314,7 +4314,7 @@
         <v>7.4</v>
       </c>
       <c r="AV15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW15">
         <v>38</v>
@@ -4338,13 +4338,13 @@
         <v>26</v>
       </c>
       <c r="BD15">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BE15">
         <v>100</v>
       </c>
       <c r="BF15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BG15">
         <v>48</v>
@@ -4353,19 +4353,19 @@
         <v>2.54</v>
       </c>
       <c r="BI15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BK15">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN15">
         <v>4.2</v>
@@ -4374,19 +4374,19 @@
         <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BQ15">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT15">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU15">
         <v>7.6</v>
@@ -4395,19 +4395,19 @@
         <v>75</v>
       </c>
       <c r="BW15">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BX15">
         <v>110</v>
       </c>
       <c r="BY15">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ15">
         <v>55</v>
       </c>
       <c r="CA15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="s">
         <v>144</v>
@@ -4433,7 +4433,7 @@
         <v>1.71</v>
       </c>
       <c r="G16">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H16">
         <v>6</v>
@@ -4442,19 +4442,19 @@
         <v>6.4</v>
       </c>
       <c r="J16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M16">
         <v>1.09</v>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O16">
         <v>1.43</v>
@@ -4484,7 +4484,7 @@
         <v>2.32</v>
       </c>
       <c r="X16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y16">
         <v>17</v>
@@ -4502,7 +4502,7 @@
         <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -4541,10 +4541,10 @@
         <v>10</v>
       </c>
       <c r="AQ16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS16">
         <v>44</v>
@@ -4559,7 +4559,7 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AX16">
         <v>8.199999999999999</v>
@@ -4583,7 +4583,7 @@
         <v>38</v>
       </c>
       <c r="BE16">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF16">
         <v>12.5</v>
@@ -4592,22 +4592,22 @@
         <v>42</v>
       </c>
       <c r="BH16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BK16">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM16">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16">
         <v>4.1</v>
@@ -4616,40 +4616,40 @@
         <v>3.65</v>
       </c>
       <c r="BP16">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR16">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BS16">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
         <v>10</v>
       </c>
       <c r="BU16">
+        <v>8</v>
+      </c>
+      <c r="BV16">
+        <v>80</v>
+      </c>
+      <c r="BW16">
         <v>8.199999999999999</v>
       </c>
-      <c r="BV16">
-        <v>70</v>
-      </c>
-      <c r="BW16">
-        <v>11.5</v>
-      </c>
       <c r="BX16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY16">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="CA16">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>144</v>
@@ -4672,19 +4672,19 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G17">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H17">
         <v>2.88</v>
       </c>
       <c r="I17">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
         <v>3.9</v>
@@ -4714,7 +4714,7 @@
         <v>3.25</v>
       </c>
       <c r="T17">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U17">
         <v>2.24</v>
@@ -4726,10 +4726,10 @@
         <v>1.64</v>
       </c>
       <c r="X17">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z17">
         <v>22</v>
@@ -4762,7 +4762,7 @@
         <v>50</v>
       </c>
       <c r="AJ17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17">
         <v>26</v>
@@ -4774,7 +4774,7 @@
         <v>90</v>
       </c>
       <c r="AN17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO17">
         <v>32</v>
@@ -4789,7 +4789,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT17">
         <v>10</v>
@@ -4801,7 +4801,7 @@
         <v>11.5</v>
       </c>
       <c r="AW17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX17">
         <v>14.5</v>
@@ -4816,7 +4816,7 @@
         <v>28</v>
       </c>
       <c r="BB17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC17">
         <v>20</v>
@@ -4825,7 +4825,7 @@
         <v>28</v>
       </c>
       <c r="BE17">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF17">
         <v>16</v>
@@ -4858,7 +4858,7 @@
         <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ17">
         <v>3.9</v>
@@ -4879,13 +4879,13 @@
         <v>27</v>
       </c>
       <c r="BW17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BX17">
         <v>40</v>
       </c>
       <c r="BY17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ17">
         <v>30</v>
@@ -4914,19 +4914,19 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H18">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I18">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J18">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K18">
         <v>3.15</v>
@@ -5159,16 +5159,16 @@
         <v>1.59</v>
       </c>
       <c r="G19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I19">
         <v>8</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>4.3</v>
@@ -5186,19 +5186,19 @@
         <v>1.37</v>
       </c>
       <c r="P19">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q19">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
         <v>1.31</v>
       </c>
       <c r="S19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T19">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U19">
         <v>1.78</v>
@@ -5207,7 +5207,7 @@
         <v>1.15</v>
       </c>
       <c r="W19">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="X19">
         <v>13.5</v>
@@ -5216,22 +5216,22 @@
         <v>21</v>
       </c>
       <c r="Z19">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA19">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="AB19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC19">
         <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AE19">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -5240,28 +5240,28 @@
         <v>10.5</v>
       </c>
       <c r="AH19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI19">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="AJ19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK19">
         <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM19">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="AN19">
         <v>11.5</v>
       </c>
       <c r="AO19">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="AP19">
         <v>11</v>
@@ -5270,22 +5270,22 @@
         <v>17.5</v>
       </c>
       <c r="AR19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX19">
         <v>7.6</v>
@@ -5294,10 +5294,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA19">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB19">
         <v>12.5</v>
@@ -5306,13 +5306,13 @@
         <v>16</v>
       </c>
       <c r="BD19">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19">
         <v>9.4</v>
       </c>
       <c r="BF19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG19">
         <v>9.4</v>
@@ -5327,13 +5327,13 @@
         <v>12</v>
       </c>
       <c r="BK19">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN19">
         <v>4</v>
@@ -5345,7 +5345,7 @@
         <v>11</v>
       </c>
       <c r="BQ19">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BR19">
         <v>32</v>
@@ -5357,13 +5357,13 @@
         <v>11</v>
       </c>
       <c r="BU19">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX19">
         <v>1000</v>
@@ -5372,7 +5372,7 @@
         <v>10.5</v>
       </c>
       <c r="BZ19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA19">
         <v>8</v>
@@ -5401,13 +5401,13 @@
         <v>2.2</v>
       </c>
       <c r="G20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H20">
         <v>3.35</v>
       </c>
       <c r="I20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J20">
         <v>3.65</v>
@@ -5434,7 +5434,7 @@
         <v>1.91</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S20">
         <v>3.35</v>
@@ -5443,25 +5443,25 @@
         <v>1.73</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V20">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X20">
         <v>16</v>
       </c>
       <c r="Y20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA20">
-        <v>65</v>
+        <v>550</v>
       </c>
       <c r="AB20">
         <v>11</v>
@@ -5476,7 +5476,7 @@
         <v>42</v>
       </c>
       <c r="AF20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG20">
         <v>11.5</v>
@@ -5485,10 +5485,10 @@
         <v>18</v>
       </c>
       <c r="AI20">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AJ20">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK20">
         <v>24</v>
@@ -5506,7 +5506,7 @@
         <v>38</v>
       </c>
       <c r="AP20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20">
         <v>12</v>
@@ -5515,19 +5515,19 @@
         <v>21</v>
       </c>
       <c r="AS20">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AT20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU20">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV20">
         <v>12.5</v>
       </c>
       <c r="AW20">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AX20">
         <v>12.5</v>
@@ -5536,28 +5536,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ20">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA20">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BB20">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BC20">
         <v>20</v>
       </c>
       <c r="BD20">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BE20">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BF20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG20">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BH20">
         <v>3.6</v>
@@ -5569,16 +5569,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN20">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO20">
         <v>4.5</v>
@@ -5587,37 +5587,37 @@
         <v>17</v>
       </c>
       <c r="BQ20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR20">
         <v>30</v>
       </c>
       <c r="BS20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT20">
         <v>7</v>
       </c>
       <c r="BU20">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV20">
         <v>28</v>
       </c>
       <c r="BW20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX20">
         <v>40</v>
       </c>
       <c r="BY20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ20">
         <v>25</v>
       </c>
       <c r="CA20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB20" t="s">
         <v>144</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -448,7 +448,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-05 06:05:49</t>
+    <t>2026-10-05 08:16:12</t>
   </si>
 </sst>
 </file>
@@ -1042,10 +1042,10 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H2">
         <v>4.3</v>
@@ -1054,214 +1054,214 @@
         <v>5.1</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
         <v>4</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X2">
+        <v>970</v>
+      </c>
+      <c r="Y2">
+        <v>970</v>
+      </c>
+      <c r="Z2">
+        <v>48</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>10</v>
+      </c>
+      <c r="AC2">
+        <v>970</v>
+      </c>
+      <c r="AD2">
+        <v>950</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>12</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>950</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>36</v>
+      </c>
+      <c r="AK2">
+        <v>32</v>
+      </c>
+      <c r="AL2">
+        <v>85</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>19.5</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2">
+        <v>12.5</v>
+      </c>
+      <c r="AR2">
+        <v>20</v>
+      </c>
+      <c r="AS2">
+        <v>4.5</v>
+      </c>
+      <c r="AT2">
+        <v>7.8</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
         <v>13.5</v>
       </c>
-      <c r="Y2">
-        <v>16</v>
-      </c>
-      <c r="Z2">
-        <v>36</v>
-      </c>
-      <c r="AA2">
-        <v>130</v>
-      </c>
-      <c r="AB2">
-        <v>11</v>
-      </c>
-      <c r="AC2">
-        <v>9</v>
-      </c>
-      <c r="AD2">
-        <v>21</v>
-      </c>
-      <c r="AE2">
-        <v>80</v>
-      </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>90</v>
-      </c>
-      <c r="AJ2">
-        <v>27</v>
-      </c>
-      <c r="AK2">
-        <v>26</v>
-      </c>
-      <c r="AL2">
-        <v>50</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>21</v>
-      </c>
-      <c r="AO2">
-        <v>100</v>
-      </c>
-      <c r="AP2">
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
+      <c r="AW2">
+        <v>4.3</v>
+      </c>
+      <c r="AX2">
+        <v>9.6</v>
+      </c>
+      <c r="AY2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>14.5</v>
+      </c>
+      <c r="BA2">
+        <v>4.4</v>
+      </c>
+      <c r="BB2">
+        <v>19.5</v>
+      </c>
+      <c r="BC2">
+        <v>18.5</v>
+      </c>
+      <c r="BD2">
+        <v>4.2</v>
+      </c>
+      <c r="BE2">
         <v>4.5</v>
       </c>
-      <c r="AS2">
-        <v>4.9</v>
-      </c>
-      <c r="AT2">
-        <v>7.6</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
-        <v>15.5</v>
-      </c>
-      <c r="AW2">
-        <v>4.8</v>
-      </c>
-      <c r="AX2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY2">
-        <v>9</v>
-      </c>
-      <c r="AZ2">
-        <v>17.5</v>
-      </c>
-      <c r="BA2">
-        <v>4.8</v>
-      </c>
-      <c r="BB2">
-        <v>4.3</v>
-      </c>
-      <c r="BC2">
-        <v>4.3</v>
-      </c>
-      <c r="BD2">
-        <v>4.7</v>
-      </c>
-      <c r="BE2">
-        <v>5</v>
-      </c>
       <c r="BF2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH2">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
         <v>17</v>
       </c>
       <c r="BQ2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT2">
         <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV2">
         <v>48</v>
       </c>
       <c r="BW2">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2">
         <v>36</v>
       </c>
       <c r="CA2">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="s">
         <v>144</v>
@@ -1526,226 +1526,226 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="H4">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T4">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AA4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>36</v>
+      </c>
+      <c r="AK4">
+        <v>32</v>
+      </c>
+      <c r="AL4">
         <v>85</v>
       </c>
-      <c r="AJ4">
-        <v>38</v>
-      </c>
-      <c r="AK4">
-        <v>29</v>
-      </c>
-      <c r="AL4">
-        <v>42</v>
-      </c>
       <c r="AM4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AO4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
         <v>11</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR4">
         <v>19</v>
       </c>
       <c r="AS4">
-        <v>30</v>
+        <v>3.25</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4">
+        <v>15</v>
+      </c>
+      <c r="AW4">
+        <v>3.2</v>
+      </c>
+      <c r="AX4">
         <v>10.5</v>
       </c>
-      <c r="AW4">
+      <c r="AY4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4">
+        <v>2.78</v>
+      </c>
+      <c r="BA4">
+        <v>3.25</v>
+      </c>
+      <c r="BB4">
+        <v>20</v>
+      </c>
+      <c r="BC4">
+        <v>19</v>
+      </c>
+      <c r="BD4">
         <v>24</v>
       </c>
-      <c r="AX4">
-        <v>11.5</v>
-      </c>
-      <c r="AY4">
+      <c r="BE4">
+        <v>3.2</v>
+      </c>
+      <c r="BF4">
+        <v>13.5</v>
+      </c>
+      <c r="BG4">
+        <v>3.15</v>
+      </c>
+      <c r="BH4">
+        <v>3.4</v>
+      </c>
+      <c r="BI4">
+        <v>2.72</v>
+      </c>
+      <c r="BJ4">
+        <v>10.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
         <v>10</v>
       </c>
-      <c r="AZ4">
-        <v>15.5</v>
-      </c>
-      <c r="BA4">
+      <c r="BN4">
+        <v>4.8</v>
+      </c>
+      <c r="BO4">
+        <v>3.7</v>
+      </c>
+      <c r="BP4">
+        <v>15</v>
+      </c>
+      <c r="BQ4">
+        <v>6.2</v>
+      </c>
+      <c r="BR4">
         <v>32</v>
       </c>
-      <c r="BB4">
-        <v>23</v>
-      </c>
-      <c r="BC4">
-        <v>12</v>
-      </c>
-      <c r="BD4">
-        <v>27</v>
-      </c>
-      <c r="BE4">
-        <v>50</v>
-      </c>
-      <c r="BF4">
-        <v>21</v>
-      </c>
-      <c r="BG4">
-        <v>23</v>
-      </c>
-      <c r="BH4">
-        <v>3.25</v>
-      </c>
-      <c r="BI4">
-        <v>2.66</v>
-      </c>
-      <c r="BJ4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4">
-        <v>5.8</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>13</v>
-      </c>
-      <c r="BN4">
-        <v>5.4</v>
-      </c>
-      <c r="BO4">
-        <v>4.2</v>
-      </c>
-      <c r="BP4">
-        <v>19.5</v>
-      </c>
-      <c r="BQ4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4">
-        <v>36</v>
-      </c>
       <c r="BS4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA4">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="s">
         <v>144</v>
@@ -1768,22 +1768,22 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G5">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.3</v>
@@ -1792,142 +1792,142 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T5">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AF5">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.27</v>
+      </c>
+      <c r="AQ5">
+        <v>1.27</v>
+      </c>
+      <c r="AR5">
+        <v>20</v>
+      </c>
+      <c r="AS5">
+        <v>1.27</v>
+      </c>
+      <c r="AT5">
+        <v>1.27</v>
+      </c>
+      <c r="AU5">
+        <v>1.12</v>
+      </c>
+      <c r="AV5">
+        <v>1.27</v>
+      </c>
+      <c r="AW5">
+        <v>1.24</v>
+      </c>
+      <c r="AX5">
+        <v>1.27</v>
+      </c>
+      <c r="AY5">
+        <v>1.15</v>
+      </c>
+      <c r="AZ5">
+        <v>1.27</v>
+      </c>
+      <c r="BA5">
+        <v>1.27</v>
+      </c>
+      <c r="BB5">
+        <v>1.27</v>
+      </c>
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
+        <v>21</v>
+      </c>
+      <c r="BE5">
+        <v>1.27</v>
+      </c>
+      <c r="BF5">
+        <v>1.27</v>
+      </c>
+      <c r="BG5">
         <v>12.5</v>
-      </c>
-      <c r="AO5">
-        <v>26</v>
-      </c>
-      <c r="AP5">
-        <v>19</v>
-      </c>
-      <c r="AQ5">
-        <v>14.5</v>
-      </c>
-      <c r="AR5">
-        <v>21</v>
-      </c>
-      <c r="AS5">
-        <v>36</v>
-      </c>
-      <c r="AT5">
-        <v>11.5</v>
-      </c>
-      <c r="AU5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV5">
-        <v>12</v>
-      </c>
-      <c r="AW5">
-        <v>21</v>
-      </c>
-      <c r="AX5">
-        <v>14.5</v>
-      </c>
-      <c r="AY5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ5">
-        <v>13</v>
-      </c>
-      <c r="BA5">
-        <v>24</v>
-      </c>
-      <c r="BB5">
-        <v>21</v>
-      </c>
-      <c r="BC5">
-        <v>17.5</v>
-      </c>
-      <c r="BD5">
-        <v>22</v>
-      </c>
-      <c r="BE5">
-        <v>46</v>
-      </c>
-      <c r="BF5">
-        <v>10</v>
-      </c>
-      <c r="BG5">
-        <v>18.5</v>
       </c>
       <c r="BH5">
         <v>5</v>
@@ -2013,223 +2013,223 @@
         <v>1.33</v>
       </c>
       <c r="G6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>15</v>
       </c>
       <c r="J6">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
         <v>2.4</v>
       </c>
       <c r="Q6">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="R6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S6">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="T6">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
         <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="X6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU6">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD6">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6">
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BO6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BQ6">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
         <v>24</v>
       </c>
       <c r="BS6">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU6">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
+        <v>10</v>
+      </c>
+      <c r="BZ6">
         <v>12.5</v>
       </c>
-      <c r="BZ6">
-        <v>12</v>
-      </c>
       <c r="CA6">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="s">
         <v>144</v>
@@ -2252,22 +2252,22 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G7">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2276,13 +2276,13 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q7">
         <v>1.94</v>
@@ -2300,10 +2300,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2494,19 +2494,19 @@
         <v>131</v>
       </c>
       <c r="F8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I8">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="J8">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K8">
         <v>5.3</v>
@@ -2524,34 +2524,34 @@
         <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q8">
         <v>1.26</v>
       </c>
       <c r="R8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="S8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T8">
         <v>1.34</v>
       </c>
       <c r="U8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="V8">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Y8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z8">
         <v>23</v>
@@ -2563,16 +2563,16 @@
         <v>48</v>
       </c>
       <c r="AC8">
+        <v>16.5</v>
+      </c>
+      <c r="AD8">
+        <v>12</v>
+      </c>
+      <c r="AE8">
         <v>16</v>
       </c>
-      <c r="AD8">
-        <v>13</v>
-      </c>
-      <c r="AE8">
-        <v>16.5</v>
-      </c>
       <c r="AF8">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AG8">
         <v>22</v>
@@ -2581,58 +2581,58 @@
         <v>15</v>
       </c>
       <c r="AI8">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AJ8">
         <v>110</v>
       </c>
       <c r="AK8">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM8">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AN8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AP8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AQ8">
+        <v>23</v>
+      </c>
+      <c r="AR8">
+        <v>19</v>
+      </c>
+      <c r="AS8">
         <v>22</v>
       </c>
-      <c r="AR8">
-        <v>18.5</v>
-      </c>
-      <c r="AS8">
-        <v>20</v>
-      </c>
       <c r="AT8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV8">
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AY8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA8">
         <v>16</v>
@@ -2641,79 +2641,79 @@
         <v>55</v>
       </c>
       <c r="BC8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD8">
         <v>23</v>
       </c>
       <c r="BE8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BF8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG8">
         <v>4.1</v>
       </c>
       <c r="BH8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>144</v>
@@ -2736,226 +2736,226 @@
         <v>132</v>
       </c>
       <c r="F9">
+        <v>1.57</v>
+      </c>
+      <c r="G9">
+        <v>1.64</v>
+      </c>
+      <c r="H9">
+        <v>7.4</v>
+      </c>
+      <c r="I9">
+        <v>10.5</v>
+      </c>
+      <c r="J9">
+        <v>3.65</v>
+      </c>
+      <c r="K9">
+        <v>4.4</v>
+      </c>
+      <c r="L9">
+        <v>1.53</v>
+      </c>
+      <c r="M9">
+        <v>1.1</v>
+      </c>
+      <c r="N9">
+        <v>2.92</v>
+      </c>
+      <c r="O9">
+        <v>1.45</v>
+      </c>
+      <c r="P9">
+        <v>1.65</v>
+      </c>
+      <c r="Q9">
+        <v>2.36</v>
+      </c>
+      <c r="R9">
+        <v>1.23</v>
+      </c>
+      <c r="S9">
+        <v>4.7</v>
+      </c>
+      <c r="T9">
+        <v>2.26</v>
+      </c>
+      <c r="U9">
         <v>1.67</v>
       </c>
-      <c r="G9">
-        <v>1.76</v>
-      </c>
-      <c r="H9">
-        <v>6.6</v>
-      </c>
-      <c r="I9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J9">
-        <v>3.4</v>
-      </c>
-      <c r="K9">
-        <v>3.95</v>
-      </c>
-      <c r="L9">
-        <v>1.56</v>
-      </c>
-      <c r="M9">
+      <c r="V9">
         <v>1.11</v>
       </c>
-      <c r="N9">
-        <v>2.72</v>
-      </c>
-      <c r="O9">
-        <v>1.5</v>
-      </c>
-      <c r="P9">
-        <v>1.57</v>
-      </c>
-      <c r="Q9">
+      <c r="W9">
         <v>2.52</v>
       </c>
-      <c r="R9">
-        <v>1.19</v>
-      </c>
-      <c r="S9">
-        <v>5.2</v>
-      </c>
-      <c r="T9">
-        <v>2.34</v>
-      </c>
-      <c r="U9">
-        <v>1.6</v>
-      </c>
-      <c r="V9">
-        <v>1.14</v>
-      </c>
-      <c r="W9">
-        <v>2.3</v>
-      </c>
       <c r="X9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6.8</v>
+        <v>1.15</v>
       </c>
       <c r="AQ9">
-        <v>14</v>
+        <v>1.15</v>
       </c>
       <c r="AR9">
-        <v>5.2</v>
+        <v>1.15</v>
       </c>
       <c r="AS9">
-        <v>5.5</v>
+        <v>1.15</v>
       </c>
       <c r="AT9">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>7.4</v>
+        <v>1.15</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>1.15</v>
       </c>
       <c r="AW9">
-        <v>5.5</v>
+        <v>1.15</v>
       </c>
       <c r="AX9">
-        <v>7.2</v>
+        <v>1.15</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AZ9">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="BA9">
-        <v>5.5</v>
+        <v>1.15</v>
       </c>
       <c r="BB9">
-        <v>12.5</v>
+        <v>1.15</v>
       </c>
       <c r="BC9">
-        <v>20</v>
+        <v>1.15</v>
       </c>
       <c r="BD9">
-        <v>5.2</v>
+        <v>1.15</v>
       </c>
       <c r="BE9">
-        <v>5.5</v>
+        <v>1.15</v>
       </c>
       <c r="BF9">
-        <v>14.5</v>
+        <v>1.15</v>
       </c>
       <c r="BG9">
-        <v>5.5</v>
+        <v>1.15</v>
       </c>
       <c r="BH9">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.28</v>
+        <v>1.3</v>
       </c>
       <c r="BJ9">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>144</v>
@@ -2978,13 +2978,13 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10">
         <v>4.5</v>
@@ -3002,67 +3002,67 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O10">
         <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q10">
         <v>1.99</v>
       </c>
       <c r="R10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S10">
         <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z10">
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE10">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AF10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
         <v>65</v>
@@ -3071,133 +3071,133 @@
         <v>23</v>
       </c>
       <c r="AK10">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AL10">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM10">
         <v>110</v>
       </c>
       <c r="AN10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO10">
         <v>60</v>
       </c>
       <c r="AP10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10">
         <v>14</v>
       </c>
       <c r="AR10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS10">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AT10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU10">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AW10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX10">
         <v>11</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BB10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD10">
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BF10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG10">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BH10">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>4.6</v>
+        <v>2.28</v>
       </c>
       <c r="BL10">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="BN10">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BO10">
-        <v>4.2</v>
+        <v>1.77</v>
       </c>
       <c r="BP10">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>5.4</v>
+        <v>2.64</v>
       </c>
       <c r="BR10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>6.2</v>
+        <v>2.64</v>
       </c>
       <c r="BT10">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="BV10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>6.4</v>
+        <v>2.64</v>
       </c>
       <c r="BX10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>6.6</v>
+        <v>2.64</v>
       </c>
       <c r="BZ10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="CB10" t="s">
         <v>144</v>
@@ -3220,226 +3220,226 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="H11">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="I11">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L11">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
         <v>1.53</v>
       </c>
       <c r="S11">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T11">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V11">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="W11">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="AA11">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AB11">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD11">
         <v>10.5</v>
       </c>
       <c r="AE11">
+        <v>220</v>
+      </c>
+      <c r="AF11">
+        <v>40</v>
+      </c>
+      <c r="AG11">
         <v>19</v>
       </c>
-      <c r="AF11">
-        <v>32</v>
-      </c>
-      <c r="AG11">
-        <v>16</v>
-      </c>
       <c r="AH11">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="AI11">
         <v>32</v>
       </c>
       <c r="AJ11">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK11">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM11">
         <v>80</v>
       </c>
       <c r="AN11">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AO11">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT11">
-        <v>17</v>
+        <v>4.9</v>
       </c>
       <c r="AU11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>3.95</v>
       </c>
       <c r="AW11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11">
-        <v>26</v>
+        <v>5.5</v>
       </c>
       <c r="AY11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ11">
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
-        <v>60</v>
+        <v>6.2</v>
       </c>
       <c r="BC11">
-        <v>36</v>
+        <v>5.7</v>
       </c>
       <c r="BD11">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE11">
-        <v>55</v>
+        <v>5.9</v>
       </c>
       <c r="BF11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BG11">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>144</v>
@@ -3471,7 +3471,7 @@
         <v>5.2</v>
       </c>
       <c r="I12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
         <v>3.2</v>
@@ -3480,10 +3480,10 @@
         <v>3.3</v>
       </c>
       <c r="L12">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N12">
         <v>2.54</v>
@@ -3495,16 +3495,16 @@
         <v>1.49</v>
       </c>
       <c r="Q12">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
         <v>6.6</v>
       </c>
       <c r="T12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U12">
         <v>1.66</v>
@@ -3516,13 +3516,13 @@
         <v>2.02</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3534,37 +3534,37 @@
         <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AJ12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AM12">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AN12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO12">
         <v>1000</v>
@@ -3573,25 +3573,25 @@
         <v>7.4</v>
       </c>
       <c r="AQ12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AS12">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AT12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW12">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX12">
         <v>9</v>
@@ -3600,31 +3600,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA12">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="BB12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE12">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BF12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG12">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BH12">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BI12">
         <v>2.42</v>
@@ -3633,34 +3633,34 @@
         <v>15.5</v>
       </c>
       <c r="BK12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BN12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP12">
         <v>19.5</v>
       </c>
       <c r="BQ12">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BR12">
         <v>55</v>
       </c>
       <c r="BS12">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU12">
         <v>7.6</v>
@@ -3669,19 +3669,19 @@
         <v>80</v>
       </c>
       <c r="BW12">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BX12">
         <v>110</v>
       </c>
       <c r="BY12">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12">
         <v>60</v>
       </c>
       <c r="CA12">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="s">
         <v>144</v>
@@ -3704,10 +3704,10 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G13">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H13">
         <v>4.6</v>
@@ -3716,37 +3716,37 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
         <v>1.43</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P13">
         <v>1.9</v>
       </c>
       <c r="Q13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T13">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -3755,28 +3755,28 @@
         <v>1.25</v>
       </c>
       <c r="W13">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X13">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Y13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z13">
         <v>38</v>
       </c>
       <c r="AA13">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB13">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC13">
         <v>8.4</v>
       </c>
       <c r="AD13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE13">
         <v>70</v>
@@ -3794,94 +3794,94 @@
         <v>75</v>
       </c>
       <c r="AJ13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK13">
         <v>22</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO13">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR13">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS13">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="AT13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW13">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="AX13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA13">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB13">
         <v>18</v>
       </c>
       <c r="BC13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD13">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BE13">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BF13">
         <v>12</v>
       </c>
       <c r="BG13">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI13">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN13">
         <v>4.7</v>
@@ -3893,10 +3893,10 @@
         <v>14</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS13">
         <v>7.8</v>
@@ -3905,7 +3905,7 @@
         <v>8.4</v>
       </c>
       <c r="BU13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV13">
         <v>44</v>
@@ -3917,13 +3917,13 @@
         <v>55</v>
       </c>
       <c r="BY13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>27</v>
       </c>
       <c r="CA13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="s">
         <v>144</v>
@@ -3949,10 +3949,10 @@
         <v>3.1</v>
       </c>
       <c r="G14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H14">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I14">
         <v>3.1</v>
@@ -3961,7 +3961,7 @@
         <v>2.68</v>
       </c>
       <c r="K14">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="L14">
         <v>1.71</v>
@@ -3973,7 +3973,7 @@
         <v>2.26</v>
       </c>
       <c r="O14">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="P14">
         <v>1.4</v>
@@ -3982,13 +3982,13 @@
         <v>3.25</v>
       </c>
       <c r="R14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S14">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="T14">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
         <v>1.59</v>
@@ -4000,112 +4000,112 @@
         <v>1.4</v>
       </c>
       <c r="X14">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="AD14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>5.4</v>
+        <v>1.16</v>
       </c>
       <c r="AQ14">
-        <v>6</v>
+        <v>1.35</v>
       </c>
       <c r="AR14">
-        <v>13</v>
+        <v>1.35</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AT14">
-        <v>6.6</v>
+        <v>1.35</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>1.35</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AX14">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="AY14">
-        <v>12</v>
+        <v>1.35</v>
       </c>
       <c r="AZ14">
-        <v>21</v>
+        <v>1.35</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BH14">
         <v>2.66</v>
@@ -4117,55 +4117,55 @@
         <v>14.5</v>
       </c>
       <c r="BK14">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BN14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP14">
         <v>40</v>
       </c>
       <c r="BQ14">
+        <v>5.4</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
         <v>5.7</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>6</v>
       </c>
       <c r="BT14">
         <v>6.4</v>
       </c>
       <c r="BU14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV14">
         <v>34</v>
       </c>
       <c r="BW14">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB14" t="s">
         <v>144</v>
@@ -4188,16 +4188,16 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G15">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H15">
         <v>5.1</v>
       </c>
       <c r="I15">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J15">
         <v>3.3</v>
@@ -4206,7 +4206,7 @@
         <v>3.4</v>
       </c>
       <c r="L15">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M15">
         <v>1.14</v>
@@ -4215,31 +4215,31 @@
         <v>2.5</v>
       </c>
       <c r="O15">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P15">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R15">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S15">
         <v>6.4</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V15">
         <v>1.22</v>
       </c>
       <c r="W15">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X15">
         <v>7.8</v>
@@ -4248,7 +4248,7 @@
         <v>12.5</v>
       </c>
       <c r="Z15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4260,37 +4260,37 @@
         <v>8</v>
       </c>
       <c r="AD15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE15">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
       </c>
       <c r="AH15">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK15">
+        <v>34</v>
+      </c>
+      <c r="AL15">
+        <v>990</v>
+      </c>
+      <c r="AM15">
+        <v>270</v>
+      </c>
+      <c r="AN15">
         <v>30</v>
-      </c>
-      <c r="AL15">
-        <v>75</v>
-      </c>
-      <c r="AM15">
-        <v>320</v>
-      </c>
-      <c r="AN15">
-        <v>28</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4305,7 +4305,7 @@
         <v>32</v>
       </c>
       <c r="AS15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT15">
         <v>5.5</v>
@@ -4314,19 +4314,19 @@
         <v>7.4</v>
       </c>
       <c r="AV15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW15">
         <v>38</v>
       </c>
       <c r="AX15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY15">
         <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA15">
         <v>44</v>
@@ -4335,79 +4335,79 @@
         <v>20</v>
       </c>
       <c r="BC15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15">
         <v>44</v>
       </c>
       <c r="BE15">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="BF15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH15">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BI15">
         <v>2.42</v>
       </c>
       <c r="BJ15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK15">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
         <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ15">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR15">
         <v>55</v>
       </c>
       <c r="BS15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT15">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV15">
         <v>75</v>
       </c>
       <c r="BW15">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BX15">
         <v>110</v>
       </c>
       <c r="BY15">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15">
         <v>55</v>
       </c>
       <c r="CA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB15" t="s">
         <v>144</v>
@@ -4433,28 +4433,28 @@
         <v>1.71</v>
       </c>
       <c r="G16">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H16">
         <v>6</v>
       </c>
       <c r="I16">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
         <v>3.8</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M16">
         <v>1.09</v>
       </c>
       <c r="N16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
         <v>1.43</v>
@@ -4463,10 +4463,10 @@
         <v>1.73</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S16">
         <v>4.5</v>
@@ -4484,13 +4484,13 @@
         <v>2.32</v>
       </c>
       <c r="X16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y16">
         <v>17</v>
       </c>
       <c r="Z16">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AA16">
         <v>1000</v>
@@ -4502,37 +4502,37 @@
         <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE16">
         <v>1000</v>
       </c>
       <c r="AF16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG16">
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AI16">
         <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL16">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM16">
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4541,10 +4541,10 @@
         <v>10</v>
       </c>
       <c r="AQ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS16">
         <v>44</v>
@@ -4559,7 +4559,7 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AX16">
         <v>8.199999999999999</v>
@@ -4571,7 +4571,7 @@
         <v>21</v>
       </c>
       <c r="BA16">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BB16">
         <v>15.5</v>
@@ -4580,76 +4580,76 @@
         <v>18</v>
       </c>
       <c r="BD16">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BE16">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BF16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG16">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH16">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="BJ16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="BL16">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>8.800000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="BN16">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="BP16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="BR16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="BT16">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BV16">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="BX16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>8.199999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="BZ16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>1.33</v>
       </c>
       <c r="CB16" t="s">
         <v>144</v>
@@ -4672,16 +4672,16 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G17">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H17">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J17">
         <v>3.65</v>
@@ -4702,10 +4702,10 @@
         <v>1.29</v>
       </c>
       <c r="P17">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q17">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R17">
         <v>1.41</v>
@@ -4717,121 +4717,121 @@
         <v>1.71</v>
       </c>
       <c r="U17">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X17">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="Y17">
+        <v>15.5</v>
+      </c>
+      <c r="Z17">
+        <v>24</v>
+      </c>
+      <c r="AA17">
+        <v>70</v>
+      </c>
+      <c r="AB17">
+        <v>13.5</v>
+      </c>
+      <c r="AC17">
+        <v>9.6</v>
+      </c>
+      <c r="AD17">
+        <v>17</v>
+      </c>
+      <c r="AE17">
+        <v>55</v>
+      </c>
+      <c r="AF17">
+        <v>23</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>23</v>
+      </c>
+      <c r="AI17">
+        <v>70</v>
+      </c>
+      <c r="AJ17">
+        <v>260</v>
+      </c>
+      <c r="AK17">
+        <v>200</v>
+      </c>
+      <c r="AL17">
+        <v>220</v>
+      </c>
+      <c r="AM17">
+        <v>140</v>
+      </c>
+      <c r="AN17">
+        <v>32</v>
+      </c>
+      <c r="AO17">
+        <v>38</v>
+      </c>
+      <c r="AP17">
         <v>14</v>
       </c>
-      <c r="Z17">
-        <v>22</v>
-      </c>
-      <c r="AA17">
-        <v>55</v>
-      </c>
-      <c r="AB17">
-        <v>13</v>
-      </c>
-      <c r="AC17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD17">
-        <v>14</v>
-      </c>
-      <c r="AE17">
-        <v>34</v>
-      </c>
-      <c r="AF17">
-        <v>17.5</v>
-      </c>
-      <c r="AG17">
-        <v>12</v>
-      </c>
-      <c r="AH17">
-        <v>17.5</v>
-      </c>
-      <c r="AI17">
-        <v>50</v>
-      </c>
-      <c r="AJ17">
-        <v>36</v>
-      </c>
-      <c r="AK17">
-        <v>26</v>
-      </c>
-      <c r="AL17">
-        <v>36</v>
-      </c>
-      <c r="AM17">
-        <v>90</v>
-      </c>
-      <c r="AN17">
-        <v>22</v>
-      </c>
-      <c r="AO17">
-        <v>32</v>
-      </c>
-      <c r="AP17">
-        <v>14.5</v>
-      </c>
       <c r="AQ17">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AS17">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AT17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV17">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX17">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA17">
         <v>28</v>
       </c>
       <c r="BB17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD17">
         <v>28</v>
       </c>
       <c r="BE17">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BF17">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BG17">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="BH17">
         <v>4.2</v>
@@ -4876,7 +4876,7 @@
         <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW17">
         <v>3.95</v>
@@ -4885,7 +4885,7 @@
         <v>40</v>
       </c>
       <c r="BY17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ17">
         <v>30</v>
@@ -4917,16 +4917,16 @@
         <v>2.86</v>
       </c>
       <c r="G18">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H18">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I18">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J18">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="K18">
         <v>3.15</v>
@@ -5159,13 +5159,13 @@
         <v>1.59</v>
       </c>
       <c r="G19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -5180,7 +5180,7 @@
         <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O19">
         <v>1.37</v>
@@ -5189,7 +5189,7 @@
         <v>1.86</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R19">
         <v>1.31</v>
@@ -5198,82 +5198,82 @@
         <v>3.9</v>
       </c>
       <c r="T19">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U19">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="V19">
         <v>1.15</v>
       </c>
       <c r="W19">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="X19">
         <v>13.5</v>
       </c>
       <c r="Y19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z19">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AA19">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AB19">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC19">
         <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE19">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="AF19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG19">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
         <v>27</v>
       </c>
       <c r="AI19">
-        <v>420</v>
+        <v>310</v>
       </c>
       <c r="AJ19">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK19">
         <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AN19">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO19">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="AP19">
         <v>11</v>
       </c>
       <c r="AQ19">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR19">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS19">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT19">
         <v>6.2</v>
@@ -5282,100 +5282,100 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AW19">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX19">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ19">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BA19">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB19">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC19">
         <v>16</v>
       </c>
       <c r="BD19">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE19">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF19">
         <v>9.4</v>
       </c>
       <c r="BG19">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH19">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI19">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ19">
         <v>12</v>
       </c>
       <c r="BK19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO19">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BP19">
         <v>11</v>
       </c>
       <c r="BQ19">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR19">
         <v>32</v>
       </c>
       <c r="BS19">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT19">
         <v>11</v>
       </c>
       <c r="BU19">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA19">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB19" t="s">
         <v>144</v>
@@ -5398,22 +5398,22 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G20">
         <v>2.28</v>
       </c>
       <c r="H20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I20">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J20">
         <v>3.65</v>
       </c>
       <c r="K20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L20">
         <v>1.39</v>
@@ -5428,22 +5428,22 @@
         <v>1.3</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q20">
         <v>1.91</v>
       </c>
       <c r="R20">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S20">
         <v>3.35</v>
       </c>
       <c r="T20">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
         <v>1.4</v>
@@ -5452,7 +5452,7 @@
         <v>1.78</v>
       </c>
       <c r="X20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y20">
         <v>14</v>
@@ -5461,7 +5461,7 @@
         <v>25</v>
       </c>
       <c r="AA20">
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="AB20">
         <v>11</v>
@@ -5470,88 +5470,88 @@
         <v>8.4</v>
       </c>
       <c r="AD20">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE20">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AF20">
         <v>15</v>
       </c>
       <c r="AG20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI20">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ20">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AK20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL20">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AM20">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO20">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AP20">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20">
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AS20">
         <v>40</v>
       </c>
       <c r="AT20">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>12.5</v>
       </c>
       <c r="AW20">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY20">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20">
+        <v>15</v>
+      </c>
+      <c r="BA20">
+        <v>32</v>
+      </c>
+      <c r="BB20">
+        <v>19</v>
+      </c>
+      <c r="BC20">
         <v>16</v>
       </c>
-      <c r="BA20">
-        <v>30</v>
-      </c>
-      <c r="BB20">
-        <v>21</v>
-      </c>
-      <c r="BC20">
-        <v>20</v>
-      </c>
       <c r="BD20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE20">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BF20">
         <v>14.5</v>
@@ -5560,28 +5560,28 @@
         <v>22</v>
       </c>
       <c r="BH20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20">
         <v>9.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN20">
         <v>5.2</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP20">
         <v>17</v>
@@ -5593,31 +5593,31 @@
         <v>30</v>
       </c>
       <c r="BS20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT20">
         <v>7</v>
       </c>
       <c r="BU20">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV20">
         <v>28</v>
       </c>
       <c r="BW20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX20">
         <v>40</v>
       </c>
       <c r="BY20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB20" t="s">
         <v>144</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-05.xlsx
@@ -448,7 +448,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-10-05 08:16:12</t>
+    <t>2026-10-05 10:27:43</t>
   </si>
 </sst>
 </file>
@@ -1042,226 +1042,226 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I2">
+        <v>5.3</v>
+      </c>
+      <c r="J2">
+        <v>2.88</v>
+      </c>
+      <c r="K2">
+        <v>3.05</v>
+      </c>
+      <c r="L2">
+        <v>2.56</v>
+      </c>
+      <c r="M2">
+        <v>1.18</v>
+      </c>
+      <c r="N2">
+        <v>2.14</v>
+      </c>
+      <c r="O2">
+        <v>1.87</v>
+      </c>
+      <c r="P2">
+        <v>1.32</v>
+      </c>
+      <c r="Q2">
+        <v>3.85</v>
+      </c>
+      <c r="R2">
+        <v>1.1</v>
+      </c>
+      <c r="S2">
+        <v>9.4</v>
+      </c>
+      <c r="T2">
+        <v>2.72</v>
+      </c>
+      <c r="U2">
+        <v>1.44</v>
+      </c>
+      <c r="V2">
+        <v>1.23</v>
+      </c>
+      <c r="W2">
+        <v>1.8</v>
+      </c>
+      <c r="X2">
+        <v>6.4</v>
+      </c>
+      <c r="Y2">
+        <v>10.5</v>
+      </c>
+      <c r="Z2">
+        <v>38</v>
+      </c>
+      <c r="AA2">
+        <v>190</v>
+      </c>
+      <c r="AB2">
+        <v>5.9</v>
+      </c>
+      <c r="AC2">
+        <v>7.4</v>
+      </c>
+      <c r="AD2">
+        <v>32</v>
+      </c>
+      <c r="AE2">
+        <v>160</v>
+      </c>
+      <c r="AF2">
+        <v>10.5</v>
+      </c>
+      <c r="AG2">
+        <v>14</v>
+      </c>
+      <c r="AH2">
+        <v>50</v>
+      </c>
+      <c r="AI2">
+        <v>260</v>
+      </c>
+      <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>140</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>70</v>
+      </c>
+      <c r="AO2">
+        <v>450</v>
+      </c>
+      <c r="AP2">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2">
+        <v>8.6</v>
+      </c>
+      <c r="AR2">
+        <v>25</v>
+      </c>
+      <c r="AS2">
+        <v>110</v>
+      </c>
+      <c r="AT2">
         <v>5.1</v>
-      </c>
-      <c r="J2">
-        <v>3.4</v>
-      </c>
-      <c r="K2">
-        <v>3.7</v>
-      </c>
-      <c r="L2">
-        <v>1.45</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.4</v>
-      </c>
-      <c r="O2">
-        <v>1.37</v>
-      </c>
-      <c r="P2">
-        <v>1.8</v>
-      </c>
-      <c r="Q2">
-        <v>2.14</v>
-      </c>
-      <c r="R2">
-        <v>1.29</v>
-      </c>
-      <c r="S2">
-        <v>4</v>
-      </c>
-      <c r="T2">
-        <v>1.91</v>
-      </c>
-      <c r="U2">
-        <v>2</v>
-      </c>
-      <c r="V2">
-        <v>1.25</v>
-      </c>
-      <c r="W2">
-        <v>1.96</v>
-      </c>
-      <c r="X2">
-        <v>970</v>
-      </c>
-      <c r="Y2">
-        <v>970</v>
-      </c>
-      <c r="Z2">
-        <v>48</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>10</v>
-      </c>
-      <c r="AC2">
-        <v>970</v>
-      </c>
-      <c r="AD2">
-        <v>950</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>12</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>950</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>36</v>
-      </c>
-      <c r="AK2">
-        <v>32</v>
-      </c>
-      <c r="AL2">
-        <v>85</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>19.5</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>12.5</v>
-      </c>
-      <c r="AR2">
-        <v>20</v>
-      </c>
-      <c r="AS2">
-        <v>4.5</v>
-      </c>
-      <c r="AT2">
-        <v>7.8</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>4.3</v>
+        <v>85</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BA2">
-        <v>4.4</v>
+        <v>140</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BD2">
-        <v>4.2</v>
+        <v>90</v>
       </c>
       <c r="BE2">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BG2">
-        <v>4.5</v>
+        <v>170</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BK2">
+        <v>27</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>13</v>
+      </c>
+      <c r="BN2">
+        <v>5.4</v>
+      </c>
+      <c r="BO2">
+        <v>4.6</v>
+      </c>
+      <c r="BP2">
+        <v>50</v>
+      </c>
+      <c r="BQ2">
+        <v>36</v>
+      </c>
+      <c r="BR2">
+        <v>910</v>
+      </c>
+      <c r="BS2">
+        <v>140</v>
+      </c>
+      <c r="BT2">
+        <v>11.5</v>
+      </c>
+      <c r="BU2">
         <v>8.4</v>
       </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>7.4</v>
-      </c>
-      <c r="BN2">
-        <v>4.7</v>
-      </c>
-      <c r="BO2">
-        <v>3.95</v>
-      </c>
-      <c r="BP2">
-        <v>17</v>
-      </c>
-      <c r="BQ2">
-        <v>5.5</v>
-      </c>
-      <c r="BR2">
-        <v>38</v>
-      </c>
-      <c r="BS2">
-        <v>6.4</v>
-      </c>
-      <c r="BT2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU2">
-        <v>6.6</v>
-      </c>
       <c r="BV2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>90</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="BY2">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>960</v>
       </c>
       <c r="CA2">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>144</v>
@@ -1359,7 +1359,7 @@
         <v>1000</v>
       </c>
       <c r="AE3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
         <v>1000</v>
@@ -1392,22 +1392,22 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AV3">
         <v>2.44</v>
@@ -1416,7 +1416,7 @@
         <v>1.59</v>
       </c>
       <c r="AX3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
         <v>3</v>
@@ -1425,22 +1425,22 @@
         <v>2.02</v>
       </c>
       <c r="BA3">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.05</v>
+        <v>1.46</v>
       </c>
       <c r="BD3">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BG3">
         <v>3.95</v>
@@ -1526,226 +1526,226 @@
         <v>127</v>
       </c>
       <c r="F4">
+        <v>2.02</v>
+      </c>
+      <c r="G4">
+        <v>2.1</v>
+      </c>
+      <c r="H4">
+        <v>4.3</v>
+      </c>
+      <c r="I4">
+        <v>4.5</v>
+      </c>
+      <c r="J4">
+        <v>3.35</v>
+      </c>
+      <c r="K4">
+        <v>3.55</v>
+      </c>
+      <c r="L4">
+        <v>1.49</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
+        <v>3.15</v>
+      </c>
+      <c r="O4">
+        <v>1.43</v>
+      </c>
+      <c r="P4">
+        <v>1.72</v>
+      </c>
+      <c r="Q4">
+        <v>2.24</v>
+      </c>
+      <c r="R4">
+        <v>1.26</v>
+      </c>
+      <c r="S4">
+        <v>4.2</v>
+      </c>
+      <c r="T4">
         <v>1.99</v>
       </c>
-      <c r="G4">
-        <v>2.08</v>
-      </c>
-      <c r="H4">
-        <v>4.1</v>
-      </c>
-      <c r="I4">
-        <v>4.6</v>
-      </c>
-      <c r="J4">
-        <v>3.45</v>
-      </c>
-      <c r="K4">
-        <v>3.9</v>
-      </c>
-      <c r="L4">
-        <v>1.42</v>
-      </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>3.3</v>
-      </c>
-      <c r="O4">
-        <v>1.37</v>
-      </c>
-      <c r="P4">
-        <v>1.81</v>
-      </c>
-      <c r="Q4">
-        <v>2.06</v>
-      </c>
-      <c r="R4">
-        <v>1.31</v>
-      </c>
-      <c r="S4">
-        <v>3.8</v>
-      </c>
-      <c r="T4">
-        <v>1.85</v>
-      </c>
       <c r="U4">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X4">
+        <v>11.5</v>
+      </c>
+      <c r="Y4">
         <v>13.5</v>
-      </c>
-      <c r="Y4">
-        <v>15</v>
       </c>
       <c r="Z4">
         <v>34</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>19</v>
       </c>
       <c r="AE4">
+        <v>85</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>22</v>
+      </c>
+      <c r="AI4">
+        <v>95</v>
+      </c>
+      <c r="AJ4">
+        <v>25</v>
+      </c>
+      <c r="AK4">
+        <v>25</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>520</v>
+      </c>
+      <c r="AN4">
+        <v>19</v>
+      </c>
+      <c r="AO4">
         <v>120</v>
       </c>
-      <c r="AF4">
-        <v>14</v>
-      </c>
-      <c r="AG4">
-        <v>970</v>
-      </c>
-      <c r="AH4">
-        <v>21</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>36</v>
-      </c>
-      <c r="AK4">
-        <v>32</v>
-      </c>
-      <c r="AL4">
-        <v>85</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>17</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
       <c r="AP4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AS4">
-        <v>3.25</v>
+        <v>65</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>3.2</v>
+        <v>40</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>2.78</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>3.25</v>
+        <v>46</v>
       </c>
       <c r="BB4">
         <v>20</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE4">
-        <v>3.2</v>
+        <v>90</v>
       </c>
       <c r="BF4">
+        <v>16</v>
+      </c>
+      <c r="BG4">
+        <v>50</v>
+      </c>
+      <c r="BH4">
+        <v>3.1</v>
+      </c>
+      <c r="BI4">
+        <v>2.8</v>
+      </c>
+      <c r="BJ4">
+        <v>11</v>
+      </c>
+      <c r="BK4">
+        <v>9</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
         <v>13.5</v>
       </c>
-      <c r="BG4">
-        <v>3.15</v>
-      </c>
-      <c r="BH4">
-        <v>3.4</v>
-      </c>
-      <c r="BI4">
-        <v>2.72</v>
-      </c>
-      <c r="BJ4">
-        <v>10.5</v>
-      </c>
-      <c r="BK4">
-        <v>5.3</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>10</v>
-      </c>
       <c r="BN4">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP4">
         <v>15</v>
       </c>
       <c r="BQ4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
+        <v>34</v>
+      </c>
+      <c r="BS4">
+        <v>10</v>
+      </c>
+      <c r="BT4">
+        <v>7.8</v>
+      </c>
+      <c r="BU4">
+        <v>6.6</v>
+      </c>
+      <c r="BV4">
+        <v>60</v>
+      </c>
+      <c r="BW4">
+        <v>11</v>
+      </c>
+      <c r="BX4">
+        <v>60</v>
+      </c>
+      <c r="BY4">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4">
         <v>32</v>
       </c>
-      <c r="BS4">
-        <v>8</v>
-      </c>
-      <c r="BT4">
-        <v>8</v>
-      </c>
-      <c r="BU4">
-        <v>6</v>
-      </c>
-      <c r="BV4">
-        <v>40</v>
-      </c>
-      <c r="BW4">
-        <v>8.4</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ4">
-        <v>28</v>
-      </c>
       <c r="CA4">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>144</v>
@@ -1768,22 +1768,22 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G5">
         <v>2.4</v>
       </c>
       <c r="H5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.3</v>
@@ -1795,199 +1795,199 @@
         <v>5.5</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
+        <v>1.6</v>
+      </c>
+      <c r="S5">
+        <v>2.56</v>
+      </c>
+      <c r="T5">
         <v>1.58</v>
       </c>
-      <c r="S5">
-        <v>2.6</v>
-      </c>
-      <c r="T5">
-        <v>1.5</v>
-      </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
+        <v>42</v>
+      </c>
+      <c r="AF5">
+        <v>18</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>16</v>
+      </c>
+      <c r="AI5">
+        <v>48</v>
+      </c>
+      <c r="AJ5">
+        <v>36</v>
+      </c>
+      <c r="AK5">
+        <v>23</v>
+      </c>
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>70</v>
+      </c>
+      <c r="AN5">
+        <v>12.5</v>
+      </c>
+      <c r="AO5">
+        <v>25</v>
+      </c>
+      <c r="AP5">
+        <v>20</v>
+      </c>
+      <c r="AQ5">
+        <v>15</v>
+      </c>
+      <c r="AR5">
+        <v>21</v>
+      </c>
+      <c r="AS5">
+        <v>34</v>
+      </c>
+      <c r="AT5">
+        <v>12.5</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>11.5</v>
+      </c>
+      <c r="AW5">
+        <v>23</v>
+      </c>
+      <c r="AX5">
+        <v>15</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>13</v>
+      </c>
+      <c r="BA5">
+        <v>26</v>
+      </c>
+      <c r="BB5">
+        <v>25</v>
+      </c>
+      <c r="BC5">
+        <v>18</v>
+      </c>
+      <c r="BD5">
+        <v>22</v>
+      </c>
+      <c r="BE5">
         <v>46</v>
       </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>970</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>1.27</v>
-      </c>
-      <c r="AQ5">
-        <v>1.27</v>
-      </c>
-      <c r="AR5">
-        <v>20</v>
-      </c>
-      <c r="AS5">
-        <v>1.27</v>
-      </c>
-      <c r="AT5">
-        <v>1.27</v>
-      </c>
-      <c r="AU5">
-        <v>1.12</v>
-      </c>
-      <c r="AV5">
-        <v>1.27</v>
-      </c>
-      <c r="AW5">
-        <v>1.24</v>
-      </c>
-      <c r="AX5">
-        <v>1.27</v>
-      </c>
-      <c r="AY5">
-        <v>1.15</v>
-      </c>
-      <c r="AZ5">
-        <v>1.27</v>
-      </c>
-      <c r="BA5">
-        <v>1.27</v>
-      </c>
-      <c r="BB5">
-        <v>1.27</v>
-      </c>
-      <c r="BC5">
-        <v>15.5</v>
-      </c>
-      <c r="BD5">
-        <v>21</v>
-      </c>
-      <c r="BE5">
-        <v>1.27</v>
-      </c>
       <c r="BF5">
-        <v>1.27</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BH5">
         <v>5</v>
       </c>
       <c r="BI5">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BN5">
         <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
         <v>18</v>
       </c>
       <c r="BQ5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BR5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
         <v>27</v>
       </c>
       <c r="BW5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB5" t="s">
         <v>144</v>
@@ -2013,19 +2013,19 @@
         <v>1.33</v>
       </c>
       <c r="G6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
         <v>1.3</v>
@@ -2034,19 +2034,19 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O6">
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
         <v>2.58</v>
@@ -2055,121 +2055,121 @@
         <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT6">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB6">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF6">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH6">
         <v>4.3</v>
@@ -2181,55 +2181,55 @@
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO6">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BP6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR6">
         <v>24</v>
       </c>
       <c r="BS6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT6">
         <v>14.5</v>
       </c>
       <c r="BU6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>144</v>
@@ -2252,22 +2252,22 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G7">
         <v>2.04</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J7">
         <v>3.4</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2282,16 +2282,16 @@
         <v>1.3</v>
       </c>
       <c r="P7">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2300,7 +2300,7 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
         <v>1.96</v>
@@ -2497,22 +2497,22 @@
         <v>4.2</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I8">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J8">
         <v>5.1</v>
       </c>
       <c r="K8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L8">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2536,25 +2536,25 @@
         <v>1.66</v>
       </c>
       <c r="T8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="U8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="V8">
         <v>2.34</v>
       </c>
       <c r="W8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X8">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="Y8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA8">
         <v>26</v>
@@ -2563,40 +2563,40 @@
         <v>48</v>
       </c>
       <c r="AC8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
         <v>16</v>
       </c>
       <c r="AF8">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AJ8">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AK8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL8">
         <v>32</v>
       </c>
       <c r="AM8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AN8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO8">
         <v>4.5</v>
@@ -2623,13 +2623,13 @@
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX8">
         <v>50</v>
       </c>
       <c r="AY8">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2641,79 +2641,79 @@
         <v>55</v>
       </c>
       <c r="BC8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE8">
         <v>29</v>
       </c>
       <c r="BF8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG8">
         <v>4.1</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB8" t="s">
         <v>144</v>
@@ -2736,226 +2736,226 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P9">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q9">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="R9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T9">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U9">
         <v>1.67</v>
       </c>
       <c r="V9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W9">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB9">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP9">
-        <v>1.15</v>
+        <v>3.95</v>
       </c>
       <c r="AQ9">
-        <v>1.15</v>
+        <v>4.5</v>
       </c>
       <c r="AR9">
-        <v>1.15</v>
+        <v>5.2</v>
       </c>
       <c r="AS9">
-        <v>1.15</v>
+        <v>5.5</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU9">
-        <v>1.15</v>
+        <v>7.8</v>
       </c>
       <c r="AV9">
-        <v>1.15</v>
+        <v>21</v>
       </c>
       <c r="AW9">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="AX9">
-        <v>1.15</v>
+        <v>3.55</v>
       </c>
       <c r="AY9">
-        <v>1.15</v>
+        <v>3.85</v>
       </c>
       <c r="AZ9">
-        <v>1.15</v>
+        <v>4.7</v>
       </c>
       <c r="BA9">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="BB9">
-        <v>1.15</v>
+        <v>11</v>
       </c>
       <c r="BC9">
-        <v>1.15</v>
+        <v>4.4</v>
       </c>
       <c r="BD9">
-        <v>1.15</v>
+        <v>5.1</v>
       </c>
       <c r="BE9">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="BF9">
-        <v>1.15</v>
+        <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI9">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="s">
         <v>144</v>
@@ -2978,82 +2978,82 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H10">
         <v>4.3</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
         <v>3.8</v>
       </c>
       <c r="L10">
+        <v>1.4</v>
+      </c>
+      <c r="M10">
+        <v>1.06</v>
+      </c>
+      <c r="N10">
+        <v>4.3</v>
+      </c>
+      <c r="O10">
+        <v>1.29</v>
+      </c>
+      <c r="P10">
+        <v>2.1</v>
+      </c>
+      <c r="Q10">
+        <v>1.88</v>
+      </c>
+      <c r="R10">
         <v>1.42</v>
       </c>
-      <c r="M10">
-        <v>1.07</v>
-      </c>
-      <c r="N10">
-        <v>3.95</v>
-      </c>
-      <c r="O10">
-        <v>1.33</v>
-      </c>
-      <c r="P10">
-        <v>1.99</v>
-      </c>
-      <c r="Q10">
-        <v>1.99</v>
-      </c>
-      <c r="R10">
-        <v>1.38</v>
-      </c>
       <c r="S10">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y10">
+        <v>17</v>
+      </c>
+      <c r="Z10">
+        <v>34</v>
+      </c>
+      <c r="AA10">
+        <v>90</v>
+      </c>
+      <c r="AB10">
+        <v>10.5</v>
+      </c>
+      <c r="AC10">
+        <v>8.4</v>
+      </c>
+      <c r="AD10">
         <v>16.5</v>
       </c>
-      <c r="Z10">
-        <v>32</v>
-      </c>
-      <c r="AA10">
-        <v>100</v>
-      </c>
-      <c r="AB10">
-        <v>9</v>
-      </c>
-      <c r="AC10">
-        <v>9</v>
-      </c>
-      <c r="AD10">
-        <v>17</v>
-      </c>
       <c r="AE10">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AF10">
         <v>12</v>
@@ -3062,52 +3062,52 @@
         <v>10</v>
       </c>
       <c r="AH10">
+        <v>17.5</v>
+      </c>
+      <c r="AI10">
+        <v>60</v>
+      </c>
+      <c r="AJ10">
+        <v>22</v>
+      </c>
+      <c r="AK10">
         <v>19.5</v>
       </c>
-      <c r="AI10">
-        <v>65</v>
-      </c>
-      <c r="AJ10">
-        <v>23</v>
-      </c>
-      <c r="AK10">
+      <c r="AL10">
+        <v>36</v>
+      </c>
+      <c r="AM10">
+        <v>90</v>
+      </c>
+      <c r="AN10">
+        <v>12</v>
+      </c>
+      <c r="AO10">
         <v>55</v>
       </c>
-      <c r="AL10">
-        <v>44</v>
-      </c>
-      <c r="AM10">
-        <v>110</v>
-      </c>
-      <c r="AN10">
-        <v>14</v>
-      </c>
-      <c r="AO10">
-        <v>60</v>
-      </c>
       <c r="AP10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR10">
         <v>29</v>
       </c>
       <c r="AS10">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AT10">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
         <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AX10">
         <v>11</v>
@@ -3116,88 +3116,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BB10">
         <v>20</v>
       </c>
       <c r="BC10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD10">
+        <v>30</v>
+      </c>
+      <c r="BE10">
+        <v>20</v>
+      </c>
+      <c r="BF10">
+        <v>11</v>
+      </c>
+      <c r="BG10">
         <v>32</v>
       </c>
-      <c r="BE10">
-        <v>19.5</v>
-      </c>
-      <c r="BF10">
-        <v>12.5</v>
-      </c>
-      <c r="BG10">
-        <v>48</v>
-      </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BN10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO10">
-        <v>1.77</v>
+        <v>3.75</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="CB10" t="s">
         <v>144</v>
@@ -3220,19 +3220,19 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G11">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I11">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="J11">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K11">
         <v>5.3</v>
@@ -3250,52 +3250,52 @@
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
         <v>2.72</v>
       </c>
       <c r="T11">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V11">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W11">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Y11">
         <v>11.5</v>
       </c>
       <c r="Z11">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="AA11">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD11">
         <v>10.5</v>
       </c>
       <c r="AE11">
-        <v>220</v>
+        <v>16.5</v>
       </c>
       <c r="AF11">
         <v>40</v>
@@ -3304,142 +3304,142 @@
         <v>19</v>
       </c>
       <c r="AH11">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AI11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ11">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AK11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN11">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AO11">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
         <v>10</v>
       </c>
       <c r="AR11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT11">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="AU11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV11">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX11">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="AY11">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ11">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BB11">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="BC11">
-        <v>5.7</v>
+        <v>44</v>
       </c>
       <c r="BD11">
         <v>44</v>
       </c>
       <c r="BE11">
-        <v>5.9</v>
+        <v>60</v>
       </c>
       <c r="BF11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BG11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB11" t="s">
         <v>144</v>
@@ -3462,13 +3462,13 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I12">
         <v>5.5</v>
@@ -3480,64 +3480,64 @@
         <v>3.3</v>
       </c>
       <c r="L12">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N12">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S12">
         <v>6.6</v>
       </c>
       <c r="T12">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="U12">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X12">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y12">
         <v>12.5</v>
       </c>
       <c r="Z12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE12">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="AF12">
         <v>9.800000000000001</v>
@@ -3546,49 +3546,49 @@
         <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI12">
-        <v>990</v>
+        <v>160</v>
       </c>
       <c r="AJ12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL12">
-        <v>310</v>
+        <v>75</v>
       </c>
       <c r="AM12">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AN12">
         <v>28</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS12">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AT12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW12">
         <v>38</v>
@@ -3600,7 +3600,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA12">
         <v>44</v>
@@ -3609,22 +3609,22 @@
         <v>21</v>
       </c>
       <c r="BC12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD12">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BE12">
         <v>95</v>
       </c>
       <c r="BF12">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BG12">
         <v>90</v>
       </c>
       <c r="BH12">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BI12">
         <v>2.42</v>
@@ -3633,34 +3633,34 @@
         <v>15.5</v>
       </c>
       <c r="BK12">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="BM12">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BN12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO12">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ12">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR12">
         <v>55</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BT12">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU12">
         <v>7.6</v>
@@ -3669,19 +3669,19 @@
         <v>80</v>
       </c>
       <c r="BW12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BX12">
         <v>110</v>
       </c>
       <c r="BY12">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12">
         <v>60</v>
       </c>
       <c r="CA12">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
         <v>144</v>
@@ -3704,10 +3704,10 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G13">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H13">
         <v>4.6</v>
@@ -3716,10 +3716,10 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
         <v>1.43</v>
@@ -3728,25 +3728,25 @@
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O13">
         <v>1.35</v>
       </c>
       <c r="P13">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q13">
         <v>2.04</v>
       </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S13">
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -3755,19 +3755,19 @@
         <v>1.25</v>
       </c>
       <c r="W13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X13">
+        <v>14</v>
+      </c>
+      <c r="Y13">
         <v>16</v>
-      </c>
-      <c r="Y13">
-        <v>17</v>
       </c>
       <c r="Z13">
         <v>38</v>
       </c>
       <c r="AA13">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB13">
         <v>8.4</v>
@@ -3779,10 +3779,10 @@
         <v>20</v>
       </c>
       <c r="AE13">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG13">
         <v>11</v>
@@ -3791,61 +3791,61 @@
         <v>21</v>
       </c>
       <c r="AI13">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13">
         <v>40</v>
       </c>
       <c r="AM13">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR13">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AS13">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AT13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
         <v>17</v>
       </c>
       <c r="AW13">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AX13">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY13">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BB13">
         <v>18</v>
@@ -3854,76 +3854,76 @@
         <v>18.5</v>
       </c>
       <c r="BD13">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BE13">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BF13">
         <v>12</v>
       </c>
       <c r="BG13">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BH13">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI13">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="BJ13">
         <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN13">
         <v>4.7</v>
       </c>
       <c r="BO13">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP13">
         <v>14</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR13">
         <v>30</v>
       </c>
       <c r="BS13">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT13">
         <v>8.4</v>
       </c>
       <c r="BU13">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV13">
         <v>44</v>
       </c>
       <c r="BW13">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13">
         <v>55</v>
       </c>
       <c r="BY13">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
         <v>27</v>
       </c>
       <c r="CA13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB13" t="s">
         <v>144</v>
@@ -3946,178 +3946,178 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G14">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H14">
         <v>2.8</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="K14">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L14">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N14">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="O14">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="P14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q14">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R14">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S14">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="T14">
         <v>2.3</v>
       </c>
       <c r="U14">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X14">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC14">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP14">
-        <v>1.16</v>
+        <v>5.9</v>
       </c>
       <c r="AQ14">
-        <v>1.35</v>
+        <v>6.2</v>
       </c>
       <c r="AR14">
-        <v>1.35</v>
+        <v>13</v>
       </c>
       <c r="AS14">
-        <v>1.35</v>
+        <v>4.9</v>
       </c>
       <c r="AT14">
-        <v>1.35</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
-        <v>1.17</v>
+        <v>5.8</v>
       </c>
       <c r="AV14">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="AW14">
-        <v>1.35</v>
+        <v>4.9</v>
       </c>
       <c r="AX14">
-        <v>1.35</v>
+        <v>15</v>
       </c>
       <c r="AY14">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="AZ14">
-        <v>1.35</v>
+        <v>21</v>
       </c>
       <c r="BA14">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="BB14">
-        <v>1.35</v>
+        <v>5.3</v>
       </c>
       <c r="BC14">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="BD14">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="BE14">
-        <v>1.35</v>
+        <v>5.3</v>
       </c>
       <c r="BF14">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="BG14">
-        <v>1.35</v>
+        <v>5.3</v>
       </c>
       <c r="BH14">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BI14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK14">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4132,16 +4132,16 @@
         <v>4.8</v>
       </c>
       <c r="BP14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ14">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BT14">
         <v>6.4</v>
@@ -4153,19 +4153,19 @@
         <v>34</v>
       </c>
       <c r="BW14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
+        <v>5.6</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
         <v>5.7</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
-      <c r="CA14">
-        <v>5.8</v>
       </c>
       <c r="CB14" t="s">
         <v>144</v>
@@ -4188,7 +4188,7 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G15">
         <v>1.97</v>
@@ -4203,7 +4203,7 @@
         <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L15">
         <v>1.67</v>
@@ -4215,13 +4215,13 @@
         <v>2.5</v>
       </c>
       <c r="O15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P15">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q15">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R15">
         <v>1.17</v>
@@ -4233,10 +4233,10 @@
         <v>2.48</v>
       </c>
       <c r="U15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W15">
         <v>2.02</v>
@@ -4245,34 +4245,34 @@
         <v>7.8</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z15">
         <v>42</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE15">
         <v>110</v>
       </c>
       <c r="AF15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
       </c>
       <c r="AH15">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AI15">
         <v>150</v>
@@ -4281,37 +4281,37 @@
         <v>23</v>
       </c>
       <c r="AK15">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL15">
-        <v>990</v>
+        <v>70</v>
       </c>
       <c r="AM15">
         <v>270</v>
       </c>
       <c r="AN15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP15">
         <v>7.4</v>
       </c>
       <c r="AQ15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR15">
         <v>32</v>
       </c>
       <c r="AS15">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AT15">
         <v>5.5</v>
       </c>
       <c r="AU15">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV15">
         <v>21</v>
@@ -4320,16 +4320,16 @@
         <v>38</v>
       </c>
       <c r="AX15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15">
         <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA15">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BB15">
         <v>20</v>
@@ -4338,19 +4338,19 @@
         <v>27</v>
       </c>
       <c r="BD15">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BE15">
         <v>55</v>
       </c>
       <c r="BF15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG15">
         <v>50</v>
       </c>
       <c r="BH15">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI15">
         <v>2.42</v>
@@ -4359,55 +4359,55 @@
         <v>14.5</v>
       </c>
       <c r="BK15">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="BM15">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BN15">
         <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ15">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BR15">
         <v>55</v>
       </c>
       <c r="BS15">
+        <v>11</v>
+      </c>
+      <c r="BT15">
         <v>9</v>
       </c>
-      <c r="BT15">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BU15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV15">
         <v>75</v>
       </c>
       <c r="BW15">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BX15">
         <v>110</v>
       </c>
       <c r="BY15">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BZ15">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
         <v>144</v>
@@ -4433,22 +4433,22 @@
         <v>1.71</v>
       </c>
       <c r="G16">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H16">
         <v>6</v>
       </c>
       <c r="I16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J16">
         <v>3.8</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M16">
         <v>1.09</v>
@@ -4460,10 +4460,10 @@
         <v>1.43</v>
       </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
         <v>1.27</v>
@@ -4478,10 +4478,10 @@
         <v>1.8</v>
       </c>
       <c r="V16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W16">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X16">
         <v>11.5</v>
@@ -4490,10 +4490,10 @@
         <v>17</v>
       </c>
       <c r="Z16">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB16">
         <v>6.8</v>
@@ -4505,7 +4505,7 @@
         <v>26</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -4514,10 +4514,10 @@
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ16">
         <v>17.5</v>
@@ -4526,16 +4526,16 @@
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN16">
         <v>14</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP16">
         <v>10</v>
@@ -4544,7 +4544,7 @@
         <v>14.5</v>
       </c>
       <c r="AR16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AS16">
         <v>44</v>
@@ -4556,7 +4556,7 @@
         <v>7.8</v>
       </c>
       <c r="AV16">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW16">
         <v>38</v>
@@ -4565,10 +4565,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY16">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA16">
         <v>40</v>
@@ -4580,76 +4580,76 @@
         <v>18</v>
       </c>
       <c r="BD16">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE16">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="BF16">
         <v>12</v>
       </c>
       <c r="BG16">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI16">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK16">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM16">
-        <v>1.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO16">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS16">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU16">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW16">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY16">
-        <v>1.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA16">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>144</v>
@@ -4678,16 +4678,16 @@
         <v>2.6</v>
       </c>
       <c r="H17">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I17">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L17">
         <v>1.39</v>
@@ -4696,154 +4696,154 @@
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T17">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U17">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
         <v>1.62</v>
       </c>
       <c r="X17">
+        <v>18.5</v>
+      </c>
+      <c r="Y17">
+        <v>13.5</v>
+      </c>
+      <c r="Z17">
+        <v>21</v>
+      </c>
+      <c r="AA17">
+        <v>48</v>
+      </c>
+      <c r="AB17">
+        <v>12.5</v>
+      </c>
+      <c r="AC17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17">
+        <v>13.5</v>
+      </c>
+      <c r="AE17">
+        <v>34</v>
+      </c>
+      <c r="AF17">
+        <v>18</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>18.5</v>
+      </c>
+      <c r="AI17">
+        <v>44</v>
+      </c>
+      <c r="AJ17">
+        <v>38</v>
+      </c>
+      <c r="AK17">
+        <v>28</v>
+      </c>
+      <c r="AL17">
+        <v>38</v>
+      </c>
+      <c r="AM17">
+        <v>100</v>
+      </c>
+      <c r="AN17">
         <v>26</v>
       </c>
-      <c r="Y17">
-        <v>15.5</v>
-      </c>
-      <c r="Z17">
-        <v>24</v>
-      </c>
-      <c r="AA17">
-        <v>70</v>
-      </c>
-      <c r="AB17">
-        <v>13.5</v>
-      </c>
-      <c r="AC17">
-        <v>9.6</v>
-      </c>
-      <c r="AD17">
-        <v>17</v>
-      </c>
-      <c r="AE17">
-        <v>55</v>
-      </c>
-      <c r="AF17">
-        <v>23</v>
-      </c>
-      <c r="AG17">
-        <v>13</v>
-      </c>
-      <c r="AH17">
-        <v>23</v>
-      </c>
-      <c r="AI17">
-        <v>70</v>
-      </c>
-      <c r="AJ17">
-        <v>260</v>
-      </c>
-      <c r="AK17">
-        <v>200</v>
-      </c>
-      <c r="AL17">
-        <v>220</v>
-      </c>
-      <c r="AM17">
-        <v>140</v>
-      </c>
-      <c r="AN17">
-        <v>32</v>
-      </c>
       <c r="AO17">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AP17">
         <v>14</v>
       </c>
       <c r="AQ17">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR17">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS17">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AT17">
         <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
+        <v>25</v>
+      </c>
+      <c r="AX17">
+        <v>15</v>
+      </c>
+      <c r="AY17">
+        <v>10</v>
+      </c>
+      <c r="AZ17">
+        <v>15.5</v>
+      </c>
+      <c r="BA17">
+        <v>32</v>
+      </c>
+      <c r="BB17">
+        <v>30</v>
+      </c>
+      <c r="BC17">
         <v>21</v>
       </c>
-      <c r="AX17">
-        <v>13.5</v>
-      </c>
-      <c r="AY17">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17">
-        <v>12.5</v>
-      </c>
-      <c r="BA17">
-        <v>28</v>
-      </c>
-      <c r="BB17">
-        <v>26</v>
-      </c>
-      <c r="BC17">
-        <v>19.5</v>
-      </c>
       <c r="BD17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE17">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BF17">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BG17">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BH17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI17">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17">
         <v>11</v>
       </c>
       <c r="BK17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BL17">
         <v>130</v>
@@ -4861,13 +4861,13 @@
         <v>24</v>
       </c>
       <c r="BQ17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR17">
         <v>38</v>
       </c>
       <c r="BS17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BT17">
         <v>7.2</v>
@@ -4876,10 +4876,10 @@
         <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW17">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX17">
         <v>40</v>
@@ -4888,10 +4888,10 @@
         <v>4.2</v>
       </c>
       <c r="BZ17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB17" t="s">
         <v>144</v>
@@ -4920,16 +4920,16 @@
         <v>3.15</v>
       </c>
       <c r="H18">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I18">
         <v>3.05</v>
       </c>
       <c r="J18">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5156,19 +5156,19 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G19">
         <v>1.63</v>
       </c>
       <c r="H19">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I19">
         <v>7.8</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
         <v>4.3</v>
@@ -5183,13 +5183,13 @@
         <v>3.4</v>
       </c>
       <c r="O19">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P19">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
         <v>1.31</v>
@@ -5198,25 +5198,25 @@
         <v>3.9</v>
       </c>
       <c r="T19">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U19">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
         <v>1.15</v>
       </c>
       <c r="W19">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z19">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA19">
         <v>320</v>
@@ -5228,13 +5228,13 @@
         <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AE19">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="AF19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>12.5</v>
@@ -5243,7 +5243,7 @@
         <v>27</v>
       </c>
       <c r="AI19">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="AJ19">
         <v>14.5</v>
@@ -5252,28 +5252,28 @@
         <v>19.5</v>
       </c>
       <c r="AL19">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM19">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="AN19">
         <v>13.5</v>
       </c>
       <c r="AO19">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="AP19">
         <v>11</v>
       </c>
       <c r="AQ19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR19">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS19">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT19">
         <v>6.2</v>
@@ -5282,40 +5282,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW19">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY19">
         <v>9</v>
       </c>
       <c r="AZ19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA19">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB19">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC19">
         <v>16</v>
       </c>
       <c r="BD19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE19">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG19">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH19">
         <v>3.3</v>
@@ -5327,19 +5327,19 @@
         <v>12</v>
       </c>
       <c r="BK19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN19">
         <v>3.95</v>
       </c>
       <c r="BO19">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BP19">
         <v>11</v>
@@ -5351,13 +5351,13 @@
         <v>32</v>
       </c>
       <c r="BS19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT19">
         <v>11</v>
       </c>
       <c r="BU19">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BV19">
         <v>1000</v>
@@ -5401,199 +5401,199 @@
         <v>2.22</v>
       </c>
       <c r="G20">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H20">
         <v>3.3</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M20">
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P20">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q20">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S20">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
         <v>1.78</v>
       </c>
       <c r="X20">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA20">
-        <v>620</v>
+        <v>60</v>
       </c>
       <c r="AB20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
+        <v>15</v>
+      </c>
+      <c r="AE20">
+        <v>38</v>
+      </c>
+      <c r="AF20">
         <v>15.5</v>
       </c>
-      <c r="AE20">
-        <v>60</v>
-      </c>
-      <c r="AF20">
+      <c r="AG20">
+        <v>11.5</v>
+      </c>
+      <c r="AH20">
+        <v>17.5</v>
+      </c>
+      <c r="AI20">
+        <v>46</v>
+      </c>
+      <c r="AJ20">
+        <v>30</v>
+      </c>
+      <c r="AK20">
+        <v>23</v>
+      </c>
+      <c r="AL20">
+        <v>36</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>15.5</v>
+      </c>
+      <c r="AO20">
+        <v>32</v>
+      </c>
+      <c r="AP20">
         <v>15</v>
       </c>
-      <c r="AG20">
-        <v>12</v>
-      </c>
-      <c r="AH20">
-        <v>19.5</v>
-      </c>
-      <c r="AI20">
-        <v>180</v>
-      </c>
-      <c r="AJ20">
-        <v>38</v>
-      </c>
-      <c r="AK20">
-        <v>25</v>
-      </c>
-      <c r="AL20">
-        <v>75</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>17.5</v>
-      </c>
-      <c r="AO20">
-        <v>70</v>
-      </c>
-      <c r="AP20">
-        <v>12.5</v>
-      </c>
       <c r="AQ20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AS20">
         <v>40</v>
       </c>
       <c r="AT20">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU20">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV20">
         <v>12.5</v>
       </c>
       <c r="AW20">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AX20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY20">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC20">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BD20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE20">
         <v>36</v>
       </c>
       <c r="BF20">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH20">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BI20">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ20">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK20">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN20">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS20">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT20">
         <v>7</v>
@@ -5602,19 +5602,19 @@
         <v>5.8</v>
       </c>
       <c r="BV20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX20">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ20">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CA20">
         <v>8.199999999999999</v>
